--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796190ED-19A5-4826-88A9-ABE2A700F528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7364B32D-010E-49D6-8F0B-CB2A5349ABDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="41">
   <si>
     <t>Aluno</t>
   </si>
@@ -595,7 +595,9 @@
       <c r="M1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
@@ -714,7 +716,9 @@
       <c r="M2" s="1">
         <v>46079</v>
       </c>
-      <c r="N2" s="1"/>
+      <c r="N2" s="1">
+        <v>46084</v>
+      </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
@@ -815,6 +819,9 @@
         <v>31</v>
       </c>
       <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -933,6 +940,9 @@
       <c r="M4" t="s">
         <v>31</v>
       </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1049,6 +1059,9 @@
       <c r="M5" t="s">
         <v>31</v>
       </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1165,6 +1178,9 @@
       <c r="M6" t="s">
         <v>31</v>
       </c>
+      <c r="N6" t="s">
+        <v>31</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1281,6 +1297,9 @@
       <c r="M7" t="s">
         <v>31</v>
       </c>
+      <c r="N7" t="s">
+        <v>31</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1397,6 +1416,9 @@
       <c r="M8" t="s">
         <v>31</v>
       </c>
+      <c r="N8" t="s">
+        <v>31</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1513,6 +1535,9 @@
       <c r="M9" t="s">
         <v>31</v>
       </c>
+      <c r="N9" t="s">
+        <v>31</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1629,6 +1654,9 @@
       <c r="M10" t="s">
         <v>31</v>
       </c>
+      <c r="N10" t="s">
+        <v>31</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1745,6 +1773,9 @@
       <c r="M11" t="s">
         <v>31</v>
       </c>
+      <c r="N11" t="s">
+        <v>31</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1861,6 +1892,9 @@
       <c r="M12" t="s">
         <v>31</v>
       </c>
+      <c r="N12" t="s">
+        <v>31</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -1977,7 +2011,9 @@
       <c r="M13" t="s">
         <v>31</v>
       </c>
-      <c r="N13" s="8"/>
+      <c r="N13" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2094,6 +2130,9 @@
       <c r="M14" t="s">
         <v>31</v>
       </c>
+      <c r="N14" t="s">
+        <v>31</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2210,6 +2249,9 @@
       <c r="M15" t="s">
         <v>31</v>
       </c>
+      <c r="N15" t="s">
+        <v>31</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2326,6 +2368,9 @@
       <c r="M16" t="s">
         <v>31</v>
       </c>
+      <c r="N16" t="s">
+        <v>31</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2442,6 +2487,9 @@
       <c r="M17" t="s">
         <v>31</v>
       </c>
+      <c r="N17" t="s">
+        <v>31</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2558,6 +2606,9 @@
       <c r="M18" t="s">
         <v>31</v>
       </c>
+      <c r="N18" t="s">
+        <v>31</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2674,6 +2725,9 @@
       <c r="M19" t="s">
         <v>31</v>
       </c>
+      <c r="N19" t="s">
+        <v>32</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2790,6 +2844,9 @@
       <c r="M20" t="s">
         <v>31</v>
       </c>
+      <c r="N20" t="s">
+        <v>31</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -2906,6 +2963,9 @@
       <c r="M21" t="s">
         <v>31</v>
       </c>
+      <c r="N21" t="s">
+        <v>31</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3022,6 +3082,9 @@
       <c r="M22" t="s">
         <v>31</v>
       </c>
+      <c r="N22" t="s">
+        <v>31</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3138,6 +3201,9 @@
       <c r="M23" t="s">
         <v>31</v>
       </c>
+      <c r="N23" t="s">
+        <v>31</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3254,6 +3320,9 @@
       <c r="M24" t="s">
         <v>31</v>
       </c>
+      <c r="N24" t="s">
+        <v>31</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3370,6 +3439,9 @@
       <c r="M25" t="s">
         <v>31</v>
       </c>
+      <c r="N25" t="s">
+        <v>31</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3486,6 +3558,9 @@
       <c r="M26" t="s">
         <v>31</v>
       </c>
+      <c r="N26" t="s">
+        <v>31</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3602,6 +3677,9 @@
       <c r="M27" t="s">
         <v>31</v>
       </c>
+      <c r="N27" t="s">
+        <v>31</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3718,6 +3796,9 @@
       <c r="M28" t="s">
         <v>31</v>
       </c>
+      <c r="N28" t="s">
+        <v>31</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3834,6 +3915,9 @@
       <c r="M29" t="s">
         <v>31</v>
       </c>
+      <c r="N29" t="s">
+        <v>31</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -3950,6 +4034,9 @@
       <c r="M30" t="s">
         <v>31</v>
       </c>
+      <c r="N30" t="s">
+        <v>31</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4057,6 +4144,9 @@
       <c r="M31" t="s">
         <v>31</v>
       </c>
+      <c r="N31" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -4089,8 +4179,11 @@
       <c r="M32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4109,8 +4202,11 @@
       <c r="M33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4126,6 +4222,9 @@
         <v>31</v>
       </c>
       <c r="M34" t="s">
+        <v>31</v>
+      </c>
+      <c r="N34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4137,7 +4236,7 @@
     <mergeCell ref="J3:J33"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:J3 BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 BE4:BJ9 D4:I30 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:M34">
+  <conditionalFormatting sqref="D3:J3 BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 BE4:BJ9 D4:I30 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:N34">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7364B32D-010E-49D6-8F0B-CB2A5349ABDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD74A018-292B-4813-9383-C387A44BF083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="41">
   <si>
     <t>Aluno</t>
   </si>
@@ -151,9 +151,6 @@
     <t>Samyra Leite da Silva Ferreira</t>
   </si>
   <si>
-    <t>carnaval</t>
-  </si>
-  <si>
     <t>Larissa Guarizo Tolloto</t>
   </si>
   <si>
@@ -161,6 +158,9 @@
   </si>
   <si>
     <t>4P/4F</t>
+  </si>
+  <si>
+    <t>Carnaval</t>
   </si>
 </sst>
 </file>
@@ -202,7 +202,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -210,7 +210,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="22"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -238,7 +238,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -248,8 +248,9 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -559,7 +560,9 @@
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="50" width="7.7109375" customWidth="1"/>
+    <col min="4" max="9" width="7.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="50" width="7.7109375" customWidth="1"/>
     <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
     <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
@@ -779,14 +782,13 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
       </c>
-      <c r="B3" t="str">
-        <f>alunos!B2</f>
-        <v>Ana Beatriz Alves de Lima</v>
+      <c r="B3" t="s">
+        <v>3</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -809,8 +811,8 @@
       <c r="I3" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="9" t="s">
-        <v>37</v>
+      <c r="J3" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="K3" t="s">
         <v>31</v>
@@ -905,9 +907,8 @@
         <f>alunos!A3</f>
         <v>0</v>
       </c>
-      <c r="B4" t="str">
-        <f>alunos!B3</f>
-        <v>Bianca Giovedy Pagotto</v>
+      <c r="B4" t="s">
+        <v>4</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -930,7 +931,9 @@
       <c r="I4" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="9"/>
+      <c r="J4" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K4" t="s">
         <v>31</v>
       </c>
@@ -1024,9 +1027,8 @@
         <f>alunos!A4</f>
         <v>0</v>
       </c>
-      <c r="B5" t="str">
-        <f>alunos!B4</f>
-        <v>Breno Frazão Callegari</v>
+      <c r="B5" t="s">
+        <v>5</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -1049,7 +1051,9 @@
       <c r="I5" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="9"/>
+      <c r="J5" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K5" t="s">
         <v>31</v>
       </c>
@@ -1143,9 +1147,8 @@
         <f>alunos!A5</f>
         <v>0</v>
       </c>
-      <c r="B6" t="str">
-        <f>alunos!B5</f>
-        <v>Davi Cruz Oliveira</v>
+      <c r="B6" t="s">
+        <v>6</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1168,7 +1171,9 @@
       <c r="I6" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="9"/>
+      <c r="J6" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K6" t="s">
         <v>31</v>
       </c>
@@ -1262,9 +1267,8 @@
         <f>alunos!A6</f>
         <v>0</v>
       </c>
-      <c r="B7" t="str">
-        <f>alunos!B6</f>
-        <v>Eduardo Moretti Varotti</v>
+      <c r="B7" t="s">
+        <v>7</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1287,7 +1291,9 @@
       <c r="I7" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="9"/>
+      <c r="J7" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K7" t="s">
         <v>31</v>
       </c>
@@ -1381,9 +1387,8 @@
         <f>alunos!A7</f>
         <v>0</v>
       </c>
-      <c r="B8" t="str">
-        <f>alunos!B7</f>
-        <v>Gabriela Leticia da Silva</v>
+      <c r="B8" t="s">
+        <v>8</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -1406,7 +1411,9 @@
       <c r="I8" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="9"/>
+      <c r="J8" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K8" t="s">
         <v>31</v>
       </c>
@@ -1500,9 +1507,8 @@
         <f>alunos!A8</f>
         <v>0</v>
       </c>
-      <c r="B9" t="str">
-        <f>alunos!B8</f>
-        <v>Geovanna Martins Bertuol</v>
+      <c r="B9" t="s">
+        <v>9</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -1525,7 +1531,9 @@
       <c r="I9" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="9"/>
+      <c r="J9" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K9" t="s">
         <v>31</v>
       </c>
@@ -1619,9 +1627,8 @@
         <f>alunos!A9</f>
         <v>0</v>
       </c>
-      <c r="B10" t="str">
-        <f>alunos!B9</f>
-        <v>Giulia de Godoi Silveira</v>
+      <c r="B10" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="C10">
         <v>8</v>
@@ -1644,7 +1651,9 @@
       <c r="I10" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="9"/>
+      <c r="J10" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K10" t="s">
         <v>31</v>
       </c>
@@ -1738,22 +1747,12 @@
         <f>alunos!A10</f>
         <v>0</v>
       </c>
-      <c r="B11" t="str">
-        <f>alunos!B10</f>
-        <v>Gustavo Ferelli</v>
+      <c r="B11" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="C11">
         <v>9</v>
       </c>
-      <c r="D11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" t="s">
-        <v>31</v>
-      </c>
       <c r="G11" t="s">
         <v>31</v>
       </c>
@@ -1763,9 +1762,11 @@
       <c r="I11" t="s">
         <v>31</v>
       </c>
-      <c r="J11" s="9"/>
+      <c r="J11" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L11" t="s">
         <v>31</v>
@@ -1857,9 +1858,8 @@
         <f>alunos!A11</f>
         <v>0</v>
       </c>
-      <c r="B12" t="str">
-        <f>alunos!B11</f>
-        <v>Heitor Dorigan de Angeli</v>
+      <c r="B12" t="s">
+        <v>11</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -1877,14 +1877,16 @@
         <v>31</v>
       </c>
       <c r="H12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" t="s">
         <v>32</v>
-      </c>
-      <c r="I12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" s="9"/>
-      <c r="K12" t="s">
-        <v>31</v>
       </c>
       <c r="L12" t="s">
         <v>31</v>
@@ -1976,9 +1978,8 @@
         <f>alunos!A12</f>
         <v>0</v>
       </c>
-      <c r="B13" t="str">
-        <f>alunos!B12</f>
-        <v>Helena Politti Rossi</v>
+      <c r="B13" t="s">
+        <v>12</v>
       </c>
       <c r="C13">
         <v>11</v>
@@ -1996,12 +1997,14 @@
         <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="9"/>
+      <c r="J13" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K13" t="s">
         <v>31</v>
       </c>
@@ -2011,7 +2014,7 @@
       <c r="M13" t="s">
         <v>31</v>
       </c>
-      <c r="N13" s="8" t="s">
+      <c r="N13" t="s">
         <v>31</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2095,9 +2098,8 @@
         <f>alunos!A13</f>
         <v>0</v>
       </c>
-      <c r="B14" t="str">
-        <f>alunos!B13</f>
-        <v>Isabela Marchiori Ferreira</v>
+      <c r="B14" t="s">
+        <v>13</v>
       </c>
       <c r="C14">
         <v>12</v>
@@ -2120,7 +2122,9 @@
       <c r="I14" t="s">
         <v>31</v>
       </c>
-      <c r="J14" s="9"/>
+      <c r="J14" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K14" t="s">
         <v>31</v>
       </c>
@@ -2130,7 +2134,7 @@
       <c r="M14" t="s">
         <v>31</v>
       </c>
-      <c r="N14" t="s">
+      <c r="N14" s="9" t="s">
         <v>31</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2214,9 +2218,8 @@
         <f>alunos!A14</f>
         <v>0</v>
       </c>
-      <c r="B15" t="str">
-        <f>alunos!B14</f>
-        <v>Isabelle Caroline Vizeu de Salles</v>
+      <c r="B15" t="s">
+        <v>14</v>
       </c>
       <c r="C15">
         <v>13</v>
@@ -2239,12 +2242,14 @@
       <c r="I15" t="s">
         <v>31</v>
       </c>
-      <c r="J15" s="9"/>
+      <c r="J15" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K15" t="s">
         <v>31</v>
       </c>
       <c r="L15" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="M15" t="s">
         <v>31</v>
@@ -2333,9 +2338,8 @@
         <f>alunos!A15</f>
         <v>0</v>
       </c>
-      <c r="B16" t="str">
-        <f>alunos!B15</f>
-        <v>Leandro Imenes de Oliveira</v>
+      <c r="B16" t="s">
+        <v>15</v>
       </c>
       <c r="C16">
         <v>14</v>
@@ -2358,12 +2362,14 @@
       <c r="I16" t="s">
         <v>31</v>
       </c>
-      <c r="J16" s="9"/>
+      <c r="J16" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K16" t="s">
         <v>31</v>
       </c>
       <c r="L16" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M16" t="s">
         <v>31</v>
@@ -2452,34 +2458,14 @@
         <f>alunos!A16</f>
         <v>0</v>
       </c>
-      <c r="B17" t="str">
-        <f>alunos!B16</f>
-        <v>Letícia Aparecida Pinto de Souza</v>
+      <c r="B17" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="C17">
         <v>15</v>
       </c>
-      <c r="D17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" s="9"/>
-      <c r="K17" t="s">
-        <v>31</v>
+      <c r="J17" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="L17" t="s">
         <v>31</v>
@@ -2571,9 +2557,8 @@
         <f>alunos!A17</f>
         <v>0</v>
       </c>
-      <c r="B18" t="str">
-        <f>alunos!B17</f>
-        <v>Luana Gabrielle de Oliveira</v>
+      <c r="B18" t="s">
+        <v>16</v>
       </c>
       <c r="C18">
         <v>16</v>
@@ -2596,12 +2581,14 @@
       <c r="I18" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="9"/>
+      <c r="J18" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K18" t="s">
         <v>31</v>
       </c>
       <c r="L18" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="M18" t="s">
         <v>31</v>
@@ -2690,9 +2677,8 @@
         <f>alunos!A18</f>
         <v>0</v>
       </c>
-      <c r="B19" t="str">
-        <f>alunos!B18</f>
-        <v>Marina Henrique Moretti</v>
+      <c r="B19" t="s">
+        <v>17</v>
       </c>
       <c r="C19">
         <v>17</v>
@@ -2715,7 +2701,9 @@
       <c r="I19" t="s">
         <v>31</v>
       </c>
-      <c r="J19" s="9"/>
+      <c r="J19" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K19" t="s">
         <v>31</v>
       </c>
@@ -2726,7 +2714,7 @@
         <v>31</v>
       </c>
       <c r="N19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
@@ -2809,34 +2797,14 @@
         <f>alunos!A19</f>
         <v>0</v>
       </c>
-      <c r="B20" t="str">
-        <f>alunos!B19</f>
-        <v>Matheus Dorigan Paiato</v>
+      <c r="B20" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="C20">
         <v>18</v>
       </c>
-      <c r="D20" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" s="9"/>
-      <c r="K20" t="s">
-        <v>31</v>
+      <c r="J20" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="L20" t="s">
         <v>31</v>
@@ -2928,9 +2896,8 @@
         <f>alunos!A20</f>
         <v>0</v>
       </c>
-      <c r="B21" t="str">
-        <f>alunos!B20</f>
-        <v>Maycon Silva Gonçalves de Lima</v>
+      <c r="B21" t="s">
+        <v>18</v>
       </c>
       <c r="C21">
         <v>19</v>
@@ -2953,12 +2920,14 @@
       <c r="I21" t="s">
         <v>31</v>
       </c>
-      <c r="J21" s="9"/>
+      <c r="J21" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K21" t="s">
         <v>31</v>
       </c>
       <c r="L21" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M21" t="s">
         <v>31</v>
@@ -3047,9 +3016,8 @@
         <f>alunos!A21</f>
         <v>0</v>
       </c>
-      <c r="B22" t="str">
-        <f>alunos!B21</f>
-        <v>Nicolas Augusto dos Reis Lira</v>
+      <c r="B22" t="s">
+        <v>19</v>
       </c>
       <c r="C22">
         <v>20</v>
@@ -3072,7 +3040,9 @@
       <c r="I22" t="s">
         <v>31</v>
       </c>
-      <c r="J22" s="9"/>
+      <c r="J22" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K22" t="s">
         <v>31</v>
       </c>
@@ -3083,7 +3053,7 @@
         <v>31</v>
       </c>
       <c r="N22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
@@ -3166,9 +3136,8 @@
         <f>alunos!A22</f>
         <v>0</v>
       </c>
-      <c r="B23" t="str">
-        <f>alunos!B22</f>
-        <v>Otávio Augusto Barbosa</v>
+      <c r="B23" t="s">
+        <v>20</v>
       </c>
       <c r="C23">
         <v>21</v>
@@ -3191,7 +3160,9 @@
       <c r="I23" t="s">
         <v>31</v>
       </c>
-      <c r="J23" s="9"/>
+      <c r="J23" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K23" t="s">
         <v>31</v>
       </c>
@@ -3285,9 +3256,8 @@
         <f>alunos!A23</f>
         <v>0</v>
       </c>
-      <c r="B24" t="str">
-        <f>alunos!B23</f>
-        <v>Pedro Henrique Souza Guarizo</v>
+      <c r="B24" t="s">
+        <v>21</v>
       </c>
       <c r="C24">
         <v>22</v>
@@ -3310,7 +3280,9 @@
       <c r="I24" t="s">
         <v>31</v>
       </c>
-      <c r="J24" s="9"/>
+      <c r="J24" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K24" t="s">
         <v>31</v>
       </c>
@@ -3404,9 +3376,8 @@
         <f>alunos!A24</f>
         <v>0</v>
       </c>
-      <c r="B25" t="str">
-        <f>alunos!B24</f>
-        <v>Renan Pavan Fazullo</v>
+      <c r="B25" t="s">
+        <v>22</v>
       </c>
       <c r="C25">
         <v>23</v>
@@ -3429,7 +3400,9 @@
       <c r="I25" t="s">
         <v>31</v>
       </c>
-      <c r="J25" s="9"/>
+      <c r="J25" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K25" t="s">
         <v>31</v>
       </c>
@@ -3523,9 +3496,8 @@
         <f>alunos!A25</f>
         <v>0</v>
       </c>
-      <c r="B26" t="str">
-        <f>alunos!B25</f>
-        <v>Sara de Paula Souza</v>
+      <c r="B26" t="s">
+        <v>23</v>
       </c>
       <c r="C26">
         <v>24</v>
@@ -3548,7 +3520,9 @@
       <c r="I26" t="s">
         <v>31</v>
       </c>
-      <c r="J26" s="9"/>
+      <c r="J26" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K26" t="s">
         <v>31</v>
       </c>
@@ -3642,9 +3616,8 @@
         <f>alunos!A26</f>
         <v>0</v>
       </c>
-      <c r="B27" t="str">
-        <f>alunos!B26</f>
-        <v>Sofia Ohashi Faria</v>
+      <c r="B27" t="s">
+        <v>24</v>
       </c>
       <c r="C27">
         <v>25</v>
@@ -3667,7 +3640,9 @@
       <c r="I27" t="s">
         <v>31</v>
       </c>
-      <c r="J27" s="9"/>
+      <c r="J27" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K27" t="s">
         <v>31</v>
       </c>
@@ -3761,9 +3736,8 @@
         <f>alunos!A27</f>
         <v>0</v>
       </c>
-      <c r="B28" t="str">
-        <f>alunos!B27</f>
-        <v>Tobias Gabriel Bueno de Godoi</v>
+      <c r="B28" t="s">
+        <v>25</v>
       </c>
       <c r="C28">
         <v>26</v>
@@ -3786,7 +3760,9 @@
       <c r="I28" t="s">
         <v>31</v>
       </c>
-      <c r="J28" s="9"/>
+      <c r="J28" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K28" t="s">
         <v>31</v>
       </c>
@@ -3880,22 +3856,12 @@
         <f>alunos!A28</f>
         <v>0</v>
       </c>
-      <c r="B29" t="str">
-        <f>alunos!B28</f>
-        <v>Víctor Henrique Santana Alves</v>
+      <c r="B29" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="C29">
         <v>27</v>
       </c>
-      <c r="D29" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F29" t="s">
-        <v>31</v>
-      </c>
       <c r="G29" t="s">
         <v>31</v>
       </c>
@@ -3905,7 +3871,9 @@
       <c r="I29" t="s">
         <v>31</v>
       </c>
-      <c r="J29" s="9"/>
+      <c r="J29" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K29" t="s">
         <v>31</v>
       </c>
@@ -3999,9 +3967,8 @@
         <f>alunos!A29</f>
         <v>0</v>
       </c>
-      <c r="B30" t="str">
-        <f>alunos!B29</f>
-        <v>Vitória Bueno da Silva</v>
+      <c r="B30" t="s">
+        <v>26</v>
       </c>
       <c r="C30">
         <v>28</v>
@@ -4024,7 +3991,9 @@
       <c r="I30" t="s">
         <v>31</v>
       </c>
-      <c r="J30" s="9"/>
+      <c r="J30" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K30" t="s">
         <v>31</v>
       </c>
@@ -4118,13 +4087,21 @@
         <f>alunos!A30</f>
         <v>0</v>
       </c>
-      <c r="B31" t="str">
-        <f>alunos!B30</f>
-        <v>Giuseppe de Moraes Vieira</v>
+      <c r="B31" t="s">
+        <v>27</v>
       </c>
       <c r="C31">
         <v>29</v>
       </c>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" t="s">
+        <v>31</v>
+      </c>
+      <c r="F31" t="s">
+        <v>31</v>
+      </c>
       <c r="G31" t="s">
         <v>31</v>
       </c>
@@ -4134,7 +4111,9 @@
       <c r="I31" t="s">
         <v>31</v>
       </c>
-      <c r="J31" s="9"/>
+      <c r="J31" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K31" t="s">
         <v>31</v>
       </c>
@@ -4153,13 +4132,21 @@
         <f>alunos!A31</f>
         <v>0</v>
       </c>
-      <c r="B32" t="str">
-        <f>alunos!B31</f>
-        <v>Samyra Leite da Silva Ferreira</v>
+      <c r="B32" t="s">
+        <v>28</v>
       </c>
       <c r="C32">
         <v>30</v>
       </c>
+      <c r="D32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" t="s">
+        <v>31</v>
+      </c>
+      <c r="F32" t="s">
+        <v>31</v>
+      </c>
       <c r="G32" t="s">
         <v>31</v>
       </c>
@@ -4169,7 +4156,9 @@
       <c r="I32" t="s">
         <v>31</v>
       </c>
-      <c r="J32" s="9"/>
+      <c r="J32" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="K32" t="s">
         <v>31</v>
       </c>
@@ -4188,14 +4177,36 @@
         <f>alunos!A32</f>
         <v>0</v>
       </c>
-      <c r="B33" t="str">
-        <f>alunos!B32</f>
-        <v>Larissa Guarizo Tolloto</v>
+      <c r="B33" t="s">
+        <v>29</v>
       </c>
       <c r="C33">
         <v>31</v>
       </c>
-      <c r="J33" s="9"/>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" t="s">
+        <v>31</v>
+      </c>
+      <c r="F33" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K33" t="s">
+        <v>31</v>
+      </c>
       <c r="L33" t="s">
         <v>31</v>
       </c>
@@ -4211,13 +4222,36 @@
         <f>alunos!A33</f>
         <v>0</v>
       </c>
-      <c r="B34" t="str">
-        <f>alunos!B33</f>
-        <v>Liara Guarizo Tolloto</v>
+      <c r="B34" t="s">
+        <v>30</v>
       </c>
       <c r="C34">
         <v>32</v>
       </c>
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K34" t="s">
+        <v>31</v>
+      </c>
       <c r="L34" t="s">
         <v>31</v>
       </c>
@@ -4229,14 +4263,11 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B30">
-    <sortCondition ref="B3:B30"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:N34">
+    <sortCondition ref="B3:B34"/>
   </sortState>
-  <mergeCells count="1">
-    <mergeCell ref="J3:J33"/>
-  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:J3 BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 BE4:BJ9 D4:I30 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:N34">
+  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 BE4:BJ9 D3:I30 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 L31:N34 H33:I33">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4422,12 +4453,12 @@
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD74A018-292B-4813-9383-C387A44BF083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD8FA9F-42D7-425A-BDF5-E798AAF7A663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="41">
   <si>
     <t>Aluno</t>
   </si>
@@ -167,7 +167,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,14 +195,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -238,7 +230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -247,11 +239,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,7 +592,9 @@
       <c r="N1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="1"/>
+      <c r="O1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -722,7 +715,9 @@
       <c r="N2" s="1">
         <v>46084</v>
       </c>
-      <c r="O2" s="1"/>
+      <c r="O2" s="1">
+        <v>46086</v>
+      </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -811,7 +806,7 @@
       <c r="I3" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K3" t="s">
@@ -824,6 +819,9 @@
         <v>31</v>
       </c>
       <c r="N3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -931,7 +929,7 @@
       <c r="I4" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K4" t="s">
@@ -944,6 +942,9 @@
         <v>31</v>
       </c>
       <c r="N4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" t="s">
         <v>31</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1051,7 +1052,7 @@
       <c r="I5" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K5" t="s">
@@ -1064,6 +1065,9 @@
         <v>31</v>
       </c>
       <c r="N5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" t="s">
         <v>31</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1171,7 +1175,7 @@
       <c r="I6" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K6" t="s">
@@ -1184,6 +1188,9 @@
         <v>31</v>
       </c>
       <c r="N6" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" t="s">
         <v>31</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1291,7 +1298,7 @@
       <c r="I7" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K7" t="s">
@@ -1304,6 +1311,9 @@
         <v>31</v>
       </c>
       <c r="N7" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" t="s">
         <v>31</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1411,7 +1421,7 @@
       <c r="I8" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K8" t="s">
@@ -1424,6 +1434,9 @@
         <v>31</v>
       </c>
       <c r="N8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O8" t="s">
         <v>31</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1531,7 +1544,7 @@
       <c r="I9" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K9" t="s">
@@ -1544,6 +1557,9 @@
         <v>31</v>
       </c>
       <c r="N9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" t="s">
         <v>31</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1627,7 +1643,7 @@
         <f>alunos!A9</f>
         <v>0</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C10">
@@ -1651,7 +1667,7 @@
       <c r="I10" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K10" t="s">
@@ -1665,6 +1681,9 @@
       </c>
       <c r="N10" t="s">
         <v>31</v>
+      </c>
+      <c r="O10" t="s">
+        <v>32</v>
       </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
@@ -1747,7 +1766,7 @@
         <f>alunos!A10</f>
         <v>0</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" t="s">
         <v>35</v>
       </c>
       <c r="C11">
@@ -1762,7 +1781,7 @@
       <c r="I11" t="s">
         <v>31</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K11" t="s">
@@ -1775,6 +1794,9 @@
         <v>31</v>
       </c>
       <c r="N11" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" t="s">
         <v>31</v>
       </c>
       <c r="AU11" s="2"/>
@@ -1882,7 +1904,7 @@
       <c r="I12" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K12" t="s">
@@ -1895,6 +1917,9 @@
         <v>31</v>
       </c>
       <c r="N12" t="s">
+        <v>31</v>
+      </c>
+      <c r="O12" t="s">
         <v>31</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2002,7 +2027,7 @@
       <c r="I13" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K13" t="s">
@@ -2015,6 +2040,9 @@
         <v>31</v>
       </c>
       <c r="N13" t="s">
+        <v>31</v>
+      </c>
+      <c r="O13" t="s">
         <v>31</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2122,7 +2150,7 @@
       <c r="I14" t="s">
         <v>31</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="J14" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K14" t="s">
@@ -2134,7 +2162,10 @@
       <c r="M14" t="s">
         <v>31</v>
       </c>
-      <c r="N14" s="9" t="s">
+      <c r="N14" t="s">
+        <v>31</v>
+      </c>
+      <c r="O14" t="s">
         <v>31</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2242,7 +2273,7 @@
       <c r="I15" t="s">
         <v>31</v>
       </c>
-      <c r="J15" s="10" t="s">
+      <c r="J15" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K15" t="s">
@@ -2255,6 +2286,9 @@
         <v>31</v>
       </c>
       <c r="N15" t="s">
+        <v>31</v>
+      </c>
+      <c r="O15" t="s">
         <v>31</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2362,7 +2396,7 @@
       <c r="I16" t="s">
         <v>31</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="J16" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K16" t="s">
@@ -2375,6 +2409,9 @@
         <v>31</v>
       </c>
       <c r="N16" t="s">
+        <v>31</v>
+      </c>
+      <c r="O16" t="s">
         <v>31</v>
       </c>
       <c r="AU16" s="2"/>
@@ -2458,13 +2495,13 @@
         <f>alunos!A16</f>
         <v>0</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17">
         <v>15</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="J17" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L17" t="s">
@@ -2474,6 +2511,9 @@
         <v>31</v>
       </c>
       <c r="N17" t="s">
+        <v>31</v>
+      </c>
+      <c r="O17" t="s">
         <v>31</v>
       </c>
       <c r="AU17" s="2"/>
@@ -2581,7 +2621,7 @@
       <c r="I18" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="J18" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K18" t="s">
@@ -2594,6 +2634,9 @@
         <v>31</v>
       </c>
       <c r="N18" t="s">
+        <v>31</v>
+      </c>
+      <c r="O18" t="s">
         <v>31</v>
       </c>
       <c r="AU18" s="2"/>
@@ -2701,7 +2744,7 @@
       <c r="I19" t="s">
         <v>31</v>
       </c>
-      <c r="J19" s="10" t="s">
+      <c r="J19" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K19" t="s">
@@ -2714,6 +2757,9 @@
         <v>31</v>
       </c>
       <c r="N19" t="s">
+        <v>31</v>
+      </c>
+      <c r="O19" t="s">
         <v>31</v>
       </c>
       <c r="AU19" s="2"/>
@@ -2797,13 +2843,13 @@
         <f>alunos!A19</f>
         <v>0</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20">
         <v>18</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J20" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L20" t="s">
@@ -2813,6 +2859,9 @@
         <v>31</v>
       </c>
       <c r="N20" t="s">
+        <v>31</v>
+      </c>
+      <c r="O20" t="s">
         <v>31</v>
       </c>
       <c r="AU20" s="2"/>
@@ -2920,7 +2969,7 @@
       <c r="I21" t="s">
         <v>31</v>
       </c>
-      <c r="J21" s="10" t="s">
+      <c r="J21" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K21" t="s">
@@ -2933,6 +2982,9 @@
         <v>31</v>
       </c>
       <c r="N21" t="s">
+        <v>31</v>
+      </c>
+      <c r="O21" t="s">
         <v>31</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3040,7 +3092,7 @@
       <c r="I22" t="s">
         <v>31</v>
       </c>
-      <c r="J22" s="10" t="s">
+      <c r="J22" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K22" t="s">
@@ -3054,6 +3106,9 @@
       </c>
       <c r="N22" t="s">
         <v>32</v>
+      </c>
+      <c r="O22" t="s">
+        <v>31</v>
       </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
@@ -3160,7 +3215,7 @@
       <c r="I23" t="s">
         <v>31</v>
       </c>
-      <c r="J23" s="10" t="s">
+      <c r="J23" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K23" t="s">
@@ -3173,6 +3228,9 @@
         <v>31</v>
       </c>
       <c r="N23" t="s">
+        <v>31</v>
+      </c>
+      <c r="O23" t="s">
         <v>31</v>
       </c>
       <c r="AU23" s="2"/>
@@ -3280,7 +3338,7 @@
       <c r="I24" t="s">
         <v>31</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="J24" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K24" t="s">
@@ -3293,6 +3351,9 @@
         <v>31</v>
       </c>
       <c r="N24" t="s">
+        <v>31</v>
+      </c>
+      <c r="O24" t="s">
         <v>31</v>
       </c>
       <c r="AU24" s="2"/>
@@ -3400,7 +3461,7 @@
       <c r="I25" t="s">
         <v>31</v>
       </c>
-      <c r="J25" s="10" t="s">
+      <c r="J25" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K25" t="s">
@@ -3413,6 +3474,9 @@
         <v>31</v>
       </c>
       <c r="N25" t="s">
+        <v>31</v>
+      </c>
+      <c r="O25" t="s">
         <v>31</v>
       </c>
       <c r="AU25" s="2"/>
@@ -3520,7 +3584,7 @@
       <c r="I26" t="s">
         <v>31</v>
       </c>
-      <c r="J26" s="10" t="s">
+      <c r="J26" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K26" t="s">
@@ -3533,6 +3597,9 @@
         <v>31</v>
       </c>
       <c r="N26" t="s">
+        <v>31</v>
+      </c>
+      <c r="O26" t="s">
         <v>31</v>
       </c>
       <c r="AU26" s="2"/>
@@ -3640,7 +3707,7 @@
       <c r="I27" t="s">
         <v>31</v>
       </c>
-      <c r="J27" s="10" t="s">
+      <c r="J27" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K27" t="s">
@@ -3653,6 +3720,9 @@
         <v>31</v>
       </c>
       <c r="N27" t="s">
+        <v>31</v>
+      </c>
+      <c r="O27" t="s">
         <v>31</v>
       </c>
       <c r="AU27" s="2"/>
@@ -3760,7 +3830,7 @@
       <c r="I28" t="s">
         <v>31</v>
       </c>
-      <c r="J28" s="10" t="s">
+      <c r="J28" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K28" t="s">
@@ -3773,6 +3843,9 @@
         <v>31</v>
       </c>
       <c r="N28" t="s">
+        <v>31</v>
+      </c>
+      <c r="O28" t="s">
         <v>31</v>
       </c>
       <c r="AU28" s="2"/>
@@ -3856,7 +3929,7 @@
         <f>alunos!A28</f>
         <v>0</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" t="s">
         <v>36</v>
       </c>
       <c r="C29">
@@ -3871,7 +3944,7 @@
       <c r="I29" t="s">
         <v>31</v>
       </c>
-      <c r="J29" s="10" t="s">
+      <c r="J29" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K29" t="s">
@@ -3884,6 +3957,9 @@
         <v>31</v>
       </c>
       <c r="N29" t="s">
+        <v>31</v>
+      </c>
+      <c r="O29" t="s">
         <v>31</v>
       </c>
       <c r="AU29" s="2"/>
@@ -3991,7 +4067,7 @@
       <c r="I30" t="s">
         <v>31</v>
       </c>
-      <c r="J30" s="10" t="s">
+      <c r="J30" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K30" t="s">
@@ -4004,6 +4080,9 @@
         <v>31</v>
       </c>
       <c r="N30" t="s">
+        <v>31</v>
+      </c>
+      <c r="O30" t="s">
         <v>31</v>
       </c>
       <c r="AU30" s="2"/>
@@ -4111,7 +4190,7 @@
       <c r="I31" t="s">
         <v>31</v>
       </c>
-      <c r="J31" s="10" t="s">
+      <c r="J31" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K31" t="s">
@@ -4124,6 +4203,9 @@
         <v>31</v>
       </c>
       <c r="N31" t="s">
+        <v>31</v>
+      </c>
+      <c r="O31" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4156,7 +4238,7 @@
       <c r="I32" t="s">
         <v>31</v>
       </c>
-      <c r="J32" s="10" t="s">
+      <c r="J32" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K32" t="s">
@@ -4171,8 +4253,11 @@
       <c r="N32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4201,7 +4286,7 @@
       <c r="I33" t="s">
         <v>31</v>
       </c>
-      <c r="J33" s="10" t="s">
+      <c r="J33" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K33" t="s">
@@ -4216,8 +4301,11 @@
       <c r="N33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4246,7 +4334,7 @@
       <c r="I34" t="s">
         <v>31</v>
       </c>
-      <c r="J34" s="10" t="s">
+      <c r="J34" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K34" t="s">
@@ -4259,6 +4347,9 @@
         <v>31</v>
       </c>
       <c r="N34" t="s">
+        <v>31</v>
+      </c>
+      <c r="O34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4267,13 +4358,13 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 BE4:BJ9 D3:I30 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 L31:N34 H33:I33">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+  <conditionalFormatting sqref="G31:I32">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G31:I32">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:O34">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4343,125 +4434,128 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B33">
+    <sortCondition ref="B1:B33"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4469,7 +4563,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
-  <dimension ref="A2:A33"/>
+  <dimension ref="A2:A34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
@@ -4531,139 +4625,145 @@
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
-        <v>Gustavo Ferelli</v>
+        <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
-        <v>Heitor Dorigan de Angeli</v>
+        <v>Gustavo Ferelli</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
-        <v>Helena Politti Rossi</v>
+        <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
-        <v>Isabela Marchiori Ferreira</v>
+        <v>Helena Politti Rossi</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
-        <v>Isabelle Caroline Vizeu de Salles</v>
+        <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
-        <v>Leandro Imenes de Oliveira</v>
+        <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
-        <v>Letícia Aparecida Pinto de Souza</v>
+        <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
-        <v>Luana Gabrielle de Oliveira</v>
+        <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
-        <v>Marina Henrique Moretti</v>
+        <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
-        <v>Matheus Dorigan Paiato</v>
+        <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
-        <v>Maycon Silva Gonçalves de Lima</v>
+        <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
-        <v>Nicolas Augusto dos Reis Lira</v>
+        <v>Marina Henrique Moretti</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
-        <v>Otávio Augusto Barbosa</v>
+        <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
-        <v>Pedro Henrique Souza Guarizo</v>
+        <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
-        <v>Renan Pavan Fazullo</v>
+        <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
-        <v>Sara de Paula Souza</v>
+        <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
-        <v>Sofia Ohashi Faria</v>
+        <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
-        <v>Tobias Gabriel Bueno de Godoi</v>
+        <v>Renan Pavan Fazullo</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
-        <v>Víctor Henrique Santana Alves</v>
+        <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
-        <v>Vitória Bueno da Silva</v>
+        <v>Sara de Paula Souza</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
-        <v>Giuseppe de Moraes Vieira</v>
+        <v>Sofia Ohashi Faria</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
-        <v>Samyra Leite da Silva Ferreira</v>
+        <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
-        <v>Larissa Guarizo Tolloto</v>
+        <v>Víctor Henrique Santana Alves</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="str">
+        <f>alunos!B33</f>
+        <v>Vitória Bueno da Silva</v>
       </c>
     </row>
   </sheetData>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD8FA9F-42D7-425A-BDF5-E798AAF7A663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63468A47-7F6F-458D-B62A-DD6684C54C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -162,6 +162,9 @@
   <si>
     <t>Carnaval</t>
   </si>
+  <si>
+    <t>05/012</t>
+  </si>
 </sst>
 </file>
 
@@ -230,7 +233,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -242,7 +245,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -689,10 +691,10 @@
         <v>46051</v>
       </c>
       <c r="F2" s="1">
-        <v>46055</v>
-      </c>
-      <c r="G2" s="1">
-        <v>46057</v>
+        <v>46056</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H2" s="1">
         <v>46063</v>
@@ -1643,7 +1645,7 @@
         <f>alunos!A9</f>
         <v>0</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10">
@@ -4363,7 +4365,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:O34">
+  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 L31:O34 H33:I33">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63468A47-7F6F-458D-B62A-DD6684C54C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4DBDC2-D89D-4CE5-8444-4E2B9A35858D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -597,7 +597,9 @@
       <c r="O1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
@@ -720,7 +722,9 @@
       <c r="O2" s="1">
         <v>46086</v>
       </c>
-      <c r="P2" s="1"/>
+      <c r="P2" s="1">
+        <v>46091</v>
+      </c>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -824,6 +828,9 @@
         <v>31</v>
       </c>
       <c r="O3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -949,6 +956,9 @@
       <c r="O4" t="s">
         <v>31</v>
       </c>
+      <c r="P4" t="s">
+        <v>31</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1072,6 +1082,9 @@
       <c r="O5" t="s">
         <v>31</v>
       </c>
+      <c r="P5" t="s">
+        <v>31</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1195,6 +1208,9 @@
       <c r="O6" t="s">
         <v>31</v>
       </c>
+      <c r="P6" t="s">
+        <v>31</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1318,6 +1334,9 @@
       <c r="O7" t="s">
         <v>31</v>
       </c>
+      <c r="P7" t="s">
+        <v>31</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1441,6 +1460,9 @@
       <c r="O8" t="s">
         <v>31</v>
       </c>
+      <c r="P8" t="s">
+        <v>31</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1564,6 +1586,9 @@
       <c r="O9" t="s">
         <v>31</v>
       </c>
+      <c r="P9" t="s">
+        <v>31</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1687,6 +1712,9 @@
       <c r="O10" t="s">
         <v>32</v>
       </c>
+      <c r="P10" t="s">
+        <v>31</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1801,6 +1829,9 @@
       <c r="O11" t="s">
         <v>31</v>
       </c>
+      <c r="P11" t="s">
+        <v>31</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1924,6 +1955,9 @@
       <c r="O12" t="s">
         <v>31</v>
       </c>
+      <c r="P12" t="s">
+        <v>31</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2047,6 +2081,9 @@
       <c r="O13" t="s">
         <v>31</v>
       </c>
+      <c r="P13" t="s">
+        <v>31</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2170,6 +2207,9 @@
       <c r="O14" t="s">
         <v>31</v>
       </c>
+      <c r="P14" t="s">
+        <v>31</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2293,6 +2333,9 @@
       <c r="O15" t="s">
         <v>31</v>
       </c>
+      <c r="P15" t="s">
+        <v>31</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2416,6 +2459,9 @@
       <c r="O16" t="s">
         <v>31</v>
       </c>
+      <c r="P16" t="s">
+        <v>31</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2518,6 +2564,9 @@
       <c r="O17" t="s">
         <v>31</v>
       </c>
+      <c r="P17" t="s">
+        <v>31</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2641,6 +2690,9 @@
       <c r="O18" t="s">
         <v>31</v>
       </c>
+      <c r="P18" t="s">
+        <v>31</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2764,6 +2816,9 @@
       <c r="O19" t="s">
         <v>31</v>
       </c>
+      <c r="P19" t="s">
+        <v>31</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2866,6 +2921,9 @@
       <c r="O20" t="s">
         <v>31</v>
       </c>
+      <c r="P20" t="s">
+        <v>31</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -2989,6 +3047,9 @@
       <c r="O21" t="s">
         <v>31</v>
       </c>
+      <c r="P21" t="s">
+        <v>31</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3112,6 +3173,9 @@
       <c r="O22" t="s">
         <v>31</v>
       </c>
+      <c r="P22" t="s">
+        <v>31</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3235,6 +3299,9 @@
       <c r="O23" t="s">
         <v>31</v>
       </c>
+      <c r="P23" t="s">
+        <v>31</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3358,6 +3425,9 @@
       <c r="O24" t="s">
         <v>31</v>
       </c>
+      <c r="P24" t="s">
+        <v>31</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3481,6 +3551,9 @@
       <c r="O25" t="s">
         <v>31</v>
       </c>
+      <c r="P25" t="s">
+        <v>31</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3604,6 +3677,9 @@
       <c r="O26" t="s">
         <v>31</v>
       </c>
+      <c r="P26" t="s">
+        <v>31</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3727,6 +3803,9 @@
       <c r="O27" t="s">
         <v>31</v>
       </c>
+      <c r="P27" t="s">
+        <v>31</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3850,6 +3929,9 @@
       <c r="O28" t="s">
         <v>31</v>
       </c>
+      <c r="P28" t="s">
+        <v>31</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3964,6 +4046,9 @@
       <c r="O29" t="s">
         <v>31</v>
       </c>
+      <c r="P29" t="s">
+        <v>31</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4087,6 +4172,9 @@
       <c r="O30" t="s">
         <v>31</v>
       </c>
+      <c r="P30" t="s">
+        <v>31</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4210,6 +4298,9 @@
       <c r="O31" t="s">
         <v>31</v>
       </c>
+      <c r="P31" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -4258,8 +4349,11 @@
       <c r="O32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4306,8 +4400,11 @@
       <c r="O33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4352,6 +4449,9 @@
         <v>31</v>
       </c>
       <c r="O34" t="s">
+        <v>31</v>
+      </c>
+      <c r="P34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4365,7 +4465,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 L31:O34 H33:I33">
+  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:P34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4DBDC2-D89D-4CE5-8444-4E2B9A35858D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F887E9-E8B7-40A1-A04A-2F28F35E7C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -600,7 +600,9 @@
       <c r="P1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="1"/>
+      <c r="Q1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
@@ -725,7 +727,9 @@
       <c r="P2" s="1">
         <v>46091</v>
       </c>
-      <c r="Q2" s="1"/>
+      <c r="Q2" s="1">
+        <v>46098</v>
+      </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
@@ -831,6 +835,9 @@
         <v>31</v>
       </c>
       <c r="P3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -959,6 +966,9 @@
       <c r="P4" t="s">
         <v>31</v>
       </c>
+      <c r="Q4" t="s">
+        <v>31</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1085,6 +1095,9 @@
       <c r="P5" t="s">
         <v>31</v>
       </c>
+      <c r="Q5" t="s">
+        <v>31</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1211,6 +1224,9 @@
       <c r="P6" t="s">
         <v>31</v>
       </c>
+      <c r="Q6" t="s">
+        <v>31</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1337,6 +1353,9 @@
       <c r="P7" t="s">
         <v>31</v>
       </c>
+      <c r="Q7" t="s">
+        <v>31</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1463,6 +1482,9 @@
       <c r="P8" t="s">
         <v>31</v>
       </c>
+      <c r="Q8" t="s">
+        <v>31</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1589,6 +1611,9 @@
       <c r="P9" t="s">
         <v>31</v>
       </c>
+      <c r="Q9" t="s">
+        <v>31</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1715,6 +1740,9 @@
       <c r="P10" t="s">
         <v>31</v>
       </c>
+      <c r="Q10" t="s">
+        <v>31</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1832,6 +1860,9 @@
       <c r="P11" t="s">
         <v>31</v>
       </c>
+      <c r="Q11" t="s">
+        <v>31</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1958,6 +1989,9 @@
       <c r="P12" t="s">
         <v>31</v>
       </c>
+      <c r="Q12" t="s">
+        <v>31</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2084,6 +2118,9 @@
       <c r="P13" t="s">
         <v>31</v>
       </c>
+      <c r="Q13" t="s">
+        <v>31</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2210,6 +2247,9 @@
       <c r="P14" t="s">
         <v>31</v>
       </c>
+      <c r="Q14" t="s">
+        <v>31</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2336,6 +2376,9 @@
       <c r="P15" t="s">
         <v>31</v>
       </c>
+      <c r="Q15" t="s">
+        <v>31</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2462,6 +2505,9 @@
       <c r="P16" t="s">
         <v>31</v>
       </c>
+      <c r="Q16" t="s">
+        <v>31</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2567,6 +2613,9 @@
       <c r="P17" t="s">
         <v>31</v>
       </c>
+      <c r="Q17" t="s">
+        <v>31</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2693,6 +2742,9 @@
       <c r="P18" t="s">
         <v>31</v>
       </c>
+      <c r="Q18" t="s">
+        <v>31</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2819,6 +2871,9 @@
       <c r="P19" t="s">
         <v>31</v>
       </c>
+      <c r="Q19" t="s">
+        <v>31</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2924,6 +2979,9 @@
       <c r="P20" t="s">
         <v>31</v>
       </c>
+      <c r="Q20" t="s">
+        <v>31</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3050,6 +3108,9 @@
       <c r="P21" t="s">
         <v>31</v>
       </c>
+      <c r="Q21" t="s">
+        <v>31</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3176,6 +3237,9 @@
       <c r="P22" t="s">
         <v>31</v>
       </c>
+      <c r="Q22" t="s">
+        <v>31</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3302,6 +3366,9 @@
       <c r="P23" t="s">
         <v>31</v>
       </c>
+      <c r="Q23" t="s">
+        <v>31</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3428,6 +3495,9 @@
       <c r="P24" t="s">
         <v>31</v>
       </c>
+      <c r="Q24" t="s">
+        <v>31</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3554,6 +3624,9 @@
       <c r="P25" t="s">
         <v>31</v>
       </c>
+      <c r="Q25" t="s">
+        <v>31</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3680,6 +3753,9 @@
       <c r="P26" t="s">
         <v>31</v>
       </c>
+      <c r="Q26" t="s">
+        <v>31</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3806,6 +3882,9 @@
       <c r="P27" t="s">
         <v>31</v>
       </c>
+      <c r="Q27" t="s">
+        <v>31</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3932,6 +4011,9 @@
       <c r="P28" t="s">
         <v>31</v>
       </c>
+      <c r="Q28" t="s">
+        <v>31</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4049,6 +4131,9 @@
       <c r="P29" t="s">
         <v>31</v>
       </c>
+      <c r="Q29" t="s">
+        <v>31</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4175,6 +4260,9 @@
       <c r="P30" t="s">
         <v>31</v>
       </c>
+      <c r="Q30" t="s">
+        <v>31</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4301,6 +4389,9 @@
       <c r="P31" t="s">
         <v>31</v>
       </c>
+      <c r="Q31" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -4352,8 +4443,11 @@
       <c r="P32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4403,8 +4497,11 @@
       <c r="P33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4452,6 +4549,9 @@
         <v>31</v>
       </c>
       <c r="P34" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4465,7 +4565,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:P34">
+  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:Q34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F887E9-E8B7-40A1-A04A-2F28F35E7C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C74FCC-5625-449F-AE4C-0EF2CCEC8121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -601,11 +601,17 @@
         <v>33</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
+      <c r="S1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
@@ -730,7 +736,9 @@
       <c r="Q2" s="1">
         <v>46098</v>
       </c>
-      <c r="R2" s="1"/>
+      <c r="R2" s="1">
+        <v>46100</v>
+      </c>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
@@ -838,6 +846,9 @@
         <v>31</v>
       </c>
       <c r="Q3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -969,6 +980,9 @@
       <c r="Q4" t="s">
         <v>31</v>
       </c>
+      <c r="R4" t="s">
+        <v>31</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1098,6 +1112,9 @@
       <c r="Q5" t="s">
         <v>31</v>
       </c>
+      <c r="R5" t="s">
+        <v>31</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1227,6 +1244,9 @@
       <c r="Q6" t="s">
         <v>31</v>
       </c>
+      <c r="R6" t="s">
+        <v>31</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1356,6 +1376,9 @@
       <c r="Q7" t="s">
         <v>31</v>
       </c>
+      <c r="R7" t="s">
+        <v>31</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1485,6 +1508,9 @@
       <c r="Q8" t="s">
         <v>31</v>
       </c>
+      <c r="R8" t="s">
+        <v>31</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1614,6 +1640,9 @@
       <c r="Q9" t="s">
         <v>31</v>
       </c>
+      <c r="R9" t="s">
+        <v>31</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1743,6 +1772,9 @@
       <c r="Q10" t="s">
         <v>31</v>
       </c>
+      <c r="R10" t="s">
+        <v>31</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1863,6 +1895,9 @@
       <c r="Q11" t="s">
         <v>31</v>
       </c>
+      <c r="R11" t="s">
+        <v>32</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1992,6 +2027,9 @@
       <c r="Q12" t="s">
         <v>31</v>
       </c>
+      <c r="R12" t="s">
+        <v>31</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2121,6 +2159,9 @@
       <c r="Q13" t="s">
         <v>31</v>
       </c>
+      <c r="R13" t="s">
+        <v>31</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2250,6 +2291,9 @@
       <c r="Q14" t="s">
         <v>31</v>
       </c>
+      <c r="R14" t="s">
+        <v>31</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2379,6 +2423,9 @@
       <c r="Q15" t="s">
         <v>31</v>
       </c>
+      <c r="R15" t="s">
+        <v>31</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2508,6 +2555,9 @@
       <c r="Q16" t="s">
         <v>31</v>
       </c>
+      <c r="R16" t="s">
+        <v>31</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2616,6 +2666,9 @@
       <c r="Q17" t="s">
         <v>31</v>
       </c>
+      <c r="R17" t="s">
+        <v>31</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2745,6 +2798,9 @@
       <c r="Q18" t="s">
         <v>31</v>
       </c>
+      <c r="R18" t="s">
+        <v>31</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2874,6 +2930,9 @@
       <c r="Q19" t="s">
         <v>31</v>
       </c>
+      <c r="R19" t="s">
+        <v>31</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2982,6 +3041,9 @@
       <c r="Q20" t="s">
         <v>31</v>
       </c>
+      <c r="R20" t="s">
+        <v>31</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3111,6 +3173,9 @@
       <c r="Q21" t="s">
         <v>31</v>
       </c>
+      <c r="R21" t="s">
+        <v>31</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3240,6 +3305,9 @@
       <c r="Q22" t="s">
         <v>31</v>
       </c>
+      <c r="R22" t="s">
+        <v>31</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3369,6 +3437,9 @@
       <c r="Q23" t="s">
         <v>31</v>
       </c>
+      <c r="R23" t="s">
+        <v>31</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3498,6 +3569,9 @@
       <c r="Q24" t="s">
         <v>31</v>
       </c>
+      <c r="R24" t="s">
+        <v>31</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3627,6 +3701,9 @@
       <c r="Q25" t="s">
         <v>31</v>
       </c>
+      <c r="R25" t="s">
+        <v>31</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3756,6 +3833,9 @@
       <c r="Q26" t="s">
         <v>31</v>
       </c>
+      <c r="R26" t="s">
+        <v>31</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3885,6 +3965,9 @@
       <c r="Q27" t="s">
         <v>31</v>
       </c>
+      <c r="R27" t="s">
+        <v>31</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4014,6 +4097,9 @@
       <c r="Q28" t="s">
         <v>31</v>
       </c>
+      <c r="R28" t="s">
+        <v>31</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4134,6 +4220,9 @@
       <c r="Q29" t="s">
         <v>31</v>
       </c>
+      <c r="R29" t="s">
+        <v>31</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4263,6 +4352,9 @@
       <c r="Q30" t="s">
         <v>31</v>
       </c>
+      <c r="R30" t="s">
+        <v>31</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4392,6 +4484,9 @@
       <c r="Q31" t="s">
         <v>31</v>
       </c>
+      <c r="R31" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -4446,8 +4541,11 @@
       <c r="Q32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4500,8 +4598,11 @@
       <c r="Q33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4552,6 +4653,9 @@
         <v>31</v>
       </c>
       <c r="Q34" t="s">
+        <v>31</v>
+      </c>
+      <c r="R34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4565,7 +4669,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:Q34">
+  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:R34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C74FCC-5625-449F-AE4C-0EF2CCEC8121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36CA4BD-73D3-450F-A262-3ED95374F7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -548,19 +548,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="7.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.21875" bestFit="1" customWidth="1"/>
+    <col min="21" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -684,7 +690,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -739,7 +745,9 @@
       <c r="R2" s="1">
         <v>46100</v>
       </c>
-      <c r="S2" s="1"/>
+      <c r="S2" s="1">
+        <v>46105</v>
+      </c>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -795,7 +803,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -849,6 +857,9 @@
         <v>31</v>
       </c>
       <c r="R3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -927,7 +938,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -981,6 +992,9 @@
         <v>31</v>
       </c>
       <c r="R4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S4" t="s">
         <v>31</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1059,7 +1073,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1113,6 +1127,9 @@
         <v>31</v>
       </c>
       <c r="R5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S5" t="s">
         <v>31</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1191,7 +1208,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1245,6 +1262,9 @@
         <v>31</v>
       </c>
       <c r="R6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S6" t="s">
         <v>31</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1323,7 +1343,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1377,6 +1397,9 @@
         <v>31</v>
       </c>
       <c r="R7" t="s">
+        <v>31</v>
+      </c>
+      <c r="S7" t="s">
         <v>31</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1455,7 +1478,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1509,6 +1532,9 @@
         <v>31</v>
       </c>
       <c r="R8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S8" t="s">
         <v>31</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1587,7 +1613,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1641,6 +1667,9 @@
         <v>31</v>
       </c>
       <c r="R9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S9" t="s">
         <v>31</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1719,7 +1748,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -1773,6 +1802,9 @@
         <v>31</v>
       </c>
       <c r="R10" t="s">
+        <v>31</v>
+      </c>
+      <c r="S10" t="s">
         <v>31</v>
       </c>
       <c r="AU10" s="2"/>
@@ -1851,7 +1883,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -1897,6 +1929,9 @@
       </c>
       <c r="R11" t="s">
         <v>32</v>
+      </c>
+      <c r="S11" t="s">
+        <v>31</v>
       </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
@@ -1974,7 +2009,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -2028,6 +2063,9 @@
         <v>31</v>
       </c>
       <c r="R12" t="s">
+        <v>31</v>
+      </c>
+      <c r="S12" t="s">
         <v>31</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2106,7 +2144,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2160,6 +2198,9 @@
         <v>31</v>
       </c>
       <c r="R13" t="s">
+        <v>31</v>
+      </c>
+      <c r="S13" t="s">
         <v>31</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2238,7 +2279,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2292,6 +2333,9 @@
         <v>31</v>
       </c>
       <c r="R14" t="s">
+        <v>31</v>
+      </c>
+      <c r="S14" t="s">
         <v>31</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2370,7 +2414,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2424,6 +2468,9 @@
         <v>31</v>
       </c>
       <c r="R15" t="s">
+        <v>31</v>
+      </c>
+      <c r="S15" t="s">
         <v>31</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2502,7 +2549,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2556,6 +2603,9 @@
         <v>31</v>
       </c>
       <c r="R16" t="s">
+        <v>31</v>
+      </c>
+      <c r="S16" t="s">
         <v>31</v>
       </c>
       <c r="AU16" s="2"/>
@@ -2634,7 +2684,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -2667,6 +2717,9 @@
         <v>31</v>
       </c>
       <c r="R17" t="s">
+        <v>31</v>
+      </c>
+      <c r="S17" t="s">
         <v>31</v>
       </c>
       <c r="AU17" s="2"/>
@@ -2745,7 +2798,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -2799,6 +2852,9 @@
         <v>31</v>
       </c>
       <c r="R18" t="s">
+        <v>31</v>
+      </c>
+      <c r="S18" t="s">
         <v>31</v>
       </c>
       <c r="AU18" s="2"/>
@@ -2877,7 +2933,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -2931,6 +2987,9 @@
         <v>31</v>
       </c>
       <c r="R19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S19" t="s">
         <v>31</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3009,7 +3068,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -3042,6 +3101,9 @@
         <v>31</v>
       </c>
       <c r="R20" t="s">
+        <v>31</v>
+      </c>
+      <c r="S20" t="s">
         <v>31</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3120,7 +3182,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3174,6 +3236,9 @@
         <v>31</v>
       </c>
       <c r="R21" t="s">
+        <v>31</v>
+      </c>
+      <c r="S21" t="s">
         <v>31</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3252,7 +3317,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3306,6 +3371,9 @@
         <v>31</v>
       </c>
       <c r="R22" t="s">
+        <v>31</v>
+      </c>
+      <c r="S22" t="s">
         <v>31</v>
       </c>
       <c r="AU22" s="2"/>
@@ -3384,7 +3452,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3438,6 +3506,9 @@
         <v>31</v>
       </c>
       <c r="R23" t="s">
+        <v>31</v>
+      </c>
+      <c r="S23" t="s">
         <v>31</v>
       </c>
       <c r="AU23" s="2"/>
@@ -3516,7 +3587,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -3570,6 +3641,9 @@
         <v>31</v>
       </c>
       <c r="R24" t="s">
+        <v>31</v>
+      </c>
+      <c r="S24" t="s">
         <v>31</v>
       </c>
       <c r="AU24" s="2"/>
@@ -3648,7 +3722,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -3702,6 +3776,9 @@
         <v>31</v>
       </c>
       <c r="R25" t="s">
+        <v>31</v>
+      </c>
+      <c r="S25" t="s">
         <v>31</v>
       </c>
       <c r="AU25" s="2"/>
@@ -3780,7 +3857,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -3834,6 +3911,9 @@
         <v>31</v>
       </c>
       <c r="R26" t="s">
+        <v>31</v>
+      </c>
+      <c r="S26" t="s">
         <v>31</v>
       </c>
       <c r="AU26" s="2"/>
@@ -3912,7 +3992,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -3966,6 +4046,9 @@
         <v>31</v>
       </c>
       <c r="R27" t="s">
+        <v>31</v>
+      </c>
+      <c r="S27" t="s">
         <v>31</v>
       </c>
       <c r="AU27" s="2"/>
@@ -4044,7 +4127,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -4098,6 +4181,9 @@
         <v>31</v>
       </c>
       <c r="R28" t="s">
+        <v>31</v>
+      </c>
+      <c r="S28" t="s">
         <v>31</v>
       </c>
       <c r="AU28" s="2"/>
@@ -4176,7 +4262,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -4221,6 +4307,9 @@
         <v>31</v>
       </c>
       <c r="R29" t="s">
+        <v>31</v>
+      </c>
+      <c r="S29" t="s">
         <v>31</v>
       </c>
       <c r="AU29" s="2"/>
@@ -4299,7 +4388,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -4353,6 +4442,9 @@
         <v>31</v>
       </c>
       <c r="R30" t="s">
+        <v>31</v>
+      </c>
+      <c r="S30" t="s">
         <v>31</v>
       </c>
       <c r="AU30" s="2"/>
@@ -4431,7 +4523,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -4487,8 +4579,11 @@
       <c r="R31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="S31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>0</v>
@@ -4544,8 +4639,11 @@
       <c r="R32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4601,8 +4699,11 @@
       <c r="R33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4656,6 +4757,9 @@
         <v>31</v>
       </c>
       <c r="R34" t="s">
+        <v>31</v>
+      </c>
+      <c r="S34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4669,7 +4773,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:R34">
+  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:S34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4682,15 +4786,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4698,162 +4802,162 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>30</v>
       </c>
@@ -4870,203 +4974,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36CA4BD-73D3-450F-A262-3ED95374F7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E345C5-D9C5-49D8-832E-95AB0E78D0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -559,8 +559,7 @@
     <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="20" width="7" bestFit="1" customWidth="1"/>
     <col min="21" max="50" width="7.6640625" customWidth="1"/>
     <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
     <col min="52" max="106" width="7.6640625" customWidth="1"/>
@@ -748,7 +747,9 @@
       <c r="S2" s="1">
         <v>46105</v>
       </c>
-      <c r="T2" s="1"/>
+      <c r="T2" s="1">
+        <v>46107</v>
+      </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
@@ -860,6 +861,9 @@
         <v>31</v>
       </c>
       <c r="S3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -997,6 +1001,9 @@
       <c r="S4" t="s">
         <v>31</v>
       </c>
+      <c r="T4" t="s">
+        <v>31</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1132,6 +1139,9 @@
       <c r="S5" t="s">
         <v>31</v>
       </c>
+      <c r="T5" t="s">
+        <v>31</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1267,6 +1277,9 @@
       <c r="S6" t="s">
         <v>31</v>
       </c>
+      <c r="T6" t="s">
+        <v>31</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1402,6 +1415,9 @@
       <c r="S7" t="s">
         <v>31</v>
       </c>
+      <c r="T7" t="s">
+        <v>31</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1537,6 +1553,9 @@
       <c r="S8" t="s">
         <v>31</v>
       </c>
+      <c r="T8" t="s">
+        <v>31</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1672,6 +1691,9 @@
       <c r="S9" t="s">
         <v>31</v>
       </c>
+      <c r="T9" t="s">
+        <v>31</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1807,6 +1829,9 @@
       <c r="S10" t="s">
         <v>31</v>
       </c>
+      <c r="T10" t="s">
+        <v>31</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1933,6 +1958,9 @@
       <c r="S11" t="s">
         <v>31</v>
       </c>
+      <c r="T11" t="s">
+        <v>31</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2068,6 +2096,9 @@
       <c r="S12" t="s">
         <v>31</v>
       </c>
+      <c r="T12" t="s">
+        <v>31</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2203,6 +2234,9 @@
       <c r="S13" t="s">
         <v>31</v>
       </c>
+      <c r="T13" t="s">
+        <v>31</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2338,6 +2372,9 @@
       <c r="S14" t="s">
         <v>31</v>
       </c>
+      <c r="T14" t="s">
+        <v>31</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2473,6 +2510,9 @@
       <c r="S15" t="s">
         <v>31</v>
       </c>
+      <c r="T15" t="s">
+        <v>31</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2608,6 +2648,9 @@
       <c r="S16" t="s">
         <v>31</v>
       </c>
+      <c r="T16" t="s">
+        <v>31</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2722,6 +2765,9 @@
       <c r="S17" t="s">
         <v>31</v>
       </c>
+      <c r="T17" t="s">
+        <v>31</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2857,6 +2903,9 @@
       <c r="S18" t="s">
         <v>31</v>
       </c>
+      <c r="T18" t="s">
+        <v>31</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2992,6 +3041,9 @@
       <c r="S19" t="s">
         <v>31</v>
       </c>
+      <c r="T19" t="s">
+        <v>31</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3106,6 +3158,9 @@
       <c r="S20" t="s">
         <v>31</v>
       </c>
+      <c r="T20" t="s">
+        <v>31</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3241,6 +3296,9 @@
       <c r="S21" t="s">
         <v>31</v>
       </c>
+      <c r="T21" t="s">
+        <v>31</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3376,6 +3434,9 @@
       <c r="S22" t="s">
         <v>31</v>
       </c>
+      <c r="T22" t="s">
+        <v>31</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3511,6 +3572,9 @@
       <c r="S23" t="s">
         <v>31</v>
       </c>
+      <c r="T23" t="s">
+        <v>31</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3646,6 +3710,9 @@
       <c r="S24" t="s">
         <v>31</v>
       </c>
+      <c r="T24" t="s">
+        <v>31</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3781,6 +3848,9 @@
       <c r="S25" t="s">
         <v>31</v>
       </c>
+      <c r="T25" t="s">
+        <v>31</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3916,6 +3986,9 @@
       <c r="S26" t="s">
         <v>31</v>
       </c>
+      <c r="T26" t="s">
+        <v>31</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4051,6 +4124,9 @@
       <c r="S27" t="s">
         <v>31</v>
       </c>
+      <c r="T27" t="s">
+        <v>31</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4186,6 +4262,9 @@
       <c r="S28" t="s">
         <v>31</v>
       </c>
+      <c r="T28" t="s">
+        <v>31</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4312,6 +4391,9 @@
       <c r="S29" t="s">
         <v>31</v>
       </c>
+      <c r="T29" t="s">
+        <v>31</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4447,6 +4529,9 @@
       <c r="S30" t="s">
         <v>31</v>
       </c>
+      <c r="T30" t="s">
+        <v>31</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4582,6 +4667,9 @@
       <c r="S31" t="s">
         <v>31</v>
       </c>
+      <c r="T31" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
@@ -4642,8 +4730,11 @@
       <c r="S32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4702,8 +4793,11 @@
       <c r="S33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4760,6 +4854,9 @@
         <v>31</v>
       </c>
       <c r="S34" t="s">
+        <v>31</v>
+      </c>
+      <c r="T34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4773,7 +4870,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:S34">
+  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:T34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E345C5-D9C5-49D8-832E-95AB0E78D0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8437F31-FB67-4912-AB71-E799F9A339C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -548,24 +548,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="20" width="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="21" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -617,7 +616,9 @@
       <c r="T1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="U1" s="1"/>
+      <c r="U1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
@@ -689,7 +690,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -750,7 +751,9 @@
       <c r="T2" s="1">
         <v>46107</v>
       </c>
-      <c r="U2" s="1"/>
+      <c r="U2" s="1">
+        <v>46112</v>
+      </c>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
@@ -804,7 +807,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -864,6 +867,9 @@
         <v>31</v>
       </c>
       <c r="T3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -942,7 +948,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -1002,6 +1008,9 @@
         <v>31</v>
       </c>
       <c r="T4" t="s">
+        <v>31</v>
+      </c>
+      <c r="U4" t="s">
         <v>31</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1080,7 +1089,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1140,6 +1149,9 @@
         <v>31</v>
       </c>
       <c r="T5" t="s">
+        <v>31</v>
+      </c>
+      <c r="U5" t="s">
         <v>31</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1218,7 +1230,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1278,6 +1290,9 @@
         <v>31</v>
       </c>
       <c r="T6" t="s">
+        <v>31</v>
+      </c>
+      <c r="U6" t="s">
         <v>31</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1356,7 +1371,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1416,6 +1431,9 @@
         <v>31</v>
       </c>
       <c r="T7" t="s">
+        <v>31</v>
+      </c>
+      <c r="U7" t="s">
         <v>31</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1494,7 +1512,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1554,6 +1572,9 @@
         <v>31</v>
       </c>
       <c r="T8" t="s">
+        <v>31</v>
+      </c>
+      <c r="U8" t="s">
         <v>31</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1632,7 +1653,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1692,6 +1713,9 @@
         <v>31</v>
       </c>
       <c r="T9" t="s">
+        <v>31</v>
+      </c>
+      <c r="U9" t="s">
         <v>31</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1770,7 +1794,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -1830,6 +1854,9 @@
         <v>31</v>
       </c>
       <c r="T10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U10" t="s">
         <v>31</v>
       </c>
       <c r="AU10" s="2"/>
@@ -1908,7 +1935,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -1959,6 +1986,9 @@
         <v>31</v>
       </c>
       <c r="T11" t="s">
+        <v>31</v>
+      </c>
+      <c r="U11" t="s">
         <v>31</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2037,7 +2067,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -2098,6 +2128,9 @@
       </c>
       <c r="T12" t="s">
         <v>31</v>
+      </c>
+      <c r="U12" t="s">
+        <v>32</v>
       </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
@@ -2175,7 +2208,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2235,6 +2268,9 @@
         <v>31</v>
       </c>
       <c r="T13" t="s">
+        <v>31</v>
+      </c>
+      <c r="U13" t="s">
         <v>31</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2313,7 +2349,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2373,6 +2409,9 @@
         <v>31</v>
       </c>
       <c r="T14" t="s">
+        <v>31</v>
+      </c>
+      <c r="U14" t="s">
         <v>31</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2451,7 +2490,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2511,6 +2550,9 @@
         <v>31</v>
       </c>
       <c r="T15" t="s">
+        <v>31</v>
+      </c>
+      <c r="U15" t="s">
         <v>31</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2589,7 +2631,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2649,6 +2691,9 @@
         <v>31</v>
       </c>
       <c r="T16" t="s">
+        <v>31</v>
+      </c>
+      <c r="U16" t="s">
         <v>31</v>
       </c>
       <c r="AU16" s="2"/>
@@ -2727,7 +2772,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -2766,6 +2811,9 @@
         <v>31</v>
       </c>
       <c r="T17" t="s">
+        <v>31</v>
+      </c>
+      <c r="U17" t="s">
         <v>31</v>
       </c>
       <c r="AU17" s="2"/>
@@ -2844,7 +2892,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -2904,6 +2952,9 @@
         <v>31</v>
       </c>
       <c r="T18" t="s">
+        <v>31</v>
+      </c>
+      <c r="U18" t="s">
         <v>31</v>
       </c>
       <c r="AU18" s="2"/>
@@ -2982,7 +3033,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -3042,6 +3093,9 @@
         <v>31</v>
       </c>
       <c r="T19" t="s">
+        <v>31</v>
+      </c>
+      <c r="U19" t="s">
         <v>31</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3120,7 +3174,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -3159,6 +3213,9 @@
         <v>31</v>
       </c>
       <c r="T20" t="s">
+        <v>31</v>
+      </c>
+      <c r="U20" t="s">
         <v>31</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3237,7 +3294,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3297,6 +3354,9 @@
         <v>31</v>
       </c>
       <c r="T21" t="s">
+        <v>31</v>
+      </c>
+      <c r="U21" t="s">
         <v>31</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3375,7 +3435,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3435,6 +3495,9 @@
         <v>31</v>
       </c>
       <c r="T22" t="s">
+        <v>31</v>
+      </c>
+      <c r="U22" t="s">
         <v>31</v>
       </c>
       <c r="AU22" s="2"/>
@@ -3513,7 +3576,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3574,6 +3637,9 @@
       </c>
       <c r="T23" t="s">
         <v>31</v>
+      </c>
+      <c r="U23" t="s">
+        <v>32</v>
       </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
@@ -3651,7 +3717,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -3711,6 +3777,9 @@
         <v>31</v>
       </c>
       <c r="T24" t="s">
+        <v>31</v>
+      </c>
+      <c r="U24" t="s">
         <v>31</v>
       </c>
       <c r="AU24" s="2"/>
@@ -3789,7 +3858,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -3849,6 +3918,9 @@
         <v>31</v>
       </c>
       <c r="T25" t="s">
+        <v>31</v>
+      </c>
+      <c r="U25" t="s">
         <v>31</v>
       </c>
       <c r="AU25" s="2"/>
@@ -3927,7 +3999,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -3987,6 +4059,9 @@
         <v>31</v>
       </c>
       <c r="T26" t="s">
+        <v>31</v>
+      </c>
+      <c r="U26" t="s">
         <v>31</v>
       </c>
       <c r="AU26" s="2"/>
@@ -4065,7 +4140,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -4125,6 +4200,9 @@
         <v>31</v>
       </c>
       <c r="T27" t="s">
+        <v>31</v>
+      </c>
+      <c r="U27" t="s">
         <v>31</v>
       </c>
       <c r="AU27" s="2"/>
@@ -4203,7 +4281,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -4263,6 +4341,9 @@
         <v>31</v>
       </c>
       <c r="T28" t="s">
+        <v>31</v>
+      </c>
+      <c r="U28" t="s">
         <v>31</v>
       </c>
       <c r="AU28" s="2"/>
@@ -4341,7 +4422,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -4392,6 +4473,9 @@
         <v>31</v>
       </c>
       <c r="T29" t="s">
+        <v>31</v>
+      </c>
+      <c r="U29" t="s">
         <v>31</v>
       </c>
       <c r="AU29" s="2"/>
@@ -4470,7 +4554,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -4530,6 +4614,9 @@
         <v>31</v>
       </c>
       <c r="T30" t="s">
+        <v>31</v>
+      </c>
+      <c r="U30" t="s">
         <v>31</v>
       </c>
       <c r="AU30" s="2"/>
@@ -4608,7 +4695,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -4670,8 +4757,11 @@
       <c r="T31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="U31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>0</v>
@@ -4733,8 +4823,11 @@
       <c r="T32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4796,8 +4889,11 @@
       <c r="T33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4857,6 +4953,9 @@
         <v>31</v>
       </c>
       <c r="T34" t="s">
+        <v>31</v>
+      </c>
+      <c r="U34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4870,7 +4969,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 L3:AZ9 K3:K10 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 L10:BA10 BC10:BJ21 K11:BA21 K22:BJ30 K31:K33 H33:I33 L31:T34">
+  <conditionalFormatting sqref="BE3:DG3 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 K3:T30 BC10:BJ21 K31:K33 L31:T34 H33:I33 V22:BJ30 V10:BA21 V3:AZ9 U3:U34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4883,15 +4982,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4899,162 +4998,162 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>30</v>
       </c>
@@ -5071,203 +5170,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{C8437F31-FB67-4912-AB71-E799F9A339C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -4969,7 +4969,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 BB3:BB21 D3:I30 BE4:BJ9 BK4:DG30 K3:T30 BC10:BJ21 K31:K33 L31:T34 H33:I33 V22:BJ30 V10:BA21 V3:AZ9 U3:U34">
+  <conditionalFormatting sqref="BE3:DG3 V3:AZ9 BB3:BB21 D3:I30 K3:T30 U3:U34 BE4:BJ9 BK4:DG30 V10:BA21 BC10:BJ21 V22:BJ30 K31:K33 L31:T34 H33:I33">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8437F31-FB67-4912-AB71-E799F9A339C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F4E629-092A-4146-9AD0-F26E606C016C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -548,23 +548,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="20" width="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="21" max="21" width="7.6640625" customWidth="1"/>
+    <col min="22" max="22" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -619,7 +621,9 @@
       <c r="U1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="V1" s="1"/>
+      <c r="V1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
@@ -690,7 +694,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -754,7 +758,9 @@
       <c r="U2" s="1">
         <v>46112</v>
       </c>
-      <c r="V2" s="1"/>
+      <c r="V2" s="1">
+        <v>46114</v>
+      </c>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
@@ -807,7 +813,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -870,6 +876,9 @@
         <v>31</v>
       </c>
       <c r="U3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -948,7 +957,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -1011,6 +1020,9 @@
         <v>31</v>
       </c>
       <c r="U4" t="s">
+        <v>31</v>
+      </c>
+      <c r="V4" t="s">
         <v>31</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1089,7 +1101,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1152,6 +1164,9 @@
         <v>31</v>
       </c>
       <c r="U5" t="s">
+        <v>31</v>
+      </c>
+      <c r="V5" t="s">
         <v>31</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1230,7 +1245,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1293,6 +1308,9 @@
         <v>31</v>
       </c>
       <c r="U6" t="s">
+        <v>31</v>
+      </c>
+      <c r="V6" t="s">
         <v>31</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1371,7 +1389,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1434,6 +1452,9 @@
         <v>31</v>
       </c>
       <c r="U7" t="s">
+        <v>31</v>
+      </c>
+      <c r="V7" t="s">
         <v>31</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1512,7 +1533,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1575,6 +1596,9 @@
         <v>31</v>
       </c>
       <c r="U8" t="s">
+        <v>31</v>
+      </c>
+      <c r="V8" t="s">
         <v>31</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1653,7 +1677,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1716,6 +1740,9 @@
         <v>31</v>
       </c>
       <c r="U9" t="s">
+        <v>31</v>
+      </c>
+      <c r="V9" t="s">
         <v>31</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1794,7 +1821,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -1857,6 +1884,9 @@
         <v>31</v>
       </c>
       <c r="U10" t="s">
+        <v>31</v>
+      </c>
+      <c r="V10" t="s">
         <v>31</v>
       </c>
       <c r="AU10" s="2"/>
@@ -1935,7 +1965,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -1989,6 +2019,9 @@
         <v>31</v>
       </c>
       <c r="U11" t="s">
+        <v>31</v>
+      </c>
+      <c r="V11" t="s">
         <v>31</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2067,7 +2100,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -2131,6 +2164,9 @@
       </c>
       <c r="U12" t="s">
         <v>32</v>
+      </c>
+      <c r="V12" t="s">
+        <v>31</v>
       </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
@@ -2208,7 +2244,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2271,6 +2307,9 @@
         <v>31</v>
       </c>
       <c r="U13" t="s">
+        <v>31</v>
+      </c>
+      <c r="V13" t="s">
         <v>31</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2349,7 +2388,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2412,6 +2451,9 @@
         <v>31</v>
       </c>
       <c r="U14" t="s">
+        <v>31</v>
+      </c>
+      <c r="V14" t="s">
         <v>31</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2490,7 +2532,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2553,6 +2595,9 @@
         <v>31</v>
       </c>
       <c r="U15" t="s">
+        <v>31</v>
+      </c>
+      <c r="V15" t="s">
         <v>31</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2631,7 +2676,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2694,6 +2739,9 @@
         <v>31</v>
       </c>
       <c r="U16" t="s">
+        <v>31</v>
+      </c>
+      <c r="V16" t="s">
         <v>31</v>
       </c>
       <c r="AU16" s="2"/>
@@ -2772,7 +2820,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -2814,6 +2862,9 @@
         <v>31</v>
       </c>
       <c r="U17" t="s">
+        <v>31</v>
+      </c>
+      <c r="V17" t="s">
         <v>31</v>
       </c>
       <c r="AU17" s="2"/>
@@ -2892,7 +2943,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -2955,6 +3006,9 @@
         <v>31</v>
       </c>
       <c r="U18" t="s">
+        <v>31</v>
+      </c>
+      <c r="V18" t="s">
         <v>31</v>
       </c>
       <c r="AU18" s="2"/>
@@ -3033,7 +3087,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -3096,6 +3150,9 @@
         <v>31</v>
       </c>
       <c r="U19" t="s">
+        <v>31</v>
+      </c>
+      <c r="V19" t="s">
         <v>31</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3174,7 +3231,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -3216,6 +3273,9 @@
         <v>31</v>
       </c>
       <c r="U20" t="s">
+        <v>31</v>
+      </c>
+      <c r="V20" t="s">
         <v>31</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3294,7 +3354,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3357,6 +3417,9 @@
         <v>31</v>
       </c>
       <c r="U21" t="s">
+        <v>31</v>
+      </c>
+      <c r="V21" t="s">
         <v>31</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3435,7 +3498,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3498,6 +3561,9 @@
         <v>31</v>
       </c>
       <c r="U22" t="s">
+        <v>31</v>
+      </c>
+      <c r="V22" t="s">
         <v>31</v>
       </c>
       <c r="AU22" s="2"/>
@@ -3576,7 +3642,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3640,6 +3706,9 @@
       </c>
       <c r="U23" t="s">
         <v>32</v>
+      </c>
+      <c r="V23" t="s">
+        <v>31</v>
       </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
@@ -3717,7 +3786,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -3780,6 +3849,9 @@
         <v>31</v>
       </c>
       <c r="U24" t="s">
+        <v>31</v>
+      </c>
+      <c r="V24" t="s">
         <v>31</v>
       </c>
       <c r="AU24" s="2"/>
@@ -3858,7 +3930,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -3921,6 +3993,9 @@
         <v>31</v>
       </c>
       <c r="U25" t="s">
+        <v>31</v>
+      </c>
+      <c r="V25" t="s">
         <v>31</v>
       </c>
       <c r="AU25" s="2"/>
@@ -3999,7 +4074,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -4062,6 +4137,9 @@
         <v>31</v>
       </c>
       <c r="U26" t="s">
+        <v>31</v>
+      </c>
+      <c r="V26" t="s">
         <v>31</v>
       </c>
       <c r="AU26" s="2"/>
@@ -4140,7 +4218,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -4203,6 +4281,9 @@
         <v>31</v>
       </c>
       <c r="U27" t="s">
+        <v>31</v>
+      </c>
+      <c r="V27" t="s">
         <v>31</v>
       </c>
       <c r="AU27" s="2"/>
@@ -4281,7 +4362,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -4344,6 +4425,9 @@
         <v>31</v>
       </c>
       <c r="U28" t="s">
+        <v>31</v>
+      </c>
+      <c r="V28" t="s">
         <v>31</v>
       </c>
       <c r="AU28" s="2"/>
@@ -4422,7 +4506,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -4476,6 +4560,9 @@
         <v>31</v>
       </c>
       <c r="U29" t="s">
+        <v>31</v>
+      </c>
+      <c r="V29" t="s">
         <v>31</v>
       </c>
       <c r="AU29" s="2"/>
@@ -4554,7 +4641,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -4617,6 +4704,9 @@
         <v>31</v>
       </c>
       <c r="U30" t="s">
+        <v>31</v>
+      </c>
+      <c r="V30" t="s">
         <v>31</v>
       </c>
       <c r="AU30" s="2"/>
@@ -4695,7 +4785,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -4760,8 +4850,11 @@
       <c r="U31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="V31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>0</v>
@@ -4826,8 +4919,11 @@
       <c r="U32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4892,8 +4988,11 @@
       <c r="U33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -4956,6 +5055,9 @@
         <v>31</v>
       </c>
       <c r="U34" t="s">
+        <v>31</v>
+      </c>
+      <c r="V34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4969,7 +5071,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 V3:AZ9 BB3:BB21 D3:I30 K3:T30 U3:U34 BE4:BJ9 BK4:DG30 V10:BA21 BC10:BJ21 V22:BJ30 K31:K33 L31:T34 H33:I33">
+  <conditionalFormatting sqref="BE3:DG3 V3:AZ3 BB3:BB21 D3:I30 K3:T30 U3:U34 BE4:BJ9 BK4:DG30 W10:BA21 BC10:BJ21 W22:BJ30 K31:K33 L31:T34 H33:I33 W4:AZ9 V4:V34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4982,15 +5084,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4998,162 +5100,162 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>30</v>
       </c>
@@ -5170,203 +5272,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F4E629-092A-4146-9AD0-F26E606C016C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D669A50-A893-4036-9B47-1C675E5B7C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -548,25 +548,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="20" width="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.6640625" customWidth="1"/>
-    <col min="22" max="22" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="34" width="6" customWidth="1"/>
+    <col min="35" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -622,9 +622,11 @@
         <v>33</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
@@ -694,7 +696,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -761,7 +763,9 @@
       <c r="V2" s="1">
         <v>46114</v>
       </c>
-      <c r="W2" s="1"/>
+      <c r="W2" s="1">
+        <v>46119</v>
+      </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
@@ -769,6 +773,10 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -813,7 +821,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -879,6 +887,9 @@
         <v>31</v>
       </c>
       <c r="V3" t="s">
+        <v>31</v>
+      </c>
+      <c r="W3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -957,7 +968,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -1023,6 +1034,9 @@
         <v>31</v>
       </c>
       <c r="V4" t="s">
+        <v>31</v>
+      </c>
+      <c r="W4" t="s">
         <v>31</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1101,7 +1115,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1167,6 +1181,9 @@
         <v>31</v>
       </c>
       <c r="V5" t="s">
+        <v>31</v>
+      </c>
+      <c r="W5" t="s">
         <v>31</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1245,7 +1262,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1311,6 +1328,9 @@
         <v>31</v>
       </c>
       <c r="V6" t="s">
+        <v>31</v>
+      </c>
+      <c r="W6" t="s">
         <v>31</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1389,7 +1409,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1455,6 +1475,9 @@
         <v>31</v>
       </c>
       <c r="V7" t="s">
+        <v>31</v>
+      </c>
+      <c r="W7" t="s">
         <v>31</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1533,7 +1556,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1599,6 +1622,9 @@
         <v>31</v>
       </c>
       <c r="V8" t="s">
+        <v>31</v>
+      </c>
+      <c r="W8" t="s">
         <v>31</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1677,7 +1703,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1743,6 +1769,9 @@
         <v>31</v>
       </c>
       <c r="V9" t="s">
+        <v>31</v>
+      </c>
+      <c r="W9" t="s">
         <v>31</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1821,7 +1850,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -1887,6 +1916,9 @@
         <v>31</v>
       </c>
       <c r="V10" t="s">
+        <v>31</v>
+      </c>
+      <c r="W10" t="s">
         <v>31</v>
       </c>
       <c r="AU10" s="2"/>
@@ -1965,7 +1997,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -2022,6 +2054,9 @@
         <v>31</v>
       </c>
       <c r="V11" t="s">
+        <v>31</v>
+      </c>
+      <c r="W11" t="s">
         <v>31</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2100,7 +2135,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -2166,6 +2201,9 @@
         <v>32</v>
       </c>
       <c r="V12" t="s">
+        <v>31</v>
+      </c>
+      <c r="W12" t="s">
         <v>31</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2244,7 +2282,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2310,6 +2348,9 @@
         <v>31</v>
       </c>
       <c r="V13" t="s">
+        <v>31</v>
+      </c>
+      <c r="W13" t="s">
         <v>31</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2388,7 +2429,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2454,6 +2495,9 @@
         <v>31</v>
       </c>
       <c r="V14" t="s">
+        <v>31</v>
+      </c>
+      <c r="W14" t="s">
         <v>31</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2532,7 +2576,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2598,6 +2642,9 @@
         <v>31</v>
       </c>
       <c r="V15" t="s">
+        <v>31</v>
+      </c>
+      <c r="W15" t="s">
         <v>31</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2676,7 +2723,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2743,6 +2790,9 @@
       </c>
       <c r="V16" t="s">
         <v>31</v>
+      </c>
+      <c r="W16" t="s">
+        <v>32</v>
       </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
@@ -2820,7 +2870,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -2865,6 +2915,9 @@
         <v>31</v>
       </c>
       <c r="V17" t="s">
+        <v>31</v>
+      </c>
+      <c r="W17" t="s">
         <v>31</v>
       </c>
       <c r="AU17" s="2"/>
@@ -2943,7 +2996,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -3009,6 +3062,9 @@
         <v>31</v>
       </c>
       <c r="V18" t="s">
+        <v>31</v>
+      </c>
+      <c r="W18" t="s">
         <v>31</v>
       </c>
       <c r="AU18" s="2"/>
@@ -3087,7 +3143,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -3153,6 +3209,9 @@
         <v>31</v>
       </c>
       <c r="V19" t="s">
+        <v>31</v>
+      </c>
+      <c r="W19" t="s">
         <v>31</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3231,7 +3290,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -3276,6 +3335,9 @@
         <v>31</v>
       </c>
       <c r="V20" t="s">
+        <v>31</v>
+      </c>
+      <c r="W20" t="s">
         <v>31</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3354,7 +3416,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3420,6 +3482,9 @@
         <v>31</v>
       </c>
       <c r="V21" t="s">
+        <v>31</v>
+      </c>
+      <c r="W21" t="s">
         <v>31</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3498,7 +3563,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3564,6 +3629,9 @@
         <v>31</v>
       </c>
       <c r="V22" t="s">
+        <v>31</v>
+      </c>
+      <c r="W22" t="s">
         <v>31</v>
       </c>
       <c r="AU22" s="2"/>
@@ -3642,7 +3710,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3708,6 +3776,9 @@
         <v>32</v>
       </c>
       <c r="V23" t="s">
+        <v>31</v>
+      </c>
+      <c r="W23" t="s">
         <v>31</v>
       </c>
       <c r="AU23" s="2"/>
@@ -3786,7 +3857,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -3852,6 +3923,9 @@
         <v>31</v>
       </c>
       <c r="V24" t="s">
+        <v>31</v>
+      </c>
+      <c r="W24" t="s">
         <v>31</v>
       </c>
       <c r="AU24" s="2"/>
@@ -3930,7 +4004,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -3996,6 +4070,9 @@
         <v>31</v>
       </c>
       <c r="V25" t="s">
+        <v>31</v>
+      </c>
+      <c r="W25" t="s">
         <v>31</v>
       </c>
       <c r="AU25" s="2"/>
@@ -4074,7 +4151,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -4140,6 +4217,9 @@
         <v>31</v>
       </c>
       <c r="V26" t="s">
+        <v>31</v>
+      </c>
+      <c r="W26" t="s">
         <v>31</v>
       </c>
       <c r="AU26" s="2"/>
@@ -4218,7 +4298,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -4284,6 +4364,9 @@
         <v>31</v>
       </c>
       <c r="V27" t="s">
+        <v>31</v>
+      </c>
+      <c r="W27" t="s">
         <v>31</v>
       </c>
       <c r="AU27" s="2"/>
@@ -4362,7 +4445,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -4428,6 +4511,9 @@
         <v>31</v>
       </c>
       <c r="V28" t="s">
+        <v>31</v>
+      </c>
+      <c r="W28" t="s">
         <v>31</v>
       </c>
       <c r="AU28" s="2"/>
@@ -4506,7 +4592,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -4563,6 +4649,9 @@
         <v>31</v>
       </c>
       <c r="V29" t="s">
+        <v>31</v>
+      </c>
+      <c r="W29" t="s">
         <v>31</v>
       </c>
       <c r="AU29" s="2"/>
@@ -4641,7 +4730,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -4707,6 +4796,9 @@
         <v>31</v>
       </c>
       <c r="V30" t="s">
+        <v>31</v>
+      </c>
+      <c r="W30" t="s">
         <v>31</v>
       </c>
       <c r="AU30" s="2"/>
@@ -4785,7 +4877,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -4853,8 +4945,11 @@
       <c r="V31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="W31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>0</v>
@@ -4922,8 +5017,11 @@
       <c r="V32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4991,8 +5089,11 @@
       <c r="V33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -5058,6 +5159,9 @@
         <v>31</v>
       </c>
       <c r="V34" t="s">
+        <v>31</v>
+      </c>
+      <c r="W34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5071,7 +5175,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 V3:AZ3 BB3:BB21 D3:I30 K3:T30 U3:U34 BE4:BJ9 BK4:DG30 W10:BA21 BC10:BJ21 W22:BJ30 K31:K33 L31:T34 H33:I33 W4:AZ9 V4:V34">
+  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 W4:AZ9 BE4:BJ9 BK4:DG30 V4:V34 W10:BA21 BC10:BJ21 W22:BJ30 K31:K33 L31:T34 H33:I33 W31:W34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -5084,15 +5188,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5100,162 +5204,162 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>30</v>
       </c>
@@ -5272,203 +5376,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D669A50-A893-4036-9B47-1C675E5B7C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C24AAF70-B4F2-451E-9FE3-272EB499A915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -559,8 +559,8 @@
     <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="34" width="6" customWidth="1"/>
+    <col min="22" max="24" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="34" width="6" customWidth="1"/>
     <col min="35" max="50" width="7.7109375" customWidth="1"/>
     <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
     <col min="52" max="106" width="7.7109375" customWidth="1"/>
@@ -627,7 +627,9 @@
       <c r="W1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="1"/>
+      <c r="X1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
@@ -766,7 +768,9 @@
       <c r="W2" s="1">
         <v>46119</v>
       </c>
-      <c r="X2" s="1"/>
+      <c r="X2" s="1">
+        <v>46121</v>
+      </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
@@ -890,6 +894,9 @@
         <v>31</v>
       </c>
       <c r="W3" t="s">
+        <v>31</v>
+      </c>
+      <c r="X3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1039,6 +1046,9 @@
       <c r="W4" t="s">
         <v>31</v>
       </c>
+      <c r="X4" t="s">
+        <v>31</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1186,6 +1196,9 @@
       <c r="W5" t="s">
         <v>31</v>
       </c>
+      <c r="X5" t="s">
+        <v>31</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1333,6 +1346,9 @@
       <c r="W6" t="s">
         <v>31</v>
       </c>
+      <c r="X6" t="s">
+        <v>31</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1480,6 +1496,9 @@
       <c r="W7" t="s">
         <v>31</v>
       </c>
+      <c r="X7" t="s">
+        <v>31</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1627,6 +1646,9 @@
       <c r="W8" t="s">
         <v>31</v>
       </c>
+      <c r="X8" t="s">
+        <v>31</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1774,6 +1796,9 @@
       <c r="W9" t="s">
         <v>31</v>
       </c>
+      <c r="X9" t="s">
+        <v>31</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1921,6 +1946,9 @@
       <c r="W10" t="s">
         <v>31</v>
       </c>
+      <c r="X10" t="s">
+        <v>31</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2059,6 +2087,9 @@
       <c r="W11" t="s">
         <v>31</v>
       </c>
+      <c r="X11" t="s">
+        <v>31</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2206,6 +2237,9 @@
       <c r="W12" t="s">
         <v>31</v>
       </c>
+      <c r="X12" t="s">
+        <v>31</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2353,6 +2387,9 @@
       <c r="W13" t="s">
         <v>31</v>
       </c>
+      <c r="X13" t="s">
+        <v>31</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2500,6 +2537,9 @@
       <c r="W14" t="s">
         <v>31</v>
       </c>
+      <c r="X14" t="s">
+        <v>31</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2647,6 +2687,9 @@
       <c r="W15" t="s">
         <v>31</v>
       </c>
+      <c r="X15" t="s">
+        <v>31</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2794,6 +2837,9 @@
       <c r="W16" t="s">
         <v>32</v>
       </c>
+      <c r="X16" t="s">
+        <v>31</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2920,6 +2966,9 @@
       <c r="W17" t="s">
         <v>31</v>
       </c>
+      <c r="X17" t="s">
+        <v>31</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3067,6 +3116,9 @@
       <c r="W18" t="s">
         <v>31</v>
       </c>
+      <c r="X18" t="s">
+        <v>31</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3214,6 +3266,9 @@
       <c r="W19" t="s">
         <v>31</v>
       </c>
+      <c r="X19" t="s">
+        <v>31</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3340,6 +3395,9 @@
       <c r="W20" t="s">
         <v>31</v>
       </c>
+      <c r="X20" t="s">
+        <v>31</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3487,6 +3545,9 @@
       <c r="W21" t="s">
         <v>31</v>
       </c>
+      <c r="X21" t="s">
+        <v>31</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3634,6 +3695,9 @@
       <c r="W22" t="s">
         <v>31</v>
       </c>
+      <c r="X22" t="s">
+        <v>31</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3781,6 +3845,9 @@
       <c r="W23" t="s">
         <v>31</v>
       </c>
+      <c r="X23" t="s">
+        <v>31</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3928,6 +3995,9 @@
       <c r="W24" t="s">
         <v>31</v>
       </c>
+      <c r="X24" t="s">
+        <v>31</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4075,6 +4145,9 @@
       <c r="W25" t="s">
         <v>31</v>
       </c>
+      <c r="X25" t="s">
+        <v>31</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4222,6 +4295,9 @@
       <c r="W26" t="s">
         <v>31</v>
       </c>
+      <c r="X26" t="s">
+        <v>31</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4369,6 +4445,9 @@
       <c r="W27" t="s">
         <v>31</v>
       </c>
+      <c r="X27" t="s">
+        <v>31</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4516,6 +4595,9 @@
       <c r="W28" t="s">
         <v>31</v>
       </c>
+      <c r="X28" t="s">
+        <v>31</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4654,6 +4736,9 @@
       <c r="W29" t="s">
         <v>31</v>
       </c>
+      <c r="X29" t="s">
+        <v>31</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4801,6 +4886,9 @@
       <c r="W30" t="s">
         <v>31</v>
       </c>
+      <c r="X30" t="s">
+        <v>31</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4948,6 +5036,9 @@
       <c r="W31" t="s">
         <v>31</v>
       </c>
+      <c r="X31" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -5020,8 +5111,11 @@
       <c r="W32" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -5092,8 +5186,11 @@
       <c r="W33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -5162,6 +5259,9 @@
         <v>31</v>
       </c>
       <c r="W34" t="s">
+        <v>31</v>
+      </c>
+      <c r="X34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5175,7 +5275,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 W4:AZ9 BE4:BJ9 BK4:DG30 V4:V34 W10:BA21 BC10:BJ21 W22:BJ30 K31:K33 L31:T34 H33:I33 W31:W34">
+  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 W4:AZ9 BE4:BJ9 BK4:DG30 V4:V34 W10:BA21 BC10:BJ21 W22:BJ30 K31:K33 L31:T34 H33:I33 W31:X34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C24AAF70-B4F2-451E-9FE3-272EB499A915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD5087BF-2717-4F24-BF1B-20B4454859A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -559,8 +559,8 @@
     <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="34" width="6" customWidth="1"/>
+    <col min="22" max="25" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="34" width="6" customWidth="1"/>
     <col min="35" max="50" width="7.7109375" customWidth="1"/>
     <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
     <col min="52" max="106" width="7.7109375" customWidth="1"/>
@@ -630,7 +630,9 @@
       <c r="X1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="1"/>
+      <c r="Y1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
@@ -771,7 +773,9 @@
       <c r="X2" s="1">
         <v>46121</v>
       </c>
-      <c r="Y2" s="1"/>
+      <c r="Y2" s="1">
+        <v>46123</v>
+      </c>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
@@ -897,6 +901,9 @@
         <v>31</v>
       </c>
       <c r="X3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1049,6 +1056,9 @@
       <c r="X4" t="s">
         <v>31</v>
       </c>
+      <c r="Y4" t="s">
+        <v>31</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1199,6 +1209,9 @@
       <c r="X5" t="s">
         <v>31</v>
       </c>
+      <c r="Y5" t="s">
+        <v>31</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1349,6 +1362,9 @@
       <c r="X6" t="s">
         <v>31</v>
       </c>
+      <c r="Y6" t="s">
+        <v>31</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1499,6 +1515,9 @@
       <c r="X7" t="s">
         <v>31</v>
       </c>
+      <c r="Y7" t="s">
+        <v>31</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1649,6 +1668,9 @@
       <c r="X8" t="s">
         <v>31</v>
       </c>
+      <c r="Y8" t="s">
+        <v>31</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1799,6 +1821,9 @@
       <c r="X9" t="s">
         <v>31</v>
       </c>
+      <c r="Y9" t="s">
+        <v>31</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1949,6 +1974,9 @@
       <c r="X10" t="s">
         <v>31</v>
       </c>
+      <c r="Y10" t="s">
+        <v>32</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2090,6 +2118,9 @@
       <c r="X11" t="s">
         <v>31</v>
       </c>
+      <c r="Y11" t="s">
+        <v>31</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2240,6 +2271,9 @@
       <c r="X12" t="s">
         <v>31</v>
       </c>
+      <c r="Y12" t="s">
+        <v>31</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2390,6 +2424,9 @@
       <c r="X13" t="s">
         <v>31</v>
       </c>
+      <c r="Y13" t="s">
+        <v>31</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2540,6 +2577,9 @@
       <c r="X14" t="s">
         <v>31</v>
       </c>
+      <c r="Y14" t="s">
+        <v>31</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2690,6 +2730,9 @@
       <c r="X15" t="s">
         <v>31</v>
       </c>
+      <c r="Y15" t="s">
+        <v>31</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2840,6 +2883,9 @@
       <c r="X16" t="s">
         <v>31</v>
       </c>
+      <c r="Y16" t="s">
+        <v>31</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2969,6 +3015,9 @@
       <c r="X17" t="s">
         <v>31</v>
       </c>
+      <c r="Y17" t="s">
+        <v>31</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3119,6 +3168,9 @@
       <c r="X18" t="s">
         <v>31</v>
       </c>
+      <c r="Y18" t="s">
+        <v>31</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3269,6 +3321,9 @@
       <c r="X19" t="s">
         <v>31</v>
       </c>
+      <c r="Y19" t="s">
+        <v>31</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3398,6 +3453,9 @@
       <c r="X20" t="s">
         <v>31</v>
       </c>
+      <c r="Y20" t="s">
+        <v>31</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3548,6 +3606,9 @@
       <c r="X21" t="s">
         <v>31</v>
       </c>
+      <c r="Y21" t="s">
+        <v>31</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3698,6 +3759,9 @@
       <c r="X22" t="s">
         <v>31</v>
       </c>
+      <c r="Y22" t="s">
+        <v>31</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3848,6 +3912,9 @@
       <c r="X23" t="s">
         <v>31</v>
       </c>
+      <c r="Y23" t="s">
+        <v>31</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3998,6 +4065,9 @@
       <c r="X24" t="s">
         <v>31</v>
       </c>
+      <c r="Y24" t="s">
+        <v>31</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4148,6 +4218,9 @@
       <c r="X25" t="s">
         <v>31</v>
       </c>
+      <c r="Y25" t="s">
+        <v>31</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4298,6 +4371,9 @@
       <c r="X26" t="s">
         <v>31</v>
       </c>
+      <c r="Y26" t="s">
+        <v>31</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4448,6 +4524,9 @@
       <c r="X27" t="s">
         <v>31</v>
       </c>
+      <c r="Y27" t="s">
+        <v>31</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4598,6 +4677,9 @@
       <c r="X28" t="s">
         <v>31</v>
       </c>
+      <c r="Y28" t="s">
+        <v>31</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4739,6 +4821,9 @@
       <c r="X29" t="s">
         <v>31</v>
       </c>
+      <c r="Y29" t="s">
+        <v>31</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4889,6 +4974,9 @@
       <c r="X30" t="s">
         <v>31</v>
       </c>
+      <c r="Y30" t="s">
+        <v>31</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -5039,6 +5127,9 @@
       <c r="X31" t="s">
         <v>31</v>
       </c>
+      <c r="Y31" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -5114,8 +5205,11 @@
       <c r="X32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -5189,8 +5283,11 @@
       <c r="X33" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -5262,6 +5359,9 @@
         <v>31</v>
       </c>
       <c r="X34" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5275,7 +5375,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 W4:AZ9 BE4:BJ9 BK4:DG30 V4:V34 W10:BA21 BC10:BJ21 W22:BJ30 K31:K33 L31:T34 H33:I33 W31:X34">
+  <conditionalFormatting sqref="BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 BE4:BJ9 BK4:DG30 BC10:BJ21 K31:K33 L31:T34 H33:I33 V3:AZ3 Z22:BJ30 Z10:BA21 Z4:AZ9 V4:Y34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD5087BF-2717-4F24-BF1B-20B4454859A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CA668B-5D67-4C33-8CFC-33E5C80E3527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -548,25 +548,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="26" max="34" width="6" customWidth="1"/>
-    <col min="35" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="35" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -700,7 +700,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -774,7 +774,7 @@
         <v>46121</v>
       </c>
       <c r="Y2" s="1">
-        <v>46123</v>
+        <v>46126</v>
       </c>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
@@ -829,7 +829,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -982,7 +982,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -1135,7 +1135,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1288,7 +1288,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1441,7 +1441,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1594,7 +1594,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1747,7 +1747,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1900,7 +1900,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -2053,7 +2053,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -2197,7 +2197,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -2350,7 +2350,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2503,7 +2503,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2656,7 +2656,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2809,7 +2809,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2962,7 +2962,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -3094,7 +3094,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -3247,7 +3247,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -3400,7 +3400,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -3532,7 +3532,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3685,7 +3685,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3838,7 +3838,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3991,7 +3991,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -4144,7 +4144,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -4297,7 +4297,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -4450,7 +4450,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -4603,7 +4603,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -4756,7 +4756,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -4900,7 +4900,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -5053,7 +5053,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -5131,7 +5131,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>0</v>
@@ -5209,7 +5209,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -5287,7 +5287,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>0</v>
@@ -5375,7 +5375,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 BE4:BJ9 BK4:DG30 BC10:BJ21 K31:K33 L31:T34 H33:I33 V3:AZ3 Z22:BJ30 Z10:BA21 Z4:AZ9 V4:Y34">
+  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 Z4:AZ9 BE4:BJ9 BK4:DG30 V4:Y34 Z10:BA21 BC10:BJ21 Z22:BJ30 K31:K33 L31:T34 H33:I33">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -5388,15 +5388,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5404,162 +5404,162 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>30</v>
       </c>
@@ -5576,203 +5576,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CA668B-5D67-4C33-8CFC-33E5C80E3527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA723C1-AABC-425E-9F2A-0FFD61E36EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -550,7 +550,7 @@
   <dimension ref="A1:DS34"/>
   <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
@@ -832,7 +832,7 @@
     <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
-        <v>0</v>
+        <v>26132246</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -985,7 +985,7 @@
     <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
-        <v>0</v>
+        <v>26132200</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -1138,7 +1138,7 @@
     <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
-        <v>0</v>
+        <v>26132302</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -1291,7 +1291,7 @@
     <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
-        <v>0</v>
+        <v>26132277</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -1444,7 +1444,7 @@
     <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
-        <v>0</v>
+        <v>26132197</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -1597,7 +1597,7 @@
     <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
-        <v>0</v>
+        <v>26132286</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -1750,7 +1750,7 @@
     <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
-        <v>0</v>
+        <v>26132281</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -1903,7 +1903,7 @@
     <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
-        <v>0</v>
+        <v>26132340</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -2056,7 +2056,7 @@
     <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
-        <v>0</v>
+        <v>26133020</v>
       </c>
       <c r="B11" t="s">
         <v>35</v>
@@ -2200,7 +2200,7 @@
     <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
-        <v>0</v>
+        <v>26132271</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -2353,7 +2353,7 @@
     <row r="13" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
-        <v>0</v>
+        <v>26132244</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -2506,7 +2506,7 @@
     <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
-        <v>0</v>
+        <v>26132204</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -2659,7 +2659,7 @@
     <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
-        <v>0</v>
+        <v>26132220</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -2812,7 +2812,7 @@
     <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
-        <v>0</v>
+        <v>26132184</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
@@ -2965,7 +2965,7 @@
     <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
-        <v>0</v>
+        <v>26133029</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
@@ -3097,7 +3097,7 @@
     <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
-        <v>0</v>
+        <v>26132288</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
@@ -3250,7 +3250,7 @@
     <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
-        <v>0</v>
+        <v>26132330</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -3403,7 +3403,7 @@
     <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
-        <v>0</v>
+        <v>26133024</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
@@ -3535,7 +3535,7 @@
     <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
-        <v>0</v>
+        <v>26132248</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
@@ -3688,7 +3688,7 @@
     <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
-        <v>0</v>
+        <v>26132180</v>
       </c>
       <c r="B22" t="s">
         <v>19</v>
@@ -3841,7 +3841,7 @@
     <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
-        <v>0</v>
+        <v>26132269</v>
       </c>
       <c r="B23" t="s">
         <v>20</v>
@@ -3994,7 +3994,7 @@
     <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
-        <v>0</v>
+        <v>26132202</v>
       </c>
       <c r="B24" t="s">
         <v>21</v>
@@ -4147,7 +4147,7 @@
     <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
-        <v>0</v>
+        <v>26132265</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
@@ -4300,7 +4300,7 @@
     <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
-        <v>0</v>
+        <v>26132252</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
@@ -4453,7 +4453,7 @@
     <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
-        <v>0</v>
+        <v>26132242</v>
       </c>
       <c r="B27" t="s">
         <v>24</v>
@@ -4606,7 +4606,7 @@
     <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
-        <v>0</v>
+        <v>26132240</v>
       </c>
       <c r="B28" t="s">
         <v>25</v>
@@ -4759,7 +4759,7 @@
     <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
-        <v>0</v>
+        <v>26133022</v>
       </c>
       <c r="B29" t="s">
         <v>36</v>
@@ -4903,7 +4903,7 @@
     <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
-        <v>0</v>
+        <v>26132250</v>
       </c>
       <c r="B30" t="s">
         <v>26</v>
@@ -5056,7 +5056,7 @@
     <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
-        <v>0</v>
+        <v>26132238</v>
       </c>
       <c r="B31" t="s">
         <v>27</v>
@@ -5134,7 +5134,7 @@
     <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
-        <v>0</v>
+        <v>26132275</v>
       </c>
       <c r="B32" t="s">
         <v>28</v>
@@ -5212,7 +5212,7 @@
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
-        <v>0</v>
+        <v>26132256</v>
       </c>
       <c r="B33" t="s">
         <v>29</v>
@@ -5290,7 +5290,7 @@
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
-        <v>0</v>
+        <v>26132304</v>
       </c>
       <c r="B34" t="s">
         <v>30</v>
@@ -5390,10 +5390,7 @@
   <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -5405,167 +5402,263 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>26132246</v>
+      </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>26132200</v>
+      </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>26132302</v>
+      </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>26132277</v>
+      </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>26132197</v>
+      </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>26132286</v>
+      </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>26132281</v>
+      </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>26132340</v>
+      </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>26133020</v>
+      </c>
       <c r="B10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>26132271</v>
+      </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>26132244</v>
+      </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>26132204</v>
+      </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>26132220</v>
+      </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>26132184</v>
+      </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>26133029</v>
+      </c>
       <c r="B16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>26132288</v>
+      </c>
       <c r="B17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>26132330</v>
+      </c>
       <c r="B18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>26133024</v>
+      </c>
       <c r="B19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>26132248</v>
+      </c>
       <c r="B20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>26132180</v>
+      </c>
       <c r="B21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>26132269</v>
+      </c>
       <c r="B22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>26132202</v>
+      </c>
       <c r="B23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>26132265</v>
+      </c>
       <c r="B24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>26132252</v>
+      </c>
       <c r="B25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>26132242</v>
+      </c>
       <c r="B26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26132240</v>
+      </c>
       <c r="B27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>26133022</v>
+      </c>
       <c r="B28" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>26132250</v>
+      </c>
       <c r="B29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>26132238</v>
+      </c>
       <c r="B30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>26132275</v>
+      </c>
       <c r="B31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>26132256</v>
+      </c>
       <c r="B32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>26132304</v>
+      </c>
       <c r="B33" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B33">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B33">
     <sortCondition ref="B1:B33"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA723C1-AABC-425E-9F2A-0FFD61E36EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A5DCF1-6516-4FE3-A466-41E13F2D8354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -548,25 +548,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="34" width="6" customWidth="1"/>
-    <col min="35" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="34" width="6" customWidth="1"/>
+    <col min="35" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -633,7 +633,9 @@
       <c r="Y1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Z1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
@@ -700,7 +702,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -776,7 +778,9 @@
       <c r="Y2" s="1">
         <v>46126</v>
       </c>
-      <c r="Z2" s="1"/>
+      <c r="Z2" s="1">
+        <v>46128</v>
+      </c>
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
@@ -829,7 +833,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -904,6 +908,9 @@
         <v>31</v>
       </c>
       <c r="Y3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -982,7 +989,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1057,6 +1064,9 @@
         <v>31</v>
       </c>
       <c r="Y4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z4" t="s">
         <v>31</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1135,7 +1145,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1210,6 +1220,9 @@
         <v>31</v>
       </c>
       <c r="Y5" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z5" t="s">
         <v>31</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1288,7 +1301,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1363,6 +1376,9 @@
         <v>31</v>
       </c>
       <c r="Y6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z6" t="s">
         <v>31</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1441,7 +1457,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -1516,6 +1532,9 @@
         <v>31</v>
       </c>
       <c r="Y7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z7" t="s">
         <v>31</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1594,7 +1613,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -1669,6 +1688,9 @@
         <v>31</v>
       </c>
       <c r="Y8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z8" t="s">
         <v>31</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1747,7 +1769,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -1822,6 +1844,9 @@
         <v>31</v>
       </c>
       <c r="Y9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z9" t="s">
         <v>31</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1900,7 +1925,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -1975,6 +2000,9 @@
         <v>31</v>
       </c>
       <c r="Y10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z10" t="s">
         <v>32</v>
       </c>
       <c r="AU10" s="2"/>
@@ -2053,7 +2081,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2119,6 +2147,9 @@
         <v>31</v>
       </c>
       <c r="Y11" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z11" t="s">
         <v>31</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2197,7 +2228,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -2272,6 +2303,9 @@
         <v>31</v>
       </c>
       <c r="Y12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z12" t="s">
         <v>31</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2350,7 +2384,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -2425,6 +2459,9 @@
         <v>31</v>
       </c>
       <c r="Y13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z13" t="s">
         <v>31</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2503,7 +2540,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -2578,6 +2615,9 @@
         <v>31</v>
       </c>
       <c r="Y14" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z14" t="s">
         <v>31</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2656,7 +2696,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -2731,6 +2771,9 @@
         <v>31</v>
       </c>
       <c r="Y15" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z15" t="s">
         <v>31</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2809,7 +2852,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -2884,6 +2927,9 @@
         <v>31</v>
       </c>
       <c r="Y16" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z16" t="s">
         <v>31</v>
       </c>
       <c r="AU16" s="2"/>
@@ -2962,7 +3008,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -3016,6 +3062,9 @@
         <v>31</v>
       </c>
       <c r="Y17" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z17" t="s">
         <v>31</v>
       </c>
       <c r="AU17" s="2"/>
@@ -3094,7 +3143,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -3169,6 +3218,9 @@
         <v>31</v>
       </c>
       <c r="Y18" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z18" t="s">
         <v>31</v>
       </c>
       <c r="AU18" s="2"/>
@@ -3247,7 +3299,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -3322,6 +3374,9 @@
         <v>31</v>
       </c>
       <c r="Y19" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z19" t="s">
         <v>31</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3400,7 +3455,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -3454,6 +3509,9 @@
         <v>31</v>
       </c>
       <c r="Y20" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z20" t="s">
         <v>31</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3532,7 +3590,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -3607,6 +3665,9 @@
         <v>31</v>
       </c>
       <c r="Y21" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z21" t="s">
         <v>31</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3685,7 +3746,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -3760,6 +3821,9 @@
         <v>31</v>
       </c>
       <c r="Y22" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z22" t="s">
         <v>31</v>
       </c>
       <c r="AU22" s="2"/>
@@ -3838,7 +3902,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -3913,6 +3977,9 @@
         <v>31</v>
       </c>
       <c r="Y23" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z23" t="s">
         <v>31</v>
       </c>
       <c r="AU23" s="2"/>
@@ -3991,7 +4058,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -4066,6 +4133,9 @@
         <v>31</v>
       </c>
       <c r="Y24" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z24" t="s">
         <v>31</v>
       </c>
       <c r="AU24" s="2"/>
@@ -4144,7 +4214,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -4219,6 +4289,9 @@
         <v>31</v>
       </c>
       <c r="Y25" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z25" t="s">
         <v>31</v>
       </c>
       <c r="AU25" s="2"/>
@@ -4297,7 +4370,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -4372,6 +4445,9 @@
         <v>31</v>
       </c>
       <c r="Y26" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z26" t="s">
         <v>31</v>
       </c>
       <c r="AU26" s="2"/>
@@ -4450,7 +4526,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -4525,6 +4601,9 @@
         <v>31</v>
       </c>
       <c r="Y27" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z27" t="s">
         <v>31</v>
       </c>
       <c r="AU27" s="2"/>
@@ -4603,7 +4682,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -4678,6 +4757,9 @@
         <v>31</v>
       </c>
       <c r="Y28" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z28" t="s">
         <v>31</v>
       </c>
       <c r="AU28" s="2"/>
@@ -4756,7 +4838,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -4823,6 +4905,9 @@
       </c>
       <c r="Y29" t="s">
         <v>31</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>32</v>
       </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
@@ -4900,7 +4985,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -4975,6 +5060,9 @@
         <v>31</v>
       </c>
       <c r="Y30" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z30" t="s">
         <v>31</v>
       </c>
       <c r="AU30" s="2"/>
@@ -5053,7 +5141,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -5130,8 +5218,11 @@
       <c r="Y31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="Z31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -5208,8 +5299,11 @@
       <c r="Y32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -5286,8 +5380,11 @@
       <c r="Y33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -5362,6 +5459,9 @@
         <v>31</v>
       </c>
       <c r="Y34" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5375,7 +5475,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 Z4:AZ9 BE4:BJ9 BK4:DG30 V4:Y34 Z10:BA21 BC10:BJ21 Z22:BJ30 K31:K33 L31:T34 H33:I33">
+  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 Z4:AZ9 BE4:BJ9 BK4:DG30 V4:Y34 Z10:BA21 BC10:BJ21 Z22:BJ30 K31:K33 L31:T34 H33:I33 Z31:Z34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -5388,12 +5488,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5401,7 +5501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -5409,7 +5509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -5417,7 +5517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -5425,7 +5525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -5433,7 +5533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -5441,7 +5541,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -5449,7 +5549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -5457,7 +5557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -5465,7 +5565,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -5473,7 +5573,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -5481,7 +5581,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -5489,7 +5589,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -5497,7 +5597,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -5505,7 +5605,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -5513,7 +5613,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -5521,7 +5621,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -5529,7 +5629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -5537,7 +5637,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -5545,7 +5645,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -5553,7 +5653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -5561,7 +5661,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -5569,7 +5669,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -5577,7 +5677,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -5585,7 +5685,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -5593,7 +5693,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -5601,7 +5701,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -5609,7 +5709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -5617,7 +5717,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -5625,7 +5725,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -5633,7 +5733,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -5641,7 +5741,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -5649,7 +5749,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -5669,203 +5769,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A5DCF1-6516-4FE3-A466-41E13F2D8354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E66E4FB-C67F-4C44-B3F9-40E322AE0144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -559,8 +559,8 @@
     <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="34" width="6" customWidth="1"/>
+    <col min="22" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="34" width="6" customWidth="1"/>
     <col min="35" max="50" width="7.7109375" customWidth="1"/>
     <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
     <col min="52" max="106" width="7.7109375" customWidth="1"/>
@@ -636,7 +636,9 @@
       <c r="Z1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AA1" s="1"/>
+      <c r="AA1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
@@ -781,7 +783,9 @@
       <c r="Z2" s="1">
         <v>46128</v>
       </c>
-      <c r="AA2" s="1"/>
+      <c r="AA2" s="1">
+        <v>46135</v>
+      </c>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
@@ -911,6 +915,9 @@
         <v>31</v>
       </c>
       <c r="Z3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1069,6 +1076,9 @@
       <c r="Z4" t="s">
         <v>31</v>
       </c>
+      <c r="AA4" t="s">
+        <v>31</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1225,6 +1235,9 @@
       <c r="Z5" t="s">
         <v>31</v>
       </c>
+      <c r="AA5" t="s">
+        <v>31</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1381,6 +1394,9 @@
       <c r="Z6" t="s">
         <v>31</v>
       </c>
+      <c r="AA6" t="s">
+        <v>31</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1537,6 +1553,9 @@
       <c r="Z7" t="s">
         <v>31</v>
       </c>
+      <c r="AA7" t="s">
+        <v>31</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1693,6 +1712,9 @@
       <c r="Z8" t="s">
         <v>31</v>
       </c>
+      <c r="AA8" t="s">
+        <v>31</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1849,6 +1871,9 @@
       <c r="Z9" t="s">
         <v>31</v>
       </c>
+      <c r="AA9" t="s">
+        <v>31</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2005,6 +2030,9 @@
       <c r="Z10" t="s">
         <v>32</v>
       </c>
+      <c r="AA10" t="s">
+        <v>31</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2152,6 +2180,9 @@
       <c r="Z11" t="s">
         <v>31</v>
       </c>
+      <c r="AA11" t="s">
+        <v>31</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2308,6 +2339,9 @@
       <c r="Z12" t="s">
         <v>31</v>
       </c>
+      <c r="AA12" t="s">
+        <v>31</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2464,6 +2498,9 @@
       <c r="Z13" t="s">
         <v>31</v>
       </c>
+      <c r="AA13" t="s">
+        <v>31</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2620,6 +2657,9 @@
       <c r="Z14" t="s">
         <v>31</v>
       </c>
+      <c r="AA14" t="s">
+        <v>31</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2776,6 +2816,9 @@
       <c r="Z15" t="s">
         <v>31</v>
       </c>
+      <c r="AA15" t="s">
+        <v>31</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2932,6 +2975,9 @@
       <c r="Z16" t="s">
         <v>31</v>
       </c>
+      <c r="AA16" t="s">
+        <v>31</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3067,6 +3113,9 @@
       <c r="Z17" t="s">
         <v>31</v>
       </c>
+      <c r="AA17" t="s">
+        <v>31</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3223,6 +3272,9 @@
       <c r="Z18" t="s">
         <v>31</v>
       </c>
+      <c r="AA18" t="s">
+        <v>31</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -3379,6 +3431,9 @@
       <c r="Z19" t="s">
         <v>31</v>
       </c>
+      <c r="AA19" t="s">
+        <v>31</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -3514,6 +3569,9 @@
       <c r="Z20" t="s">
         <v>31</v>
       </c>
+      <c r="AA20" t="s">
+        <v>31</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3670,6 +3728,9 @@
       <c r="Z21" t="s">
         <v>31</v>
       </c>
+      <c r="AA21" t="s">
+        <v>31</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3826,6 +3887,9 @@
       <c r="Z22" t="s">
         <v>31</v>
       </c>
+      <c r="AA22" t="s">
+        <v>31</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3982,6 +4046,9 @@
       <c r="Z23" t="s">
         <v>31</v>
       </c>
+      <c r="AA23" t="s">
+        <v>31</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -4138,6 +4205,9 @@
       <c r="Z24" t="s">
         <v>31</v>
       </c>
+      <c r="AA24" t="s">
+        <v>31</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -4294,6 +4364,9 @@
       <c r="Z25" t="s">
         <v>31</v>
       </c>
+      <c r="AA25" t="s">
+        <v>31</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -4450,6 +4523,9 @@
       <c r="Z26" t="s">
         <v>31</v>
       </c>
+      <c r="AA26" t="s">
+        <v>31</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -4606,6 +4682,9 @@
       <c r="Z27" t="s">
         <v>31</v>
       </c>
+      <c r="AA27" t="s">
+        <v>31</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -4762,6 +4841,9 @@
       <c r="Z28" t="s">
         <v>31</v>
       </c>
+      <c r="AA28" t="s">
+        <v>31</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4909,6 +4991,9 @@
       <c r="Z29" t="s">
         <v>32</v>
       </c>
+      <c r="AA29" t="s">
+        <v>31</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -5065,6 +5150,9 @@
       <c r="Z30" t="s">
         <v>31</v>
       </c>
+      <c r="AA30" t="s">
+        <v>31</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -5221,6 +5309,9 @@
       <c r="Z31" t="s">
         <v>31</v>
       </c>
+      <c r="AA31" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -5302,8 +5393,11 @@
       <c r="Z32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -5383,8 +5477,11 @@
       <c r="Z33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -5462,6 +5559,9 @@
         <v>31</v>
       </c>
       <c r="Z34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5475,7 +5575,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 Z4:AZ9 BE4:BJ9 BK4:DG30 V4:Y34 Z10:BA21 BC10:BJ21 Z22:BJ30 K31:K33 L31:T34 H33:I33 Z31:Z34">
+  <conditionalFormatting sqref="BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 BE4:BJ9 BK4:DG30 BC10:BJ21 K31:K33 L31:T34 H33:I33 V3:AZ3 AB22:BJ30 AB10:BA21 AB4:AZ9 V4:AA34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E66E4FB-C67F-4C44-B3F9-40E322AE0144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202FE2EE-8DDC-4ED1-B569-5F9B00025AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -548,25 +548,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="34" width="6" customWidth="1"/>
-    <col min="35" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="34" width="6" customWidth="1"/>
+    <col min="35" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -639,7 +640,9 @@
       <c r="AA1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AB1" s="1"/>
+      <c r="AB1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
@@ -704,7 +707,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -786,13 +789,17 @@
       <c r="AA2" s="1">
         <v>46135</v>
       </c>
-      <c r="AB2" s="1"/>
+      <c r="AB2" s="1">
+        <v>46140</v>
+      </c>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
       <c r="AF2" s="1"/>
       <c r="AG2" s="1"/>
       <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -837,7 +844,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -918,6 +925,9 @@
         <v>31</v>
       </c>
       <c r="AA3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -996,7 +1006,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1077,6 +1087,9 @@
         <v>31</v>
       </c>
       <c r="AA4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB4" t="s">
         <v>31</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1155,7 +1168,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1236,6 +1249,9 @@
         <v>31</v>
       </c>
       <c r="AA5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB5" t="s">
         <v>31</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1314,7 +1330,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1395,6 +1411,9 @@
         <v>31</v>
       </c>
       <c r="AA6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB6" t="s">
         <v>31</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1473,7 +1492,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -1554,6 +1573,9 @@
         <v>31</v>
       </c>
       <c r="AA7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB7" t="s">
         <v>31</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1632,7 +1654,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -1713,6 +1735,9 @@
         <v>31</v>
       </c>
       <c r="AA8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB8" t="s">
         <v>31</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1791,7 +1816,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -1872,6 +1897,9 @@
         <v>31</v>
       </c>
       <c r="AA9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB9" t="s">
         <v>31</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1950,7 +1978,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2032,6 +2060,9 @@
       </c>
       <c r="AA10" t="s">
         <v>31</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>32</v>
       </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
@@ -2109,7 +2140,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2181,6 +2212,9 @@
         <v>31</v>
       </c>
       <c r="AA11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB11" t="s">
         <v>31</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2259,7 +2293,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -2340,6 +2374,9 @@
         <v>31</v>
       </c>
       <c r="AA12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB12" t="s">
         <v>31</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2418,7 +2455,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -2499,6 +2536,9 @@
         <v>31</v>
       </c>
       <c r="AA13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB13" t="s">
         <v>31</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2577,7 +2617,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -2658,6 +2698,9 @@
         <v>31</v>
       </c>
       <c r="AA14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB14" t="s">
         <v>31</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2736,7 +2779,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -2817,6 +2860,9 @@
         <v>31</v>
       </c>
       <c r="AA15" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB15" t="s">
         <v>31</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2895,7 +2941,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -2976,6 +3022,9 @@
         <v>31</v>
       </c>
       <c r="AA16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB16" t="s">
         <v>31</v>
       </c>
       <c r="AU16" s="2"/>
@@ -3054,7 +3103,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -3114,6 +3163,9 @@
         <v>31</v>
       </c>
       <c r="AA17" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB17" t="s">
         <v>31</v>
       </c>
       <c r="AU17" s="2"/>
@@ -3192,7 +3244,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -3273,6 +3325,9 @@
         <v>31</v>
       </c>
       <c r="AA18" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB18" t="s">
         <v>31</v>
       </c>
       <c r="AU18" s="2"/>
@@ -3351,7 +3406,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -3432,6 +3487,9 @@
         <v>31</v>
       </c>
       <c r="AA19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB19" t="s">
         <v>31</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3510,7 +3568,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -3570,6 +3628,9 @@
         <v>31</v>
       </c>
       <c r="AA20" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB20" t="s">
         <v>31</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3648,7 +3709,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -3729,6 +3790,9 @@
         <v>31</v>
       </c>
       <c r="AA21" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB21" t="s">
         <v>31</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3807,7 +3871,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -3888,6 +3952,9 @@
         <v>31</v>
       </c>
       <c r="AA22" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB22" t="s">
         <v>31</v>
       </c>
       <c r="AU22" s="2"/>
@@ -3966,7 +4033,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -4047,6 +4114,9 @@
         <v>31</v>
       </c>
       <c r="AA23" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB23" t="s">
         <v>31</v>
       </c>
       <c r="AU23" s="2"/>
@@ -4125,7 +4195,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -4206,6 +4276,9 @@
         <v>31</v>
       </c>
       <c r="AA24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB24" t="s">
         <v>31</v>
       </c>
       <c r="AU24" s="2"/>
@@ -4284,7 +4357,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -4365,6 +4438,9 @@
         <v>31</v>
       </c>
       <c r="AA25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB25" t="s">
         <v>31</v>
       </c>
       <c r="AU25" s="2"/>
@@ -4443,7 +4519,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -4524,6 +4600,9 @@
         <v>31</v>
       </c>
       <c r="AA26" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB26" t="s">
         <v>31</v>
       </c>
       <c r="AU26" s="2"/>
@@ -4602,7 +4681,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -4683,6 +4762,9 @@
         <v>31</v>
       </c>
       <c r="AA27" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB27" t="s">
         <v>31</v>
       </c>
       <c r="AU27" s="2"/>
@@ -4761,7 +4843,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -4842,6 +4924,9 @@
         <v>31</v>
       </c>
       <c r="AA28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB28" t="s">
         <v>31</v>
       </c>
       <c r="AU28" s="2"/>
@@ -4920,7 +5005,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -4992,6 +5077,9 @@
         <v>32</v>
       </c>
       <c r="AA29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB29" t="s">
         <v>31</v>
       </c>
       <c r="AU29" s="2"/>
@@ -5070,7 +5158,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -5151,6 +5239,9 @@
         <v>31</v>
       </c>
       <c r="AA30" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB30" t="s">
         <v>31</v>
       </c>
       <c r="AU30" s="2"/>
@@ -5229,7 +5320,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -5312,8 +5403,11 @@
       <c r="AA31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AB31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -5396,8 +5490,11 @@
       <c r="AA32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -5480,8 +5577,11 @@
       <c r="AA33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -5562,6 +5662,9 @@
         <v>31</v>
       </c>
       <c r="AA34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5575,7 +5678,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 BE4:BJ9 BK4:DG30 BC10:BJ21 K31:K33 L31:T34 H33:I33 V3:AZ3 AB22:BJ30 AB10:BA21 AB4:AZ9 V4:AA34">
+  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 AB4:AZ9 BE4:BJ9 BK4:DG30 V4:AA34 AB10:BA21 BC10:BJ21 AB22:BJ30 K31:K33 L31:T34 AB31:AB34 H33:I33">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -5588,12 +5691,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5601,7 +5704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -5609,7 +5712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -5617,7 +5720,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -5625,7 +5728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -5633,7 +5736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -5641,7 +5744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -5649,7 +5752,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -5657,7 +5760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -5665,7 +5768,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -5673,7 +5776,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -5681,7 +5784,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -5689,7 +5792,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -5697,7 +5800,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -5705,7 +5808,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -5713,7 +5816,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -5721,7 +5824,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -5729,7 +5832,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -5737,7 +5840,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -5745,7 +5848,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -5753,7 +5856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -5761,7 +5864,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -5769,7 +5872,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -5777,7 +5880,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -5785,7 +5888,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -5793,7 +5896,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -5801,7 +5904,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -5809,7 +5912,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -5817,7 +5920,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -5825,7 +5928,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -5833,7 +5936,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -5841,7 +5944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -5849,7 +5952,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -5869,203 +5972,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202FE2EE-8DDC-4ED1-B569-5F9B00025AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16314824-AAA0-4D56-8647-F1FD50712F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="43">
   <si>
     <t>Aluno</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>05/012</t>
+  </si>
+  <si>
+    <t>QUA</t>
   </si>
 </sst>
 </file>
@@ -548,26 +551,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="34" width="6" customWidth="1"/>
-    <col min="35" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="34" width="6" customWidth="1"/>
+    <col min="35" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -643,7 +647,9 @@
       <c r="AB1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AC1" s="1"/>
+      <c r="AC1" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
@@ -707,7 +713,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -792,7 +798,9 @@
       <c r="AB2" s="1">
         <v>46140</v>
       </c>
-      <c r="AC2" s="1"/>
+      <c r="AC2" s="1">
+        <v>46142</v>
+      </c>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
       <c r="AF2" s="1"/>
@@ -844,7 +852,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -928,6 +936,9 @@
         <v>31</v>
       </c>
       <c r="AB3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1006,7 +1017,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1090,6 +1101,9 @@
         <v>31</v>
       </c>
       <c r="AB4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC4" t="s">
         <v>31</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1168,7 +1182,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1252,6 +1266,9 @@
         <v>31</v>
       </c>
       <c r="AB5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC5" t="s">
         <v>31</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1330,7 +1347,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1414,6 +1431,9 @@
         <v>31</v>
       </c>
       <c r="AB6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC6" t="s">
         <v>31</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1492,7 +1512,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -1576,6 +1596,9 @@
         <v>31</v>
       </c>
       <c r="AB7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC7" t="s">
         <v>31</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1654,7 +1677,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -1738,6 +1761,9 @@
         <v>31</v>
       </c>
       <c r="AB8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC8" t="s">
         <v>31</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1816,7 +1842,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -1900,6 +1926,9 @@
         <v>31</v>
       </c>
       <c r="AB9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC9" t="s">
         <v>31</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1978,7 +2007,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2063,6 +2092,9 @@
       </c>
       <c r="AB10" t="s">
         <v>32</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>31</v>
       </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
@@ -2140,7 +2172,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2215,6 +2247,9 @@
         <v>31</v>
       </c>
       <c r="AB11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC11" t="s">
         <v>31</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2293,7 +2328,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -2377,6 +2412,9 @@
         <v>31</v>
       </c>
       <c r="AB12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC12" t="s">
         <v>31</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2455,7 +2493,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -2539,6 +2577,9 @@
         <v>31</v>
       </c>
       <c r="AB13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC13" t="s">
         <v>31</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2617,7 +2658,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -2701,6 +2742,9 @@
         <v>31</v>
       </c>
       <c r="AB14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC14" t="s">
         <v>31</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2779,7 +2823,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -2863,6 +2907,9 @@
         <v>31</v>
       </c>
       <c r="AB15" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC15" t="s">
         <v>31</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2941,7 +2988,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -3025,6 +3072,9 @@
         <v>31</v>
       </c>
       <c r="AB16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC16" t="s">
         <v>31</v>
       </c>
       <c r="AU16" s="2"/>
@@ -3103,7 +3153,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -3166,6 +3216,9 @@
         <v>31</v>
       </c>
       <c r="AB17" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC17" t="s">
         <v>31</v>
       </c>
       <c r="AU17" s="2"/>
@@ -3244,7 +3297,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -3328,6 +3381,9 @@
         <v>31</v>
       </c>
       <c r="AB18" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC18" t="s">
         <v>31</v>
       </c>
       <c r="AU18" s="2"/>
@@ -3406,7 +3462,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -3490,6 +3546,9 @@
         <v>31</v>
       </c>
       <c r="AB19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC19" t="s">
         <v>31</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3568,7 +3627,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -3631,6 +3690,9 @@
         <v>31</v>
       </c>
       <c r="AB20" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC20" t="s">
         <v>31</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3709,7 +3771,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -3793,6 +3855,9 @@
         <v>31</v>
       </c>
       <c r="AB21" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC21" t="s">
         <v>31</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3871,7 +3936,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -3955,6 +4020,9 @@
         <v>31</v>
       </c>
       <c r="AB22" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC22" t="s">
         <v>31</v>
       </c>
       <c r="AU22" s="2"/>
@@ -4033,7 +4101,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -4117,6 +4185,9 @@
         <v>31</v>
       </c>
       <c r="AB23" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC23" t="s">
         <v>31</v>
       </c>
       <c r="AU23" s="2"/>
@@ -4195,7 +4266,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -4279,6 +4350,9 @@
         <v>31</v>
       </c>
       <c r="AB24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC24" t="s">
         <v>31</v>
       </c>
       <c r="AU24" s="2"/>
@@ -4357,7 +4431,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -4441,6 +4515,9 @@
         <v>31</v>
       </c>
       <c r="AB25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC25" t="s">
         <v>31</v>
       </c>
       <c r="AU25" s="2"/>
@@ -4519,7 +4596,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -4604,6 +4681,9 @@
       </c>
       <c r="AB26" t="s">
         <v>31</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>32</v>
       </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
@@ -4681,7 +4761,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -4765,6 +4845,9 @@
         <v>31</v>
       </c>
       <c r="AB27" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC27" t="s">
         <v>31</v>
       </c>
       <c r="AU27" s="2"/>
@@ -4843,7 +4926,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -4927,6 +5010,9 @@
         <v>31</v>
       </c>
       <c r="AB28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC28" t="s">
         <v>31</v>
       </c>
       <c r="AU28" s="2"/>
@@ -5005,7 +5091,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -5080,6 +5166,9 @@
         <v>31</v>
       </c>
       <c r="AB29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC29" t="s">
         <v>31</v>
       </c>
       <c r="AU29" s="2"/>
@@ -5158,7 +5247,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -5242,6 +5331,9 @@
         <v>31</v>
       </c>
       <c r="AB30" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC30" t="s">
         <v>31</v>
       </c>
       <c r="AU30" s="2"/>
@@ -5320,7 +5412,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -5406,8 +5498,11 @@
       <c r="AB31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="AC31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -5493,8 +5588,11 @@
       <c r="AB32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -5580,8 +5678,11 @@
       <c r="AB33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -5665,6 +5766,9 @@
         <v>31</v>
       </c>
       <c r="AB34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5678,7 +5782,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 AB4:AZ9 BE4:BJ9 BK4:DG30 V4:AA34 AB10:BA21 BC10:BJ21 AB22:BJ30 K31:K33 L31:T34 AB31:AB34 H33:I33">
+  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 AB4:AZ9 BE4:BJ9 BK4:DG30 V4:AA34 AB10:BA21 BC10:BJ21 AB22:BJ30 K31:K33 L31:T34 H33:I33 AB31:AC34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -5691,12 +5795,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5704,7 +5808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -5712,7 +5816,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -5720,7 +5824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -5728,7 +5832,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -5736,7 +5840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -5744,7 +5848,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -5752,7 +5856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -5760,7 +5864,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -5768,7 +5872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -5776,7 +5880,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -5784,7 +5888,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -5792,7 +5896,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -5800,7 +5904,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -5808,7 +5912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -5816,7 +5920,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -5824,7 +5928,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -5832,7 +5936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -5840,7 +5944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -5848,7 +5952,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -5856,7 +5960,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -5864,7 +5968,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -5872,7 +5976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -5880,7 +5984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -5888,7 +5992,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -5896,7 +6000,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -5904,7 +6008,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -5912,7 +6016,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -5920,7 +6024,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -5928,7 +6032,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -5936,7 +6040,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -5944,7 +6048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -5952,7 +6056,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -5972,203 +6076,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16314824-AAA0-4D56-8647-F1FD50712F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F06AD5AD-432C-43F5-99C3-908D4A04B026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2094,7 +2094,7 @@
         <v>32</v>
       </c>
       <c r="AC10" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
@@ -5782,7 +5782,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 AB4:AZ9 BE4:BJ9 BK4:DG30 V4:AA34 AB10:BA21 BC10:BJ21 AB22:BJ30 K31:K33 L31:T34 H33:I33 AB31:AC34">
+  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 AB4:AZ9 BE4:BJ9 BK4:DG30 V4:AA34 AB10:BA21 BC10:BJ21 AB22:BJ30 K31:K33 L31:T34 AB31:AC34 H33:I33">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F06AD5AD-432C-43F5-99C3-908D4A04B026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C474A0-C7BD-4C25-B5F4-583D072B0BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="43">
   <si>
     <t>Aluno</t>
   </si>
@@ -551,27 +551,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="34" width="6" customWidth="1"/>
-    <col min="35" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
+    <col min="22" max="29" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="6" customWidth="1"/>
+    <col min="35" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -650,8 +650,12 @@
       <c r="AC1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
+      <c r="AD1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
       <c r="AH1" s="1"/>
@@ -713,7 +717,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -801,8 +805,12 @@
       <c r="AC2" s="1">
         <v>46142</v>
       </c>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
+      <c r="AD2" s="1">
+        <v>46147</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>46149</v>
+      </c>
       <c r="AF2" s="1"/>
       <c r="AG2" s="1"/>
       <c r="AH2" s="1"/>
@@ -852,7 +860,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -939,6 +947,9 @@
         <v>31</v>
       </c>
       <c r="AC3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1017,7 +1028,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1104,6 +1115,9 @@
         <v>31</v>
       </c>
       <c r="AC4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD4" t="s">
         <v>31</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1182,7 +1196,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1269,6 +1283,9 @@
         <v>31</v>
       </c>
       <c r="AC5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD5" t="s">
         <v>31</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1347,7 +1364,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1434,6 +1451,9 @@
         <v>31</v>
       </c>
       <c r="AC6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD6" t="s">
         <v>31</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1512,7 +1532,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -1599,6 +1619,9 @@
         <v>31</v>
       </c>
       <c r="AC7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD7" t="s">
         <v>31</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1677,7 +1700,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -1764,6 +1787,9 @@
         <v>31</v>
       </c>
       <c r="AC8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD8" t="s">
         <v>31</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1842,7 +1868,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -1929,6 +1955,9 @@
         <v>31</v>
       </c>
       <c r="AC9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD9" t="s">
         <v>31</v>
       </c>
       <c r="AU9" s="2"/>
@@ -2007,7 +2036,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2095,6 +2124,9 @@
       </c>
       <c r="AC10" t="s">
         <v>39</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>31</v>
       </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
@@ -2172,7 +2204,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2250,6 +2282,9 @@
         <v>31</v>
       </c>
       <c r="AC11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD11" t="s">
         <v>31</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2328,7 +2363,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -2415,6 +2450,9 @@
         <v>31</v>
       </c>
       <c r="AC12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD12" t="s">
         <v>31</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2493,7 +2531,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -2580,6 +2618,9 @@
         <v>31</v>
       </c>
       <c r="AC13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD13" t="s">
         <v>31</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2658,7 +2699,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -2745,6 +2786,9 @@
         <v>31</v>
       </c>
       <c r="AC14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD14" t="s">
         <v>31</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2823,7 +2867,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -2910,6 +2954,9 @@
         <v>31</v>
       </c>
       <c r="AC15" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD15" t="s">
         <v>31</v>
       </c>
       <c r="AU15" s="2"/>
@@ -2988,7 +3035,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -3075,6 +3122,9 @@
         <v>31</v>
       </c>
       <c r="AC16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD16" t="s">
         <v>31</v>
       </c>
       <c r="AU16" s="2"/>
@@ -3153,7 +3203,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -3219,6 +3269,9 @@
         <v>31</v>
       </c>
       <c r="AC17" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD17" t="s">
         <v>31</v>
       </c>
       <c r="AU17" s="2"/>
@@ -3297,7 +3350,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -3384,6 +3437,9 @@
         <v>31</v>
       </c>
       <c r="AC18" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD18" t="s">
         <v>31</v>
       </c>
       <c r="AU18" s="2"/>
@@ -3462,7 +3518,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -3549,6 +3605,9 @@
         <v>31</v>
       </c>
       <c r="AC19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD19" t="s">
         <v>31</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3627,7 +3686,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -3693,6 +3752,9 @@
         <v>31</v>
       </c>
       <c r="AC20" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD20" t="s">
         <v>31</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3771,7 +3833,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -3858,6 +3920,9 @@
         <v>31</v>
       </c>
       <c r="AC21" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD21" t="s">
         <v>31</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3936,7 +4001,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -4023,6 +4088,9 @@
         <v>31</v>
       </c>
       <c r="AC22" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD22" t="s">
         <v>31</v>
       </c>
       <c r="AU22" s="2"/>
@@ -4101,7 +4169,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -4188,6 +4256,9 @@
         <v>31</v>
       </c>
       <c r="AC23" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD23" t="s">
         <v>31</v>
       </c>
       <c r="AU23" s="2"/>
@@ -4266,7 +4337,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -4353,6 +4424,9 @@
         <v>31</v>
       </c>
       <c r="AC24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD24" t="s">
         <v>31</v>
       </c>
       <c r="AU24" s="2"/>
@@ -4431,7 +4505,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -4518,6 +4592,9 @@
         <v>31</v>
       </c>
       <c r="AC25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD25" t="s">
         <v>31</v>
       </c>
       <c r="AU25" s="2"/>
@@ -4596,7 +4673,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -4684,6 +4761,9 @@
       </c>
       <c r="AC26" t="s">
         <v>32</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>31</v>
       </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
@@ -4761,7 +4841,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -4848,6 +4928,9 @@
         <v>31</v>
       </c>
       <c r="AC27" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD27" t="s">
         <v>31</v>
       </c>
       <c r="AU27" s="2"/>
@@ -4926,7 +5009,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -5013,6 +5096,9 @@
         <v>31</v>
       </c>
       <c r="AC28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD28" t="s">
         <v>31</v>
       </c>
       <c r="AU28" s="2"/>
@@ -5091,7 +5177,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -5169,6 +5255,9 @@
         <v>31</v>
       </c>
       <c r="AC29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD29" t="s">
         <v>31</v>
       </c>
       <c r="AU29" s="2"/>
@@ -5247,7 +5336,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -5334,6 +5423,9 @@
         <v>31</v>
       </c>
       <c r="AC30" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD30" t="s">
         <v>31</v>
       </c>
       <c r="AU30" s="2"/>
@@ -5412,7 +5504,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -5501,8 +5593,11 @@
       <c r="AC31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AD31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -5591,8 +5686,11 @@
       <c r="AC32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -5681,8 +5779,11 @@
       <c r="AC33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -5769,6 +5870,9 @@
         <v>31</v>
       </c>
       <c r="AC34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5782,7 +5886,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 AB4:AZ9 BE4:BJ9 BK4:DG30 V4:AA34 AB10:BA21 BC10:BJ21 AB22:BJ30 K31:K33 L31:T34 AB31:AC34 H33:I33">
+  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 AB4:AZ9 BE4:BJ9 BK4:DG30 V4:AA34 AB10:BA21 BC10:BJ21 AB22:BJ30 K31:K33 L31:T34 H33:I33 AB31:AD34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -5795,12 +5899,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5808,7 +5912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -5816,7 +5920,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -5824,7 +5928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -5832,7 +5936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -5840,7 +5944,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -5848,7 +5952,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -5856,7 +5960,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -5864,7 +5968,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -5872,7 +5976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -5880,7 +5984,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -5888,7 +5992,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -5896,7 +6000,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -5904,7 +6008,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -5912,7 +6016,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -5920,7 +6024,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -5928,7 +6032,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -5936,7 +6040,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -5944,7 +6048,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -5952,7 +6056,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -5960,7 +6064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -5968,7 +6072,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -5976,7 +6080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -5984,7 +6088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -5992,7 +6096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -6000,7 +6104,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -6008,7 +6112,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -6016,7 +6120,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -6024,7 +6128,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -6032,7 +6136,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -6040,7 +6144,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -6048,7 +6152,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -6056,7 +6160,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -6076,203 +6180,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C474A0-C7BD-4C25-B5F4-583D072B0BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BB1A55-D9DD-4ED6-9869-12F6BFAC83E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="43">
   <si>
     <t>Aluno</t>
   </si>
@@ -551,27 +551,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="29" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="29" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="32" max="34" width="6" customWidth="1"/>
-    <col min="35" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="35" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -717,7 +716,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -860,7 +859,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -950,6 +949,9 @@
         <v>31</v>
       </c>
       <c r="AD3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1028,7 +1030,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1118,6 +1120,9 @@
         <v>31</v>
       </c>
       <c r="AD4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE4" t="s">
         <v>31</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1196,7 +1201,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1286,6 +1291,9 @@
         <v>31</v>
       </c>
       <c r="AD5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE5" t="s">
         <v>31</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1364,7 +1372,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1454,6 +1462,9 @@
         <v>31</v>
       </c>
       <c r="AD6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE6" t="s">
         <v>31</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1532,7 +1543,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -1622,6 +1633,9 @@
         <v>31</v>
       </c>
       <c r="AD7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE7" t="s">
         <v>31</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1700,7 +1714,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -1790,6 +1804,9 @@
         <v>31</v>
       </c>
       <c r="AD8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE8" t="s">
         <v>31</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1868,7 +1885,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -1958,6 +1975,9 @@
         <v>31</v>
       </c>
       <c r="AD9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE9" t="s">
         <v>31</v>
       </c>
       <c r="AU9" s="2"/>
@@ -2036,7 +2056,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2126,6 +2146,9 @@
         <v>39</v>
       </c>
       <c r="AD10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE10" t="s">
         <v>31</v>
       </c>
       <c r="AU10" s="2"/>
@@ -2204,7 +2227,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2285,6 +2308,9 @@
         <v>31</v>
       </c>
       <c r="AD11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE11" t="s">
         <v>31</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2363,7 +2389,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -2453,6 +2479,9 @@
         <v>31</v>
       </c>
       <c r="AD12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE12" t="s">
         <v>31</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2531,7 +2560,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -2621,6 +2650,9 @@
         <v>31</v>
       </c>
       <c r="AD13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE13" t="s">
         <v>31</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2699,7 +2731,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -2789,6 +2821,9 @@
         <v>31</v>
       </c>
       <c r="AD14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE14" t="s">
         <v>31</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2867,7 +2902,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -2957,6 +2992,9 @@
         <v>31</v>
       </c>
       <c r="AD15" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE15" t="s">
         <v>31</v>
       </c>
       <c r="AU15" s="2"/>
@@ -3035,7 +3073,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -3125,6 +3163,9 @@
         <v>31</v>
       </c>
       <c r="AD16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE16" t="s">
         <v>31</v>
       </c>
       <c r="AU16" s="2"/>
@@ -3203,7 +3244,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -3272,6 +3313,9 @@
         <v>31</v>
       </c>
       <c r="AD17" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE17" t="s">
         <v>31</v>
       </c>
       <c r="AU17" s="2"/>
@@ -3350,7 +3394,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -3440,6 +3484,9 @@
         <v>31</v>
       </c>
       <c r="AD18" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE18" t="s">
         <v>31</v>
       </c>
       <c r="AU18" s="2"/>
@@ -3518,7 +3565,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -3608,6 +3655,9 @@
         <v>31</v>
       </c>
       <c r="AD19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE19" t="s">
         <v>31</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3686,7 +3736,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -3755,6 +3805,9 @@
         <v>31</v>
       </c>
       <c r="AD20" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE20" t="s">
         <v>31</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3833,7 +3886,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -3923,6 +3976,9 @@
         <v>31</v>
       </c>
       <c r="AD21" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE21" t="s">
         <v>31</v>
       </c>
       <c r="AU21" s="2"/>
@@ -4001,7 +4057,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -4091,6 +4147,9 @@
         <v>31</v>
       </c>
       <c r="AD22" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE22" t="s">
         <v>31</v>
       </c>
       <c r="AU22" s="2"/>
@@ -4169,7 +4228,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -4259,6 +4318,9 @@
         <v>31</v>
       </c>
       <c r="AD23" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE23" t="s">
         <v>31</v>
       </c>
       <c r="AU23" s="2"/>
@@ -4337,7 +4399,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -4427,6 +4489,9 @@
         <v>31</v>
       </c>
       <c r="AD24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE24" t="s">
         <v>31</v>
       </c>
       <c r="AU24" s="2"/>
@@ -4505,7 +4570,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -4595,6 +4660,9 @@
         <v>31</v>
       </c>
       <c r="AD25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE25" t="s">
         <v>31</v>
       </c>
       <c r="AU25" s="2"/>
@@ -4673,7 +4741,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -4763,6 +4831,9 @@
         <v>32</v>
       </c>
       <c r="AD26" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE26" t="s">
         <v>31</v>
       </c>
       <c r="AU26" s="2"/>
@@ -4841,7 +4912,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -4931,6 +5002,9 @@
         <v>31</v>
       </c>
       <c r="AD27" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE27" t="s">
         <v>31</v>
       </c>
       <c r="AU27" s="2"/>
@@ -5009,7 +5083,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -5099,6 +5173,9 @@
         <v>31</v>
       </c>
       <c r="AD28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE28" t="s">
         <v>31</v>
       </c>
       <c r="AU28" s="2"/>
@@ -5177,7 +5254,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -5258,6 +5335,9 @@
         <v>31</v>
       </c>
       <c r="AD29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE29" t="s">
         <v>31</v>
       </c>
       <c r="AU29" s="2"/>
@@ -5336,7 +5416,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -5426,6 +5506,9 @@
         <v>31</v>
       </c>
       <c r="AD30" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE30" t="s">
         <v>31</v>
       </c>
       <c r="AU30" s="2"/>
@@ -5504,7 +5587,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -5596,8 +5679,11 @@
       <c r="AD31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="AE31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -5689,8 +5775,11 @@
       <c r="AD32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -5782,8 +5871,11 @@
       <c r="AD33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -5873,6 +5965,9 @@
         <v>31</v>
       </c>
       <c r="AD34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5886,7 +5981,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 AB4:AZ9 BE4:BJ9 BK4:DG30 V4:AA34 AB10:BA21 BC10:BJ21 AB22:BJ30 K31:K33 L31:T34 H33:I33 AB31:AD34">
+  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 AB4:AZ9 BE4:BJ9 BK4:DG30 V4:AA34 AB10:BA21 BC10:BJ21 AB22:BJ30 K31:K33 L31:T34 H33:I33 AB31:AE34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -5899,12 +5994,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5912,7 +6007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -5920,7 +6015,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -5928,7 +6023,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -5936,7 +6031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -5944,7 +6039,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -5952,7 +6047,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -5960,7 +6055,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -5968,7 +6063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -5976,7 +6071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -5984,7 +6079,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -5992,7 +6087,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -6000,7 +6095,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -6008,7 +6103,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -6016,7 +6111,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -6024,7 +6119,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -6032,7 +6127,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -6040,7 +6135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -6048,7 +6143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -6056,7 +6151,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -6064,7 +6159,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -6072,7 +6167,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -6080,7 +6175,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -6088,7 +6183,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -6096,7 +6191,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -6104,7 +6199,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -6112,7 +6207,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -6120,7 +6215,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -6128,7 +6223,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -6136,7 +6231,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -6144,7 +6239,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -6152,7 +6247,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -6160,7 +6255,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -6180,203 +6275,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BB1A55-D9DD-4ED6-9869-12F6BFAC83E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95783F54-915C-4A8E-B12D-9CB07DACFAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="43">
   <si>
     <t>Aluno</t>
   </si>
@@ -551,26 +551,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="29" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="6" customWidth="1"/>
-    <col min="35" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="22" max="29" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="33" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6" customWidth="1"/>
+    <col min="35" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -655,8 +656,12 @@
       <c r="AE1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
+      <c r="AF1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
@@ -716,7 +721,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -810,8 +815,12 @@
       <c r="AE2" s="1">
         <v>46149</v>
       </c>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
+      <c r="AF2" s="1">
+        <v>46154</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>46156</v>
+      </c>
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -859,7 +868,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -952,6 +961,12 @@
         <v>31</v>
       </c>
       <c r="AE3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG3" t="s">
         <v>31</v>
       </c>
       <c r="AU3" s="2"/>
@@ -1030,7 +1045,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1123,6 +1138,12 @@
         <v>31</v>
       </c>
       <c r="AE4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG4" t="s">
         <v>31</v>
       </c>
       <c r="AU4" s="2"/>
@@ -1201,7 +1222,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1294,6 +1315,12 @@
         <v>31</v>
       </c>
       <c r="AE5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG5" t="s">
         <v>31</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1372,7 +1399,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1465,6 +1492,12 @@
         <v>31</v>
       </c>
       <c r="AE6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG6" t="s">
         <v>31</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1543,7 +1576,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -1636,6 +1669,12 @@
         <v>31</v>
       </c>
       <c r="AE7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG7" t="s">
         <v>31</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1714,7 +1753,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -1807,6 +1846,12 @@
         <v>31</v>
       </c>
       <c r="AE8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG8" t="s">
         <v>31</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1885,7 +1930,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -1978,6 +2023,12 @@
         <v>31</v>
       </c>
       <c r="AE9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG9" t="s">
         <v>31</v>
       </c>
       <c r="AU9" s="2"/>
@@ -2056,7 +2107,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2149,6 +2200,12 @@
         <v>31</v>
       </c>
       <c r="AE10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG10" t="s">
         <v>31</v>
       </c>
       <c r="AU10" s="2"/>
@@ -2227,7 +2284,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2311,6 +2368,12 @@
         <v>31</v>
       </c>
       <c r="AE11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG11" t="s">
         <v>31</v>
       </c>
       <c r="AU11" s="2"/>
@@ -2389,7 +2452,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -2482,6 +2545,12 @@
         <v>31</v>
       </c>
       <c r="AE12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG12" t="s">
         <v>31</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2560,7 +2629,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -2653,6 +2722,12 @@
         <v>31</v>
       </c>
       <c r="AE13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG13" t="s">
         <v>31</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2731,7 +2806,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -2824,6 +2899,12 @@
         <v>31</v>
       </c>
       <c r="AE14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG14" t="s">
         <v>31</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2902,7 +2983,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -2995,6 +3076,12 @@
         <v>31</v>
       </c>
       <c r="AE15" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG15" t="s">
         <v>31</v>
       </c>
       <c r="AU15" s="2"/>
@@ -3073,7 +3160,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -3166,6 +3253,12 @@
         <v>31</v>
       </c>
       <c r="AE16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG16" t="s">
         <v>31</v>
       </c>
       <c r="AU16" s="2"/>
@@ -3244,7 +3337,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -3316,6 +3409,12 @@
         <v>31</v>
       </c>
       <c r="AE17" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG17" t="s">
         <v>31</v>
       </c>
       <c r="AU17" s="2"/>
@@ -3394,7 +3493,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -3487,6 +3586,12 @@
         <v>31</v>
       </c>
       <c r="AE18" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG18" t="s">
         <v>31</v>
       </c>
       <c r="AU18" s="2"/>
@@ -3565,7 +3670,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -3658,6 +3763,12 @@
         <v>31</v>
       </c>
       <c r="AE19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG19" t="s">
         <v>31</v>
       </c>
       <c r="AU19" s="2"/>
@@ -3736,7 +3847,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -3808,6 +3919,12 @@
         <v>31</v>
       </c>
       <c r="AE20" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG20" t="s">
         <v>31</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3886,7 +4003,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -3979,6 +4096,12 @@
         <v>31</v>
       </c>
       <c r="AE21" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG21" t="s">
         <v>31</v>
       </c>
       <c r="AU21" s="2"/>
@@ -4057,7 +4180,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -4150,6 +4273,12 @@
         <v>31</v>
       </c>
       <c r="AE22" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG22" t="s">
         <v>31</v>
       </c>
       <c r="AU22" s="2"/>
@@ -4228,7 +4357,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -4321,6 +4450,12 @@
         <v>31</v>
       </c>
       <c r="AE23" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG23" t="s">
         <v>31</v>
       </c>
       <c r="AU23" s="2"/>
@@ -4399,7 +4534,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -4492,6 +4627,12 @@
         <v>31</v>
       </c>
       <c r="AE24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG24" t="s">
         <v>31</v>
       </c>
       <c r="AU24" s="2"/>
@@ -4570,7 +4711,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -4663,6 +4804,12 @@
         <v>31</v>
       </c>
       <c r="AE25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG25" t="s">
         <v>31</v>
       </c>
       <c r="AU25" s="2"/>
@@ -4741,7 +4888,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -4834,6 +4981,12 @@
         <v>31</v>
       </c>
       <c r="AE26" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG26" t="s">
         <v>31</v>
       </c>
       <c r="AU26" s="2"/>
@@ -4912,7 +5065,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -5005,6 +5158,12 @@
         <v>31</v>
       </c>
       <c r="AE27" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG27" t="s">
         <v>31</v>
       </c>
       <c r="AU27" s="2"/>
@@ -5083,7 +5242,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -5176,6 +5335,12 @@
         <v>31</v>
       </c>
       <c r="AE28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG28" t="s">
         <v>31</v>
       </c>
       <c r="AU28" s="2"/>
@@ -5254,7 +5419,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -5338,6 +5503,12 @@
         <v>31</v>
       </c>
       <c r="AE29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG29" t="s">
         <v>31</v>
       </c>
       <c r="AU29" s="2"/>
@@ -5416,7 +5587,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -5509,6 +5680,12 @@
         <v>31</v>
       </c>
       <c r="AE30" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG30" t="s">
         <v>31</v>
       </c>
       <c r="AU30" s="2"/>
@@ -5587,7 +5764,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -5682,8 +5859,14 @@
       <c r="AE31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+      <c r="AF31" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -5778,8 +5961,14 @@
       <c r="AE32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF32" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -5874,8 +6063,14 @@
       <c r="AE33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF33" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -5968,6 +6163,12 @@
         <v>31</v>
       </c>
       <c r="AE34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5981,7 +6182,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V3:AZ3 BE3:DG3 BB3:BB21 D3:I30 K3:T30 U3:U34 AB4:AZ9 BE4:BJ9 BK4:DG30 V4:AA34 AB10:BA21 BC10:BJ21 AB22:BJ30 K31:K33 L31:T34 H33:I33 AB31:AE34">
+  <conditionalFormatting sqref="BE3:DG3 BB3:BB21 D3:I30 K3:T30 BE4:BJ9 BK4:DG30 BC10:BJ21 K31:K33 L31:T34 H33:I33 AH22:BJ30 AH10:BA21 AH3:AZ9 U3:AG34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -5994,12 +6195,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6007,7 +6208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -6015,7 +6216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -6023,7 +6224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -6031,7 +6232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -6039,7 +6240,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -6047,7 +6248,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -6055,7 +6256,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -6063,7 +6264,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -6071,7 +6272,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -6079,7 +6280,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -6087,7 +6288,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -6095,7 +6296,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -6103,7 +6304,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -6111,7 +6312,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -6119,7 +6320,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -6127,7 +6328,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -6135,7 +6336,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -6143,7 +6344,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -6151,7 +6352,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -6159,7 +6360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -6167,7 +6368,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -6175,7 +6376,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -6183,7 +6384,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -6191,7 +6392,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -6199,7 +6400,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -6207,7 +6408,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -6215,7 +6416,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -6223,7 +6424,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -6231,7 +6432,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -6239,7 +6440,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -6247,7 +6448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -6255,7 +6456,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -6275,203 +6476,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95783F54-915C-4A8E-B12D-9CB07DACFAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B430E6-385D-435A-A029-6099B7B6F24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="44">
   <si>
     <t>Aluno</t>
   </si>
@@ -166,7 +166,10 @@
     <t>05/012</t>
   </si>
   <si>
-    <t>QUA</t>
+    <t>feriado</t>
+  </si>
+  <si>
+    <t>P/5</t>
   </si>
 </sst>
 </file>
@@ -550,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DS34"/>
+  <dimension ref="A1:DT34"/>
   <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -563,15 +566,17 @@
     <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="29" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="33" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6" customWidth="1"/>
-    <col min="35" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="22" max="26" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="34" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="6" customWidth="1"/>
+    <col min="36" max="51" width="7.6640625" customWidth="1"/>
+    <col min="52" max="52" width="7.6640625" style="5" customWidth="1"/>
+    <col min="53" max="107" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -642,27 +647,29 @@
         <v>34</v>
       </c>
       <c r="AA1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AC1" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="AD1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AE1" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="AF1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AG1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH1" s="1"/>
+      <c r="AH1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
@@ -675,11 +682,11 @@
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
-      <c r="AU1" s="3"/>
+      <c r="AU1" s="1"/>
       <c r="AV1" s="3"/>
       <c r="AW1" s="3"/>
-      <c r="AX1" s="1"/>
-      <c r="AY1" s="4"/>
+      <c r="AX1" s="3"/>
+      <c r="AY1" s="1"/>
       <c r="AZ1" s="4"/>
       <c r="BA1" s="4"/>
       <c r="BB1" s="4"/>
@@ -714,14 +721,15 @@
       <c r="CE1" s="4"/>
       <c r="CF1" s="4"/>
       <c r="CG1" s="4"/>
-      <c r="CH1" s="1"/>
-      <c r="CI1" s="4"/>
+      <c r="CH1" s="4"/>
+      <c r="CI1" s="1"/>
       <c r="CJ1" s="4"/>
       <c r="CK1" s="4"/>
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
-    </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="CN1" s="4"/>
+    </row>
+    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -801,33 +809,35 @@
         <v>46128</v>
       </c>
       <c r="AA2" s="1">
+        <v>46133</v>
+      </c>
+      <c r="AB2" s="1">
         <v>46135</v>
       </c>
-      <c r="AB2" s="1">
+      <c r="AC2" s="1">
         <v>46140</v>
       </c>
-      <c r="AC2" s="1">
+      <c r="AD2" s="1">
         <v>46142</v>
       </c>
-      <c r="AD2" s="1">
+      <c r="AE2" s="1">
         <v>46147</v>
       </c>
-      <c r="AE2" s="1">
+      <c r="AF2" s="1">
         <v>46149</v>
       </c>
-      <c r="AF2" s="1">
+      <c r="AG2" s="1">
         <v>46154</v>
       </c>
-      <c r="AG2" s="1">
+      <c r="AH2" s="1">
         <v>46156</v>
       </c>
-      <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
-      <c r="AU2" s="2"/>
+      <c r="AK2" s="1"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
-      <c r="AZ2" s="5"/>
+      <c r="AX2" s="2"/>
       <c r="BA2" s="5"/>
       <c r="BB2" s="5"/>
       <c r="BC2" s="5"/>
@@ -867,8 +877,9 @@
       <c r="CK2" s="5"/>
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
-    </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="CN2" s="5"/>
+    </row>
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -949,7 +960,7 @@
         <v>31</v>
       </c>
       <c r="AA3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB3" t="s">
         <v>31</v>
@@ -969,10 +980,12 @@
       <c r="AG3" t="s">
         <v>31</v>
       </c>
-      <c r="AU3" s="2"/>
+      <c r="AH3" t="s">
+        <v>31</v>
+      </c>
       <c r="AV3" s="2"/>
       <c r="AW3" s="2"/>
-      <c r="AZ3" s="5"/>
+      <c r="AX3" s="2"/>
       <c r="BA3" s="5"/>
       <c r="BB3" s="5"/>
       <c r="BC3" s="5"/>
@@ -1044,8 +1057,9 @@
       <c r="DQ3" s="5"/>
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
-    </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT3" s="5"/>
+    </row>
+    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1126,7 +1140,7 @@
         <v>31</v>
       </c>
       <c r="AA4" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB4" t="s">
         <v>31</v>
@@ -1146,10 +1160,12 @@
       <c r="AG4" t="s">
         <v>31</v>
       </c>
-      <c r="AU4" s="2"/>
+      <c r="AH4" t="s">
+        <v>31</v>
+      </c>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
-      <c r="AZ4" s="5"/>
+      <c r="AX4" s="2"/>
       <c r="BA4" s="5"/>
       <c r="BB4" s="5"/>
       <c r="BC4" s="5"/>
@@ -1221,8 +1237,9 @@
       <c r="DQ4" s="5"/>
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
-    </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT4" s="5"/>
+    </row>
+    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1303,7 +1320,7 @@
         <v>31</v>
       </c>
       <c r="AA5" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB5" t="s">
         <v>31</v>
@@ -1323,10 +1340,12 @@
       <c r="AG5" t="s">
         <v>31</v>
       </c>
-      <c r="AU5" s="2"/>
+      <c r="AH5" t="s">
+        <v>31</v>
+      </c>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
-      <c r="AZ5" s="5"/>
+      <c r="AX5" s="2"/>
       <c r="BA5" s="5"/>
       <c r="BB5" s="5"/>
       <c r="BC5" s="5"/>
@@ -1398,8 +1417,9 @@
       <c r="DQ5" s="5"/>
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
-    </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT5" s="5"/>
+    </row>
+    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1480,7 +1500,7 @@
         <v>31</v>
       </c>
       <c r="AA6" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB6" t="s">
         <v>31</v>
@@ -1500,10 +1520,12 @@
       <c r="AG6" t="s">
         <v>31</v>
       </c>
-      <c r="AU6" s="2"/>
+      <c r="AH6" t="s">
+        <v>31</v>
+      </c>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
-      <c r="AZ6" s="5"/>
+      <c r="AX6" s="2"/>
       <c r="BA6" s="5"/>
       <c r="BB6" s="5"/>
       <c r="BC6" s="5"/>
@@ -1538,8 +1560,8 @@
       <c r="CF6" s="5"/>
       <c r="CG6" s="5"/>
       <c r="CH6" s="5"/>
-      <c r="CI6" s="7"/>
-      <c r="CJ6" s="5"/>
+      <c r="CI6" s="5"/>
+      <c r="CJ6" s="7"/>
       <c r="CK6" s="5"/>
       <c r="CL6" s="5"/>
       <c r="CM6" s="5"/>
@@ -1575,8 +1597,9 @@
       <c r="DQ6" s="5"/>
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
-    </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT6" s="5"/>
+    </row>
+    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -1657,7 +1680,7 @@
         <v>31</v>
       </c>
       <c r="AA7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB7" t="s">
         <v>31</v>
@@ -1677,10 +1700,12 @@
       <c r="AG7" t="s">
         <v>31</v>
       </c>
-      <c r="AU7" s="2"/>
+      <c r="AH7" t="s">
+        <v>31</v>
+      </c>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
-      <c r="AZ7" s="5"/>
+      <c r="AX7" s="2"/>
       <c r="BA7" s="5"/>
       <c r="BB7" s="5"/>
       <c r="BC7" s="5"/>
@@ -1715,8 +1740,8 @@
       <c r="CF7" s="5"/>
       <c r="CG7" s="5"/>
       <c r="CH7" s="5"/>
-      <c r="CI7" s="6"/>
-      <c r="CJ7" s="5"/>
+      <c r="CI7" s="5"/>
+      <c r="CJ7" s="6"/>
       <c r="CK7" s="5"/>
       <c r="CL7" s="5"/>
       <c r="CM7" s="5"/>
@@ -1752,8 +1777,9 @@
       <c r="DQ7" s="5"/>
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
-    </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT7" s="5"/>
+    </row>
+    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -1834,7 +1860,7 @@
         <v>31</v>
       </c>
       <c r="AA8" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB8" t="s">
         <v>31</v>
@@ -1854,10 +1880,12 @@
       <c r="AG8" t="s">
         <v>31</v>
       </c>
-      <c r="AU8" s="2"/>
+      <c r="AH8" t="s">
+        <v>31</v>
+      </c>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
-      <c r="AZ8" s="5"/>
+      <c r="AX8" s="2"/>
       <c r="BA8" s="5"/>
       <c r="BB8" s="5"/>
       <c r="BC8" s="5"/>
@@ -1929,8 +1957,9 @@
       <c r="DQ8" s="5"/>
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
-    </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT8" s="5"/>
+    </row>
+    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2011,7 +2040,7 @@
         <v>31</v>
       </c>
       <c r="AA9" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB9" t="s">
         <v>31</v>
@@ -2031,10 +2060,12 @@
       <c r="AG9" t="s">
         <v>31</v>
       </c>
-      <c r="AU9" s="2"/>
+      <c r="AH9" t="s">
+        <v>31</v>
+      </c>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
-      <c r="AZ9" s="5"/>
+      <c r="AX9" s="2"/>
       <c r="BA9" s="5"/>
       <c r="BB9" s="5"/>
       <c r="BC9" s="5"/>
@@ -2106,8 +2137,9 @@
       <c r="DQ9" s="5"/>
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
-    </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT9" s="5"/>
+    </row>
+    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2188,16 +2220,16 @@
         <v>32</v>
       </c>
       <c r="AA10" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC10" t="s">
         <v>32</v>
       </c>
-      <c r="AC10" t="s">
-        <v>39</v>
-      </c>
       <c r="AD10" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="AE10" t="s">
         <v>31</v>
@@ -2208,10 +2240,12 @@
       <c r="AG10" t="s">
         <v>31</v>
       </c>
-      <c r="AU10" s="2"/>
+      <c r="AH10" t="s">
+        <v>31</v>
+      </c>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
-      <c r="AZ10" s="5"/>
+      <c r="AX10" s="2"/>
       <c r="BA10" s="5"/>
       <c r="BB10" s="5"/>
       <c r="BC10" s="5"/>
@@ -2283,8 +2317,9 @@
       <c r="DQ10" s="5"/>
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
-    </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT10" s="5"/>
+    </row>
+    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2356,7 +2391,7 @@
         <v>31</v>
       </c>
       <c r="AA11" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB11" t="s">
         <v>31</v>
@@ -2376,10 +2411,12 @@
       <c r="AG11" t="s">
         <v>31</v>
       </c>
-      <c r="AU11" s="2"/>
+      <c r="AH11" t="s">
+        <v>31</v>
+      </c>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
-      <c r="AZ11" s="5"/>
+      <c r="AX11" s="2"/>
       <c r="BA11" s="5"/>
       <c r="BB11" s="5"/>
       <c r="BC11" s="5"/>
@@ -2451,8 +2488,9 @@
       <c r="DQ11" s="5"/>
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
-    </row>
-    <row r="12" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="DT11" s="5"/>
+    </row>
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -2533,7 +2571,7 @@
         <v>31</v>
       </c>
       <c r="AA12" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB12" t="s">
         <v>31</v>
@@ -2553,10 +2591,12 @@
       <c r="AG12" t="s">
         <v>31</v>
       </c>
-      <c r="AU12" s="2"/>
+      <c r="AH12" t="s">
+        <v>31</v>
+      </c>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
-      <c r="AZ12" s="5"/>
+      <c r="AX12" s="2"/>
       <c r="BA12" s="5"/>
       <c r="BB12" s="5"/>
       <c r="BC12" s="5"/>
@@ -2628,8 +2668,9 @@
       <c r="DQ12" s="5"/>
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
-    </row>
-    <row r="13" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT12" s="5"/>
+    </row>
+    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -2710,7 +2751,7 @@
         <v>31</v>
       </c>
       <c r="AA13" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB13" t="s">
         <v>31</v>
@@ -2730,10 +2771,12 @@
       <c r="AG13" t="s">
         <v>31</v>
       </c>
-      <c r="AU13" s="2"/>
+      <c r="AH13" t="s">
+        <v>31</v>
+      </c>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
-      <c r="AZ13" s="5"/>
+      <c r="AX13" s="2"/>
       <c r="BA13" s="5"/>
       <c r="BB13" s="5"/>
       <c r="BC13" s="5"/>
@@ -2805,8 +2848,9 @@
       <c r="DQ13" s="5"/>
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
-    </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT13" s="5"/>
+    </row>
+    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -2887,7 +2931,7 @@
         <v>31</v>
       </c>
       <c r="AA14" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB14" t="s">
         <v>31</v>
@@ -2907,10 +2951,12 @@
       <c r="AG14" t="s">
         <v>31</v>
       </c>
-      <c r="AU14" s="2"/>
+      <c r="AH14" t="s">
+        <v>31</v>
+      </c>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
-      <c r="AZ14" s="5"/>
+      <c r="AX14" s="2"/>
       <c r="BA14" s="5"/>
       <c r="BB14" s="5"/>
       <c r="BC14" s="5"/>
@@ -2982,8 +3028,9 @@
       <c r="DQ14" s="5"/>
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
-    </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT14" s="5"/>
+    </row>
+    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -3064,7 +3111,7 @@
         <v>31</v>
       </c>
       <c r="AA15" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB15" t="s">
         <v>31</v>
@@ -3084,10 +3131,12 @@
       <c r="AG15" t="s">
         <v>31</v>
       </c>
-      <c r="AU15" s="2"/>
+      <c r="AH15" t="s">
+        <v>31</v>
+      </c>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
-      <c r="AZ15" s="5"/>
+      <c r="AX15" s="2"/>
       <c r="BA15" s="5"/>
       <c r="BB15" s="5"/>
       <c r="BC15" s="5"/>
@@ -3159,8 +3208,9 @@
       <c r="DQ15" s="5"/>
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
-    </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT15" s="5"/>
+    </row>
+    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -3241,7 +3291,7 @@
         <v>31</v>
       </c>
       <c r="AA16" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB16" t="s">
         <v>31</v>
@@ -3261,10 +3311,12 @@
       <c r="AG16" t="s">
         <v>31</v>
       </c>
-      <c r="AU16" s="2"/>
+      <c r="AH16" t="s">
+        <v>31</v>
+      </c>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
-      <c r="AZ16" s="5"/>
+      <c r="AX16" s="2"/>
       <c r="BA16" s="5"/>
       <c r="BB16" s="5"/>
       <c r="BC16" s="5"/>
@@ -3336,8 +3388,9 @@
       <c r="DQ16" s="5"/>
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
-    </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT16" s="5"/>
+    </row>
+    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -3397,7 +3450,7 @@
         <v>31</v>
       </c>
       <c r="AA17" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB17" t="s">
         <v>31</v>
@@ -3417,10 +3470,12 @@
       <c r="AG17" t="s">
         <v>31</v>
       </c>
-      <c r="AU17" s="2"/>
+      <c r="AH17" t="s">
+        <v>31</v>
+      </c>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
-      <c r="AZ17" s="5"/>
+      <c r="AX17" s="2"/>
       <c r="BA17" s="5"/>
       <c r="BB17" s="5"/>
       <c r="BC17" s="5"/>
@@ -3492,8 +3547,9 @@
       <c r="DQ17" s="5"/>
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
-    </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT17" s="5"/>
+    </row>
+    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -3574,7 +3630,7 @@
         <v>31</v>
       </c>
       <c r="AA18" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB18" t="s">
         <v>31</v>
@@ -3594,10 +3650,12 @@
       <c r="AG18" t="s">
         <v>31</v>
       </c>
-      <c r="AU18" s="2"/>
+      <c r="AH18" t="s">
+        <v>31</v>
+      </c>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
-      <c r="AZ18" s="5"/>
+      <c r="AX18" s="2"/>
       <c r="BA18" s="5"/>
       <c r="BB18" s="5"/>
       <c r="BC18" s="5"/>
@@ -3669,8 +3727,9 @@
       <c r="DQ18" s="5"/>
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
-    </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT18" s="5"/>
+    </row>
+    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -3751,7 +3810,7 @@
         <v>31</v>
       </c>
       <c r="AA19" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB19" t="s">
         <v>31</v>
@@ -3771,10 +3830,12 @@
       <c r="AG19" t="s">
         <v>31</v>
       </c>
-      <c r="AU19" s="2"/>
+      <c r="AH19" t="s">
+        <v>31</v>
+      </c>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
-      <c r="AZ19" s="5"/>
+      <c r="AX19" s="2"/>
       <c r="BA19" s="5"/>
       <c r="BB19" s="5"/>
       <c r="BC19" s="5"/>
@@ -3846,8 +3907,9 @@
       <c r="DQ19" s="5"/>
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
-    </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT19" s="5"/>
+    </row>
+    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -3907,7 +3969,7 @@
         <v>31</v>
       </c>
       <c r="AA20" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB20" t="s">
         <v>31</v>
@@ -3927,10 +3989,12 @@
       <c r="AG20" t="s">
         <v>31</v>
       </c>
-      <c r="AU20" s="2"/>
+      <c r="AH20" t="s">
+        <v>31</v>
+      </c>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
-      <c r="AZ20" s="5"/>
+      <c r="AX20" s="2"/>
       <c r="BA20" s="5"/>
       <c r="BB20" s="5"/>
       <c r="BC20" s="5"/>
@@ -4002,8 +4066,9 @@
       <c r="DQ20" s="5"/>
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
-    </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT20" s="5"/>
+    </row>
+    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -4084,7 +4149,7 @@
         <v>31</v>
       </c>
       <c r="AA21" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB21" t="s">
         <v>31</v>
@@ -4104,10 +4169,12 @@
       <c r="AG21" t="s">
         <v>31</v>
       </c>
-      <c r="AU21" s="2"/>
+      <c r="AH21" t="s">
+        <v>31</v>
+      </c>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
-      <c r="AZ21" s="5"/>
+      <c r="AX21" s="2"/>
       <c r="BA21" s="5"/>
       <c r="BB21" s="5"/>
       <c r="BC21" s="5"/>
@@ -4179,8 +4246,9 @@
       <c r="DQ21" s="5"/>
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
-    </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT21" s="5"/>
+    </row>
+    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -4261,7 +4329,7 @@
         <v>31</v>
       </c>
       <c r="AA22" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB22" t="s">
         <v>31</v>
@@ -4281,10 +4349,12 @@
       <c r="AG22" t="s">
         <v>31</v>
       </c>
-      <c r="AU22" s="2"/>
+      <c r="AH22" t="s">
+        <v>31</v>
+      </c>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
-      <c r="AZ22" s="5"/>
+      <c r="AX22" s="2"/>
       <c r="BA22" s="5"/>
       <c r="BB22" s="5"/>
       <c r="BC22" s="5"/>
@@ -4356,8 +4426,9 @@
       <c r="DQ22" s="5"/>
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
-    </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT22" s="5"/>
+    </row>
+    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -4438,7 +4509,7 @@
         <v>31</v>
       </c>
       <c r="AA23" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB23" t="s">
         <v>31</v>
@@ -4458,10 +4529,12 @@
       <c r="AG23" t="s">
         <v>31</v>
       </c>
-      <c r="AU23" s="2"/>
+      <c r="AH23" t="s">
+        <v>31</v>
+      </c>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
-      <c r="AZ23" s="5"/>
+      <c r="AX23" s="2"/>
       <c r="BA23" s="5"/>
       <c r="BB23" s="5"/>
       <c r="BC23" s="5"/>
@@ -4533,8 +4606,9 @@
       <c r="DQ23" s="5"/>
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
-    </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT23" s="5"/>
+    </row>
+    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -4615,7 +4689,7 @@
         <v>31</v>
       </c>
       <c r="AA24" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB24" t="s">
         <v>31</v>
@@ -4635,10 +4709,12 @@
       <c r="AG24" t="s">
         <v>31</v>
       </c>
-      <c r="AU24" s="2"/>
+      <c r="AH24" t="s">
+        <v>31</v>
+      </c>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
-      <c r="AZ24" s="5"/>
+      <c r="AX24" s="2"/>
       <c r="BA24" s="5"/>
       <c r="BB24" s="5"/>
       <c r="BC24" s="5"/>
@@ -4710,8 +4786,9 @@
       <c r="DQ24" s="5"/>
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
-    </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT24" s="5"/>
+    </row>
+    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -4792,7 +4869,7 @@
         <v>31</v>
       </c>
       <c r="AA25" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB25" t="s">
         <v>31</v>
@@ -4812,10 +4889,12 @@
       <c r="AG25" t="s">
         <v>31</v>
       </c>
-      <c r="AU25" s="2"/>
+      <c r="AH25" t="s">
+        <v>31</v>
+      </c>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
-      <c r="AZ25" s="5"/>
+      <c r="AX25" s="2"/>
       <c r="BA25" s="5"/>
       <c r="BB25" s="5"/>
       <c r="BC25" s="5"/>
@@ -4887,8 +4966,9 @@
       <c r="DQ25" s="5"/>
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
-    </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT25" s="5"/>
+    </row>
+    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -4969,17 +5049,17 @@
         <v>31</v>
       </c>
       <c r="AA26" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB26" t="s">
         <v>31</v>
       </c>
       <c r="AC26" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD26" t="s">
         <v>32</v>
       </c>
-      <c r="AD26" t="s">
-        <v>31</v>
-      </c>
       <c r="AE26" t="s">
         <v>31</v>
       </c>
@@ -4989,10 +5069,12 @@
       <c r="AG26" t="s">
         <v>31</v>
       </c>
-      <c r="AU26" s="2"/>
+      <c r="AH26" t="s">
+        <v>31</v>
+      </c>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
-      <c r="AZ26" s="5"/>
+      <c r="AX26" s="2"/>
       <c r="BA26" s="5"/>
       <c r="BB26" s="5"/>
       <c r="BC26" s="5"/>
@@ -5064,8 +5146,9 @@
       <c r="DQ26" s="5"/>
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
-    </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT26" s="5"/>
+    </row>
+    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -5146,7 +5229,7 @@
         <v>31</v>
       </c>
       <c r="AA27" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB27" t="s">
         <v>31</v>
@@ -5166,10 +5249,12 @@
       <c r="AG27" t="s">
         <v>31</v>
       </c>
-      <c r="AU27" s="2"/>
+      <c r="AH27" t="s">
+        <v>31</v>
+      </c>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
-      <c r="AZ27" s="5"/>
+      <c r="AX27" s="2"/>
       <c r="BA27" s="5"/>
       <c r="BB27" s="5"/>
       <c r="BC27" s="5"/>
@@ -5241,8 +5326,9 @@
       <c r="DQ27" s="5"/>
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
-    </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT27" s="5"/>
+    </row>
+    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -5323,7 +5409,7 @@
         <v>31</v>
       </c>
       <c r="AA28" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB28" t="s">
         <v>31</v>
@@ -5343,10 +5429,12 @@
       <c r="AG28" t="s">
         <v>31</v>
       </c>
-      <c r="AU28" s="2"/>
+      <c r="AH28" t="s">
+        <v>31</v>
+      </c>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
-      <c r="AZ28" s="5"/>
+      <c r="AX28" s="2"/>
       <c r="BA28" s="5"/>
       <c r="BB28" s="5"/>
       <c r="BC28" s="5"/>
@@ -5418,8 +5506,9 @@
       <c r="DQ28" s="5"/>
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
-    </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT28" s="5"/>
+    </row>
+    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -5491,7 +5580,7 @@
         <v>32</v>
       </c>
       <c r="AA29" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB29" t="s">
         <v>31</v>
@@ -5511,10 +5600,12 @@
       <c r="AG29" t="s">
         <v>31</v>
       </c>
-      <c r="AU29" s="2"/>
+      <c r="AH29" t="s">
+        <v>31</v>
+      </c>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
-      <c r="AZ29" s="5"/>
+      <c r="AX29" s="2"/>
       <c r="BA29" s="5"/>
       <c r="BB29" s="5"/>
       <c r="BC29" s="5"/>
@@ -5586,8 +5677,9 @@
       <c r="DQ29" s="5"/>
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
-    </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT29" s="5"/>
+    </row>
+    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -5668,7 +5760,7 @@
         <v>31</v>
       </c>
       <c r="AA30" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB30" t="s">
         <v>31</v>
@@ -5688,10 +5780,12 @@
       <c r="AG30" t="s">
         <v>31</v>
       </c>
-      <c r="AU30" s="2"/>
+      <c r="AH30" t="s">
+        <v>31</v>
+      </c>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
-      <c r="AZ30" s="5"/>
+      <c r="AX30" s="2"/>
       <c r="BA30" s="5"/>
       <c r="BB30" s="5"/>
       <c r="BC30" s="5"/>
@@ -5763,8 +5857,9 @@
       <c r="DQ30" s="5"/>
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
-    </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="DT30" s="5"/>
+    </row>
+    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -5845,7 +5940,7 @@
         <v>31</v>
       </c>
       <c r="AA31" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB31" t="s">
         <v>31</v>
@@ -5865,8 +5960,11 @@
       <c r="AG31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+      <c r="AH31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -5947,7 +6045,7 @@
         <v>31</v>
       </c>
       <c r="AA32" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB32" t="s">
         <v>31</v>
@@ -5967,8 +6065,11 @@
       <c r="AG32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AH32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -6049,7 +6150,7 @@
         <v>31</v>
       </c>
       <c r="AA33" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB33" t="s">
         <v>31</v>
@@ -6069,8 +6170,11 @@
       <c r="AG33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AH33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -6151,7 +6255,7 @@
         <v>31</v>
       </c>
       <c r="AA34" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="AB34" t="s">
         <v>31</v>
@@ -6169,6 +6273,9 @@
         <v>31</v>
       </c>
       <c r="AG34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6182,7 +6289,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3:DG3 BB3:BB21 D3:I30 K3:T30 BE4:BJ9 BK4:DG30 BC10:BJ21 K31:K33 L31:T34 H33:I33 AH22:BJ30 AH10:BA21 AH3:AZ9 U3:AG34">
+  <conditionalFormatting sqref="BF3:DH3 AI3:BA9 BC3:BC21 D3:I30 K3:T30 U3:AH34 BF4:BK9 BL4:DH30 AI10:BB21 BD10:BK21 AI22:BK30 K31:K33 L31:T34 H33:I33">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B430E6-385D-435A-A029-6099B7B6F24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22963490-B70E-4E4C-BBA7-6A888EA4EC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="44">
   <si>
     <t>Aluno</t>
   </si>
@@ -554,29 +554,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="34" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="6" customWidth="1"/>
-    <col min="36" max="51" width="7.6640625" customWidth="1"/>
-    <col min="52" max="52" width="7.6640625" style="5" customWidth="1"/>
-    <col min="53" max="107" width="7.6640625" customWidth="1"/>
+    <col min="22" max="26" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="35" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="51" width="7.7109375" customWidth="1"/>
+    <col min="52" max="52" width="7.7109375" style="5" customWidth="1"/>
+    <col min="53" max="107" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -670,8 +668,12 @@
       <c r="AH1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
+      <c r="AI1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
@@ -729,7 +731,7 @@
       <c r="CM1" s="4"/>
       <c r="CN1" s="4"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -832,8 +834,12 @@
       <c r="AH2" s="1">
         <v>46156</v>
       </c>
-      <c r="AI2" s="1"/>
-      <c r="AJ2" s="1"/>
+      <c r="AI2" s="1">
+        <v>46161</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>46163</v>
+      </c>
       <c r="AK2" s="1"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -879,7 +885,7 @@
       <c r="CM2" s="5"/>
       <c r="CN2" s="5"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -981,6 +987,12 @@
         <v>31</v>
       </c>
       <c r="AH3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>31</v>
       </c>
       <c r="AV3" s="2"/>
@@ -1059,7 +1071,7 @@
       <c r="DS3" s="5"/>
       <c r="DT3" s="5"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1161,6 +1173,12 @@
         <v>31</v>
       </c>
       <c r="AH4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ4" t="s">
         <v>31</v>
       </c>
       <c r="AV4" s="2"/>
@@ -1239,7 +1257,7 @@
       <c r="DS4" s="5"/>
       <c r="DT4" s="5"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1341,6 +1359,12 @@
         <v>31</v>
       </c>
       <c r="AH5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ5" t="s">
         <v>31</v>
       </c>
       <c r="AV5" s="2"/>
@@ -1419,7 +1443,7 @@
       <c r="DS5" s="5"/>
       <c r="DT5" s="5"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1521,6 +1545,12 @@
         <v>31</v>
       </c>
       <c r="AH6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ6" t="s">
         <v>31</v>
       </c>
       <c r="AV6" s="2"/>
@@ -1599,7 +1629,7 @@
       <c r="DS6" s="5"/>
       <c r="DT6" s="5"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -1701,6 +1731,12 @@
         <v>31</v>
       </c>
       <c r="AH7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ7" t="s">
         <v>31</v>
       </c>
       <c r="AV7" s="2"/>
@@ -1779,7 +1815,7 @@
       <c r="DS7" s="5"/>
       <c r="DT7" s="5"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -1881,6 +1917,12 @@
         <v>31</v>
       </c>
       <c r="AH8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ8" t="s">
         <v>31</v>
       </c>
       <c r="AV8" s="2"/>
@@ -1959,7 +2001,7 @@
       <c r="DS8" s="5"/>
       <c r="DT8" s="5"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2061,6 +2103,12 @@
         <v>31</v>
       </c>
       <c r="AH9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ9" t="s">
         <v>31</v>
       </c>
       <c r="AV9" s="2"/>
@@ -2139,7 +2187,7 @@
       <c r="DS9" s="5"/>
       <c r="DT9" s="5"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2241,6 +2289,12 @@
         <v>31</v>
       </c>
       <c r="AH10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ10" t="s">
         <v>31</v>
       </c>
       <c r="AV10" s="2"/>
@@ -2319,7 +2373,7 @@
       <c r="DS10" s="5"/>
       <c r="DT10" s="5"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2412,6 +2466,12 @@
         <v>31</v>
       </c>
       <c r="AH11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ11" t="s">
         <v>31</v>
       </c>
       <c r="AV11" s="2"/>
@@ -2490,7 +2550,7 @@
       <c r="DS11" s="5"/>
       <c r="DT11" s="5"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -2592,6 +2652,12 @@
         <v>31</v>
       </c>
       <c r="AH12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ12" t="s">
         <v>31</v>
       </c>
       <c r="AV12" s="2"/>
@@ -2670,7 +2736,7 @@
       <c r="DS12" s="5"/>
       <c r="DT12" s="5"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -2772,6 +2838,12 @@
         <v>31</v>
       </c>
       <c r="AH13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ13" t="s">
         <v>31</v>
       </c>
       <c r="AV13" s="2"/>
@@ -2850,7 +2922,7 @@
       <c r="DS13" s="5"/>
       <c r="DT13" s="5"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -2952,6 +3024,12 @@
         <v>31</v>
       </c>
       <c r="AH14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ14" t="s">
         <v>31</v>
       </c>
       <c r="AV14" s="2"/>
@@ -3030,7 +3108,7 @@
       <c r="DS14" s="5"/>
       <c r="DT14" s="5"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -3132,6 +3210,12 @@
         <v>31</v>
       </c>
       <c r="AH15" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ15" t="s">
         <v>31</v>
       </c>
       <c r="AV15" s="2"/>
@@ -3210,7 +3294,7 @@
       <c r="DS15" s="5"/>
       <c r="DT15" s="5"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -3312,6 +3396,12 @@
         <v>31</v>
       </c>
       <c r="AH16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ16" t="s">
         <v>31</v>
       </c>
       <c r="AV16" s="2"/>
@@ -3390,7 +3480,7 @@
       <c r="DS16" s="5"/>
       <c r="DT16" s="5"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -3471,6 +3561,12 @@
         <v>31</v>
       </c>
       <c r="AH17" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ17" t="s">
         <v>31</v>
       </c>
       <c r="AV17" s="2"/>
@@ -3549,7 +3645,7 @@
       <c r="DS17" s="5"/>
       <c r="DT17" s="5"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -3651,6 +3747,12 @@
         <v>31</v>
       </c>
       <c r="AH18" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ18" t="s">
         <v>31</v>
       </c>
       <c r="AV18" s="2"/>
@@ -3729,7 +3831,7 @@
       <c r="DS18" s="5"/>
       <c r="DT18" s="5"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -3831,6 +3933,12 @@
         <v>31</v>
       </c>
       <c r="AH19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ19" t="s">
         <v>31</v>
       </c>
       <c r="AV19" s="2"/>
@@ -3909,7 +4017,7 @@
       <c r="DS19" s="5"/>
       <c r="DT19" s="5"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -3990,6 +4098,12 @@
         <v>31</v>
       </c>
       <c r="AH20" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ20" t="s">
         <v>31</v>
       </c>
       <c r="AV20" s="2"/>
@@ -4068,7 +4182,7 @@
       <c r="DS20" s="5"/>
       <c r="DT20" s="5"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -4170,6 +4284,12 @@
         <v>31</v>
       </c>
       <c r="AH21" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ21" t="s">
         <v>31</v>
       </c>
       <c r="AV21" s="2"/>
@@ -4248,7 +4368,7 @@
       <c r="DS21" s="5"/>
       <c r="DT21" s="5"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -4350,6 +4470,12 @@
         <v>31</v>
       </c>
       <c r="AH22" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ22" t="s">
         <v>31</v>
       </c>
       <c r="AV22" s="2"/>
@@ -4428,7 +4554,7 @@
       <c r="DS22" s="5"/>
       <c r="DT22" s="5"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -4530,6 +4656,12 @@
         <v>31</v>
       </c>
       <c r="AH23" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ23" t="s">
         <v>31</v>
       </c>
       <c r="AV23" s="2"/>
@@ -4608,7 +4740,7 @@
       <c r="DS23" s="5"/>
       <c r="DT23" s="5"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -4710,6 +4842,12 @@
         <v>31</v>
       </c>
       <c r="AH24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ24" t="s">
         <v>31</v>
       </c>
       <c r="AV24" s="2"/>
@@ -4788,7 +4926,7 @@
       <c r="DS24" s="5"/>
       <c r="DT24" s="5"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -4890,6 +5028,12 @@
         <v>31</v>
       </c>
       <c r="AH25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ25" t="s">
         <v>31</v>
       </c>
       <c r="AV25" s="2"/>
@@ -4968,7 +5112,7 @@
       <c r="DS25" s="5"/>
       <c r="DT25" s="5"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -5070,6 +5214,12 @@
         <v>31</v>
       </c>
       <c r="AH26" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ26" t="s">
         <v>31</v>
       </c>
       <c r="AV26" s="2"/>
@@ -5148,7 +5298,7 @@
       <c r="DS26" s="5"/>
       <c r="DT26" s="5"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -5250,6 +5400,12 @@
         <v>31</v>
       </c>
       <c r="AH27" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ27" t="s">
         <v>31</v>
       </c>
       <c r="AV27" s="2"/>
@@ -5328,7 +5484,7 @@
       <c r="DS27" s="5"/>
       <c r="DT27" s="5"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -5430,6 +5586,12 @@
         <v>31</v>
       </c>
       <c r="AH28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ28" t="s">
         <v>31</v>
       </c>
       <c r="AV28" s="2"/>
@@ -5508,7 +5670,7 @@
       <c r="DS28" s="5"/>
       <c r="DT28" s="5"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -5602,6 +5764,12 @@
       </c>
       <c r="AH29" t="s">
         <v>31</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>32</v>
       </c>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -5679,7 +5847,7 @@
       <c r="DS29" s="5"/>
       <c r="DT29" s="5"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -5781,6 +5949,12 @@
         <v>31</v>
       </c>
       <c r="AH30" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ30" t="s">
         <v>31</v>
       </c>
       <c r="AV30" s="2"/>
@@ -5859,7 +6033,7 @@
       <c r="DS30" s="5"/>
       <c r="DT30" s="5"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -5963,8 +6137,14 @@
       <c r="AH31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
+      <c r="AI31" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -6068,8 +6248,14 @@
       <c r="AH32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI32" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -6173,8 +6359,14 @@
       <c r="AH33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI33" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -6276,6 +6468,12 @@
         <v>31</v>
       </c>
       <c r="AH34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6289,7 +6487,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF3:DH3 AI3:BA9 BC3:BC21 D3:I30 K3:T30 U3:AH34 BF4:BK9 BL4:DH30 AI10:BB21 BD10:BK21 AI22:BK30 K31:K33 L31:T34 H33:I33">
+  <conditionalFormatting sqref="BF3:DH3 BC3:BC21 D3:I30 K3:T30 U3:AH34 BF4:BK9 BL4:DH30 AK10:BB21 BD10:BK21 AK22:BK30 K31:K33 L31:T34 H33:I33 AI3:BA3 AK4:BA9 AI4:AJ34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -6302,12 +6500,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6315,7 +6513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -6323,7 +6521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -6331,7 +6529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -6339,7 +6537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -6347,7 +6545,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -6355,7 +6553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -6363,7 +6561,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -6371,7 +6569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -6379,7 +6577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -6387,7 +6585,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -6395,7 +6593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -6403,7 +6601,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -6411,7 +6609,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -6419,7 +6617,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -6427,7 +6625,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -6435,7 +6633,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -6443,7 +6641,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -6451,7 +6649,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -6459,7 +6657,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -6467,7 +6665,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -6475,7 +6673,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -6483,7 +6681,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -6491,7 +6689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -6499,7 +6697,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -6507,7 +6705,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -6515,7 +6713,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -6523,7 +6721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -6531,7 +6729,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -6539,7 +6737,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -6547,7 +6745,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -6555,7 +6753,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -6563,7 +6761,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -6583,203 +6781,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22963490-B70E-4E4C-BBA7-6A888EA4EC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD3BB68-4AD8-4915-9FB1-0F2363D5210E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -554,27 +554,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="35" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="51" width="7.7109375" customWidth="1"/>
-    <col min="52" max="52" width="7.7109375" style="5" customWidth="1"/>
-    <col min="53" max="107" width="7.7109375" customWidth="1"/>
+    <col min="22" max="26" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="35" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="51" width="7.6640625" customWidth="1"/>
+    <col min="52" max="52" width="7.6640625" style="5" customWidth="1"/>
+    <col min="53" max="107" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -731,7 +731,7 @@
       <c r="CM1" s="4"/>
       <c r="CN1" s="4"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -841,6 +841,7 @@
         <v>46163</v>
       </c>
       <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
       <c r="AX2" s="2"/>
@@ -885,7 +886,7 @@
       <c r="CM2" s="5"/>
       <c r="CN2" s="5"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1071,7 +1072,7 @@
       <c r="DS3" s="5"/>
       <c r="DT3" s="5"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1257,7 +1258,7 @@
       <c r="DS4" s="5"/>
       <c r="DT4" s="5"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1443,7 +1444,7 @@
       <c r="DS5" s="5"/>
       <c r="DT5" s="5"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1629,7 +1630,7 @@
       <c r="DS6" s="5"/>
       <c r="DT6" s="5"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -1737,7 +1738,7 @@
         <v>31</v>
       </c>
       <c r="AJ7" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1815,7 +1816,7 @@
       <c r="DS7" s="5"/>
       <c r="DT7" s="5"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2001,7 +2002,7 @@
       <c r="DS8" s="5"/>
       <c r="DT8" s="5"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2187,7 +2188,7 @@
       <c r="DS9" s="5"/>
       <c r="DT9" s="5"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2373,7 +2374,7 @@
       <c r="DS10" s="5"/>
       <c r="DT10" s="5"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2550,7 +2551,7 @@
       <c r="DS11" s="5"/>
       <c r="DT11" s="5"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -2736,7 +2737,7 @@
       <c r="DS12" s="5"/>
       <c r="DT12" s="5"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -2922,7 +2923,7 @@
       <c r="DS13" s="5"/>
       <c r="DT13" s="5"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3108,7 +3109,7 @@
       <c r="DS14" s="5"/>
       <c r="DT14" s="5"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -3294,7 +3295,7 @@
       <c r="DS15" s="5"/>
       <c r="DT15" s="5"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -3480,7 +3481,7 @@
       <c r="DS16" s="5"/>
       <c r="DT16" s="5"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -3645,7 +3646,7 @@
       <c r="DS17" s="5"/>
       <c r="DT17" s="5"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -3831,7 +3832,7 @@
       <c r="DS18" s="5"/>
       <c r="DT18" s="5"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -4017,7 +4018,7 @@
       <c r="DS19" s="5"/>
       <c r="DT19" s="5"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -4182,7 +4183,7 @@
       <c r="DS20" s="5"/>
       <c r="DT20" s="5"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -4368,7 +4369,7 @@
       <c r="DS21" s="5"/>
       <c r="DT21" s="5"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -4554,7 +4555,7 @@
       <c r="DS22" s="5"/>
       <c r="DT22" s="5"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -4740,7 +4741,7 @@
       <c r="DS23" s="5"/>
       <c r="DT23" s="5"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -4926,7 +4927,7 @@
       <c r="DS24" s="5"/>
       <c r="DT24" s="5"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -5112,7 +5113,7 @@
       <c r="DS25" s="5"/>
       <c r="DT25" s="5"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -5298,7 +5299,7 @@
       <c r="DS26" s="5"/>
       <c r="DT26" s="5"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -5484,7 +5485,7 @@
       <c r="DS27" s="5"/>
       <c r="DT27" s="5"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -5670,7 +5671,7 @@
       <c r="DS28" s="5"/>
       <c r="DT28" s="5"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -5847,7 +5848,7 @@
       <c r="DS29" s="5"/>
       <c r="DT29" s="5"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -6033,7 +6034,7 @@
       <c r="DS30" s="5"/>
       <c r="DT30" s="5"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -6144,7 +6145,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -6255,7 +6256,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -6366,7 +6367,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -6487,7 +6488,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF3:DH3 BC3:BC21 D3:I30 K3:T30 U3:AH34 BF4:BK9 BL4:DH30 AK10:BB21 BD10:BK21 AK22:BK30 K31:K33 L31:T34 H33:I33 AI3:BA3 AK4:BA9 AI4:AJ34">
+  <conditionalFormatting sqref="AI3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 U3:AH34 AK4:BA9 BF4:BK9 BL4:DH30 AI4:AJ34 AK10:BB21 BD10:BK21 AK22:BK30 K31:K33 L31:T34 H33:I33">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -6500,12 +6501,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6513,7 +6514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -6521,7 +6522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -6529,7 +6530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -6537,7 +6538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -6545,7 +6546,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -6553,7 +6554,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -6561,7 +6562,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -6569,7 +6570,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -6577,7 +6578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -6585,7 +6586,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -6593,7 +6594,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -6601,7 +6602,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -6609,7 +6610,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -6617,7 +6618,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -6625,7 +6626,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -6633,7 +6634,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -6641,7 +6642,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -6649,7 +6650,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -6657,7 +6658,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -6665,7 +6666,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -6673,7 +6674,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -6681,7 +6682,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -6689,7 +6690,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -6697,7 +6698,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -6705,7 +6706,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -6713,7 +6714,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -6721,7 +6722,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -6729,7 +6730,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -6737,7 +6738,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -6745,7 +6746,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -6753,7 +6754,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -6761,7 +6762,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -6781,203 +6782,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD3BB68-4AD8-4915-9FB1-0F2363D5210E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73C6390-ED70-44C3-A1D4-F6D5902914AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="44">
   <si>
     <t>Aluno</t>
   </si>
@@ -674,8 +674,12 @@
       <c r="AJ1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
+      <c r="AK1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="AM1" s="1"/>
       <c r="AN1" s="1"/>
       <c r="AO1" s="1"/>
@@ -840,8 +844,12 @@
       <c r="AJ2" s="1">
         <v>46163</v>
       </c>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="1"/>
+      <c r="AK2" s="1">
+        <v>46168</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>46170</v>
+      </c>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
       <c r="AX2" s="2"/>
@@ -994,6 +1002,9 @@
         <v>31</v>
       </c>
       <c r="AJ3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK3" t="s">
         <v>31</v>
       </c>
       <c r="AV3" s="2"/>
@@ -1182,6 +1193,9 @@
       <c r="AJ4" t="s">
         <v>31</v>
       </c>
+      <c r="AK4" t="s">
+        <v>31</v>
+      </c>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
       <c r="AX4" s="2"/>
@@ -1368,6 +1382,9 @@
       <c r="AJ5" t="s">
         <v>31</v>
       </c>
+      <c r="AK5" t="s">
+        <v>31</v>
+      </c>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
       <c r="AX5" s="2"/>
@@ -1554,6 +1571,9 @@
       <c r="AJ6" t="s">
         <v>31</v>
       </c>
+      <c r="AK6" t="s">
+        <v>31</v>
+      </c>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
       <c r="AX6" s="2"/>
@@ -1740,6 +1760,9 @@
       <c r="AJ7" t="s">
         <v>43</v>
       </c>
+      <c r="AK7" t="s">
+        <v>31</v>
+      </c>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
       <c r="AX7" s="2"/>
@@ -1926,6 +1949,9 @@
       <c r="AJ8" t="s">
         <v>31</v>
       </c>
+      <c r="AK8" t="s">
+        <v>31</v>
+      </c>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
       <c r="AX8" s="2"/>
@@ -2112,6 +2138,9 @@
       <c r="AJ9" t="s">
         <v>31</v>
       </c>
+      <c r="AK9" t="s">
+        <v>31</v>
+      </c>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
       <c r="AX9" s="2"/>
@@ -2298,6 +2327,9 @@
       <c r="AJ10" t="s">
         <v>31</v>
       </c>
+      <c r="AK10" t="s">
+        <v>31</v>
+      </c>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
       <c r="AX10" s="2"/>
@@ -2475,6 +2507,9 @@
       <c r="AJ11" t="s">
         <v>31</v>
       </c>
+      <c r="AK11" t="s">
+        <v>31</v>
+      </c>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
       <c r="AX11" s="2"/>
@@ -2661,6 +2696,9 @@
       <c r="AJ12" t="s">
         <v>31</v>
       </c>
+      <c r="AK12" t="s">
+        <v>31</v>
+      </c>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
       <c r="AX12" s="2"/>
@@ -2847,6 +2885,9 @@
       <c r="AJ13" t="s">
         <v>31</v>
       </c>
+      <c r="AK13" t="s">
+        <v>31</v>
+      </c>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
       <c r="AX13" s="2"/>
@@ -3033,6 +3074,9 @@
       <c r="AJ14" t="s">
         <v>31</v>
       </c>
+      <c r="AK14" t="s">
+        <v>31</v>
+      </c>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
       <c r="AX14" s="2"/>
@@ -3219,6 +3263,9 @@
       <c r="AJ15" t="s">
         <v>31</v>
       </c>
+      <c r="AK15" t="s">
+        <v>31</v>
+      </c>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
       <c r="AX15" s="2"/>
@@ -3405,6 +3452,9 @@
       <c r="AJ16" t="s">
         <v>31</v>
       </c>
+      <c r="AK16" t="s">
+        <v>31</v>
+      </c>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
       <c r="AX16" s="2"/>
@@ -3570,6 +3620,9 @@
       <c r="AJ17" t="s">
         <v>31</v>
       </c>
+      <c r="AK17" t="s">
+        <v>31</v>
+      </c>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
       <c r="AX17" s="2"/>
@@ -3756,6 +3809,9 @@
       <c r="AJ18" t="s">
         <v>31</v>
       </c>
+      <c r="AK18" t="s">
+        <v>31</v>
+      </c>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
       <c r="AX18" s="2"/>
@@ -3942,6 +3998,9 @@
       <c r="AJ19" t="s">
         <v>31</v>
       </c>
+      <c r="AK19" t="s">
+        <v>31</v>
+      </c>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
       <c r="AX19" s="2"/>
@@ -4107,6 +4166,9 @@
       <c r="AJ20" t="s">
         <v>31</v>
       </c>
+      <c r="AK20" t="s">
+        <v>31</v>
+      </c>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
       <c r="AX20" s="2"/>
@@ -4293,6 +4355,9 @@
       <c r="AJ21" t="s">
         <v>31</v>
       </c>
+      <c r="AK21" t="s">
+        <v>31</v>
+      </c>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
       <c r="AX21" s="2"/>
@@ -4479,6 +4544,9 @@
       <c r="AJ22" t="s">
         <v>31</v>
       </c>
+      <c r="AK22" t="s">
+        <v>31</v>
+      </c>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
       <c r="AX22" s="2"/>
@@ -4665,6 +4733,9 @@
       <c r="AJ23" t="s">
         <v>31</v>
       </c>
+      <c r="AK23" t="s">
+        <v>31</v>
+      </c>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
       <c r="AX23" s="2"/>
@@ -4851,6 +4922,9 @@
       <c r="AJ24" t="s">
         <v>31</v>
       </c>
+      <c r="AK24" t="s">
+        <v>31</v>
+      </c>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
       <c r="AX24" s="2"/>
@@ -5037,6 +5111,9 @@
       <c r="AJ25" t="s">
         <v>31</v>
       </c>
+      <c r="AK25" t="s">
+        <v>31</v>
+      </c>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
       <c r="AX25" s="2"/>
@@ -5223,6 +5300,9 @@
       <c r="AJ26" t="s">
         <v>31</v>
       </c>
+      <c r="AK26" t="s">
+        <v>31</v>
+      </c>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
       <c r="AX26" s="2"/>
@@ -5409,6 +5489,9 @@
       <c r="AJ27" t="s">
         <v>31</v>
       </c>
+      <c r="AK27" t="s">
+        <v>31</v>
+      </c>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
       <c r="AX27" s="2"/>
@@ -5595,6 +5678,9 @@
       <c r="AJ28" t="s">
         <v>31</v>
       </c>
+      <c r="AK28" t="s">
+        <v>31</v>
+      </c>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
       <c r="AX28" s="2"/>
@@ -5772,6 +5858,9 @@
       <c r="AJ29" t="s">
         <v>32</v>
       </c>
+      <c r="AK29" t="s">
+        <v>31</v>
+      </c>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
       <c r="AX29" s="2"/>
@@ -5958,6 +6047,9 @@
       <c r="AJ30" t="s">
         <v>31</v>
       </c>
+      <c r="AK30" t="s">
+        <v>31</v>
+      </c>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
       <c r="AX30" s="2"/>
@@ -6144,6 +6236,9 @@
       <c r="AJ31" t="s">
         <v>31</v>
       </c>
+      <c r="AK31" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
@@ -6255,8 +6350,11 @@
       <c r="AJ32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -6366,8 +6464,11 @@
       <c r="AJ33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -6475,6 +6576,9 @@
         <v>31</v>
       </c>
       <c r="AJ34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6488,7 +6592,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 U3:AH34 AK4:BA9 BF4:BK9 BL4:DH30 AI4:AJ34 AK10:BB21 BD10:BK21 AK22:BK30 K31:K33 L31:T34 H33:I33">
+  <conditionalFormatting sqref="AI3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 U3:AH34 AK4:BA9 BF4:BK9 BL4:DH30 AI4:AJ34 AK10:BB21 BD10:BK21 AK22:BK30 K31:K33 L31:T34 H33:I33 AK31:AK34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73C6390-ED70-44C3-A1D4-F6D5902914AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C697674-5F45-41D6-82A2-81211A0013A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="44">
   <si>
     <t>Aluno</t>
   </si>
@@ -1007,6 +1007,9 @@
       <c r="AK3" t="s">
         <v>31</v>
       </c>
+      <c r="AL3" t="s">
+        <v>31</v>
+      </c>
       <c r="AV3" s="2"/>
       <c r="AW3" s="2"/>
       <c r="AX3" s="2"/>
@@ -1196,6 +1199,9 @@
       <c r="AK4" t="s">
         <v>31</v>
       </c>
+      <c r="AL4" t="s">
+        <v>31</v>
+      </c>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
       <c r="AX4" s="2"/>
@@ -1385,6 +1391,9 @@
       <c r="AK5" t="s">
         <v>31</v>
       </c>
+      <c r="AL5" t="s">
+        <v>31</v>
+      </c>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
       <c r="AX5" s="2"/>
@@ -1574,6 +1583,9 @@
       <c r="AK6" t="s">
         <v>31</v>
       </c>
+      <c r="AL6" t="s">
+        <v>31</v>
+      </c>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
       <c r="AX6" s="2"/>
@@ -1763,6 +1775,9 @@
       <c r="AK7" t="s">
         <v>31</v>
       </c>
+      <c r="AL7" t="s">
+        <v>31</v>
+      </c>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
       <c r="AX7" s="2"/>
@@ -1952,6 +1967,9 @@
       <c r="AK8" t="s">
         <v>31</v>
       </c>
+      <c r="AL8" t="s">
+        <v>31</v>
+      </c>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
       <c r="AX8" s="2"/>
@@ -2141,6 +2159,9 @@
       <c r="AK9" t="s">
         <v>31</v>
       </c>
+      <c r="AL9" t="s">
+        <v>31</v>
+      </c>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
       <c r="AX9" s="2"/>
@@ -2330,6 +2351,9 @@
       <c r="AK10" t="s">
         <v>31</v>
       </c>
+      <c r="AL10" t="s">
+        <v>31</v>
+      </c>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
       <c r="AX10" s="2"/>
@@ -2510,6 +2534,9 @@
       <c r="AK11" t="s">
         <v>31</v>
       </c>
+      <c r="AL11" t="s">
+        <v>31</v>
+      </c>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
       <c r="AX11" s="2"/>
@@ -2699,6 +2726,9 @@
       <c r="AK12" t="s">
         <v>31</v>
       </c>
+      <c r="AL12" t="s">
+        <v>31</v>
+      </c>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
       <c r="AX12" s="2"/>
@@ -2888,6 +2918,9 @@
       <c r="AK13" t="s">
         <v>31</v>
       </c>
+      <c r="AL13" t="s">
+        <v>31</v>
+      </c>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
       <c r="AX13" s="2"/>
@@ -3077,6 +3110,9 @@
       <c r="AK14" t="s">
         <v>31</v>
       </c>
+      <c r="AL14" t="s">
+        <v>31</v>
+      </c>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
       <c r="AX14" s="2"/>
@@ -3266,6 +3302,9 @@
       <c r="AK15" t="s">
         <v>31</v>
       </c>
+      <c r="AL15" t="s">
+        <v>31</v>
+      </c>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
       <c r="AX15" s="2"/>
@@ -3455,6 +3494,9 @@
       <c r="AK16" t="s">
         <v>31</v>
       </c>
+      <c r="AL16" t="s">
+        <v>31</v>
+      </c>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
       <c r="AX16" s="2"/>
@@ -3623,6 +3665,9 @@
       <c r="AK17" t="s">
         <v>31</v>
       </c>
+      <c r="AL17" t="s">
+        <v>31</v>
+      </c>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
       <c r="AX17" s="2"/>
@@ -3812,6 +3857,9 @@
       <c r="AK18" t="s">
         <v>31</v>
       </c>
+      <c r="AL18" t="s">
+        <v>31</v>
+      </c>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
       <c r="AX18" s="2"/>
@@ -4001,6 +4049,9 @@
       <c r="AK19" t="s">
         <v>31</v>
       </c>
+      <c r="AL19" t="s">
+        <v>31</v>
+      </c>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
       <c r="AX19" s="2"/>
@@ -4169,6 +4220,9 @@
       <c r="AK20" t="s">
         <v>31</v>
       </c>
+      <c r="AL20" t="s">
+        <v>31</v>
+      </c>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
       <c r="AX20" s="2"/>
@@ -4358,6 +4412,9 @@
       <c r="AK21" t="s">
         <v>31</v>
       </c>
+      <c r="AL21" t="s">
+        <v>31</v>
+      </c>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
       <c r="AX21" s="2"/>
@@ -4547,6 +4604,9 @@
       <c r="AK22" t="s">
         <v>31</v>
       </c>
+      <c r="AL22" t="s">
+        <v>31</v>
+      </c>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
       <c r="AX22" s="2"/>
@@ -4736,6 +4796,9 @@
       <c r="AK23" t="s">
         <v>31</v>
       </c>
+      <c r="AL23" t="s">
+        <v>31</v>
+      </c>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
       <c r="AX23" s="2"/>
@@ -4925,6 +4988,9 @@
       <c r="AK24" t="s">
         <v>31</v>
       </c>
+      <c r="AL24" t="s">
+        <v>31</v>
+      </c>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
       <c r="AX24" s="2"/>
@@ -5114,6 +5180,9 @@
       <c r="AK25" t="s">
         <v>31</v>
       </c>
+      <c r="AL25" t="s">
+        <v>31</v>
+      </c>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
       <c r="AX25" s="2"/>
@@ -5303,6 +5372,9 @@
       <c r="AK26" t="s">
         <v>31</v>
       </c>
+      <c r="AL26" t="s">
+        <v>31</v>
+      </c>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
       <c r="AX26" s="2"/>
@@ -5492,6 +5564,9 @@
       <c r="AK27" t="s">
         <v>31</v>
       </c>
+      <c r="AL27" t="s">
+        <v>31</v>
+      </c>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
       <c r="AX27" s="2"/>
@@ -5681,6 +5756,9 @@
       <c r="AK28" t="s">
         <v>31</v>
       </c>
+      <c r="AL28" t="s">
+        <v>31</v>
+      </c>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
       <c r="AX28" s="2"/>
@@ -5861,6 +5939,9 @@
       <c r="AK29" t="s">
         <v>31</v>
       </c>
+      <c r="AL29" t="s">
+        <v>31</v>
+      </c>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
       <c r="AX29" s="2"/>
@@ -6050,6 +6131,9 @@
       <c r="AK30" t="s">
         <v>31</v>
       </c>
+      <c r="AL30" t="s">
+        <v>31</v>
+      </c>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
       <c r="AX30" s="2"/>
@@ -6239,6 +6323,9 @@
       <c r="AK31" t="s">
         <v>31</v>
       </c>
+      <c r="AL31" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
@@ -6353,8 +6440,11 @@
       <c r="AK32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -6467,8 +6557,11 @@
       <c r="AK33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -6579,6 +6672,9 @@
         <v>31</v>
       </c>
       <c r="AK34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AL34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6592,7 +6688,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 U3:AH34 AK4:BA9 BF4:BK9 BL4:DH30 AI4:AJ34 AK10:BB21 BD10:BK21 AK22:BK30 K31:K33 L31:T34 H33:I33 AK31:AK34">
+  <conditionalFormatting sqref="AI3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 U3:AH34 AK4:BA9 BF4:BK9 BL4:DH30 AI4:AJ34 AK10:BB21 BD10:BK21 AK22:BK30 K31:K33 L31:T34 H33:I33 AK31:AL34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C697674-5F45-41D6-82A2-81211A0013A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B38A35-BCBB-486D-99BE-3EFA156852DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="45">
   <si>
     <t>Aluno</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>P/5</t>
+  </si>
+  <si>
+    <t>Feriado</t>
   </si>
 </sst>
 </file>
@@ -680,10 +683,18 @@
       <c r="AL1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1"/>
-      <c r="AP1" s="1"/>
+      <c r="AM1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="AQ1" s="1"/>
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
@@ -850,6 +861,18 @@
       <c r="AL2" s="1">
         <v>46170</v>
       </c>
+      <c r="AM2" s="1">
+        <v>46175</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>46177</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>46182</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>46184</v>
+      </c>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
       <c r="AX2" s="2"/>
@@ -1009,6 +1032,12 @@
       </c>
       <c r="AL3" t="s">
         <v>31</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>44</v>
       </c>
       <c r="AV3" s="2"/>
       <c r="AW3" s="2"/>
@@ -1202,6 +1231,12 @@
       <c r="AL4" t="s">
         <v>31</v>
       </c>
+      <c r="AM4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>44</v>
+      </c>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
       <c r="AX4" s="2"/>
@@ -1394,6 +1429,12 @@
       <c r="AL5" t="s">
         <v>31</v>
       </c>
+      <c r="AM5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>44</v>
+      </c>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
       <c r="AX5" s="2"/>
@@ -1586,6 +1627,12 @@
       <c r="AL6" t="s">
         <v>31</v>
       </c>
+      <c r="AM6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>44</v>
+      </c>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
       <c r="AX6" s="2"/>
@@ -1778,6 +1825,12 @@
       <c r="AL7" t="s">
         <v>31</v>
       </c>
+      <c r="AM7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>44</v>
+      </c>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
       <c r="AX7" s="2"/>
@@ -1970,6 +2023,12 @@
       <c r="AL8" t="s">
         <v>31</v>
       </c>
+      <c r="AM8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>44</v>
+      </c>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
       <c r="AX8" s="2"/>
@@ -2162,6 +2221,12 @@
       <c r="AL9" t="s">
         <v>31</v>
       </c>
+      <c r="AM9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>44</v>
+      </c>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
       <c r="AX9" s="2"/>
@@ -2354,6 +2419,12 @@
       <c r="AL10" t="s">
         <v>31</v>
       </c>
+      <c r="AM10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>44</v>
+      </c>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
       <c r="AX10" s="2"/>
@@ -2537,6 +2608,12 @@
       <c r="AL11" t="s">
         <v>31</v>
       </c>
+      <c r="AM11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>44</v>
+      </c>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
       <c r="AX11" s="2"/>
@@ -2729,6 +2806,12 @@
       <c r="AL12" t="s">
         <v>31</v>
       </c>
+      <c r="AM12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>44</v>
+      </c>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
       <c r="AX12" s="2"/>
@@ -2921,6 +3004,12 @@
       <c r="AL13" t="s">
         <v>31</v>
       </c>
+      <c r="AM13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>44</v>
+      </c>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
       <c r="AX13" s="2"/>
@@ -3113,6 +3202,12 @@
       <c r="AL14" t="s">
         <v>31</v>
       </c>
+      <c r="AM14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>44</v>
+      </c>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
       <c r="AX14" s="2"/>
@@ -3305,6 +3400,12 @@
       <c r="AL15" t="s">
         <v>31</v>
       </c>
+      <c r="AM15" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>44</v>
+      </c>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
       <c r="AX15" s="2"/>
@@ -3497,6 +3598,12 @@
       <c r="AL16" t="s">
         <v>31</v>
       </c>
+      <c r="AM16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>44</v>
+      </c>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
       <c r="AX16" s="2"/>
@@ -3668,6 +3775,12 @@
       <c r="AL17" t="s">
         <v>31</v>
       </c>
+      <c r="AM17" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>44</v>
+      </c>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
       <c r="AX17" s="2"/>
@@ -3860,6 +3973,12 @@
       <c r="AL18" t="s">
         <v>31</v>
       </c>
+      <c r="AM18" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>44</v>
+      </c>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
       <c r="AX18" s="2"/>
@@ -4052,6 +4171,12 @@
       <c r="AL19" t="s">
         <v>31</v>
       </c>
+      <c r="AM19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>44</v>
+      </c>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
       <c r="AX19" s="2"/>
@@ -4223,6 +4348,12 @@
       <c r="AL20" t="s">
         <v>31</v>
       </c>
+      <c r="AM20" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>44</v>
+      </c>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
       <c r="AX20" s="2"/>
@@ -4415,6 +4546,12 @@
       <c r="AL21" t="s">
         <v>31</v>
       </c>
+      <c r="AM21" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>44</v>
+      </c>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
       <c r="AX21" s="2"/>
@@ -4607,6 +4744,12 @@
       <c r="AL22" t="s">
         <v>31</v>
       </c>
+      <c r="AM22" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>44</v>
+      </c>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
       <c r="AX22" s="2"/>
@@ -4799,6 +4942,12 @@
       <c r="AL23" t="s">
         <v>31</v>
       </c>
+      <c r="AM23" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>44</v>
+      </c>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
       <c r="AX23" s="2"/>
@@ -4991,6 +5140,12 @@
       <c r="AL24" t="s">
         <v>31</v>
       </c>
+      <c r="AM24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>44</v>
+      </c>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
       <c r="AX24" s="2"/>
@@ -5183,6 +5338,12 @@
       <c r="AL25" t="s">
         <v>31</v>
       </c>
+      <c r="AM25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>44</v>
+      </c>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
       <c r="AX25" s="2"/>
@@ -5375,6 +5536,12 @@
       <c r="AL26" t="s">
         <v>31</v>
       </c>
+      <c r="AM26" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>44</v>
+      </c>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
       <c r="AX26" s="2"/>
@@ -5567,6 +5734,12 @@
       <c r="AL27" t="s">
         <v>31</v>
       </c>
+      <c r="AM27" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>44</v>
+      </c>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
       <c r="AX27" s="2"/>
@@ -5759,6 +5932,12 @@
       <c r="AL28" t="s">
         <v>31</v>
       </c>
+      <c r="AM28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>44</v>
+      </c>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
       <c r="AX28" s="2"/>
@@ -5942,6 +6121,12 @@
       <c r="AL29" t="s">
         <v>31</v>
       </c>
+      <c r="AM29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>44</v>
+      </c>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
       <c r="AX29" s="2"/>
@@ -6134,6 +6319,12 @@
       <c r="AL30" t="s">
         <v>31</v>
       </c>
+      <c r="AM30" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>44</v>
+      </c>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
       <c r="AX30" s="2"/>
@@ -6326,6 +6517,12 @@
       <c r="AL31" t="s">
         <v>31</v>
       </c>
+      <c r="AM31" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
@@ -6443,8 +6640,14 @@
       <c r="AL32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="AM32" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -6560,8 +6763,14 @@
       <c r="AL33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="AM33" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -6676,6 +6885,12 @@
       </c>
       <c r="AL34" t="s">
         <v>31</v>
+      </c>
+      <c r="AM34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -6688,7 +6903,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 U3:AH34 AK4:BA9 BF4:BK9 BL4:DH30 AI4:AJ34 AK10:BB21 BD10:BK21 AK22:BK30 K31:K33 L31:T34 H33:I33 AK31:AL34">
+  <conditionalFormatting sqref="AI3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 U3:AH34 BF4:BK9 BL4:DH30 BD10:BK21 K31:K33 L31:T34 H33:I33 AO22:BK30 AO10:BB21 AO4:BA9 AI4:AN34">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B38A35-BCBB-486D-99BE-3EFA156852DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA5BA1A-299B-43E3-BC56-227751C74D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="45">
   <si>
     <t>Aluno</t>
   </si>
@@ -259,7 +259,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -557,27 +567,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="35" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="51" width="7.6640625" customWidth="1"/>
-    <col min="52" max="52" width="7.6640625" style="5" customWidth="1"/>
-    <col min="53" max="107" width="7.6640625" customWidth="1"/>
+    <col min="22" max="26" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="35" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="51" width="7.7109375" customWidth="1"/>
+    <col min="52" max="52" width="7.7109375" style="5" customWidth="1"/>
+    <col min="53" max="107" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -746,7 +756,7 @@
       <c r="CM1" s="4"/>
       <c r="CN1" s="4"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -917,7 +927,7 @@
       <c r="CM2" s="5"/>
       <c r="CN2" s="5"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1038,6 +1048,9 @@
       </c>
       <c r="AN3" t="s">
         <v>44</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>31</v>
       </c>
       <c r="AV3" s="2"/>
       <c r="AW3" s="2"/>
@@ -1115,7 +1128,7 @@
       <c r="DS3" s="5"/>
       <c r="DT3" s="5"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1236,6 +1249,9 @@
       </c>
       <c r="AN4" t="s">
         <v>44</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>31</v>
       </c>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1313,7 +1329,7 @@
       <c r="DS4" s="5"/>
       <c r="DT4" s="5"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1434,6 +1450,9 @@
       </c>
       <c r="AN5" t="s">
         <v>44</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>31</v>
       </c>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1511,7 +1530,7 @@
       <c r="DS5" s="5"/>
       <c r="DT5" s="5"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1632,6 +1651,9 @@
       </c>
       <c r="AN6" t="s">
         <v>44</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>31</v>
       </c>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1709,7 +1731,7 @@
       <c r="DS6" s="5"/>
       <c r="DT6" s="5"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -1830,6 +1852,9 @@
       </c>
       <c r="AN7" t="s">
         <v>44</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>31</v>
       </c>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1907,7 +1932,7 @@
       <c r="DS7" s="5"/>
       <c r="DT7" s="5"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2028,6 +2053,9 @@
       </c>
       <c r="AN8" t="s">
         <v>44</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>31</v>
       </c>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -2105,7 +2133,7 @@
       <c r="DS8" s="5"/>
       <c r="DT8" s="5"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2226,6 +2254,9 @@
       </c>
       <c r="AN9" t="s">
         <v>44</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>32</v>
       </c>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -2303,7 +2334,7 @@
       <c r="DS9" s="5"/>
       <c r="DT9" s="5"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2424,6 +2455,9 @@
       </c>
       <c r="AN10" t="s">
         <v>44</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>31</v>
       </c>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -2501,7 +2535,7 @@
       <c r="DS10" s="5"/>
       <c r="DT10" s="5"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2613,6 +2647,9 @@
       </c>
       <c r="AN11" t="s">
         <v>44</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>31</v>
       </c>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -2690,7 +2727,7 @@
       <c r="DS11" s="5"/>
       <c r="DT11" s="5"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -2811,6 +2848,9 @@
       </c>
       <c r="AN12" t="s">
         <v>44</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>31</v>
       </c>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2888,7 +2928,7 @@
       <c r="DS12" s="5"/>
       <c r="DT12" s="5"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3009,6 +3049,9 @@
       </c>
       <c r="AN13" t="s">
         <v>44</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>31</v>
       </c>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -3086,7 +3129,7 @@
       <c r="DS13" s="5"/>
       <c r="DT13" s="5"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3207,6 +3250,9 @@
       </c>
       <c r="AN14" t="s">
         <v>44</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>31</v>
       </c>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -3284,7 +3330,7 @@
       <c r="DS14" s="5"/>
       <c r="DT14" s="5"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -3405,6 +3451,9 @@
       </c>
       <c r="AN15" t="s">
         <v>44</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>31</v>
       </c>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -3482,7 +3531,7 @@
       <c r="DS15" s="5"/>
       <c r="DT15" s="5"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -3603,6 +3652,9 @@
       </c>
       <c r="AN16" t="s">
         <v>44</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>31</v>
       </c>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -3680,7 +3732,7 @@
       <c r="DS16" s="5"/>
       <c r="DT16" s="5"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -3780,6 +3832,9 @@
       </c>
       <c r="AN17" t="s">
         <v>44</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>31</v>
       </c>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -3857,7 +3912,7 @@
       <c r="DS17" s="5"/>
       <c r="DT17" s="5"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -3978,6 +4033,9 @@
       </c>
       <c r="AN18" t="s">
         <v>44</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>31</v>
       </c>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -4055,7 +4113,7 @@
       <c r="DS18" s="5"/>
       <c r="DT18" s="5"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -4176,6 +4234,9 @@
       </c>
       <c r="AN19" t="s">
         <v>44</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>31</v>
       </c>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -4253,7 +4314,7 @@
       <c r="DS19" s="5"/>
       <c r="DT19" s="5"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -4353,6 +4414,9 @@
       </c>
       <c r="AN20" t="s">
         <v>44</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>31</v>
       </c>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -4430,7 +4494,7 @@
       <c r="DS20" s="5"/>
       <c r="DT20" s="5"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -4551,6 +4615,9 @@
       </c>
       <c r="AN21" t="s">
         <v>44</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>31</v>
       </c>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -4628,7 +4695,7 @@
       <c r="DS21" s="5"/>
       <c r="DT21" s="5"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -4749,6 +4816,9 @@
       </c>
       <c r="AN22" t="s">
         <v>44</v>
+      </c>
+      <c r="AO22" t="s">
+        <v>31</v>
       </c>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -4826,7 +4896,7 @@
       <c r="DS22" s="5"/>
       <c r="DT22" s="5"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -4947,6 +5017,9 @@
       </c>
       <c r="AN23" t="s">
         <v>44</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>32</v>
       </c>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -5024,7 +5097,7 @@
       <c r="DS23" s="5"/>
       <c r="DT23" s="5"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -5145,6 +5218,9 @@
       </c>
       <c r="AN24" t="s">
         <v>44</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>31</v>
       </c>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -5222,7 +5298,7 @@
       <c r="DS24" s="5"/>
       <c r="DT24" s="5"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -5343,6 +5419,9 @@
       </c>
       <c r="AN25" t="s">
         <v>44</v>
+      </c>
+      <c r="AO25" t="s">
+        <v>31</v>
       </c>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -5420,7 +5499,7 @@
       <c r="DS25" s="5"/>
       <c r="DT25" s="5"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -5541,6 +5620,9 @@
       </c>
       <c r="AN26" t="s">
         <v>44</v>
+      </c>
+      <c r="AO26" t="s">
+        <v>31</v>
       </c>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -5618,7 +5700,7 @@
       <c r="DS26" s="5"/>
       <c r="DT26" s="5"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -5739,6 +5821,9 @@
       </c>
       <c r="AN27" t="s">
         <v>44</v>
+      </c>
+      <c r="AO27" t="s">
+        <v>31</v>
       </c>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -5816,7 +5901,7 @@
       <c r="DS27" s="5"/>
       <c r="DT27" s="5"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -5937,6 +6022,9 @@
       </c>
       <c r="AN28" t="s">
         <v>44</v>
+      </c>
+      <c r="AO28" t="s">
+        <v>31</v>
       </c>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -6014,7 +6102,7 @@
       <c r="DS28" s="5"/>
       <c r="DT28" s="5"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -6126,6 +6214,9 @@
       </c>
       <c r="AN29" t="s">
         <v>44</v>
+      </c>
+      <c r="AO29" t="s">
+        <v>31</v>
       </c>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -6203,7 +6294,7 @@
       <c r="DS29" s="5"/>
       <c r="DT29" s="5"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -6324,6 +6415,9 @@
       </c>
       <c r="AN30" t="s">
         <v>44</v>
+      </c>
+      <c r="AO30" t="s">
+        <v>31</v>
       </c>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -6401,7 +6495,7 @@
       <c r="DS30" s="5"/>
       <c r="DT30" s="5"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -6523,8 +6617,11 @@
       <c r="AN31" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
+      <c r="AO31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -6646,8 +6743,11 @@
       <c r="AN32" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="AO32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -6769,8 +6869,11 @@
       <c r="AN33" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="AO33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -6891,6 +6994,9 @@
       </c>
       <c r="AN34" t="s">
         <v>44</v>
+      </c>
+      <c r="AO34" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -6899,12 +7005,17 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 U3:AH34 BF4:BK9 BL4:DH30 BD10:BK21 K31:K33 L31:T34 H33:I33 AO22:BK30 AO10:BB21 AO4:BA9 AI4:AN34">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+  <conditionalFormatting sqref="BF3:DH3 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 U3:AN34 AP10:BB21 BD10:BK21 AP22:BK30 K31:K33 L31:T34 H33:I33 AP3:BA9">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO3:AO34">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6916,12 +7027,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6929,7 +7040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -6937,7 +7048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -6945,7 +7056,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -6953,7 +7064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -6961,7 +7072,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -6969,7 +7080,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -6977,7 +7088,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -6985,7 +7096,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -6993,7 +7104,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -7001,7 +7112,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -7009,7 +7120,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -7017,7 +7128,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -7025,7 +7136,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -7033,7 +7144,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -7041,7 +7152,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -7049,7 +7160,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -7057,7 +7168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -7065,7 +7176,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -7073,7 +7184,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -7081,7 +7192,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -7089,7 +7200,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -7097,7 +7208,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -7105,7 +7216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -7113,7 +7224,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -7121,7 +7232,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -7129,7 +7240,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -7137,7 +7248,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -7145,7 +7256,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -7153,7 +7264,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -7161,7 +7272,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -7169,7 +7280,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -7177,7 +7288,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -7197,203 +7308,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA5BA1A-299B-43E3-BC56-227751C74D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9942EFC-1B0D-4870-8CCC-B917F1B9D6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="45">
   <si>
     <t>Aluno</t>
   </si>
@@ -259,7 +259,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1052,6 +1062,9 @@
       <c r="AO3" t="s">
         <v>31</v>
       </c>
+      <c r="AP3" t="s">
+        <v>31</v>
+      </c>
       <c r="AV3" s="2"/>
       <c r="AW3" s="2"/>
       <c r="AX3" s="2"/>
@@ -1253,6 +1266,9 @@
       <c r="AO4" t="s">
         <v>31</v>
       </c>
+      <c r="AP4" t="s">
+        <v>31</v>
+      </c>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
       <c r="AX4" s="2"/>
@@ -1454,6 +1470,9 @@
       <c r="AO5" t="s">
         <v>31</v>
       </c>
+      <c r="AP5" t="s">
+        <v>31</v>
+      </c>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
       <c r="AX5" s="2"/>
@@ -1655,6 +1674,9 @@
       <c r="AO6" t="s">
         <v>31</v>
       </c>
+      <c r="AP6" t="s">
+        <v>31</v>
+      </c>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
       <c r="AX6" s="2"/>
@@ -1856,6 +1878,9 @@
       <c r="AO7" t="s">
         <v>31</v>
       </c>
+      <c r="AP7" t="s">
+        <v>31</v>
+      </c>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
       <c r="AX7" s="2"/>
@@ -2057,6 +2082,9 @@
       <c r="AO8" t="s">
         <v>31</v>
       </c>
+      <c r="AP8" t="s">
+        <v>31</v>
+      </c>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
       <c r="AX8" s="2"/>
@@ -2258,6 +2286,9 @@
       <c r="AO9" t="s">
         <v>32</v>
       </c>
+      <c r="AP9" t="s">
+        <v>31</v>
+      </c>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
       <c r="AX9" s="2"/>
@@ -2459,6 +2490,9 @@
       <c r="AO10" t="s">
         <v>31</v>
       </c>
+      <c r="AP10" t="s">
+        <v>31</v>
+      </c>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
       <c r="AX10" s="2"/>
@@ -2651,6 +2685,9 @@
       <c r="AO11" t="s">
         <v>31</v>
       </c>
+      <c r="AP11" t="s">
+        <v>31</v>
+      </c>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
       <c r="AX11" s="2"/>
@@ -2852,6 +2889,9 @@
       <c r="AO12" t="s">
         <v>31</v>
       </c>
+      <c r="AP12" t="s">
+        <v>31</v>
+      </c>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
       <c r="AX12" s="2"/>
@@ -3053,6 +3093,9 @@
       <c r="AO13" t="s">
         <v>31</v>
       </c>
+      <c r="AP13" t="s">
+        <v>31</v>
+      </c>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
       <c r="AX13" s="2"/>
@@ -3254,6 +3297,9 @@
       <c r="AO14" t="s">
         <v>31</v>
       </c>
+      <c r="AP14" t="s">
+        <v>31</v>
+      </c>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
       <c r="AX14" s="2"/>
@@ -3455,6 +3501,9 @@
       <c r="AO15" t="s">
         <v>31</v>
       </c>
+      <c r="AP15" t="s">
+        <v>31</v>
+      </c>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
       <c r="AX15" s="2"/>
@@ -3656,6 +3705,9 @@
       <c r="AO16" t="s">
         <v>31</v>
       </c>
+      <c r="AP16" t="s">
+        <v>31</v>
+      </c>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
       <c r="AX16" s="2"/>
@@ -3836,6 +3888,9 @@
       <c r="AO17" t="s">
         <v>31</v>
       </c>
+      <c r="AP17" t="s">
+        <v>31</v>
+      </c>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
       <c r="AX17" s="2"/>
@@ -4037,6 +4092,9 @@
       <c r="AO18" t="s">
         <v>31</v>
       </c>
+      <c r="AP18" t="s">
+        <v>31</v>
+      </c>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
       <c r="AX18" s="2"/>
@@ -4238,6 +4296,9 @@
       <c r="AO19" t="s">
         <v>31</v>
       </c>
+      <c r="AP19" t="s">
+        <v>31</v>
+      </c>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
       <c r="AX19" s="2"/>
@@ -4418,6 +4479,9 @@
       <c r="AO20" t="s">
         <v>31</v>
       </c>
+      <c r="AP20" t="s">
+        <v>31</v>
+      </c>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
       <c r="AX20" s="2"/>
@@ -4619,6 +4683,9 @@
       <c r="AO21" t="s">
         <v>31</v>
       </c>
+      <c r="AP21" t="s">
+        <v>31</v>
+      </c>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
       <c r="AX21" s="2"/>
@@ -4820,6 +4887,9 @@
       <c r="AO22" t="s">
         <v>31</v>
       </c>
+      <c r="AP22" t="s">
+        <v>31</v>
+      </c>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
       <c r="AX22" s="2"/>
@@ -5021,6 +5091,9 @@
       <c r="AO23" t="s">
         <v>32</v>
       </c>
+      <c r="AP23" t="s">
+        <v>32</v>
+      </c>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
       <c r="AX23" s="2"/>
@@ -5222,6 +5295,9 @@
       <c r="AO24" t="s">
         <v>31</v>
       </c>
+      <c r="AP24" t="s">
+        <v>31</v>
+      </c>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
       <c r="AX24" s="2"/>
@@ -5423,6 +5499,9 @@
       <c r="AO25" t="s">
         <v>31</v>
       </c>
+      <c r="AP25" t="s">
+        <v>31</v>
+      </c>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
       <c r="AX25" s="2"/>
@@ -5624,6 +5703,9 @@
       <c r="AO26" t="s">
         <v>31</v>
       </c>
+      <c r="AP26" t="s">
+        <v>32</v>
+      </c>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
       <c r="AX26" s="2"/>
@@ -5825,6 +5907,9 @@
       <c r="AO27" t="s">
         <v>31</v>
       </c>
+      <c r="AP27" t="s">
+        <v>31</v>
+      </c>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
       <c r="AX27" s="2"/>
@@ -6026,6 +6111,9 @@
       <c r="AO28" t="s">
         <v>31</v>
       </c>
+      <c r="AP28" t="s">
+        <v>31</v>
+      </c>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
       <c r="AX28" s="2"/>
@@ -6218,6 +6306,9 @@
       <c r="AO29" t="s">
         <v>31</v>
       </c>
+      <c r="AP29" t="s">
+        <v>31</v>
+      </c>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
       <c r="AX29" s="2"/>
@@ -6419,6 +6510,9 @@
       <c r="AO30" t="s">
         <v>31</v>
       </c>
+      <c r="AP30" t="s">
+        <v>31</v>
+      </c>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
       <c r="AX30" s="2"/>
@@ -6620,6 +6714,9 @@
       <c r="AO31" t="s">
         <v>31</v>
       </c>
+      <c r="AP31" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -6746,8 +6843,11 @@
       <c r="AO32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -6872,8 +6972,11 @@
       <c r="AO33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -6996,6 +7099,9 @@
         <v>44</v>
       </c>
       <c r="AO34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AP34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7005,16 +7111,21 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U3:AO34">
     <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF3:DH3 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 U3:AN34 AP10:BB21 BD10:BK21 AP22:BK30 K31:K33 L31:T34 H33:I33 AP3:BA9">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+  <conditionalFormatting sqref="BF3:DH3 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 AQ10:BB21 BD10:BK21 AQ22:BK30 K31:K33 L31:T34 H33:I33 AQ3:BA9">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO3:AO34">
+  <conditionalFormatting sqref="AP3:AP34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9942EFC-1B0D-4870-8CCC-B917F1B9D6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A147FE91-BA94-4F3A-B9FC-1395C6C037B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -259,17 +259,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -577,27 +567,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="35" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="51" width="7.7109375" customWidth="1"/>
-    <col min="52" max="52" width="7.7109375" style="5" customWidth="1"/>
-    <col min="53" max="107" width="7.7109375" customWidth="1"/>
+    <col min="22" max="26" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="35" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="40" width="7.6640625" customWidth="1"/>
+    <col min="41" max="42" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="43" max="51" width="7.6640625" customWidth="1"/>
+    <col min="52" max="52" width="7.6640625" style="5" customWidth="1"/>
+    <col min="53" max="107" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -766,7 +758,7 @@
       <c r="CM1" s="4"/>
       <c r="CN1" s="4"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -937,7 +929,7 @@
       <c r="CM2" s="5"/>
       <c r="CN2" s="5"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1141,7 +1133,7 @@
       <c r="DS3" s="5"/>
       <c r="DT3" s="5"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1345,7 +1337,7 @@
       <c r="DS4" s="5"/>
       <c r="DT4" s="5"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1549,7 +1541,7 @@
       <c r="DS5" s="5"/>
       <c r="DT5" s="5"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1753,7 +1745,7 @@
       <c r="DS6" s="5"/>
       <c r="DT6" s="5"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -1957,7 +1949,7 @@
       <c r="DS7" s="5"/>
       <c r="DT7" s="5"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2161,7 +2153,7 @@
       <c r="DS8" s="5"/>
       <c r="DT8" s="5"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2365,7 +2357,7 @@
       <c r="DS9" s="5"/>
       <c r="DT9" s="5"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2569,7 +2561,7 @@
       <c r="DS10" s="5"/>
       <c r="DT10" s="5"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2764,7 +2756,7 @@
       <c r="DS11" s="5"/>
       <c r="DT11" s="5"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -2968,7 +2960,7 @@
       <c r="DS12" s="5"/>
       <c r="DT12" s="5"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3172,7 +3164,7 @@
       <c r="DS13" s="5"/>
       <c r="DT13" s="5"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3376,7 +3368,7 @@
       <c r="DS14" s="5"/>
       <c r="DT14" s="5"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -3580,7 +3572,7 @@
       <c r="DS15" s="5"/>
       <c r="DT15" s="5"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -3784,7 +3776,7 @@
       <c r="DS16" s="5"/>
       <c r="DT16" s="5"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -3967,7 +3959,7 @@
       <c r="DS17" s="5"/>
       <c r="DT17" s="5"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -4171,7 +4163,7 @@
       <c r="DS18" s="5"/>
       <c r="DT18" s="5"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -4375,7 +4367,7 @@
       <c r="DS19" s="5"/>
       <c r="DT19" s="5"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -4558,7 +4550,7 @@
       <c r="DS20" s="5"/>
       <c r="DT20" s="5"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -4762,7 +4754,7 @@
       <c r="DS21" s="5"/>
       <c r="DT21" s="5"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -4966,7 +4958,7 @@
       <c r="DS22" s="5"/>
       <c r="DT22" s="5"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -5170,7 +5162,7 @@
       <c r="DS23" s="5"/>
       <c r="DT23" s="5"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -5374,7 +5366,7 @@
       <c r="DS24" s="5"/>
       <c r="DT24" s="5"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -5578,7 +5570,7 @@
       <c r="DS25" s="5"/>
       <c r="DT25" s="5"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -5782,7 +5774,7 @@
       <c r="DS26" s="5"/>
       <c r="DT26" s="5"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -5986,7 +5978,7 @@
       <c r="DS27" s="5"/>
       <c r="DT27" s="5"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -6190,7 +6182,7 @@
       <c r="DS28" s="5"/>
       <c r="DT28" s="5"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -6385,7 +6377,7 @@
       <c r="DS29" s="5"/>
       <c r="DT29" s="5"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -6589,7 +6581,7 @@
       <c r="DS30" s="5"/>
       <c r="DT30" s="5"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -6718,7 +6710,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -6847,7 +6839,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -6976,7 +6968,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -7111,22 +7103,17 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U3:AO34">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+  <conditionalFormatting sqref="U3:AP34">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF3:DH3 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 AQ10:BB21 BD10:BK21 AQ22:BK30 K31:K33 L31:T34 H33:I33 AQ3:BA9">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
-      <formula>"F"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP3:AP34">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="BF3:DH3 AQ3:BA9 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 AQ10:BB21 BD10:BK21 AQ22:BK30 K31:K33 L31:T34 H33:I33">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7138,12 +7125,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7151,7 +7138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -7159,7 +7146,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -7167,7 +7154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -7175,7 +7162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -7183,7 +7170,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -7191,7 +7178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -7199,7 +7186,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -7207,7 +7194,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -7215,7 +7202,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -7223,7 +7210,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -7231,7 +7218,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -7239,7 +7226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -7247,7 +7234,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -7255,7 +7242,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -7263,7 +7250,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -7271,7 +7258,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -7279,7 +7266,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -7287,7 +7274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -7295,7 +7282,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -7303,7 +7290,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -7311,7 +7298,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -7319,7 +7306,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -7327,7 +7314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -7335,7 +7322,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -7343,7 +7330,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -7351,7 +7338,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -7359,7 +7346,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -7367,7 +7354,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -7375,7 +7362,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -7383,7 +7370,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -7391,7 +7378,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -7399,7 +7386,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -7419,203 +7406,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A147FE91-BA94-4F3A-B9FC-1395C6C037B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E021B0-8F22-474F-8B34-E1722102D9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t>Feriado</t>
+  </si>
+  <si>
+    <t>P / 5F</t>
   </si>
 </sst>
 </file>
@@ -567,29 +570,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="35" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="40" width="7.6640625" customWidth="1"/>
-    <col min="41" max="42" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="43" max="51" width="7.6640625" customWidth="1"/>
-    <col min="52" max="52" width="7.6640625" style="5" customWidth="1"/>
-    <col min="53" max="107" width="7.6640625" customWidth="1"/>
+    <col min="22" max="26" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="35" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="40" width="7.7109375" customWidth="1"/>
+    <col min="41" max="42" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="51" width="7.7109375" customWidth="1"/>
+    <col min="52" max="52" width="7.7109375" style="5" customWidth="1"/>
+    <col min="53" max="107" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -758,7 +761,7 @@
       <c r="CM1" s="4"/>
       <c r="CN1" s="4"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -929,7 +932,7 @@
       <c r="CM2" s="5"/>
       <c r="CN2" s="5"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1133,7 +1136,7 @@
       <c r="DS3" s="5"/>
       <c r="DT3" s="5"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1337,7 +1340,7 @@
       <c r="DS4" s="5"/>
       <c r="DT4" s="5"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1541,7 +1544,7 @@
       <c r="DS5" s="5"/>
       <c r="DT5" s="5"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1745,7 +1748,7 @@
       <c r="DS6" s="5"/>
       <c r="DT6" s="5"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -1949,7 +1952,7 @@
       <c r="DS7" s="5"/>
       <c r="DT7" s="5"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2153,7 +2156,7 @@
       <c r="DS8" s="5"/>
       <c r="DT8" s="5"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2357,7 +2360,7 @@
       <c r="DS9" s="5"/>
       <c r="DT9" s="5"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2561,7 +2564,7 @@
       <c r="DS10" s="5"/>
       <c r="DT10" s="5"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2756,7 +2759,7 @@
       <c r="DS11" s="5"/>
       <c r="DT11" s="5"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -2960,7 +2963,7 @@
       <c r="DS12" s="5"/>
       <c r="DT12" s="5"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3164,7 +3167,7 @@
       <c r="DS13" s="5"/>
       <c r="DT13" s="5"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3368,7 +3371,7 @@
       <c r="DS14" s="5"/>
       <c r="DT14" s="5"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -3572,7 +3575,7 @@
       <c r="DS15" s="5"/>
       <c r="DT15" s="5"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -3776,7 +3779,7 @@
       <c r="DS16" s="5"/>
       <c r="DT16" s="5"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -3959,7 +3962,7 @@
       <c r="DS17" s="5"/>
       <c r="DT17" s="5"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -4163,7 +4166,7 @@
       <c r="DS18" s="5"/>
       <c r="DT18" s="5"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -4367,7 +4370,7 @@
       <c r="DS19" s="5"/>
       <c r="DT19" s="5"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -4550,7 +4553,7 @@
       <c r="DS20" s="5"/>
       <c r="DT20" s="5"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -4754,7 +4757,7 @@
       <c r="DS21" s="5"/>
       <c r="DT21" s="5"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -4958,7 +4961,7 @@
       <c r="DS22" s="5"/>
       <c r="DT22" s="5"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -5162,7 +5165,7 @@
       <c r="DS23" s="5"/>
       <c r="DT23" s="5"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -5366,7 +5369,7 @@
       <c r="DS24" s="5"/>
       <c r="DT24" s="5"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -5570,7 +5573,7 @@
       <c r="DS25" s="5"/>
       <c r="DT25" s="5"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -5774,7 +5777,7 @@
       <c r="DS26" s="5"/>
       <c r="DT26" s="5"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -5978,7 +5981,7 @@
       <c r="DS27" s="5"/>
       <c r="DT27" s="5"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -6182,7 +6185,7 @@
       <c r="DS28" s="5"/>
       <c r="DT28" s="5"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -6299,7 +6302,7 @@
         <v>31</v>
       </c>
       <c r="AP29" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -6377,7 +6380,7 @@
       <c r="DS29" s="5"/>
       <c r="DT29" s="5"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -6581,7 +6584,7 @@
       <c r="DS30" s="5"/>
       <c r="DT30" s="5"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -6710,7 +6713,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -6839,7 +6842,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -6968,7 +6971,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -7125,12 +7128,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7138,7 +7141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -7146,7 +7149,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -7154,7 +7157,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -7162,7 +7165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -7170,7 +7173,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -7178,7 +7181,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -7186,7 +7189,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -7194,7 +7197,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -7202,7 +7205,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -7210,7 +7213,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -7218,7 +7221,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -7226,7 +7229,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -7234,7 +7237,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -7242,7 +7245,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -7250,7 +7253,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -7258,7 +7261,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -7266,7 +7269,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -7274,7 +7277,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -7282,7 +7285,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -7290,7 +7293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -7298,7 +7301,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -7306,7 +7309,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -7314,7 +7317,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -7322,7 +7325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -7330,7 +7333,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -7338,7 +7341,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -7346,7 +7349,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -7354,7 +7357,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -7362,7 +7365,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -7370,7 +7373,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -7378,7 +7381,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -7386,7 +7389,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -7406,203 +7409,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E021B0-8F22-474F-8B34-E1722102D9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404AE740-CB1F-4BA4-A734-E1EA91C6A3C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -570,29 +570,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="35" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="40" width="7.7109375" customWidth="1"/>
-    <col min="41" max="42" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="43" max="51" width="7.7109375" customWidth="1"/>
-    <col min="52" max="52" width="7.7109375" style="5" customWidth="1"/>
-    <col min="53" max="107" width="7.7109375" customWidth="1"/>
+    <col min="22" max="26" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="35" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="40" width="7.6640625" customWidth="1"/>
+    <col min="41" max="42" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="51" width="7.6640625" customWidth="1"/>
+    <col min="52" max="52" width="7.6640625" style="5" customWidth="1"/>
+    <col min="53" max="107" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -710,8 +710,12 @@
       <c r="AP1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AQ1" s="1"/>
-      <c r="AR1" s="1"/>
+      <c r="AQ1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
       <c r="AU1" s="1"/>
@@ -761,7 +765,7 @@
       <c r="CM1" s="4"/>
       <c r="CN1" s="4"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -887,6 +891,12 @@
       </c>
       <c r="AP2" s="1">
         <v>46184</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>46189</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>46191</v>
       </c>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -932,7 +942,7 @@
       <c r="CM2" s="5"/>
       <c r="CN2" s="5"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1058,6 +1068,9 @@
         <v>31</v>
       </c>
       <c r="AP3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>31</v>
       </c>
       <c r="AV3" s="2"/>
@@ -1136,7 +1149,7 @@
       <c r="DS3" s="5"/>
       <c r="DT3" s="5"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1262,6 +1275,9 @@
         <v>31</v>
       </c>
       <c r="AP4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ4" t="s">
         <v>31</v>
       </c>
       <c r="AV4" s="2"/>
@@ -1340,7 +1356,7 @@
       <c r="DS4" s="5"/>
       <c r="DT4" s="5"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1467,6 +1483,9 @@
       </c>
       <c r="AP5" t="s">
         <v>31</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>43</v>
       </c>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1544,7 +1563,7 @@
       <c r="DS5" s="5"/>
       <c r="DT5" s="5"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1670,6 +1689,9 @@
         <v>31</v>
       </c>
       <c r="AP6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ6" t="s">
         <v>31</v>
       </c>
       <c r="AV6" s="2"/>
@@ -1748,7 +1770,7 @@
       <c r="DS6" s="5"/>
       <c r="DT6" s="5"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -1874,6 +1896,9 @@
         <v>31</v>
       </c>
       <c r="AP7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ7" t="s">
         <v>31</v>
       </c>
       <c r="AV7" s="2"/>
@@ -1952,7 +1977,7 @@
       <c r="DS7" s="5"/>
       <c r="DT7" s="5"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2078,6 +2103,9 @@
         <v>31</v>
       </c>
       <c r="AP8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ8" t="s">
         <v>31</v>
       </c>
       <c r="AV8" s="2"/>
@@ -2156,7 +2184,7 @@
       <c r="DS8" s="5"/>
       <c r="DT8" s="5"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2282,6 +2310,9 @@
         <v>32</v>
       </c>
       <c r="AP9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ9" t="s">
         <v>31</v>
       </c>
       <c r="AV9" s="2"/>
@@ -2360,7 +2391,7 @@
       <c r="DS9" s="5"/>
       <c r="DT9" s="5"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2486,6 +2517,9 @@
         <v>31</v>
       </c>
       <c r="AP10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ10" t="s">
         <v>31</v>
       </c>
       <c r="AV10" s="2"/>
@@ -2564,7 +2598,7 @@
       <c r="DS10" s="5"/>
       <c r="DT10" s="5"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2681,6 +2715,9 @@
         <v>31</v>
       </c>
       <c r="AP11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ11" t="s">
         <v>31</v>
       </c>
       <c r="AV11" s="2"/>
@@ -2759,7 +2796,7 @@
       <c r="DS11" s="5"/>
       <c r="DT11" s="5"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -2886,6 +2923,9 @@
       </c>
       <c r="AP12" t="s">
         <v>31</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>43</v>
       </c>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2963,7 +3003,7 @@
       <c r="DS12" s="5"/>
       <c r="DT12" s="5"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3089,6 +3129,9 @@
         <v>31</v>
       </c>
       <c r="AP13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ13" t="s">
         <v>31</v>
       </c>
       <c r="AV13" s="2"/>
@@ -3167,7 +3210,7 @@
       <c r="DS13" s="5"/>
       <c r="DT13" s="5"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3293,6 +3336,9 @@
         <v>31</v>
       </c>
       <c r="AP14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ14" t="s">
         <v>31</v>
       </c>
       <c r="AV14" s="2"/>
@@ -3371,7 +3417,7 @@
       <c r="DS14" s="5"/>
       <c r="DT14" s="5"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -3497,6 +3543,9 @@
         <v>31</v>
       </c>
       <c r="AP15" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ15" t="s">
         <v>31</v>
       </c>
       <c r="AV15" s="2"/>
@@ -3575,7 +3624,7 @@
       <c r="DS15" s="5"/>
       <c r="DT15" s="5"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -3701,6 +3750,9 @@
         <v>31</v>
       </c>
       <c r="AP16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ16" t="s">
         <v>31</v>
       </c>
       <c r="AV16" s="2"/>
@@ -3779,7 +3831,7 @@
       <c r="DS16" s="5"/>
       <c r="DT16" s="5"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -3884,6 +3936,9 @@
         <v>31</v>
       </c>
       <c r="AP17" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ17" t="s">
         <v>31</v>
       </c>
       <c r="AV17" s="2"/>
@@ -3962,7 +4017,7 @@
       <c r="DS17" s="5"/>
       <c r="DT17" s="5"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -4088,6 +4143,9 @@
         <v>31</v>
       </c>
       <c r="AP18" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ18" t="s">
         <v>31</v>
       </c>
       <c r="AV18" s="2"/>
@@ -4166,7 +4224,7 @@
       <c r="DS18" s="5"/>
       <c r="DT18" s="5"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -4292,6 +4350,9 @@
         <v>31</v>
       </c>
       <c r="AP19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ19" t="s">
         <v>31</v>
       </c>
       <c r="AV19" s="2"/>
@@ -4370,7 +4431,7 @@
       <c r="DS19" s="5"/>
       <c r="DT19" s="5"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -4475,6 +4536,9 @@
         <v>31</v>
       </c>
       <c r="AP20" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ20" t="s">
         <v>31</v>
       </c>
       <c r="AV20" s="2"/>
@@ -4553,7 +4617,7 @@
       <c r="DS20" s="5"/>
       <c r="DT20" s="5"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -4679,6 +4743,9 @@
         <v>31</v>
       </c>
       <c r="AP21" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ21" t="s">
         <v>31</v>
       </c>
       <c r="AV21" s="2"/>
@@ -4757,7 +4824,7 @@
       <c r="DS21" s="5"/>
       <c r="DT21" s="5"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -4883,6 +4950,9 @@
         <v>31</v>
       </c>
       <c r="AP22" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ22" t="s">
         <v>31</v>
       </c>
       <c r="AV22" s="2"/>
@@ -4961,7 +5031,7 @@
       <c r="DS22" s="5"/>
       <c r="DT22" s="5"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -5088,6 +5158,9 @@
       </c>
       <c r="AP23" t="s">
         <v>32</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>31</v>
       </c>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -5165,7 +5238,7 @@
       <c r="DS23" s="5"/>
       <c r="DT23" s="5"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -5291,6 +5364,9 @@
         <v>31</v>
       </c>
       <c r="AP24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ24" t="s">
         <v>31</v>
       </c>
       <c r="AV24" s="2"/>
@@ -5369,7 +5445,7 @@
       <c r="DS24" s="5"/>
       <c r="DT24" s="5"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -5495,6 +5571,9 @@
         <v>31</v>
       </c>
       <c r="AP25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ25" t="s">
         <v>31</v>
       </c>
       <c r="AV25" s="2"/>
@@ -5573,7 +5652,7 @@
       <c r="DS25" s="5"/>
       <c r="DT25" s="5"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -5699,6 +5778,9 @@
         <v>31</v>
       </c>
       <c r="AP26" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ26" t="s">
         <v>32</v>
       </c>
       <c r="AV26" s="2"/>
@@ -5777,7 +5859,7 @@
       <c r="DS26" s="5"/>
       <c r="DT26" s="5"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -5903,6 +5985,9 @@
         <v>31</v>
       </c>
       <c r="AP27" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ27" t="s">
         <v>31</v>
       </c>
       <c r="AV27" s="2"/>
@@ -5981,7 +6066,7 @@
       <c r="DS27" s="5"/>
       <c r="DT27" s="5"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -6107,6 +6192,9 @@
         <v>31</v>
       </c>
       <c r="AP28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ28" t="s">
         <v>31</v>
       </c>
       <c r="AV28" s="2"/>
@@ -6185,7 +6273,7 @@
       <c r="DS28" s="5"/>
       <c r="DT28" s="5"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -6303,6 +6391,9 @@
       </c>
       <c r="AP29" t="s">
         <v>45</v>
+      </c>
+      <c r="AQ29" t="s">
+        <v>31</v>
       </c>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -6380,7 +6471,7 @@
       <c r="DS29" s="5"/>
       <c r="DT29" s="5"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -6506,6 +6597,9 @@
         <v>31</v>
       </c>
       <c r="AP30" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ30" t="s">
         <v>31</v>
       </c>
       <c r="AV30" s="2"/>
@@ -6584,7 +6678,7 @@
       <c r="DS30" s="5"/>
       <c r="DT30" s="5"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -6712,8 +6806,11 @@
       <c r="AP31" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
+      <c r="AQ31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -6841,8 +6938,11 @@
       <c r="AP32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="AQ32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -6970,8 +7070,11 @@
       <c r="AP33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="AQ33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -7097,6 +7200,9 @@
         <v>31</v>
       </c>
       <c r="AP34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7115,7 +7221,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF3:DH3 AQ3:BA9 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 AQ10:BB21 BD10:BK21 AQ22:BK30 K31:K33 L31:T34 H33:I33">
+  <conditionalFormatting sqref="BF3:DH3 AQ3:BA9 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 AQ10:BB21 BD10:BK21 AQ22:BK30 K31:K33 L31:T34 H33:I33 AQ31:AQ34">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -7128,12 +7234,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7141,7 +7247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -7149,7 +7255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -7157,7 +7263,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -7165,7 +7271,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -7173,7 +7279,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -7181,7 +7287,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -7189,7 +7295,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -7197,7 +7303,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -7205,7 +7311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -7213,7 +7319,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -7221,7 +7327,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -7229,7 +7335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -7237,7 +7343,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -7245,7 +7351,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -7253,7 +7359,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -7261,7 +7367,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -7269,7 +7375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -7277,7 +7383,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -7285,7 +7391,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -7293,7 +7399,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -7301,7 +7407,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -7309,7 +7415,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -7317,7 +7423,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -7325,7 +7431,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -7333,7 +7439,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -7341,7 +7447,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -7349,7 +7455,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -7357,7 +7463,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -7365,7 +7471,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -7373,7 +7479,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -7381,7 +7487,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -7389,7 +7495,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -7409,203 +7515,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404AE740-CB1F-4BA4-A734-E1EA91C6A3C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D60BA6-0863-4EE0-9CAD-55FEA836A8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -716,7 +716,9 @@
       <c r="AR1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="1"/>
+      <c r="AS1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="AT1" s="1"/>
       <c r="AU1" s="1"/>
       <c r="AV1" s="3"/>
@@ -898,6 +900,9 @@
       <c r="AR2" s="1">
         <v>46191</v>
       </c>
+      <c r="AS2" s="1">
+        <v>46196</v>
+      </c>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
       <c r="AX2" s="2"/>
@@ -1071,6 +1076,12 @@
         <v>31</v>
       </c>
       <c r="AQ3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS3" t="s">
         <v>31</v>
       </c>
       <c r="AV3" s="2"/>
@@ -1280,6 +1291,12 @@
       <c r="AQ4" t="s">
         <v>31</v>
       </c>
+      <c r="AR4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>31</v>
+      </c>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
       <c r="AX4" s="2"/>
@@ -1487,6 +1504,12 @@
       <c r="AQ5" t="s">
         <v>43</v>
       </c>
+      <c r="AR5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>31</v>
+      </c>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
       <c r="AX5" s="2"/>
@@ -1694,6 +1717,12 @@
       <c r="AQ6" t="s">
         <v>31</v>
       </c>
+      <c r="AR6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>31</v>
+      </c>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
       <c r="AX6" s="2"/>
@@ -1901,6 +1930,12 @@
       <c r="AQ7" t="s">
         <v>31</v>
       </c>
+      <c r="AR7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>31</v>
+      </c>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
       <c r="AX7" s="2"/>
@@ -2108,6 +2143,12 @@
       <c r="AQ8" t="s">
         <v>31</v>
       </c>
+      <c r="AR8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>31</v>
+      </c>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
       <c r="AX8" s="2"/>
@@ -2315,6 +2356,12 @@
       <c r="AQ9" t="s">
         <v>31</v>
       </c>
+      <c r="AR9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>31</v>
+      </c>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
       <c r="AX9" s="2"/>
@@ -2522,6 +2569,12 @@
       <c r="AQ10" t="s">
         <v>31</v>
       </c>
+      <c r="AR10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>31</v>
+      </c>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
       <c r="AX10" s="2"/>
@@ -2720,6 +2773,12 @@
       <c r="AQ11" t="s">
         <v>31</v>
       </c>
+      <c r="AR11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>31</v>
+      </c>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
       <c r="AX11" s="2"/>
@@ -2927,6 +2986,12 @@
       <c r="AQ12" t="s">
         <v>43</v>
       </c>
+      <c r="AR12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>31</v>
+      </c>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
       <c r="AX12" s="2"/>
@@ -3134,6 +3199,12 @@
       <c r="AQ13" t="s">
         <v>31</v>
       </c>
+      <c r="AR13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>31</v>
+      </c>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
       <c r="AX13" s="2"/>
@@ -3341,6 +3412,12 @@
       <c r="AQ14" t="s">
         <v>31</v>
       </c>
+      <c r="AR14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>31</v>
+      </c>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
       <c r="AX14" s="2"/>
@@ -3548,6 +3625,12 @@
       <c r="AQ15" t="s">
         <v>31</v>
       </c>
+      <c r="AR15" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>31</v>
+      </c>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
       <c r="AX15" s="2"/>
@@ -3755,6 +3838,12 @@
       <c r="AQ16" t="s">
         <v>31</v>
       </c>
+      <c r="AR16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>31</v>
+      </c>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
       <c r="AX16" s="2"/>
@@ -3941,6 +4030,12 @@
       <c r="AQ17" t="s">
         <v>31</v>
       </c>
+      <c r="AR17" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>31</v>
+      </c>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
       <c r="AX17" s="2"/>
@@ -4148,6 +4243,12 @@
       <c r="AQ18" t="s">
         <v>31</v>
       </c>
+      <c r="AR18" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>31</v>
+      </c>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
       <c r="AX18" s="2"/>
@@ -4355,6 +4456,12 @@
       <c r="AQ19" t="s">
         <v>31</v>
       </c>
+      <c r="AR19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS19" t="s">
+        <v>31</v>
+      </c>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
       <c r="AX19" s="2"/>
@@ -4541,6 +4648,12 @@
       <c r="AQ20" t="s">
         <v>31</v>
       </c>
+      <c r="AR20" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS20" t="s">
+        <v>31</v>
+      </c>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
       <c r="AX20" s="2"/>
@@ -4748,6 +4861,12 @@
       <c r="AQ21" t="s">
         <v>31</v>
       </c>
+      <c r="AR21" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS21" t="s">
+        <v>31</v>
+      </c>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
       <c r="AX21" s="2"/>
@@ -4955,6 +5074,12 @@
       <c r="AQ22" t="s">
         <v>31</v>
       </c>
+      <c r="AR22" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS22" t="s">
+        <v>31</v>
+      </c>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
       <c r="AX22" s="2"/>
@@ -5162,6 +5287,12 @@
       <c r="AQ23" t="s">
         <v>31</v>
       </c>
+      <c r="AR23" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS23" t="s">
+        <v>31</v>
+      </c>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
       <c r="AX23" s="2"/>
@@ -5369,6 +5500,12 @@
       <c r="AQ24" t="s">
         <v>31</v>
       </c>
+      <c r="AR24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS24" t="s">
+        <v>31</v>
+      </c>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
       <c r="AX24" s="2"/>
@@ -5576,6 +5713,12 @@
       <c r="AQ25" t="s">
         <v>31</v>
       </c>
+      <c r="AR25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS25" t="s">
+        <v>31</v>
+      </c>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
       <c r="AX25" s="2"/>
@@ -5783,6 +5926,12 @@
       <c r="AQ26" t="s">
         <v>32</v>
       </c>
+      <c r="AR26" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS26" t="s">
+        <v>31</v>
+      </c>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
       <c r="AX26" s="2"/>
@@ -5990,6 +6139,12 @@
       <c r="AQ27" t="s">
         <v>31</v>
       </c>
+      <c r="AR27" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS27" t="s">
+        <v>31</v>
+      </c>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
       <c r="AX27" s="2"/>
@@ -6197,6 +6352,12 @@
       <c r="AQ28" t="s">
         <v>31</v>
       </c>
+      <c r="AR28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS28" t="s">
+        <v>31</v>
+      </c>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
       <c r="AX28" s="2"/>
@@ -6395,6 +6556,12 @@
       <c r="AQ29" t="s">
         <v>31</v>
       </c>
+      <c r="AR29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS29" t="s">
+        <v>31</v>
+      </c>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
       <c r="AX29" s="2"/>
@@ -6602,6 +6769,12 @@
       <c r="AQ30" t="s">
         <v>31</v>
       </c>
+      <c r="AR30" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS30" t="s">
+        <v>31</v>
+      </c>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
       <c r="AX30" s="2"/>
@@ -6809,6 +6982,12 @@
       <c r="AQ31" t="s">
         <v>32</v>
       </c>
+      <c r="AR31" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS31" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
@@ -6941,8 +7120,14 @@
       <c r="AQ32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR32" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -7073,8 +7258,14 @@
       <c r="AQ33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="AR33" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -7203,6 +7394,12 @@
         <v>31</v>
       </c>
       <c r="AQ34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AR34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7221,7 +7418,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF3:DH3 AQ3:BA9 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 AQ10:BB21 BD10:BK21 AQ22:BK30 K31:K33 L31:T34 H33:I33 AQ31:AQ34">
+  <conditionalFormatting sqref="BF3:DH3 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 BD10:BK21 K31:K33 L31:T34 H33:I33 AT22:BK30 AT10:BB21 AT3:BA9 AQ3:AS34">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D60BA6-0863-4EE0-9CAD-55FEA836A8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7DA7BB-2EA6-49CA-8247-3222C6DBDE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="47">
   <si>
     <t>Aluno</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>P / 5F</t>
+  </si>
+  <si>
+    <t>FÉRIAS</t>
   </si>
 </sst>
 </file>
@@ -719,8 +722,12 @@
       <c r="AS1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AT1" s="1"/>
-      <c r="AU1" s="1"/>
+      <c r="AT1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="AV1" s="3"/>
       <c r="AW1" s="3"/>
       <c r="AX1" s="3"/>
@@ -903,16 +910,24 @@
       <c r="AS2" s="1">
         <v>46196</v>
       </c>
-      <c r="AV2" s="2"/>
-      <c r="AW2" s="2"/>
-      <c r="AX2" s="2"/>
-      <c r="BA2" s="5"/>
-      <c r="BB2" s="5"/>
-      <c r="BC2" s="5"/>
-      <c r="BD2" s="5"/>
-      <c r="BE2" s="5"/>
-      <c r="BF2" s="5"/>
-      <c r="BG2" s="5"/>
+      <c r="AT2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU2" s="1">
+        <v>46231</v>
+      </c>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
       <c r="BH2" s="5"/>
       <c r="BI2" s="5"/>
       <c r="BJ2" s="5"/>
@@ -1082,6 +1097,12 @@
         <v>31</v>
       </c>
       <c r="AS3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AT3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU3" t="s">
         <v>31</v>
       </c>
       <c r="AV3" s="2"/>
@@ -1297,6 +1318,12 @@
       <c r="AS4" t="s">
         <v>31</v>
       </c>
+      <c r="AT4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>31</v>
+      </c>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
       <c r="AX4" s="2"/>
@@ -1510,6 +1537,12 @@
       <c r="AS5" t="s">
         <v>31</v>
       </c>
+      <c r="AT5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>31</v>
+      </c>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
       <c r="AX5" s="2"/>
@@ -1723,6 +1756,12 @@
       <c r="AS6" t="s">
         <v>31</v>
       </c>
+      <c r="AT6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>31</v>
+      </c>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
       <c r="AX6" s="2"/>
@@ -1936,6 +1975,12 @@
       <c r="AS7" t="s">
         <v>31</v>
       </c>
+      <c r="AT7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>31</v>
+      </c>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
       <c r="AX7" s="2"/>
@@ -2149,6 +2194,12 @@
       <c r="AS8" t="s">
         <v>31</v>
       </c>
+      <c r="AT8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>31</v>
+      </c>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
       <c r="AX8" s="2"/>
@@ -2362,6 +2413,12 @@
       <c r="AS9" t="s">
         <v>31</v>
       </c>
+      <c r="AT9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>32</v>
+      </c>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
       <c r="AX9" s="2"/>
@@ -2575,6 +2632,12 @@
       <c r="AS10" t="s">
         <v>31</v>
       </c>
+      <c r="AT10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>32</v>
+      </c>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
       <c r="AX10" s="2"/>
@@ -2779,6 +2842,12 @@
       <c r="AS11" t="s">
         <v>31</v>
       </c>
+      <c r="AT11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>31</v>
+      </c>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
       <c r="AX11" s="2"/>
@@ -2992,6 +3061,12 @@
       <c r="AS12" t="s">
         <v>31</v>
       </c>
+      <c r="AT12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>31</v>
+      </c>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
       <c r="AX12" s="2"/>
@@ -3205,6 +3280,12 @@
       <c r="AS13" t="s">
         <v>31</v>
       </c>
+      <c r="AT13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>31</v>
+      </c>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
       <c r="AX13" s="2"/>
@@ -3418,6 +3499,12 @@
       <c r="AS14" t="s">
         <v>31</v>
       </c>
+      <c r="AT14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>31</v>
+      </c>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
       <c r="AX14" s="2"/>
@@ -3631,6 +3718,12 @@
       <c r="AS15" t="s">
         <v>31</v>
       </c>
+      <c r="AT15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU15" t="s">
+        <v>31</v>
+      </c>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
       <c r="AX15" s="2"/>
@@ -3844,6 +3937,12 @@
       <c r="AS16" t="s">
         <v>31</v>
       </c>
+      <c r="AT16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU16" t="s">
+        <v>31</v>
+      </c>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
       <c r="AX16" s="2"/>
@@ -4036,6 +4135,12 @@
       <c r="AS17" t="s">
         <v>31</v>
       </c>
+      <c r="AT17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU17" t="s">
+        <v>32</v>
+      </c>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
       <c r="AX17" s="2"/>
@@ -4249,6 +4354,12 @@
       <c r="AS18" t="s">
         <v>31</v>
       </c>
+      <c r="AT18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU18" t="s">
+        <v>31</v>
+      </c>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
       <c r="AX18" s="2"/>
@@ -4462,6 +4573,12 @@
       <c r="AS19" t="s">
         <v>31</v>
       </c>
+      <c r="AT19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU19" t="s">
+        <v>31</v>
+      </c>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
       <c r="AX19" s="2"/>
@@ -4654,6 +4771,12 @@
       <c r="AS20" t="s">
         <v>31</v>
       </c>
+      <c r="AT20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU20" t="s">
+        <v>32</v>
+      </c>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
       <c r="AX20" s="2"/>
@@ -4867,6 +4990,12 @@
       <c r="AS21" t="s">
         <v>31</v>
       </c>
+      <c r="AT21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU21" t="s">
+        <v>31</v>
+      </c>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
       <c r="AX21" s="2"/>
@@ -5080,6 +5209,12 @@
       <c r="AS22" t="s">
         <v>31</v>
       </c>
+      <c r="AT22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU22" t="s">
+        <v>31</v>
+      </c>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
       <c r="AX22" s="2"/>
@@ -5293,6 +5428,12 @@
       <c r="AS23" t="s">
         <v>31</v>
       </c>
+      <c r="AT23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU23" t="s">
+        <v>31</v>
+      </c>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
       <c r="AX23" s="2"/>
@@ -5506,6 +5647,12 @@
       <c r="AS24" t="s">
         <v>31</v>
       </c>
+      <c r="AT24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU24" t="s">
+        <v>31</v>
+      </c>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
       <c r="AX24" s="2"/>
@@ -5719,6 +5866,12 @@
       <c r="AS25" t="s">
         <v>31</v>
       </c>
+      <c r="AT25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU25" t="s">
+        <v>31</v>
+      </c>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
       <c r="AX25" s="2"/>
@@ -5932,6 +6085,12 @@
       <c r="AS26" t="s">
         <v>31</v>
       </c>
+      <c r="AT26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU26" t="s">
+        <v>31</v>
+      </c>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
       <c r="AX26" s="2"/>
@@ -6145,6 +6304,12 @@
       <c r="AS27" t="s">
         <v>31</v>
       </c>
+      <c r="AT27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU27" t="s">
+        <v>32</v>
+      </c>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
       <c r="AX27" s="2"/>
@@ -6358,6 +6523,12 @@
       <c r="AS28" t="s">
         <v>31</v>
       </c>
+      <c r="AT28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU28" t="s">
+        <v>31</v>
+      </c>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
       <c r="AX28" s="2"/>
@@ -6562,6 +6733,12 @@
       <c r="AS29" t="s">
         <v>31</v>
       </c>
+      <c r="AT29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU29" t="s">
+        <v>31</v>
+      </c>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
       <c r="AX29" s="2"/>
@@ -6775,6 +6952,12 @@
       <c r="AS30" t="s">
         <v>31</v>
       </c>
+      <c r="AT30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU30" t="s">
+        <v>31</v>
+      </c>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
       <c r="AX30" s="2"/>
@@ -6988,6 +7171,12 @@
       <c r="AS31" t="s">
         <v>31</v>
       </c>
+      <c r="AT31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU31" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
@@ -7126,8 +7315,14 @@
       <c r="AS32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="AT32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -7264,8 +7459,14 @@
       <c r="AS33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:45" x14ac:dyDescent="0.3">
+      <c r="AT33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -7400,6 +7601,12 @@
         <v>31</v>
       </c>
       <c r="AS34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AT34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU34" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7413,12 +7620,12 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U3:AP34">
+  <conditionalFormatting sqref="U3:AS34">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF3:DH3 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 BD10:BK21 K31:K33 L31:T34 H33:I33 AT22:BK30 AT10:BB21 AT3:BA9 AQ3:AS34">
+  <conditionalFormatting sqref="BF3:DH3 AU3:BA9 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 AU10:BB21 BD10:BK21 AU22:BK30 K31:K33 L31:T34 H33:I33 AU31:AU34">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7DA7BB-2EA6-49CA-8247-3222C6DBDE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A700C0A6-528C-4E56-9392-A6B55403E7BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7625,7 +7625,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF3:DH3 AU3:BA9 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 AU10:BB21 BD10:BK21 AU22:BK30 K31:K33 L31:T34 H33:I33 AU31:AU34">
+  <conditionalFormatting sqref="BF3:DH3 AU3:BA9 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 AU10:BB21 BD10:BK21 AU22:BK30 K31:K33 L31:T34 AU31:AU34 H33:I33">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A700C0A6-528C-4E56-9392-A6B55403E7BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C61BFD9-A35A-49DE-B499-4E9AECC02078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="47">
   <si>
     <t>Aluno</t>
   </si>
@@ -185,17 +185,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -246,18 +239,16 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -578,8 +569,9 @@
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
@@ -587,11 +579,14 @@
     <col min="22" max="26" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="28" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="35" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="40" width="7.6640625" customWidth="1"/>
-    <col min="41" max="42" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="43" max="51" width="7.6640625" customWidth="1"/>
-    <col min="52" max="52" width="7.6640625" style="5" customWidth="1"/>
+    <col min="31" max="38" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="49" max="51" width="7.6640625" customWidth="1"/>
+    <col min="52" max="52" width="7.6640625" style="3" customWidth="1"/>
     <col min="53" max="107" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -728,51 +723,53 @@
       <c r="AU1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AV1" s="3"/>
-      <c r="AW1" s="3"/>
-      <c r="AX1" s="3"/>
+      <c r="AV1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
       <c r="AY1" s="1"/>
-      <c r="AZ1" s="4"/>
-      <c r="BA1" s="4"/>
-      <c r="BB1" s="4"/>
-      <c r="BC1" s="4"/>
-      <c r="BD1" s="4"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="4"/>
-      <c r="BG1" s="4"/>
-      <c r="BH1" s="4"/>
-      <c r="BI1" s="4"/>
-      <c r="BJ1" s="4"/>
-      <c r="BK1" s="4"/>
-      <c r="BL1" s="4"/>
-      <c r="BM1" s="4"/>
-      <c r="BN1" s="4"/>
-      <c r="BO1" s="4"/>
-      <c r="BP1" s="4"/>
-      <c r="BQ1" s="4"/>
-      <c r="BR1" s="4"/>
-      <c r="BS1" s="4"/>
-      <c r="BT1" s="4"/>
-      <c r="BU1" s="4"/>
-      <c r="BV1" s="4"/>
-      <c r="BW1" s="4"/>
-      <c r="BX1" s="4"/>
-      <c r="BY1" s="4"/>
-      <c r="BZ1" s="4"/>
-      <c r="CA1" s="4"/>
-      <c r="CB1" s="4"/>
-      <c r="CC1" s="4"/>
-      <c r="CD1" s="4"/>
-      <c r="CE1" s="4"/>
-      <c r="CF1" s="4"/>
-      <c r="CG1" s="4"/>
-      <c r="CH1" s="4"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="2"/>
+      <c r="BU1" s="2"/>
+      <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2"/>
+      <c r="BY1" s="2"/>
+      <c r="BZ1" s="2"/>
+      <c r="CA1" s="2"/>
+      <c r="CB1" s="2"/>
+      <c r="CC1" s="2"/>
+      <c r="CD1" s="2"/>
+      <c r="CE1" s="2"/>
+      <c r="CF1" s="2"/>
+      <c r="CG1" s="2"/>
+      <c r="CH1" s="2"/>
       <c r="CI1" s="1"/>
-      <c r="CJ1" s="4"/>
-      <c r="CK1" s="4"/>
-      <c r="CL1" s="4"/>
-      <c r="CM1" s="4"/>
-      <c r="CN1" s="4"/>
+      <c r="CJ1" s="2"/>
+      <c r="CK1" s="2"/>
+      <c r="CL1" s="2"/>
+      <c r="CM1" s="2"/>
+      <c r="CN1" s="2"/>
     </row>
     <row r="2" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -916,7 +913,9 @@
       <c r="AU2" s="1">
         <v>46231</v>
       </c>
-      <c r="AV2" s="1"/>
+      <c r="AV2" s="1">
+        <v>46233</v>
+      </c>
       <c r="AW2" s="1"/>
       <c r="AX2" s="1"/>
       <c r="AY2" s="1"/>
@@ -928,39 +927,39 @@
       <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
       <c r="BG2" s="1"/>
-      <c r="BH2" s="5"/>
-      <c r="BI2" s="5"/>
-      <c r="BJ2" s="5"/>
-      <c r="BK2" s="5"/>
-      <c r="BL2" s="5"/>
-      <c r="BM2" s="5"/>
-      <c r="BN2" s="5"/>
-      <c r="BO2" s="5"/>
-      <c r="BP2" s="5"/>
-      <c r="BQ2" s="5"/>
-      <c r="BR2" s="5"/>
-      <c r="BS2" s="5"/>
-      <c r="BT2" s="5"/>
-      <c r="BU2" s="5"/>
-      <c r="BV2" s="5"/>
-      <c r="BW2" s="5"/>
-      <c r="BX2" s="5"/>
-      <c r="BY2" s="5"/>
-      <c r="BZ2" s="5"/>
-      <c r="CA2" s="5"/>
-      <c r="CB2" s="5"/>
-      <c r="CC2" s="5"/>
-      <c r="CD2" s="5"/>
-      <c r="CE2" s="5"/>
-      <c r="CF2" s="5"/>
-      <c r="CG2" s="5"/>
-      <c r="CH2" s="5"/>
-      <c r="CI2" s="5"/>
-      <c r="CJ2" s="5"/>
-      <c r="CK2" s="5"/>
-      <c r="CL2" s="5"/>
-      <c r="CM2" s="5"/>
-      <c r="CN2" s="5"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="3"/>
+      <c r="BU2" s="3"/>
+      <c r="BV2" s="3"/>
+      <c r="BW2" s="3"/>
+      <c r="BX2" s="3"/>
+      <c r="BY2" s="3"/>
+      <c r="BZ2" s="3"/>
+      <c r="CA2" s="3"/>
+      <c r="CB2" s="3"/>
+      <c r="CC2" s="3"/>
+      <c r="CD2" s="3"/>
+      <c r="CE2" s="3"/>
+      <c r="CF2" s="3"/>
+      <c r="CG2" s="3"/>
+      <c r="CH2" s="3"/>
+      <c r="CI2" s="3"/>
+      <c r="CJ2" s="3"/>
+      <c r="CK2" s="3"/>
+      <c r="CL2" s="3"/>
+      <c r="CM2" s="3"/>
+      <c r="CN2" s="3"/>
     </row>
     <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -991,7 +990,7 @@
       <c r="I3" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K3" t="s">
@@ -1105,81 +1104,84 @@
       <c r="AU3" t="s">
         <v>31</v>
       </c>
-      <c r="AV3" s="2"/>
-      <c r="AW3" s="2"/>
-      <c r="AX3" s="2"/>
-      <c r="BA3" s="5"/>
-      <c r="BB3" s="5"/>
-      <c r="BC3" s="5"/>
-      <c r="BD3" s="5"/>
-      <c r="BE3" s="5"/>
-      <c r="BF3" s="5"/>
-      <c r="BG3" s="5"/>
-      <c r="BH3" s="5"/>
-      <c r="BI3" s="5"/>
-      <c r="BJ3" s="5"/>
-      <c r="BK3" s="5"/>
-      <c r="BL3" s="5"/>
-      <c r="BM3" s="5"/>
-      <c r="BN3" s="5"/>
-      <c r="BO3" s="5"/>
-      <c r="BP3" s="5"/>
-      <c r="BQ3" s="5"/>
-      <c r="BR3" s="5"/>
-      <c r="BS3" s="5"/>
-      <c r="BT3" s="5"/>
-      <c r="BU3" s="5"/>
-      <c r="BV3" s="5"/>
-      <c r="BW3" s="5"/>
-      <c r="BX3" s="5"/>
-      <c r="BY3" s="5"/>
-      <c r="BZ3" s="5"/>
-      <c r="CA3" s="5"/>
-      <c r="CB3" s="5"/>
-      <c r="CC3" s="5"/>
-      <c r="CD3" s="5"/>
-      <c r="CE3" s="5"/>
-      <c r="CF3" s="5"/>
-      <c r="CG3" s="5"/>
-      <c r="CH3" s="5"/>
-      <c r="CI3" s="5"/>
-      <c r="CJ3" s="5"/>
-      <c r="CK3" s="5"/>
-      <c r="CL3" s="5"/>
-      <c r="CM3" s="5"/>
-      <c r="CN3" s="5"/>
-      <c r="CO3" s="5"/>
-      <c r="CP3" s="5"/>
-      <c r="CQ3" s="5"/>
-      <c r="CR3" s="5"/>
-      <c r="CS3" s="5"/>
-      <c r="CT3" s="5"/>
-      <c r="CU3" s="5"/>
-      <c r="CV3" s="5"/>
-      <c r="CW3" s="5"/>
-      <c r="CX3" s="5"/>
-      <c r="CY3" s="5"/>
-      <c r="CZ3" s="5"/>
-      <c r="DA3" s="5"/>
-      <c r="DB3" s="5"/>
-      <c r="DC3" s="5"/>
-      <c r="DD3" s="5"/>
-      <c r="DE3" s="5"/>
-      <c r="DF3" s="5"/>
-      <c r="DG3" s="5"/>
-      <c r="DH3" s="5"/>
-      <c r="DI3" s="5"/>
-      <c r="DJ3" s="5"/>
-      <c r="DK3" s="5"/>
-      <c r="DL3" s="5"/>
-      <c r="DM3" s="5"/>
-      <c r="DN3" s="5"/>
-      <c r="DO3" s="5"/>
-      <c r="DP3" s="5"/>
-      <c r="DQ3" s="5"/>
-      <c r="DR3" s="5"/>
-      <c r="DS3" s="5"/>
-      <c r="DT3" s="5"/>
+      <c r="AV3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW3" s="3"/>
+      <c r="AX3" s="3"/>
+      <c r="AY3" s="3"/>
+      <c r="BA3" s="3"/>
+      <c r="BB3" s="3"/>
+      <c r="BC3" s="3"/>
+      <c r="BD3" s="3"/>
+      <c r="BE3" s="3"/>
+      <c r="BF3" s="3"/>
+      <c r="BG3" s="3"/>
+      <c r="BH3" s="3"/>
+      <c r="BI3" s="3"/>
+      <c r="BJ3" s="3"/>
+      <c r="BK3" s="3"/>
+      <c r="BL3" s="3"/>
+      <c r="BM3" s="3"/>
+      <c r="BN3" s="3"/>
+      <c r="BO3" s="3"/>
+      <c r="BP3" s="3"/>
+      <c r="BQ3" s="3"/>
+      <c r="BR3" s="3"/>
+      <c r="BS3" s="3"/>
+      <c r="BT3" s="3"/>
+      <c r="BU3" s="3"/>
+      <c r="BV3" s="3"/>
+      <c r="BW3" s="3"/>
+      <c r="BX3" s="3"/>
+      <c r="BY3" s="3"/>
+      <c r="BZ3" s="3"/>
+      <c r="CA3" s="3"/>
+      <c r="CB3" s="3"/>
+      <c r="CC3" s="3"/>
+      <c r="CD3" s="3"/>
+      <c r="CE3" s="3"/>
+      <c r="CF3" s="3"/>
+      <c r="CG3" s="3"/>
+      <c r="CH3" s="3"/>
+      <c r="CI3" s="3"/>
+      <c r="CJ3" s="3"/>
+      <c r="CK3" s="3"/>
+      <c r="CL3" s="3"/>
+      <c r="CM3" s="3"/>
+      <c r="CN3" s="3"/>
+      <c r="CO3" s="3"/>
+      <c r="CP3" s="3"/>
+      <c r="CQ3" s="3"/>
+      <c r="CR3" s="3"/>
+      <c r="CS3" s="3"/>
+      <c r="CT3" s="3"/>
+      <c r="CU3" s="3"/>
+      <c r="CV3" s="3"/>
+      <c r="CW3" s="3"/>
+      <c r="CX3" s="3"/>
+      <c r="CY3" s="3"/>
+      <c r="CZ3" s="3"/>
+      <c r="DA3" s="3"/>
+      <c r="DB3" s="3"/>
+      <c r="DC3" s="3"/>
+      <c r="DD3" s="3"/>
+      <c r="DE3" s="3"/>
+      <c r="DF3" s="3"/>
+      <c r="DG3" s="3"/>
+      <c r="DH3" s="3"/>
+      <c r="DI3" s="3"/>
+      <c r="DJ3" s="3"/>
+      <c r="DK3" s="3"/>
+      <c r="DL3" s="3"/>
+      <c r="DM3" s="3"/>
+      <c r="DN3" s="3"/>
+      <c r="DO3" s="3"/>
+      <c r="DP3" s="3"/>
+      <c r="DQ3" s="3"/>
+      <c r="DR3" s="3"/>
+      <c r="DS3" s="3"/>
+      <c r="DT3" s="3"/>
     </row>
     <row r="4" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -1210,7 +1212,7 @@
       <c r="I4" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K4" t="s">
@@ -1324,81 +1326,84 @@
       <c r="AU4" t="s">
         <v>31</v>
       </c>
-      <c r="AV4" s="2"/>
-      <c r="AW4" s="2"/>
-      <c r="AX4" s="2"/>
-      <c r="BA4" s="5"/>
-      <c r="BB4" s="5"/>
-      <c r="BC4" s="5"/>
-      <c r="BD4" s="5"/>
-      <c r="BE4" s="5"/>
-      <c r="BF4" s="5"/>
-      <c r="BG4" s="5"/>
-      <c r="BH4" s="5"/>
-      <c r="BI4" s="5"/>
-      <c r="BJ4" s="5"/>
-      <c r="BK4" s="5"/>
-      <c r="BL4" s="5"/>
-      <c r="BM4" s="5"/>
-      <c r="BN4" s="5"/>
-      <c r="BO4" s="5"/>
-      <c r="BP4" s="5"/>
-      <c r="BQ4" s="5"/>
-      <c r="BR4" s="5"/>
-      <c r="BS4" s="5"/>
-      <c r="BT4" s="5"/>
-      <c r="BU4" s="5"/>
-      <c r="BV4" s="5"/>
-      <c r="BW4" s="5"/>
-      <c r="BX4" s="5"/>
-      <c r="BY4" s="5"/>
-      <c r="BZ4" s="5"/>
-      <c r="CA4" s="5"/>
-      <c r="CB4" s="5"/>
-      <c r="CC4" s="5"/>
-      <c r="CD4" s="5"/>
-      <c r="CE4" s="5"/>
-      <c r="CF4" s="5"/>
-      <c r="CG4" s="5"/>
-      <c r="CH4" s="5"/>
-      <c r="CI4" s="5"/>
-      <c r="CJ4" s="5"/>
-      <c r="CK4" s="5"/>
-      <c r="CL4" s="5"/>
-      <c r="CM4" s="5"/>
-      <c r="CN4" s="5"/>
-      <c r="CO4" s="5"/>
-      <c r="CP4" s="5"/>
-      <c r="CQ4" s="5"/>
-      <c r="CR4" s="5"/>
-      <c r="CS4" s="5"/>
-      <c r="CT4" s="5"/>
-      <c r="CU4" s="5"/>
-      <c r="CV4" s="5"/>
-      <c r="CW4" s="5"/>
-      <c r="CX4" s="5"/>
-      <c r="CY4" s="5"/>
-      <c r="CZ4" s="5"/>
-      <c r="DA4" s="5"/>
-      <c r="DB4" s="5"/>
-      <c r="DC4" s="5"/>
-      <c r="DD4" s="5"/>
-      <c r="DE4" s="5"/>
-      <c r="DF4" s="5"/>
-      <c r="DG4" s="5"/>
-      <c r="DH4" s="5"/>
-      <c r="DI4" s="5"/>
-      <c r="DJ4" s="5"/>
-      <c r="DK4" s="5"/>
-      <c r="DL4" s="5"/>
-      <c r="DM4" s="5"/>
-      <c r="DN4" s="5"/>
-      <c r="DO4" s="5"/>
-      <c r="DP4" s="5"/>
-      <c r="DQ4" s="5"/>
-      <c r="DR4" s="5"/>
-      <c r="DS4" s="5"/>
-      <c r="DT4" s="5"/>
+      <c r="AV4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW4" s="3"/>
+      <c r="AX4" s="3"/>
+      <c r="AY4" s="3"/>
+      <c r="BA4" s="3"/>
+      <c r="BB4" s="3"/>
+      <c r="BC4" s="3"/>
+      <c r="BD4" s="3"/>
+      <c r="BE4" s="3"/>
+      <c r="BF4" s="3"/>
+      <c r="BG4" s="3"/>
+      <c r="BH4" s="3"/>
+      <c r="BI4" s="3"/>
+      <c r="BJ4" s="3"/>
+      <c r="BK4" s="3"/>
+      <c r="BL4" s="3"/>
+      <c r="BM4" s="3"/>
+      <c r="BN4" s="3"/>
+      <c r="BO4" s="3"/>
+      <c r="BP4" s="3"/>
+      <c r="BQ4" s="3"/>
+      <c r="BR4" s="3"/>
+      <c r="BS4" s="3"/>
+      <c r="BT4" s="3"/>
+      <c r="BU4" s="3"/>
+      <c r="BV4" s="3"/>
+      <c r="BW4" s="3"/>
+      <c r="BX4" s="3"/>
+      <c r="BY4" s="3"/>
+      <c r="BZ4" s="3"/>
+      <c r="CA4" s="3"/>
+      <c r="CB4" s="3"/>
+      <c r="CC4" s="3"/>
+      <c r="CD4" s="3"/>
+      <c r="CE4" s="3"/>
+      <c r="CF4" s="3"/>
+      <c r="CG4" s="3"/>
+      <c r="CH4" s="3"/>
+      <c r="CI4" s="3"/>
+      <c r="CJ4" s="3"/>
+      <c r="CK4" s="3"/>
+      <c r="CL4" s="3"/>
+      <c r="CM4" s="3"/>
+      <c r="CN4" s="3"/>
+      <c r="CO4" s="3"/>
+      <c r="CP4" s="3"/>
+      <c r="CQ4" s="3"/>
+      <c r="CR4" s="3"/>
+      <c r="CS4" s="3"/>
+      <c r="CT4" s="3"/>
+      <c r="CU4" s="3"/>
+      <c r="CV4" s="3"/>
+      <c r="CW4" s="3"/>
+      <c r="CX4" s="3"/>
+      <c r="CY4" s="3"/>
+      <c r="CZ4" s="3"/>
+      <c r="DA4" s="3"/>
+      <c r="DB4" s="3"/>
+      <c r="DC4" s="3"/>
+      <c r="DD4" s="3"/>
+      <c r="DE4" s="3"/>
+      <c r="DF4" s="3"/>
+      <c r="DG4" s="3"/>
+      <c r="DH4" s="3"/>
+      <c r="DI4" s="3"/>
+      <c r="DJ4" s="3"/>
+      <c r="DK4" s="3"/>
+      <c r="DL4" s="3"/>
+      <c r="DM4" s="3"/>
+      <c r="DN4" s="3"/>
+      <c r="DO4" s="3"/>
+      <c r="DP4" s="3"/>
+      <c r="DQ4" s="3"/>
+      <c r="DR4" s="3"/>
+      <c r="DS4" s="3"/>
+      <c r="DT4" s="3"/>
     </row>
     <row r="5" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -1429,7 +1434,7 @@
       <c r="I5" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K5" t="s">
@@ -1543,81 +1548,84 @@
       <c r="AU5" t="s">
         <v>31</v>
       </c>
-      <c r="AV5" s="2"/>
-      <c r="AW5" s="2"/>
-      <c r="AX5" s="2"/>
-      <c r="BA5" s="5"/>
-      <c r="BB5" s="5"/>
-      <c r="BC5" s="5"/>
-      <c r="BD5" s="5"/>
-      <c r="BE5" s="5"/>
-      <c r="BF5" s="5"/>
-      <c r="BG5" s="5"/>
-      <c r="BH5" s="5"/>
-      <c r="BI5" s="5"/>
-      <c r="BJ5" s="5"/>
-      <c r="BK5" s="5"/>
-      <c r="BL5" s="5"/>
-      <c r="BM5" s="5"/>
-      <c r="BN5" s="5"/>
-      <c r="BO5" s="5"/>
-      <c r="BP5" s="5"/>
-      <c r="BQ5" s="5"/>
-      <c r="BR5" s="5"/>
-      <c r="BS5" s="5"/>
-      <c r="BT5" s="5"/>
-      <c r="BU5" s="5"/>
-      <c r="BV5" s="5"/>
-      <c r="BW5" s="5"/>
-      <c r="BX5" s="5"/>
-      <c r="BY5" s="5"/>
-      <c r="BZ5" s="5"/>
-      <c r="CA5" s="5"/>
-      <c r="CB5" s="5"/>
-      <c r="CC5" s="5"/>
-      <c r="CD5" s="5"/>
-      <c r="CE5" s="5"/>
-      <c r="CF5" s="5"/>
-      <c r="CG5" s="5"/>
-      <c r="CH5" s="5"/>
-      <c r="CI5" s="5"/>
-      <c r="CJ5" s="5"/>
-      <c r="CK5" s="5"/>
-      <c r="CL5" s="5"/>
-      <c r="CM5" s="5"/>
-      <c r="CN5" s="5"/>
-      <c r="CO5" s="5"/>
-      <c r="CP5" s="5"/>
-      <c r="CQ5" s="5"/>
-      <c r="CR5" s="5"/>
-      <c r="CS5" s="5"/>
-      <c r="CT5" s="5"/>
-      <c r="CU5" s="5"/>
-      <c r="CV5" s="5"/>
-      <c r="CW5" s="5"/>
-      <c r="CX5" s="5"/>
-      <c r="CY5" s="5"/>
-      <c r="CZ5" s="5"/>
-      <c r="DA5" s="5"/>
-      <c r="DB5" s="5"/>
-      <c r="DC5" s="5"/>
-      <c r="DD5" s="5"/>
-      <c r="DE5" s="5"/>
-      <c r="DF5" s="5"/>
-      <c r="DG5" s="5"/>
-      <c r="DH5" s="5"/>
-      <c r="DI5" s="5"/>
-      <c r="DJ5" s="5"/>
-      <c r="DK5" s="5"/>
-      <c r="DL5" s="5"/>
-      <c r="DM5" s="5"/>
-      <c r="DN5" s="5"/>
-      <c r="DO5" s="5"/>
-      <c r="DP5" s="5"/>
-      <c r="DQ5" s="5"/>
-      <c r="DR5" s="5"/>
-      <c r="DS5" s="5"/>
-      <c r="DT5" s="5"/>
+      <c r="AV5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW5" s="3"/>
+      <c r="AX5" s="3"/>
+      <c r="AY5" s="3"/>
+      <c r="BA5" s="3"/>
+      <c r="BB5" s="3"/>
+      <c r="BC5" s="3"/>
+      <c r="BD5" s="3"/>
+      <c r="BE5" s="3"/>
+      <c r="BF5" s="3"/>
+      <c r="BG5" s="3"/>
+      <c r="BH5" s="3"/>
+      <c r="BI5" s="3"/>
+      <c r="BJ5" s="3"/>
+      <c r="BK5" s="3"/>
+      <c r="BL5" s="3"/>
+      <c r="BM5" s="3"/>
+      <c r="BN5" s="3"/>
+      <c r="BO5" s="3"/>
+      <c r="BP5" s="3"/>
+      <c r="BQ5" s="3"/>
+      <c r="BR5" s="3"/>
+      <c r="BS5" s="3"/>
+      <c r="BT5" s="3"/>
+      <c r="BU5" s="3"/>
+      <c r="BV5" s="3"/>
+      <c r="BW5" s="3"/>
+      <c r="BX5" s="3"/>
+      <c r="BY5" s="3"/>
+      <c r="BZ5" s="3"/>
+      <c r="CA5" s="3"/>
+      <c r="CB5" s="3"/>
+      <c r="CC5" s="3"/>
+      <c r="CD5" s="3"/>
+      <c r="CE5" s="3"/>
+      <c r="CF5" s="3"/>
+      <c r="CG5" s="3"/>
+      <c r="CH5" s="3"/>
+      <c r="CI5" s="3"/>
+      <c r="CJ5" s="3"/>
+      <c r="CK5" s="3"/>
+      <c r="CL5" s="3"/>
+      <c r="CM5" s="3"/>
+      <c r="CN5" s="3"/>
+      <c r="CO5" s="3"/>
+      <c r="CP5" s="3"/>
+      <c r="CQ5" s="3"/>
+      <c r="CR5" s="3"/>
+      <c r="CS5" s="3"/>
+      <c r="CT5" s="3"/>
+      <c r="CU5" s="3"/>
+      <c r="CV5" s="3"/>
+      <c r="CW5" s="3"/>
+      <c r="CX5" s="3"/>
+      <c r="CY5" s="3"/>
+      <c r="CZ5" s="3"/>
+      <c r="DA5" s="3"/>
+      <c r="DB5" s="3"/>
+      <c r="DC5" s="3"/>
+      <c r="DD5" s="3"/>
+      <c r="DE5" s="3"/>
+      <c r="DF5" s="3"/>
+      <c r="DG5" s="3"/>
+      <c r="DH5" s="3"/>
+      <c r="DI5" s="3"/>
+      <c r="DJ5" s="3"/>
+      <c r="DK5" s="3"/>
+      <c r="DL5" s="3"/>
+      <c r="DM5" s="3"/>
+      <c r="DN5" s="3"/>
+      <c r="DO5" s="3"/>
+      <c r="DP5" s="3"/>
+      <c r="DQ5" s="3"/>
+      <c r="DR5" s="3"/>
+      <c r="DS5" s="3"/>
+      <c r="DT5" s="3"/>
     </row>
     <row r="6" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -1648,7 +1656,7 @@
       <c r="I6" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K6" t="s">
@@ -1762,81 +1770,84 @@
       <c r="AU6" t="s">
         <v>31</v>
       </c>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2"/>
-      <c r="AX6" s="2"/>
-      <c r="BA6" s="5"/>
-      <c r="BB6" s="5"/>
-      <c r="BC6" s="5"/>
-      <c r="BD6" s="5"/>
-      <c r="BE6" s="5"/>
-      <c r="BF6" s="5"/>
-      <c r="BG6" s="5"/>
-      <c r="BH6" s="5"/>
-      <c r="BI6" s="5"/>
-      <c r="BJ6" s="5"/>
-      <c r="BK6" s="5"/>
-      <c r="BL6" s="5"/>
-      <c r="BM6" s="5"/>
-      <c r="BN6" s="5"/>
-      <c r="BO6" s="5"/>
-      <c r="BP6" s="5"/>
-      <c r="BQ6" s="5"/>
-      <c r="BR6" s="5"/>
-      <c r="BS6" s="5"/>
-      <c r="BT6" s="5"/>
-      <c r="BU6" s="5"/>
-      <c r="BV6" s="5"/>
-      <c r="BW6" s="5"/>
-      <c r="BX6" s="5"/>
-      <c r="BY6" s="5"/>
-      <c r="BZ6" s="5"/>
-      <c r="CA6" s="5"/>
-      <c r="CB6" s="5"/>
-      <c r="CC6" s="5"/>
-      <c r="CD6" s="5"/>
-      <c r="CE6" s="5"/>
-      <c r="CF6" s="5"/>
-      <c r="CG6" s="5"/>
-      <c r="CH6" s="5"/>
-      <c r="CI6" s="5"/>
-      <c r="CJ6" s="7"/>
-      <c r="CK6" s="5"/>
-      <c r="CL6" s="5"/>
-      <c r="CM6" s="5"/>
-      <c r="CN6" s="5"/>
-      <c r="CO6" s="5"/>
-      <c r="CP6" s="5"/>
-      <c r="CQ6" s="5"/>
-      <c r="CR6" s="5"/>
-      <c r="CS6" s="5"/>
-      <c r="CT6" s="5"/>
-      <c r="CU6" s="5"/>
-      <c r="CV6" s="5"/>
-      <c r="CW6" s="5"/>
-      <c r="CX6" s="5"/>
-      <c r="CY6" s="5"/>
-      <c r="CZ6" s="5"/>
-      <c r="DA6" s="5"/>
-      <c r="DB6" s="5"/>
-      <c r="DC6" s="5"/>
-      <c r="DD6" s="5"/>
-      <c r="DE6" s="5"/>
-      <c r="DF6" s="5"/>
-      <c r="DG6" s="5"/>
-      <c r="DH6" s="5"/>
-      <c r="DI6" s="5"/>
-      <c r="DJ6" s="5"/>
-      <c r="DK6" s="5"/>
-      <c r="DL6" s="5"/>
-      <c r="DM6" s="5"/>
-      <c r="DN6" s="5"/>
-      <c r="DO6" s="5"/>
-      <c r="DP6" s="5"/>
-      <c r="DQ6" s="5"/>
-      <c r="DR6" s="5"/>
-      <c r="DS6" s="5"/>
-      <c r="DT6" s="5"/>
+      <c r="AV6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW6" s="3"/>
+      <c r="AX6" s="3"/>
+      <c r="AY6" s="3"/>
+      <c r="BA6" s="3"/>
+      <c r="BB6" s="3"/>
+      <c r="BC6" s="3"/>
+      <c r="BD6" s="3"/>
+      <c r="BE6" s="3"/>
+      <c r="BF6" s="3"/>
+      <c r="BG6" s="3"/>
+      <c r="BH6" s="3"/>
+      <c r="BI6" s="3"/>
+      <c r="BJ6" s="3"/>
+      <c r="BK6" s="3"/>
+      <c r="BL6" s="3"/>
+      <c r="BM6" s="3"/>
+      <c r="BN6" s="3"/>
+      <c r="BO6" s="3"/>
+      <c r="BP6" s="3"/>
+      <c r="BQ6" s="3"/>
+      <c r="BR6" s="3"/>
+      <c r="BS6" s="3"/>
+      <c r="BT6" s="3"/>
+      <c r="BU6" s="3"/>
+      <c r="BV6" s="3"/>
+      <c r="BW6" s="3"/>
+      <c r="BX6" s="3"/>
+      <c r="BY6" s="3"/>
+      <c r="BZ6" s="3"/>
+      <c r="CA6" s="3"/>
+      <c r="CB6" s="3"/>
+      <c r="CC6" s="3"/>
+      <c r="CD6" s="3"/>
+      <c r="CE6" s="3"/>
+      <c r="CF6" s="3"/>
+      <c r="CG6" s="3"/>
+      <c r="CH6" s="3"/>
+      <c r="CI6" s="3"/>
+      <c r="CJ6" s="5"/>
+      <c r="CK6" s="3"/>
+      <c r="CL6" s="3"/>
+      <c r="CM6" s="3"/>
+      <c r="CN6" s="3"/>
+      <c r="CO6" s="3"/>
+      <c r="CP6" s="3"/>
+      <c r="CQ6" s="3"/>
+      <c r="CR6" s="3"/>
+      <c r="CS6" s="3"/>
+      <c r="CT6" s="3"/>
+      <c r="CU6" s="3"/>
+      <c r="CV6" s="3"/>
+      <c r="CW6" s="3"/>
+      <c r="CX6" s="3"/>
+      <c r="CY6" s="3"/>
+      <c r="CZ6" s="3"/>
+      <c r="DA6" s="3"/>
+      <c r="DB6" s="3"/>
+      <c r="DC6" s="3"/>
+      <c r="DD6" s="3"/>
+      <c r="DE6" s="3"/>
+      <c r="DF6" s="3"/>
+      <c r="DG6" s="3"/>
+      <c r="DH6" s="3"/>
+      <c r="DI6" s="3"/>
+      <c r="DJ6" s="3"/>
+      <c r="DK6" s="3"/>
+      <c r="DL6" s="3"/>
+      <c r="DM6" s="3"/>
+      <c r="DN6" s="3"/>
+      <c r="DO6" s="3"/>
+      <c r="DP6" s="3"/>
+      <c r="DQ6" s="3"/>
+      <c r="DR6" s="3"/>
+      <c r="DS6" s="3"/>
+      <c r="DT6" s="3"/>
     </row>
     <row r="7" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -1867,7 +1878,7 @@
       <c r="I7" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K7" t="s">
@@ -1981,81 +1992,84 @@
       <c r="AU7" t="s">
         <v>31</v>
       </c>
-      <c r="AV7" s="2"/>
-      <c r="AW7" s="2"/>
-      <c r="AX7" s="2"/>
-      <c r="BA7" s="5"/>
-      <c r="BB7" s="5"/>
-      <c r="BC7" s="5"/>
-      <c r="BD7" s="5"/>
-      <c r="BE7" s="5"/>
-      <c r="BF7" s="5"/>
-      <c r="BG7" s="5"/>
-      <c r="BH7" s="5"/>
-      <c r="BI7" s="5"/>
-      <c r="BJ7" s="5"/>
-      <c r="BK7" s="5"/>
-      <c r="BL7" s="5"/>
-      <c r="BM7" s="5"/>
-      <c r="BN7" s="5"/>
-      <c r="BO7" s="5"/>
-      <c r="BP7" s="5"/>
-      <c r="BQ7" s="5"/>
-      <c r="BR7" s="5"/>
-      <c r="BS7" s="5"/>
-      <c r="BT7" s="5"/>
-      <c r="BU7" s="5"/>
-      <c r="BV7" s="5"/>
-      <c r="BW7" s="5"/>
-      <c r="BX7" s="5"/>
-      <c r="BY7" s="5"/>
-      <c r="BZ7" s="5"/>
-      <c r="CA7" s="5"/>
-      <c r="CB7" s="5"/>
-      <c r="CC7" s="5"/>
-      <c r="CD7" s="5"/>
-      <c r="CE7" s="5"/>
-      <c r="CF7" s="5"/>
-      <c r="CG7" s="5"/>
-      <c r="CH7" s="5"/>
-      <c r="CI7" s="5"/>
-      <c r="CJ7" s="6"/>
-      <c r="CK7" s="5"/>
-      <c r="CL7" s="5"/>
-      <c r="CM7" s="5"/>
-      <c r="CN7" s="5"/>
-      <c r="CO7" s="5"/>
-      <c r="CP7" s="5"/>
-      <c r="CQ7" s="5"/>
-      <c r="CR7" s="5"/>
-      <c r="CS7" s="5"/>
-      <c r="CT7" s="5"/>
-      <c r="CU7" s="5"/>
-      <c r="CV7" s="5"/>
-      <c r="CW7" s="5"/>
-      <c r="CX7" s="5"/>
-      <c r="CY7" s="5"/>
-      <c r="CZ7" s="5"/>
-      <c r="DA7" s="5"/>
-      <c r="DB7" s="5"/>
-      <c r="DC7" s="5"/>
-      <c r="DD7" s="5"/>
-      <c r="DE7" s="5"/>
-      <c r="DF7" s="5"/>
-      <c r="DG7" s="5"/>
-      <c r="DH7" s="5"/>
-      <c r="DI7" s="5"/>
-      <c r="DJ7" s="5"/>
-      <c r="DK7" s="5"/>
-      <c r="DL7" s="5"/>
-      <c r="DM7" s="5"/>
-      <c r="DN7" s="5"/>
-      <c r="DO7" s="5"/>
-      <c r="DP7" s="5"/>
-      <c r="DQ7" s="5"/>
-      <c r="DR7" s="5"/>
-      <c r="DS7" s="5"/>
-      <c r="DT7" s="5"/>
+      <c r="AV7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW7" s="3"/>
+      <c r="AX7" s="3"/>
+      <c r="AY7" s="3"/>
+      <c r="BA7" s="3"/>
+      <c r="BB7" s="3"/>
+      <c r="BC7" s="3"/>
+      <c r="BD7" s="3"/>
+      <c r="BE7" s="3"/>
+      <c r="BF7" s="3"/>
+      <c r="BG7" s="3"/>
+      <c r="BH7" s="3"/>
+      <c r="BI7" s="3"/>
+      <c r="BJ7" s="3"/>
+      <c r="BK7" s="3"/>
+      <c r="BL7" s="3"/>
+      <c r="BM7" s="3"/>
+      <c r="BN7" s="3"/>
+      <c r="BO7" s="3"/>
+      <c r="BP7" s="3"/>
+      <c r="BQ7" s="3"/>
+      <c r="BR7" s="3"/>
+      <c r="BS7" s="3"/>
+      <c r="BT7" s="3"/>
+      <c r="BU7" s="3"/>
+      <c r="BV7" s="3"/>
+      <c r="BW7" s="3"/>
+      <c r="BX7" s="3"/>
+      <c r="BY7" s="3"/>
+      <c r="BZ7" s="3"/>
+      <c r="CA7" s="3"/>
+      <c r="CB7" s="3"/>
+      <c r="CC7" s="3"/>
+      <c r="CD7" s="3"/>
+      <c r="CE7" s="3"/>
+      <c r="CF7" s="3"/>
+      <c r="CG7" s="3"/>
+      <c r="CH7" s="3"/>
+      <c r="CI7" s="3"/>
+      <c r="CJ7" s="4"/>
+      <c r="CK7" s="3"/>
+      <c r="CL7" s="3"/>
+      <c r="CM7" s="3"/>
+      <c r="CN7" s="3"/>
+      <c r="CO7" s="3"/>
+      <c r="CP7" s="3"/>
+      <c r="CQ7" s="3"/>
+      <c r="CR7" s="3"/>
+      <c r="CS7" s="3"/>
+      <c r="CT7" s="3"/>
+      <c r="CU7" s="3"/>
+      <c r="CV7" s="3"/>
+      <c r="CW7" s="3"/>
+      <c r="CX7" s="3"/>
+      <c r="CY7" s="3"/>
+      <c r="CZ7" s="3"/>
+      <c r="DA7" s="3"/>
+      <c r="DB7" s="3"/>
+      <c r="DC7" s="3"/>
+      <c r="DD7" s="3"/>
+      <c r="DE7" s="3"/>
+      <c r="DF7" s="3"/>
+      <c r="DG7" s="3"/>
+      <c r="DH7" s="3"/>
+      <c r="DI7" s="3"/>
+      <c r="DJ7" s="3"/>
+      <c r="DK7" s="3"/>
+      <c r="DL7" s="3"/>
+      <c r="DM7" s="3"/>
+      <c r="DN7" s="3"/>
+      <c r="DO7" s="3"/>
+      <c r="DP7" s="3"/>
+      <c r="DQ7" s="3"/>
+      <c r="DR7" s="3"/>
+      <c r="DS7" s="3"/>
+      <c r="DT7" s="3"/>
     </row>
     <row r="8" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -2086,7 +2100,7 @@
       <c r="I8" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K8" t="s">
@@ -2200,81 +2214,84 @@
       <c r="AU8" t="s">
         <v>31</v>
       </c>
-      <c r="AV8" s="2"/>
-      <c r="AW8" s="2"/>
-      <c r="AX8" s="2"/>
-      <c r="BA8" s="5"/>
-      <c r="BB8" s="5"/>
-      <c r="BC8" s="5"/>
-      <c r="BD8" s="5"/>
-      <c r="BE8" s="5"/>
-      <c r="BF8" s="5"/>
-      <c r="BG8" s="5"/>
-      <c r="BH8" s="5"/>
-      <c r="BI8" s="5"/>
-      <c r="BJ8" s="5"/>
-      <c r="BK8" s="5"/>
-      <c r="BL8" s="5"/>
-      <c r="BM8" s="5"/>
-      <c r="BN8" s="5"/>
-      <c r="BO8" s="5"/>
-      <c r="BP8" s="5"/>
-      <c r="BQ8" s="5"/>
-      <c r="BR8" s="5"/>
-      <c r="BS8" s="5"/>
-      <c r="BT8" s="5"/>
-      <c r="BU8" s="5"/>
-      <c r="BV8" s="5"/>
-      <c r="BW8" s="5"/>
-      <c r="BX8" s="5"/>
-      <c r="BY8" s="5"/>
-      <c r="BZ8" s="5"/>
-      <c r="CA8" s="5"/>
-      <c r="CB8" s="5"/>
-      <c r="CC8" s="5"/>
-      <c r="CD8" s="5"/>
-      <c r="CE8" s="5"/>
-      <c r="CF8" s="5"/>
-      <c r="CG8" s="5"/>
-      <c r="CH8" s="5"/>
-      <c r="CI8" s="5"/>
-      <c r="CJ8" s="5"/>
-      <c r="CK8" s="5"/>
-      <c r="CL8" s="5"/>
-      <c r="CM8" s="5"/>
-      <c r="CN8" s="5"/>
-      <c r="CO8" s="5"/>
-      <c r="CP8" s="5"/>
-      <c r="CQ8" s="5"/>
-      <c r="CR8" s="5"/>
-      <c r="CS8" s="5"/>
-      <c r="CT8" s="5"/>
-      <c r="CU8" s="5"/>
-      <c r="CV8" s="5"/>
-      <c r="CW8" s="5"/>
-      <c r="CX8" s="5"/>
-      <c r="CY8" s="5"/>
-      <c r="CZ8" s="5"/>
-      <c r="DA8" s="5"/>
-      <c r="DB8" s="5"/>
-      <c r="DC8" s="5"/>
-      <c r="DD8" s="5"/>
-      <c r="DE8" s="5"/>
-      <c r="DF8" s="5"/>
-      <c r="DG8" s="5"/>
-      <c r="DH8" s="5"/>
-      <c r="DI8" s="5"/>
-      <c r="DJ8" s="5"/>
-      <c r="DK8" s="5"/>
-      <c r="DL8" s="5"/>
-      <c r="DM8" s="5"/>
-      <c r="DN8" s="5"/>
-      <c r="DO8" s="5"/>
-      <c r="DP8" s="5"/>
-      <c r="DQ8" s="5"/>
-      <c r="DR8" s="5"/>
-      <c r="DS8" s="5"/>
-      <c r="DT8" s="5"/>
+      <c r="AV8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW8" s="3"/>
+      <c r="AX8" s="3"/>
+      <c r="AY8" s="3"/>
+      <c r="BA8" s="3"/>
+      <c r="BB8" s="3"/>
+      <c r="BC8" s="3"/>
+      <c r="BD8" s="3"/>
+      <c r="BE8" s="3"/>
+      <c r="BF8" s="3"/>
+      <c r="BG8" s="3"/>
+      <c r="BH8" s="3"/>
+      <c r="BI8" s="3"/>
+      <c r="BJ8" s="3"/>
+      <c r="BK8" s="3"/>
+      <c r="BL8" s="3"/>
+      <c r="BM8" s="3"/>
+      <c r="BN8" s="3"/>
+      <c r="BO8" s="3"/>
+      <c r="BP8" s="3"/>
+      <c r="BQ8" s="3"/>
+      <c r="BR8" s="3"/>
+      <c r="BS8" s="3"/>
+      <c r="BT8" s="3"/>
+      <c r="BU8" s="3"/>
+      <c r="BV8" s="3"/>
+      <c r="BW8" s="3"/>
+      <c r="BX8" s="3"/>
+      <c r="BY8" s="3"/>
+      <c r="BZ8" s="3"/>
+      <c r="CA8" s="3"/>
+      <c r="CB8" s="3"/>
+      <c r="CC8" s="3"/>
+      <c r="CD8" s="3"/>
+      <c r="CE8" s="3"/>
+      <c r="CF8" s="3"/>
+      <c r="CG8" s="3"/>
+      <c r="CH8" s="3"/>
+      <c r="CI8" s="3"/>
+      <c r="CJ8" s="3"/>
+      <c r="CK8" s="3"/>
+      <c r="CL8" s="3"/>
+      <c r="CM8" s="3"/>
+      <c r="CN8" s="3"/>
+      <c r="CO8" s="3"/>
+      <c r="CP8" s="3"/>
+      <c r="CQ8" s="3"/>
+      <c r="CR8" s="3"/>
+      <c r="CS8" s="3"/>
+      <c r="CT8" s="3"/>
+      <c r="CU8" s="3"/>
+      <c r="CV8" s="3"/>
+      <c r="CW8" s="3"/>
+      <c r="CX8" s="3"/>
+      <c r="CY8" s="3"/>
+      <c r="CZ8" s="3"/>
+      <c r="DA8" s="3"/>
+      <c r="DB8" s="3"/>
+      <c r="DC8" s="3"/>
+      <c r="DD8" s="3"/>
+      <c r="DE8" s="3"/>
+      <c r="DF8" s="3"/>
+      <c r="DG8" s="3"/>
+      <c r="DH8" s="3"/>
+      <c r="DI8" s="3"/>
+      <c r="DJ8" s="3"/>
+      <c r="DK8" s="3"/>
+      <c r="DL8" s="3"/>
+      <c r="DM8" s="3"/>
+      <c r="DN8" s="3"/>
+      <c r="DO8" s="3"/>
+      <c r="DP8" s="3"/>
+      <c r="DQ8" s="3"/>
+      <c r="DR8" s="3"/>
+      <c r="DS8" s="3"/>
+      <c r="DT8" s="3"/>
     </row>
     <row r="9" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -2305,7 +2322,7 @@
       <c r="I9" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K9" t="s">
@@ -2419,81 +2436,84 @@
       <c r="AU9" t="s">
         <v>32</v>
       </c>
-      <c r="AV9" s="2"/>
-      <c r="AW9" s="2"/>
-      <c r="AX9" s="2"/>
-      <c r="BA9" s="5"/>
-      <c r="BB9" s="5"/>
-      <c r="BC9" s="5"/>
-      <c r="BD9" s="5"/>
-      <c r="BE9" s="5"/>
-      <c r="BF9" s="5"/>
-      <c r="BG9" s="5"/>
-      <c r="BH9" s="5"/>
-      <c r="BI9" s="5"/>
-      <c r="BJ9" s="5"/>
-      <c r="BK9" s="5"/>
-      <c r="BL9" s="5"/>
-      <c r="BM9" s="5"/>
-      <c r="BN9" s="5"/>
-      <c r="BO9" s="5"/>
-      <c r="BP9" s="5"/>
-      <c r="BQ9" s="5"/>
-      <c r="BR9" s="5"/>
-      <c r="BS9" s="5"/>
-      <c r="BT9" s="5"/>
-      <c r="BU9" s="5"/>
-      <c r="BV9" s="5"/>
-      <c r="BW9" s="5"/>
-      <c r="BX9" s="5"/>
-      <c r="BY9" s="5"/>
-      <c r="BZ9" s="5"/>
-      <c r="CA9" s="5"/>
-      <c r="CB9" s="5"/>
-      <c r="CC9" s="5"/>
-      <c r="CD9" s="5"/>
-      <c r="CE9" s="5"/>
-      <c r="CF9" s="5"/>
-      <c r="CG9" s="5"/>
-      <c r="CH9" s="5"/>
-      <c r="CI9" s="5"/>
-      <c r="CJ9" s="5"/>
-      <c r="CK9" s="5"/>
-      <c r="CL9" s="5"/>
-      <c r="CM9" s="5"/>
-      <c r="CN9" s="5"/>
-      <c r="CO9" s="5"/>
-      <c r="CP9" s="5"/>
-      <c r="CQ9" s="5"/>
-      <c r="CR9" s="5"/>
-      <c r="CS9" s="5"/>
-      <c r="CT9" s="5"/>
-      <c r="CU9" s="5"/>
-      <c r="CV9" s="5"/>
-      <c r="CW9" s="5"/>
-      <c r="CX9" s="5"/>
-      <c r="CY9" s="5"/>
-      <c r="CZ9" s="5"/>
-      <c r="DA9" s="5"/>
-      <c r="DB9" s="5"/>
-      <c r="DC9" s="5"/>
-      <c r="DD9" s="5"/>
-      <c r="DE9" s="5"/>
-      <c r="DF9" s="5"/>
-      <c r="DG9" s="5"/>
-      <c r="DH9" s="5"/>
-      <c r="DI9" s="5"/>
-      <c r="DJ9" s="5"/>
-      <c r="DK9" s="5"/>
-      <c r="DL9" s="5"/>
-      <c r="DM9" s="5"/>
-      <c r="DN9" s="5"/>
-      <c r="DO9" s="5"/>
-      <c r="DP9" s="5"/>
-      <c r="DQ9" s="5"/>
-      <c r="DR9" s="5"/>
-      <c r="DS9" s="5"/>
-      <c r="DT9" s="5"/>
+      <c r="AV9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW9" s="3"/>
+      <c r="AX9" s="3"/>
+      <c r="AY9" s="3"/>
+      <c r="BA9" s="3"/>
+      <c r="BB9" s="3"/>
+      <c r="BC9" s="3"/>
+      <c r="BD9" s="3"/>
+      <c r="BE9" s="3"/>
+      <c r="BF9" s="3"/>
+      <c r="BG9" s="3"/>
+      <c r="BH9" s="3"/>
+      <c r="BI9" s="3"/>
+      <c r="BJ9" s="3"/>
+      <c r="BK9" s="3"/>
+      <c r="BL9" s="3"/>
+      <c r="BM9" s="3"/>
+      <c r="BN9" s="3"/>
+      <c r="BO9" s="3"/>
+      <c r="BP9" s="3"/>
+      <c r="BQ9" s="3"/>
+      <c r="BR9" s="3"/>
+      <c r="BS9" s="3"/>
+      <c r="BT9" s="3"/>
+      <c r="BU9" s="3"/>
+      <c r="BV9" s="3"/>
+      <c r="BW9" s="3"/>
+      <c r="BX9" s="3"/>
+      <c r="BY9" s="3"/>
+      <c r="BZ9" s="3"/>
+      <c r="CA9" s="3"/>
+      <c r="CB9" s="3"/>
+      <c r="CC9" s="3"/>
+      <c r="CD9" s="3"/>
+      <c r="CE9" s="3"/>
+      <c r="CF9" s="3"/>
+      <c r="CG9" s="3"/>
+      <c r="CH9" s="3"/>
+      <c r="CI9" s="3"/>
+      <c r="CJ9" s="3"/>
+      <c r="CK9" s="3"/>
+      <c r="CL9" s="3"/>
+      <c r="CM9" s="3"/>
+      <c r="CN9" s="3"/>
+      <c r="CO9" s="3"/>
+      <c r="CP9" s="3"/>
+      <c r="CQ9" s="3"/>
+      <c r="CR9" s="3"/>
+      <c r="CS9" s="3"/>
+      <c r="CT9" s="3"/>
+      <c r="CU9" s="3"/>
+      <c r="CV9" s="3"/>
+      <c r="CW9" s="3"/>
+      <c r="CX9" s="3"/>
+      <c r="CY9" s="3"/>
+      <c r="CZ9" s="3"/>
+      <c r="DA9" s="3"/>
+      <c r="DB9" s="3"/>
+      <c r="DC9" s="3"/>
+      <c r="DD9" s="3"/>
+      <c r="DE9" s="3"/>
+      <c r="DF9" s="3"/>
+      <c r="DG9" s="3"/>
+      <c r="DH9" s="3"/>
+      <c r="DI9" s="3"/>
+      <c r="DJ9" s="3"/>
+      <c r="DK9" s="3"/>
+      <c r="DL9" s="3"/>
+      <c r="DM9" s="3"/>
+      <c r="DN9" s="3"/>
+      <c r="DO9" s="3"/>
+      <c r="DP9" s="3"/>
+      <c r="DQ9" s="3"/>
+      <c r="DR9" s="3"/>
+      <c r="DS9" s="3"/>
+      <c r="DT9" s="3"/>
     </row>
     <row r="10" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -2524,7 +2544,7 @@
       <c r="I10" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K10" t="s">
@@ -2638,81 +2658,84 @@
       <c r="AU10" t="s">
         <v>32</v>
       </c>
-      <c r="AV10" s="2"/>
-      <c r="AW10" s="2"/>
-      <c r="AX10" s="2"/>
-      <c r="BA10" s="5"/>
-      <c r="BB10" s="5"/>
-      <c r="BC10" s="5"/>
-      <c r="BD10" s="5"/>
-      <c r="BE10" s="5"/>
-      <c r="BF10" s="5"/>
-      <c r="BG10" s="5"/>
-      <c r="BH10" s="5"/>
-      <c r="BI10" s="5"/>
-      <c r="BJ10" s="5"/>
-      <c r="BK10" s="5"/>
-      <c r="BL10" s="5"/>
-      <c r="BM10" s="5"/>
-      <c r="BN10" s="5"/>
-      <c r="BO10" s="5"/>
-      <c r="BP10" s="5"/>
-      <c r="BQ10" s="5"/>
-      <c r="BR10" s="5"/>
-      <c r="BS10" s="5"/>
-      <c r="BT10" s="5"/>
-      <c r="BU10" s="5"/>
-      <c r="BV10" s="5"/>
-      <c r="BW10" s="5"/>
-      <c r="BX10" s="5"/>
-      <c r="BY10" s="5"/>
-      <c r="BZ10" s="5"/>
-      <c r="CA10" s="5"/>
-      <c r="CB10" s="5"/>
-      <c r="CC10" s="5"/>
-      <c r="CD10" s="5"/>
-      <c r="CE10" s="5"/>
-      <c r="CF10" s="5"/>
-      <c r="CG10" s="5"/>
-      <c r="CH10" s="5"/>
-      <c r="CI10" s="5"/>
-      <c r="CJ10" s="5"/>
-      <c r="CK10" s="5"/>
-      <c r="CL10" s="5"/>
-      <c r="CM10" s="5"/>
-      <c r="CN10" s="5"/>
-      <c r="CO10" s="5"/>
-      <c r="CP10" s="5"/>
-      <c r="CQ10" s="5"/>
-      <c r="CR10" s="5"/>
-      <c r="CS10" s="5"/>
-      <c r="CT10" s="5"/>
-      <c r="CU10" s="5"/>
-      <c r="CV10" s="5"/>
-      <c r="CW10" s="5"/>
-      <c r="CX10" s="5"/>
-      <c r="CY10" s="5"/>
-      <c r="CZ10" s="5"/>
-      <c r="DA10" s="5"/>
-      <c r="DB10" s="5"/>
-      <c r="DC10" s="5"/>
-      <c r="DD10" s="5"/>
-      <c r="DE10" s="5"/>
-      <c r="DF10" s="5"/>
-      <c r="DG10" s="5"/>
-      <c r="DH10" s="5"/>
-      <c r="DI10" s="5"/>
-      <c r="DJ10" s="5"/>
-      <c r="DK10" s="5"/>
-      <c r="DL10" s="5"/>
-      <c r="DM10" s="5"/>
-      <c r="DN10" s="5"/>
-      <c r="DO10" s="5"/>
-      <c r="DP10" s="5"/>
-      <c r="DQ10" s="5"/>
-      <c r="DR10" s="5"/>
-      <c r="DS10" s="5"/>
-      <c r="DT10" s="5"/>
+      <c r="AV10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW10" s="3"/>
+      <c r="AX10" s="3"/>
+      <c r="AY10" s="3"/>
+      <c r="BA10" s="3"/>
+      <c r="BB10" s="3"/>
+      <c r="BC10" s="3"/>
+      <c r="BD10" s="3"/>
+      <c r="BE10" s="3"/>
+      <c r="BF10" s="3"/>
+      <c r="BG10" s="3"/>
+      <c r="BH10" s="3"/>
+      <c r="BI10" s="3"/>
+      <c r="BJ10" s="3"/>
+      <c r="BK10" s="3"/>
+      <c r="BL10" s="3"/>
+      <c r="BM10" s="3"/>
+      <c r="BN10" s="3"/>
+      <c r="BO10" s="3"/>
+      <c r="BP10" s="3"/>
+      <c r="BQ10" s="3"/>
+      <c r="BR10" s="3"/>
+      <c r="BS10" s="3"/>
+      <c r="BT10" s="3"/>
+      <c r="BU10" s="3"/>
+      <c r="BV10" s="3"/>
+      <c r="BW10" s="3"/>
+      <c r="BX10" s="3"/>
+      <c r="BY10" s="3"/>
+      <c r="BZ10" s="3"/>
+      <c r="CA10" s="3"/>
+      <c r="CB10" s="3"/>
+      <c r="CC10" s="3"/>
+      <c r="CD10" s="3"/>
+      <c r="CE10" s="3"/>
+      <c r="CF10" s="3"/>
+      <c r="CG10" s="3"/>
+      <c r="CH10" s="3"/>
+      <c r="CI10" s="3"/>
+      <c r="CJ10" s="3"/>
+      <c r="CK10" s="3"/>
+      <c r="CL10" s="3"/>
+      <c r="CM10" s="3"/>
+      <c r="CN10" s="3"/>
+      <c r="CO10" s="3"/>
+      <c r="CP10" s="3"/>
+      <c r="CQ10" s="3"/>
+      <c r="CR10" s="3"/>
+      <c r="CS10" s="3"/>
+      <c r="CT10" s="3"/>
+      <c r="CU10" s="3"/>
+      <c r="CV10" s="3"/>
+      <c r="CW10" s="3"/>
+      <c r="CX10" s="3"/>
+      <c r="CY10" s="3"/>
+      <c r="CZ10" s="3"/>
+      <c r="DA10" s="3"/>
+      <c r="DB10" s="3"/>
+      <c r="DC10" s="3"/>
+      <c r="DD10" s="3"/>
+      <c r="DE10" s="3"/>
+      <c r="DF10" s="3"/>
+      <c r="DG10" s="3"/>
+      <c r="DH10" s="3"/>
+      <c r="DI10" s="3"/>
+      <c r="DJ10" s="3"/>
+      <c r="DK10" s="3"/>
+      <c r="DL10" s="3"/>
+      <c r="DM10" s="3"/>
+      <c r="DN10" s="3"/>
+      <c r="DO10" s="3"/>
+      <c r="DP10" s="3"/>
+      <c r="DQ10" s="3"/>
+      <c r="DR10" s="3"/>
+      <c r="DS10" s="3"/>
+      <c r="DT10" s="3"/>
     </row>
     <row r="11" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -2734,7 +2757,7 @@
       <c r="I11" t="s">
         <v>31</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K11" t="s">
@@ -2848,81 +2871,84 @@
       <c r="AU11" t="s">
         <v>31</v>
       </c>
-      <c r="AV11" s="2"/>
-      <c r="AW11" s="2"/>
-      <c r="AX11" s="2"/>
-      <c r="BA11" s="5"/>
-      <c r="BB11" s="5"/>
-      <c r="BC11" s="5"/>
-      <c r="BD11" s="5"/>
-      <c r="BE11" s="5"/>
-      <c r="BF11" s="5"/>
-      <c r="BG11" s="5"/>
-      <c r="BH11" s="5"/>
-      <c r="BI11" s="5"/>
-      <c r="BJ11" s="5"/>
-      <c r="BK11" s="5"/>
-      <c r="BL11" s="5"/>
-      <c r="BM11" s="5"/>
-      <c r="BN11" s="5"/>
-      <c r="BO11" s="5"/>
-      <c r="BP11" s="5"/>
-      <c r="BQ11" s="5"/>
-      <c r="BR11" s="5"/>
-      <c r="BS11" s="5"/>
-      <c r="BT11" s="5"/>
-      <c r="BU11" s="5"/>
-      <c r="BV11" s="5"/>
-      <c r="BW11" s="5"/>
-      <c r="BX11" s="5"/>
-      <c r="BY11" s="5"/>
-      <c r="BZ11" s="5"/>
-      <c r="CA11" s="5"/>
-      <c r="CB11" s="5"/>
-      <c r="CC11" s="5"/>
-      <c r="CD11" s="5"/>
-      <c r="CE11" s="5"/>
-      <c r="CF11" s="5"/>
-      <c r="CG11" s="5"/>
-      <c r="CH11" s="5"/>
-      <c r="CI11" s="5"/>
-      <c r="CJ11" s="5"/>
-      <c r="CK11" s="5"/>
-      <c r="CL11" s="5"/>
-      <c r="CM11" s="5"/>
-      <c r="CN11" s="5"/>
-      <c r="CO11" s="5"/>
-      <c r="CP11" s="5"/>
-      <c r="CQ11" s="5"/>
-      <c r="CR11" s="5"/>
-      <c r="CS11" s="5"/>
-      <c r="CT11" s="5"/>
-      <c r="CU11" s="5"/>
-      <c r="CV11" s="5"/>
-      <c r="CW11" s="5"/>
-      <c r="CX11" s="5"/>
-      <c r="CY11" s="5"/>
-      <c r="CZ11" s="5"/>
-      <c r="DA11" s="5"/>
-      <c r="DB11" s="5"/>
-      <c r="DC11" s="5"/>
-      <c r="DD11" s="5"/>
-      <c r="DE11" s="5"/>
-      <c r="DF11" s="5"/>
-      <c r="DG11" s="5"/>
-      <c r="DH11" s="5"/>
-      <c r="DI11" s="5"/>
-      <c r="DJ11" s="5"/>
-      <c r="DK11" s="5"/>
-      <c r="DL11" s="5"/>
-      <c r="DM11" s="5"/>
-      <c r="DN11" s="5"/>
-      <c r="DO11" s="5"/>
-      <c r="DP11" s="5"/>
-      <c r="DQ11" s="5"/>
-      <c r="DR11" s="5"/>
-      <c r="DS11" s="5"/>
-      <c r="DT11" s="5"/>
+      <c r="AV11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW11" s="3"/>
+      <c r="AX11" s="3"/>
+      <c r="AY11" s="3"/>
+      <c r="BA11" s="3"/>
+      <c r="BB11" s="3"/>
+      <c r="BC11" s="3"/>
+      <c r="BD11" s="3"/>
+      <c r="BE11" s="3"/>
+      <c r="BF11" s="3"/>
+      <c r="BG11" s="3"/>
+      <c r="BH11" s="3"/>
+      <c r="BI11" s="3"/>
+      <c r="BJ11" s="3"/>
+      <c r="BK11" s="3"/>
+      <c r="BL11" s="3"/>
+      <c r="BM11" s="3"/>
+      <c r="BN11" s="3"/>
+      <c r="BO11" s="3"/>
+      <c r="BP11" s="3"/>
+      <c r="BQ11" s="3"/>
+      <c r="BR11" s="3"/>
+      <c r="BS11" s="3"/>
+      <c r="BT11" s="3"/>
+      <c r="BU11" s="3"/>
+      <c r="BV11" s="3"/>
+      <c r="BW11" s="3"/>
+      <c r="BX11" s="3"/>
+      <c r="BY11" s="3"/>
+      <c r="BZ11" s="3"/>
+      <c r="CA11" s="3"/>
+      <c r="CB11" s="3"/>
+      <c r="CC11" s="3"/>
+      <c r="CD11" s="3"/>
+      <c r="CE11" s="3"/>
+      <c r="CF11" s="3"/>
+      <c r="CG11" s="3"/>
+      <c r="CH11" s="3"/>
+      <c r="CI11" s="3"/>
+      <c r="CJ11" s="3"/>
+      <c r="CK11" s="3"/>
+      <c r="CL11" s="3"/>
+      <c r="CM11" s="3"/>
+      <c r="CN11" s="3"/>
+      <c r="CO11" s="3"/>
+      <c r="CP11" s="3"/>
+      <c r="CQ11" s="3"/>
+      <c r="CR11" s="3"/>
+      <c r="CS11" s="3"/>
+      <c r="CT11" s="3"/>
+      <c r="CU11" s="3"/>
+      <c r="CV11" s="3"/>
+      <c r="CW11" s="3"/>
+      <c r="CX11" s="3"/>
+      <c r="CY11" s="3"/>
+      <c r="CZ11" s="3"/>
+      <c r="DA11" s="3"/>
+      <c r="DB11" s="3"/>
+      <c r="DC11" s="3"/>
+      <c r="DD11" s="3"/>
+      <c r="DE11" s="3"/>
+      <c r="DF11" s="3"/>
+      <c r="DG11" s="3"/>
+      <c r="DH11" s="3"/>
+      <c r="DI11" s="3"/>
+      <c r="DJ11" s="3"/>
+      <c r="DK11" s="3"/>
+      <c r="DL11" s="3"/>
+      <c r="DM11" s="3"/>
+      <c r="DN11" s="3"/>
+      <c r="DO11" s="3"/>
+      <c r="DP11" s="3"/>
+      <c r="DQ11" s="3"/>
+      <c r="DR11" s="3"/>
+      <c r="DS11" s="3"/>
+      <c r="DT11" s="3"/>
     </row>
     <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -2953,7 +2979,7 @@
       <c r="I12" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K12" t="s">
@@ -3067,81 +3093,84 @@
       <c r="AU12" t="s">
         <v>31</v>
       </c>
-      <c r="AV12" s="2"/>
-      <c r="AW12" s="2"/>
-      <c r="AX12" s="2"/>
-      <c r="BA12" s="5"/>
-      <c r="BB12" s="5"/>
-      <c r="BC12" s="5"/>
-      <c r="BD12" s="5"/>
-      <c r="BE12" s="5"/>
-      <c r="BF12" s="5"/>
-      <c r="BG12" s="5"/>
-      <c r="BH12" s="5"/>
-      <c r="BI12" s="5"/>
-      <c r="BJ12" s="5"/>
-      <c r="BK12" s="5"/>
-      <c r="BL12" s="5"/>
-      <c r="BM12" s="5"/>
-      <c r="BN12" s="5"/>
-      <c r="BO12" s="5"/>
-      <c r="BP12" s="5"/>
-      <c r="BQ12" s="5"/>
-      <c r="BR12" s="5"/>
-      <c r="BS12" s="5"/>
-      <c r="BT12" s="5"/>
-      <c r="BU12" s="5"/>
-      <c r="BV12" s="5"/>
-      <c r="BW12" s="5"/>
-      <c r="BX12" s="5"/>
-      <c r="BY12" s="5"/>
-      <c r="BZ12" s="5"/>
-      <c r="CA12" s="5"/>
-      <c r="CB12" s="5"/>
-      <c r="CC12" s="5"/>
-      <c r="CD12" s="5"/>
-      <c r="CE12" s="5"/>
-      <c r="CF12" s="5"/>
-      <c r="CG12" s="5"/>
-      <c r="CH12" s="5"/>
-      <c r="CI12" s="5"/>
-      <c r="CJ12" s="5"/>
-      <c r="CK12" s="5"/>
-      <c r="CL12" s="5"/>
-      <c r="CM12" s="5"/>
-      <c r="CN12" s="5"/>
-      <c r="CO12" s="5"/>
-      <c r="CP12" s="5"/>
-      <c r="CQ12" s="5"/>
-      <c r="CR12" s="5"/>
-      <c r="CS12" s="5"/>
-      <c r="CT12" s="5"/>
-      <c r="CU12" s="5"/>
-      <c r="CV12" s="5"/>
-      <c r="CW12" s="5"/>
-      <c r="CX12" s="5"/>
-      <c r="CY12" s="5"/>
-      <c r="CZ12" s="5"/>
-      <c r="DA12" s="5"/>
-      <c r="DB12" s="5"/>
-      <c r="DC12" s="5"/>
-      <c r="DD12" s="5"/>
-      <c r="DE12" s="5"/>
-      <c r="DF12" s="5"/>
-      <c r="DG12" s="5"/>
-      <c r="DH12" s="5"/>
-      <c r="DI12" s="5"/>
-      <c r="DJ12" s="5"/>
-      <c r="DK12" s="5"/>
-      <c r="DL12" s="5"/>
-      <c r="DM12" s="5"/>
-      <c r="DN12" s="5"/>
-      <c r="DO12" s="5"/>
-      <c r="DP12" s="5"/>
-      <c r="DQ12" s="5"/>
-      <c r="DR12" s="5"/>
-      <c r="DS12" s="5"/>
-      <c r="DT12" s="5"/>
+      <c r="AV12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW12" s="3"/>
+      <c r="AX12" s="3"/>
+      <c r="AY12" s="3"/>
+      <c r="BA12" s="3"/>
+      <c r="BB12" s="3"/>
+      <c r="BC12" s="3"/>
+      <c r="BD12" s="3"/>
+      <c r="BE12" s="3"/>
+      <c r="BF12" s="3"/>
+      <c r="BG12" s="3"/>
+      <c r="BH12" s="3"/>
+      <c r="BI12" s="3"/>
+      <c r="BJ12" s="3"/>
+      <c r="BK12" s="3"/>
+      <c r="BL12" s="3"/>
+      <c r="BM12" s="3"/>
+      <c r="BN12" s="3"/>
+      <c r="BO12" s="3"/>
+      <c r="BP12" s="3"/>
+      <c r="BQ12" s="3"/>
+      <c r="BR12" s="3"/>
+      <c r="BS12" s="3"/>
+      <c r="BT12" s="3"/>
+      <c r="BU12" s="3"/>
+      <c r="BV12" s="3"/>
+      <c r="BW12" s="3"/>
+      <c r="BX12" s="3"/>
+      <c r="BY12" s="3"/>
+      <c r="BZ12" s="3"/>
+      <c r="CA12" s="3"/>
+      <c r="CB12" s="3"/>
+      <c r="CC12" s="3"/>
+      <c r="CD12" s="3"/>
+      <c r="CE12" s="3"/>
+      <c r="CF12" s="3"/>
+      <c r="CG12" s="3"/>
+      <c r="CH12" s="3"/>
+      <c r="CI12" s="3"/>
+      <c r="CJ12" s="3"/>
+      <c r="CK12" s="3"/>
+      <c r="CL12" s="3"/>
+      <c r="CM12" s="3"/>
+      <c r="CN12" s="3"/>
+      <c r="CO12" s="3"/>
+      <c r="CP12" s="3"/>
+      <c r="CQ12" s="3"/>
+      <c r="CR12" s="3"/>
+      <c r="CS12" s="3"/>
+      <c r="CT12" s="3"/>
+      <c r="CU12" s="3"/>
+      <c r="CV12" s="3"/>
+      <c r="CW12" s="3"/>
+      <c r="CX12" s="3"/>
+      <c r="CY12" s="3"/>
+      <c r="CZ12" s="3"/>
+      <c r="DA12" s="3"/>
+      <c r="DB12" s="3"/>
+      <c r="DC12" s="3"/>
+      <c r="DD12" s="3"/>
+      <c r="DE12" s="3"/>
+      <c r="DF12" s="3"/>
+      <c r="DG12" s="3"/>
+      <c r="DH12" s="3"/>
+      <c r="DI12" s="3"/>
+      <c r="DJ12" s="3"/>
+      <c r="DK12" s="3"/>
+      <c r="DL12" s="3"/>
+      <c r="DM12" s="3"/>
+      <c r="DN12" s="3"/>
+      <c r="DO12" s="3"/>
+      <c r="DP12" s="3"/>
+      <c r="DQ12" s="3"/>
+      <c r="DR12" s="3"/>
+      <c r="DS12" s="3"/>
+      <c r="DT12" s="3"/>
     </row>
     <row r="13" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -3172,7 +3201,7 @@
       <c r="I13" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K13" t="s">
@@ -3286,81 +3315,84 @@
       <c r="AU13" t="s">
         <v>31</v>
       </c>
-      <c r="AV13" s="2"/>
-      <c r="AW13" s="2"/>
-      <c r="AX13" s="2"/>
-      <c r="BA13" s="5"/>
-      <c r="BB13" s="5"/>
-      <c r="BC13" s="5"/>
-      <c r="BD13" s="5"/>
-      <c r="BE13" s="5"/>
-      <c r="BF13" s="5"/>
-      <c r="BG13" s="5"/>
-      <c r="BH13" s="5"/>
-      <c r="BI13" s="5"/>
-      <c r="BJ13" s="5"/>
-      <c r="BK13" s="5"/>
-      <c r="BL13" s="5"/>
-      <c r="BM13" s="5"/>
-      <c r="BN13" s="5"/>
-      <c r="BO13" s="5"/>
-      <c r="BP13" s="5"/>
-      <c r="BQ13" s="5"/>
-      <c r="BR13" s="5"/>
-      <c r="BS13" s="5"/>
-      <c r="BT13" s="5"/>
-      <c r="BU13" s="5"/>
-      <c r="BV13" s="5"/>
-      <c r="BW13" s="5"/>
-      <c r="BX13" s="5"/>
-      <c r="BY13" s="5"/>
-      <c r="BZ13" s="5"/>
-      <c r="CA13" s="5"/>
-      <c r="CB13" s="5"/>
-      <c r="CC13" s="5"/>
-      <c r="CD13" s="5"/>
-      <c r="CE13" s="5"/>
-      <c r="CF13" s="5"/>
-      <c r="CG13" s="5"/>
-      <c r="CH13" s="5"/>
-      <c r="CI13" s="5"/>
-      <c r="CJ13" s="5"/>
-      <c r="CK13" s="5"/>
-      <c r="CL13" s="5"/>
-      <c r="CM13" s="5"/>
-      <c r="CN13" s="5"/>
-      <c r="CO13" s="5"/>
-      <c r="CP13" s="5"/>
-      <c r="CQ13" s="5"/>
-      <c r="CR13" s="5"/>
-      <c r="CS13" s="5"/>
-      <c r="CT13" s="5"/>
-      <c r="CU13" s="5"/>
-      <c r="CV13" s="5"/>
-      <c r="CW13" s="5"/>
-      <c r="CX13" s="5"/>
-      <c r="CY13" s="5"/>
-      <c r="CZ13" s="5"/>
-      <c r="DA13" s="5"/>
-      <c r="DB13" s="5"/>
-      <c r="DC13" s="5"/>
-      <c r="DD13" s="5"/>
-      <c r="DE13" s="5"/>
-      <c r="DF13" s="5"/>
-      <c r="DG13" s="5"/>
-      <c r="DH13" s="5"/>
-      <c r="DI13" s="5"/>
-      <c r="DJ13" s="5"/>
-      <c r="DK13" s="5"/>
-      <c r="DL13" s="5"/>
-      <c r="DM13" s="5"/>
-      <c r="DN13" s="5"/>
-      <c r="DO13" s="5"/>
-      <c r="DP13" s="5"/>
-      <c r="DQ13" s="5"/>
-      <c r="DR13" s="5"/>
-      <c r="DS13" s="5"/>
-      <c r="DT13" s="5"/>
+      <c r="AV13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW13" s="3"/>
+      <c r="AX13" s="3"/>
+      <c r="AY13" s="3"/>
+      <c r="BA13" s="3"/>
+      <c r="BB13" s="3"/>
+      <c r="BC13" s="3"/>
+      <c r="BD13" s="3"/>
+      <c r="BE13" s="3"/>
+      <c r="BF13" s="3"/>
+      <c r="BG13" s="3"/>
+      <c r="BH13" s="3"/>
+      <c r="BI13" s="3"/>
+      <c r="BJ13" s="3"/>
+      <c r="BK13" s="3"/>
+      <c r="BL13" s="3"/>
+      <c r="BM13" s="3"/>
+      <c r="BN13" s="3"/>
+      <c r="BO13" s="3"/>
+      <c r="BP13" s="3"/>
+      <c r="BQ13" s="3"/>
+      <c r="BR13" s="3"/>
+      <c r="BS13" s="3"/>
+      <c r="BT13" s="3"/>
+      <c r="BU13" s="3"/>
+      <c r="BV13" s="3"/>
+      <c r="BW13" s="3"/>
+      <c r="BX13" s="3"/>
+      <c r="BY13" s="3"/>
+      <c r="BZ13" s="3"/>
+      <c r="CA13" s="3"/>
+      <c r="CB13" s="3"/>
+      <c r="CC13" s="3"/>
+      <c r="CD13" s="3"/>
+      <c r="CE13" s="3"/>
+      <c r="CF13" s="3"/>
+      <c r="CG13" s="3"/>
+      <c r="CH13" s="3"/>
+      <c r="CI13" s="3"/>
+      <c r="CJ13" s="3"/>
+      <c r="CK13" s="3"/>
+      <c r="CL13" s="3"/>
+      <c r="CM13" s="3"/>
+      <c r="CN13" s="3"/>
+      <c r="CO13" s="3"/>
+      <c r="CP13" s="3"/>
+      <c r="CQ13" s="3"/>
+      <c r="CR13" s="3"/>
+      <c r="CS13" s="3"/>
+      <c r="CT13" s="3"/>
+      <c r="CU13" s="3"/>
+      <c r="CV13" s="3"/>
+      <c r="CW13" s="3"/>
+      <c r="CX13" s="3"/>
+      <c r="CY13" s="3"/>
+      <c r="CZ13" s="3"/>
+      <c r="DA13" s="3"/>
+      <c r="DB13" s="3"/>
+      <c r="DC13" s="3"/>
+      <c r="DD13" s="3"/>
+      <c r="DE13" s="3"/>
+      <c r="DF13" s="3"/>
+      <c r="DG13" s="3"/>
+      <c r="DH13" s="3"/>
+      <c r="DI13" s="3"/>
+      <c r="DJ13" s="3"/>
+      <c r="DK13" s="3"/>
+      <c r="DL13" s="3"/>
+      <c r="DM13" s="3"/>
+      <c r="DN13" s="3"/>
+      <c r="DO13" s="3"/>
+      <c r="DP13" s="3"/>
+      <c r="DQ13" s="3"/>
+      <c r="DR13" s="3"/>
+      <c r="DS13" s="3"/>
+      <c r="DT13" s="3"/>
     </row>
     <row r="14" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -3391,7 +3423,7 @@
       <c r="I14" t="s">
         <v>31</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K14" t="s">
@@ -3505,81 +3537,84 @@
       <c r="AU14" t="s">
         <v>31</v>
       </c>
-      <c r="AV14" s="2"/>
-      <c r="AW14" s="2"/>
-      <c r="AX14" s="2"/>
-      <c r="BA14" s="5"/>
-      <c r="BB14" s="5"/>
-      <c r="BC14" s="5"/>
-      <c r="BD14" s="5"/>
-      <c r="BE14" s="5"/>
-      <c r="BF14" s="5"/>
-      <c r="BG14" s="5"/>
-      <c r="BH14" s="5"/>
-      <c r="BI14" s="5"/>
-      <c r="BJ14" s="5"/>
-      <c r="BK14" s="5"/>
-      <c r="BL14" s="5"/>
-      <c r="BM14" s="5"/>
-      <c r="BN14" s="5"/>
-      <c r="BO14" s="5"/>
-      <c r="BP14" s="5"/>
-      <c r="BQ14" s="5"/>
-      <c r="BR14" s="5"/>
-      <c r="BS14" s="5"/>
-      <c r="BT14" s="5"/>
-      <c r="BU14" s="5"/>
-      <c r="BV14" s="5"/>
-      <c r="BW14" s="5"/>
-      <c r="BX14" s="5"/>
-      <c r="BY14" s="5"/>
-      <c r="BZ14" s="5"/>
-      <c r="CA14" s="5"/>
-      <c r="CB14" s="5"/>
-      <c r="CC14" s="5"/>
-      <c r="CD14" s="5"/>
-      <c r="CE14" s="5"/>
-      <c r="CF14" s="5"/>
-      <c r="CG14" s="5"/>
-      <c r="CH14" s="5"/>
-      <c r="CI14" s="5"/>
-      <c r="CJ14" s="5"/>
-      <c r="CK14" s="5"/>
-      <c r="CL14" s="5"/>
-      <c r="CM14" s="5"/>
-      <c r="CN14" s="5"/>
-      <c r="CO14" s="5"/>
-      <c r="CP14" s="5"/>
-      <c r="CQ14" s="5"/>
-      <c r="CR14" s="5"/>
-      <c r="CS14" s="5"/>
-      <c r="CT14" s="5"/>
-      <c r="CU14" s="5"/>
-      <c r="CV14" s="5"/>
-      <c r="CW14" s="5"/>
-      <c r="CX14" s="5"/>
-      <c r="CY14" s="5"/>
-      <c r="CZ14" s="5"/>
-      <c r="DA14" s="5"/>
-      <c r="DB14" s="5"/>
-      <c r="DC14" s="5"/>
-      <c r="DD14" s="5"/>
-      <c r="DE14" s="5"/>
-      <c r="DF14" s="5"/>
-      <c r="DG14" s="5"/>
-      <c r="DH14" s="5"/>
-      <c r="DI14" s="5"/>
-      <c r="DJ14" s="5"/>
-      <c r="DK14" s="5"/>
-      <c r="DL14" s="5"/>
-      <c r="DM14" s="5"/>
-      <c r="DN14" s="5"/>
-      <c r="DO14" s="5"/>
-      <c r="DP14" s="5"/>
-      <c r="DQ14" s="5"/>
-      <c r="DR14" s="5"/>
-      <c r="DS14" s="5"/>
-      <c r="DT14" s="5"/>
+      <c r="AV14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW14" s="3"/>
+      <c r="AX14" s="3"/>
+      <c r="AY14" s="3"/>
+      <c r="BA14" s="3"/>
+      <c r="BB14" s="3"/>
+      <c r="BC14" s="3"/>
+      <c r="BD14" s="3"/>
+      <c r="BE14" s="3"/>
+      <c r="BF14" s="3"/>
+      <c r="BG14" s="3"/>
+      <c r="BH14" s="3"/>
+      <c r="BI14" s="3"/>
+      <c r="BJ14" s="3"/>
+      <c r="BK14" s="3"/>
+      <c r="BL14" s="3"/>
+      <c r="BM14" s="3"/>
+      <c r="BN14" s="3"/>
+      <c r="BO14" s="3"/>
+      <c r="BP14" s="3"/>
+      <c r="BQ14" s="3"/>
+      <c r="BR14" s="3"/>
+      <c r="BS14" s="3"/>
+      <c r="BT14" s="3"/>
+      <c r="BU14" s="3"/>
+      <c r="BV14" s="3"/>
+      <c r="BW14" s="3"/>
+      <c r="BX14" s="3"/>
+      <c r="BY14" s="3"/>
+      <c r="BZ14" s="3"/>
+      <c r="CA14" s="3"/>
+      <c r="CB14" s="3"/>
+      <c r="CC14" s="3"/>
+      <c r="CD14" s="3"/>
+      <c r="CE14" s="3"/>
+      <c r="CF14" s="3"/>
+      <c r="CG14" s="3"/>
+      <c r="CH14" s="3"/>
+      <c r="CI14" s="3"/>
+      <c r="CJ14" s="3"/>
+      <c r="CK14" s="3"/>
+      <c r="CL14" s="3"/>
+      <c r="CM14" s="3"/>
+      <c r="CN14" s="3"/>
+      <c r="CO14" s="3"/>
+      <c r="CP14" s="3"/>
+      <c r="CQ14" s="3"/>
+      <c r="CR14" s="3"/>
+      <c r="CS14" s="3"/>
+      <c r="CT14" s="3"/>
+      <c r="CU14" s="3"/>
+      <c r="CV14" s="3"/>
+      <c r="CW14" s="3"/>
+      <c r="CX14" s="3"/>
+      <c r="CY14" s="3"/>
+      <c r="CZ14" s="3"/>
+      <c r="DA14" s="3"/>
+      <c r="DB14" s="3"/>
+      <c r="DC14" s="3"/>
+      <c r="DD14" s="3"/>
+      <c r="DE14" s="3"/>
+      <c r="DF14" s="3"/>
+      <c r="DG14" s="3"/>
+      <c r="DH14" s="3"/>
+      <c r="DI14" s="3"/>
+      <c r="DJ14" s="3"/>
+      <c r="DK14" s="3"/>
+      <c r="DL14" s="3"/>
+      <c r="DM14" s="3"/>
+      <c r="DN14" s="3"/>
+      <c r="DO14" s="3"/>
+      <c r="DP14" s="3"/>
+      <c r="DQ14" s="3"/>
+      <c r="DR14" s="3"/>
+      <c r="DS14" s="3"/>
+      <c r="DT14" s="3"/>
     </row>
     <row r="15" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -3610,7 +3645,7 @@
       <c r="I15" t="s">
         <v>31</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K15" t="s">
@@ -3724,81 +3759,84 @@
       <c r="AU15" t="s">
         <v>31</v>
       </c>
-      <c r="AV15" s="2"/>
-      <c r="AW15" s="2"/>
-      <c r="AX15" s="2"/>
-      <c r="BA15" s="5"/>
-      <c r="BB15" s="5"/>
-      <c r="BC15" s="5"/>
-      <c r="BD15" s="5"/>
-      <c r="BE15" s="5"/>
-      <c r="BF15" s="5"/>
-      <c r="BG15" s="5"/>
-      <c r="BH15" s="5"/>
-      <c r="BI15" s="5"/>
-      <c r="BJ15" s="5"/>
-      <c r="BK15" s="5"/>
-      <c r="BL15" s="5"/>
-      <c r="BM15" s="5"/>
-      <c r="BN15" s="5"/>
-      <c r="BO15" s="5"/>
-      <c r="BP15" s="5"/>
-      <c r="BQ15" s="5"/>
-      <c r="BR15" s="5"/>
-      <c r="BS15" s="5"/>
-      <c r="BT15" s="5"/>
-      <c r="BU15" s="5"/>
-      <c r="BV15" s="5"/>
-      <c r="BW15" s="5"/>
-      <c r="BX15" s="5"/>
-      <c r="BY15" s="5"/>
-      <c r="BZ15" s="5"/>
-      <c r="CA15" s="5"/>
-      <c r="CB15" s="5"/>
-      <c r="CC15" s="5"/>
-      <c r="CD15" s="5"/>
-      <c r="CE15" s="5"/>
-      <c r="CF15" s="5"/>
-      <c r="CG15" s="5"/>
-      <c r="CH15" s="5"/>
-      <c r="CI15" s="5"/>
-      <c r="CJ15" s="5"/>
-      <c r="CK15" s="5"/>
-      <c r="CL15" s="5"/>
-      <c r="CM15" s="5"/>
-      <c r="CN15" s="5"/>
-      <c r="CO15" s="5"/>
-      <c r="CP15" s="5"/>
-      <c r="CQ15" s="5"/>
-      <c r="CR15" s="5"/>
-      <c r="CS15" s="5"/>
-      <c r="CT15" s="5"/>
-      <c r="CU15" s="5"/>
-      <c r="CV15" s="5"/>
-      <c r="CW15" s="5"/>
-      <c r="CX15" s="5"/>
-      <c r="CY15" s="5"/>
-      <c r="CZ15" s="5"/>
-      <c r="DA15" s="5"/>
-      <c r="DB15" s="5"/>
-      <c r="DC15" s="5"/>
-      <c r="DD15" s="5"/>
-      <c r="DE15" s="5"/>
-      <c r="DF15" s="5"/>
-      <c r="DG15" s="5"/>
-      <c r="DH15" s="5"/>
-      <c r="DI15" s="5"/>
-      <c r="DJ15" s="5"/>
-      <c r="DK15" s="5"/>
-      <c r="DL15" s="5"/>
-      <c r="DM15" s="5"/>
-      <c r="DN15" s="5"/>
-      <c r="DO15" s="5"/>
-      <c r="DP15" s="5"/>
-      <c r="DQ15" s="5"/>
-      <c r="DR15" s="5"/>
-      <c r="DS15" s="5"/>
-      <c r="DT15" s="5"/>
+      <c r="AV15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW15" s="3"/>
+      <c r="AX15" s="3"/>
+      <c r="AY15" s="3"/>
+      <c r="BA15" s="3"/>
+      <c r="BB15" s="3"/>
+      <c r="BC15" s="3"/>
+      <c r="BD15" s="3"/>
+      <c r="BE15" s="3"/>
+      <c r="BF15" s="3"/>
+      <c r="BG15" s="3"/>
+      <c r="BH15" s="3"/>
+      <c r="BI15" s="3"/>
+      <c r="BJ15" s="3"/>
+      <c r="BK15" s="3"/>
+      <c r="BL15" s="3"/>
+      <c r="BM15" s="3"/>
+      <c r="BN15" s="3"/>
+      <c r="BO15" s="3"/>
+      <c r="BP15" s="3"/>
+      <c r="BQ15" s="3"/>
+      <c r="BR15" s="3"/>
+      <c r="BS15" s="3"/>
+      <c r="BT15" s="3"/>
+      <c r="BU15" s="3"/>
+      <c r="BV15" s="3"/>
+      <c r="BW15" s="3"/>
+      <c r="BX15" s="3"/>
+      <c r="BY15" s="3"/>
+      <c r="BZ15" s="3"/>
+      <c r="CA15" s="3"/>
+      <c r="CB15" s="3"/>
+      <c r="CC15" s="3"/>
+      <c r="CD15" s="3"/>
+      <c r="CE15" s="3"/>
+      <c r="CF15" s="3"/>
+      <c r="CG15" s="3"/>
+      <c r="CH15" s="3"/>
+      <c r="CI15" s="3"/>
+      <c r="CJ15" s="3"/>
+      <c r="CK15" s="3"/>
+      <c r="CL15" s="3"/>
+      <c r="CM15" s="3"/>
+      <c r="CN15" s="3"/>
+      <c r="CO15" s="3"/>
+      <c r="CP15" s="3"/>
+      <c r="CQ15" s="3"/>
+      <c r="CR15" s="3"/>
+      <c r="CS15" s="3"/>
+      <c r="CT15" s="3"/>
+      <c r="CU15" s="3"/>
+      <c r="CV15" s="3"/>
+      <c r="CW15" s="3"/>
+      <c r="CX15" s="3"/>
+      <c r="CY15" s="3"/>
+      <c r="CZ15" s="3"/>
+      <c r="DA15" s="3"/>
+      <c r="DB15" s="3"/>
+      <c r="DC15" s="3"/>
+      <c r="DD15" s="3"/>
+      <c r="DE15" s="3"/>
+      <c r="DF15" s="3"/>
+      <c r="DG15" s="3"/>
+      <c r="DH15" s="3"/>
+      <c r="DI15" s="3"/>
+      <c r="DJ15" s="3"/>
+      <c r="DK15" s="3"/>
+      <c r="DL15" s="3"/>
+      <c r="DM15" s="3"/>
+      <c r="DN15" s="3"/>
+      <c r="DO15" s="3"/>
+      <c r="DP15" s="3"/>
+      <c r="DQ15" s="3"/>
+      <c r="DR15" s="3"/>
+      <c r="DS15" s="3"/>
+      <c r="DT15" s="3"/>
     </row>
     <row r="16" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -3829,7 +3867,7 @@
       <c r="I16" t="s">
         <v>31</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K16" t="s">
@@ -3943,81 +3981,84 @@
       <c r="AU16" t="s">
         <v>31</v>
       </c>
-      <c r="AV16" s="2"/>
-      <c r="AW16" s="2"/>
-      <c r="AX16" s="2"/>
-      <c r="BA16" s="5"/>
-      <c r="BB16" s="5"/>
-      <c r="BC16" s="5"/>
-      <c r="BD16" s="5"/>
-      <c r="BE16" s="5"/>
-      <c r="BF16" s="5"/>
-      <c r="BG16" s="5"/>
-      <c r="BH16" s="5"/>
-      <c r="BI16" s="5"/>
-      <c r="BJ16" s="5"/>
-      <c r="BK16" s="5"/>
-      <c r="BL16" s="5"/>
-      <c r="BM16" s="5"/>
-      <c r="BN16" s="5"/>
-      <c r="BO16" s="5"/>
-      <c r="BP16" s="5"/>
-      <c r="BQ16" s="5"/>
-      <c r="BR16" s="5"/>
-      <c r="BS16" s="5"/>
-      <c r="BT16" s="5"/>
-      <c r="BU16" s="5"/>
-      <c r="BV16" s="5"/>
-      <c r="BW16" s="5"/>
-      <c r="BX16" s="5"/>
-      <c r="BY16" s="5"/>
-      <c r="BZ16" s="5"/>
-      <c r="CA16" s="5"/>
-      <c r="CB16" s="5"/>
-      <c r="CC16" s="5"/>
-      <c r="CD16" s="5"/>
-      <c r="CE16" s="5"/>
-      <c r="CF16" s="5"/>
-      <c r="CG16" s="5"/>
-      <c r="CH16" s="5"/>
-      <c r="CI16" s="5"/>
-      <c r="CJ16" s="5"/>
-      <c r="CK16" s="5"/>
-      <c r="CL16" s="5"/>
-      <c r="CM16" s="5"/>
-      <c r="CN16" s="5"/>
-      <c r="CO16" s="5"/>
-      <c r="CP16" s="5"/>
-      <c r="CQ16" s="5"/>
-      <c r="CR16" s="5"/>
-      <c r="CS16" s="5"/>
-      <c r="CT16" s="5"/>
-      <c r="CU16" s="5"/>
-      <c r="CV16" s="5"/>
-      <c r="CW16" s="5"/>
-      <c r="CX16" s="5"/>
-      <c r="CY16" s="5"/>
-      <c r="CZ16" s="5"/>
-      <c r="DA16" s="5"/>
-      <c r="DB16" s="5"/>
-      <c r="DC16" s="5"/>
-      <c r="DD16" s="5"/>
-      <c r="DE16" s="5"/>
-      <c r="DF16" s="5"/>
-      <c r="DG16" s="5"/>
-      <c r="DH16" s="5"/>
-      <c r="DI16" s="5"/>
-      <c r="DJ16" s="5"/>
-      <c r="DK16" s="5"/>
-      <c r="DL16" s="5"/>
-      <c r="DM16" s="5"/>
-      <c r="DN16" s="5"/>
-      <c r="DO16" s="5"/>
-      <c r="DP16" s="5"/>
-      <c r="DQ16" s="5"/>
-      <c r="DR16" s="5"/>
-      <c r="DS16" s="5"/>
-      <c r="DT16" s="5"/>
+      <c r="AV16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW16" s="3"/>
+      <c r="AX16" s="3"/>
+      <c r="AY16" s="3"/>
+      <c r="BA16" s="3"/>
+      <c r="BB16" s="3"/>
+      <c r="BC16" s="3"/>
+      <c r="BD16" s="3"/>
+      <c r="BE16" s="3"/>
+      <c r="BF16" s="3"/>
+      <c r="BG16" s="3"/>
+      <c r="BH16" s="3"/>
+      <c r="BI16" s="3"/>
+      <c r="BJ16" s="3"/>
+      <c r="BK16" s="3"/>
+      <c r="BL16" s="3"/>
+      <c r="BM16" s="3"/>
+      <c r="BN16" s="3"/>
+      <c r="BO16" s="3"/>
+      <c r="BP16" s="3"/>
+      <c r="BQ16" s="3"/>
+      <c r="BR16" s="3"/>
+      <c r="BS16" s="3"/>
+      <c r="BT16" s="3"/>
+      <c r="BU16" s="3"/>
+      <c r="BV16" s="3"/>
+      <c r="BW16" s="3"/>
+      <c r="BX16" s="3"/>
+      <c r="BY16" s="3"/>
+      <c r="BZ16" s="3"/>
+      <c r="CA16" s="3"/>
+      <c r="CB16" s="3"/>
+      <c r="CC16" s="3"/>
+      <c r="CD16" s="3"/>
+      <c r="CE16" s="3"/>
+      <c r="CF16" s="3"/>
+      <c r="CG16" s="3"/>
+      <c r="CH16" s="3"/>
+      <c r="CI16" s="3"/>
+      <c r="CJ16" s="3"/>
+      <c r="CK16" s="3"/>
+      <c r="CL16" s="3"/>
+      <c r="CM16" s="3"/>
+      <c r="CN16" s="3"/>
+      <c r="CO16" s="3"/>
+      <c r="CP16" s="3"/>
+      <c r="CQ16" s="3"/>
+      <c r="CR16" s="3"/>
+      <c r="CS16" s="3"/>
+      <c r="CT16" s="3"/>
+      <c r="CU16" s="3"/>
+      <c r="CV16" s="3"/>
+      <c r="CW16" s="3"/>
+      <c r="CX16" s="3"/>
+      <c r="CY16" s="3"/>
+      <c r="CZ16" s="3"/>
+      <c r="DA16" s="3"/>
+      <c r="DB16" s="3"/>
+      <c r="DC16" s="3"/>
+      <c r="DD16" s="3"/>
+      <c r="DE16" s="3"/>
+      <c r="DF16" s="3"/>
+      <c r="DG16" s="3"/>
+      <c r="DH16" s="3"/>
+      <c r="DI16" s="3"/>
+      <c r="DJ16" s="3"/>
+      <c r="DK16" s="3"/>
+      <c r="DL16" s="3"/>
+      <c r="DM16" s="3"/>
+      <c r="DN16" s="3"/>
+      <c r="DO16" s="3"/>
+      <c r="DP16" s="3"/>
+      <c r="DQ16" s="3"/>
+      <c r="DR16" s="3"/>
+      <c r="DS16" s="3"/>
+      <c r="DT16" s="3"/>
     </row>
     <row r="17" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A17">
@@ -4030,7 +4071,7 @@
       <c r="C17">
         <v>15</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="6" t="s">
         <v>40</v>
       </c>
       <c r="L17" t="s">
@@ -4141,81 +4182,84 @@
       <c r="AU17" t="s">
         <v>32</v>
       </c>
-      <c r="AV17" s="2"/>
-      <c r="AW17" s="2"/>
-      <c r="AX17" s="2"/>
-      <c r="BA17" s="5"/>
-      <c r="BB17" s="5"/>
-      <c r="BC17" s="5"/>
-      <c r="BD17" s="5"/>
-      <c r="BE17" s="5"/>
-      <c r="BF17" s="5"/>
-      <c r="BG17" s="5"/>
-      <c r="BH17" s="5"/>
-      <c r="BI17" s="5"/>
-      <c r="BJ17" s="5"/>
-      <c r="BK17" s="5"/>
-      <c r="BL17" s="5"/>
-      <c r="BM17" s="5"/>
-      <c r="BN17" s="5"/>
-      <c r="BO17" s="5"/>
-      <c r="BP17" s="5"/>
-      <c r="BQ17" s="5"/>
-      <c r="BR17" s="5"/>
-      <c r="BS17" s="5"/>
-      <c r="BT17" s="5"/>
-      <c r="BU17" s="5"/>
-      <c r="BV17" s="5"/>
-      <c r="BW17" s="5"/>
-      <c r="BX17" s="5"/>
-      <c r="BY17" s="5"/>
-      <c r="BZ17" s="5"/>
-      <c r="CA17" s="5"/>
-      <c r="CB17" s="5"/>
-      <c r="CC17" s="5"/>
-      <c r="CD17" s="5"/>
-      <c r="CE17" s="5"/>
-      <c r="CF17" s="5"/>
-      <c r="CG17" s="5"/>
-      <c r="CH17" s="5"/>
-      <c r="CI17" s="5"/>
-      <c r="CJ17" s="5"/>
-      <c r="CK17" s="5"/>
-      <c r="CL17" s="5"/>
-      <c r="CM17" s="5"/>
-      <c r="CN17" s="5"/>
-      <c r="CO17" s="5"/>
-      <c r="CP17" s="5"/>
-      <c r="CQ17" s="5"/>
-      <c r="CR17" s="5"/>
-      <c r="CS17" s="5"/>
-      <c r="CT17" s="5"/>
-      <c r="CU17" s="5"/>
-      <c r="CV17" s="5"/>
-      <c r="CW17" s="5"/>
-      <c r="CX17" s="5"/>
-      <c r="CY17" s="5"/>
-      <c r="CZ17" s="5"/>
-      <c r="DA17" s="5"/>
-      <c r="DB17" s="5"/>
-      <c r="DC17" s="5"/>
-      <c r="DD17" s="5"/>
-      <c r="DE17" s="5"/>
-      <c r="DF17" s="5"/>
-      <c r="DG17" s="5"/>
-      <c r="DH17" s="5"/>
-      <c r="DI17" s="5"/>
-      <c r="DJ17" s="5"/>
-      <c r="DK17" s="5"/>
-      <c r="DL17" s="5"/>
-      <c r="DM17" s="5"/>
-      <c r="DN17" s="5"/>
-      <c r="DO17" s="5"/>
-      <c r="DP17" s="5"/>
-      <c r="DQ17" s="5"/>
-      <c r="DR17" s="5"/>
-      <c r="DS17" s="5"/>
-      <c r="DT17" s="5"/>
+      <c r="AV17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW17" s="3"/>
+      <c r="AX17" s="3"/>
+      <c r="AY17" s="3"/>
+      <c r="BA17" s="3"/>
+      <c r="BB17" s="3"/>
+      <c r="BC17" s="3"/>
+      <c r="BD17" s="3"/>
+      <c r="BE17" s="3"/>
+      <c r="BF17" s="3"/>
+      <c r="BG17" s="3"/>
+      <c r="BH17" s="3"/>
+      <c r="BI17" s="3"/>
+      <c r="BJ17" s="3"/>
+      <c r="BK17" s="3"/>
+      <c r="BL17" s="3"/>
+      <c r="BM17" s="3"/>
+      <c r="BN17" s="3"/>
+      <c r="BO17" s="3"/>
+      <c r="BP17" s="3"/>
+      <c r="BQ17" s="3"/>
+      <c r="BR17" s="3"/>
+      <c r="BS17" s="3"/>
+      <c r="BT17" s="3"/>
+      <c r="BU17" s="3"/>
+      <c r="BV17" s="3"/>
+      <c r="BW17" s="3"/>
+      <c r="BX17" s="3"/>
+      <c r="BY17" s="3"/>
+      <c r="BZ17" s="3"/>
+      <c r="CA17" s="3"/>
+      <c r="CB17" s="3"/>
+      <c r="CC17" s="3"/>
+      <c r="CD17" s="3"/>
+      <c r="CE17" s="3"/>
+      <c r="CF17" s="3"/>
+      <c r="CG17" s="3"/>
+      <c r="CH17" s="3"/>
+      <c r="CI17" s="3"/>
+      <c r="CJ17" s="3"/>
+      <c r="CK17" s="3"/>
+      <c r="CL17" s="3"/>
+      <c r="CM17" s="3"/>
+      <c r="CN17" s="3"/>
+      <c r="CO17" s="3"/>
+      <c r="CP17" s="3"/>
+      <c r="CQ17" s="3"/>
+      <c r="CR17" s="3"/>
+      <c r="CS17" s="3"/>
+      <c r="CT17" s="3"/>
+      <c r="CU17" s="3"/>
+      <c r="CV17" s="3"/>
+      <c r="CW17" s="3"/>
+      <c r="CX17" s="3"/>
+      <c r="CY17" s="3"/>
+      <c r="CZ17" s="3"/>
+      <c r="DA17" s="3"/>
+      <c r="DB17" s="3"/>
+      <c r="DC17" s="3"/>
+      <c r="DD17" s="3"/>
+      <c r="DE17" s="3"/>
+      <c r="DF17" s="3"/>
+      <c r="DG17" s="3"/>
+      <c r="DH17" s="3"/>
+      <c r="DI17" s="3"/>
+      <c r="DJ17" s="3"/>
+      <c r="DK17" s="3"/>
+      <c r="DL17" s="3"/>
+      <c r="DM17" s="3"/>
+      <c r="DN17" s="3"/>
+      <c r="DO17" s="3"/>
+      <c r="DP17" s="3"/>
+      <c r="DQ17" s="3"/>
+      <c r="DR17" s="3"/>
+      <c r="DS17" s="3"/>
+      <c r="DT17" s="3"/>
     </row>
     <row r="18" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A18">
@@ -4246,7 +4290,7 @@
       <c r="I18" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K18" t="s">
@@ -4360,81 +4404,84 @@
       <c r="AU18" t="s">
         <v>31</v>
       </c>
-      <c r="AV18" s="2"/>
-      <c r="AW18" s="2"/>
-      <c r="AX18" s="2"/>
-      <c r="BA18" s="5"/>
-      <c r="BB18" s="5"/>
-      <c r="BC18" s="5"/>
-      <c r="BD18" s="5"/>
-      <c r="BE18" s="5"/>
-      <c r="BF18" s="5"/>
-      <c r="BG18" s="5"/>
-      <c r="BH18" s="5"/>
-      <c r="BI18" s="5"/>
-      <c r="BJ18" s="5"/>
-      <c r="BK18" s="5"/>
-      <c r="BL18" s="5"/>
-      <c r="BM18" s="5"/>
-      <c r="BN18" s="5"/>
-      <c r="BO18" s="5"/>
-      <c r="BP18" s="5"/>
-      <c r="BQ18" s="5"/>
-      <c r="BR18" s="5"/>
-      <c r="BS18" s="5"/>
-      <c r="BT18" s="5"/>
-      <c r="BU18" s="5"/>
-      <c r="BV18" s="5"/>
-      <c r="BW18" s="5"/>
-      <c r="BX18" s="5"/>
-      <c r="BY18" s="5"/>
-      <c r="BZ18" s="5"/>
-      <c r="CA18" s="5"/>
-      <c r="CB18" s="5"/>
-      <c r="CC18" s="5"/>
-      <c r="CD18" s="5"/>
-      <c r="CE18" s="5"/>
-      <c r="CF18" s="5"/>
-      <c r="CG18" s="5"/>
-      <c r="CH18" s="5"/>
-      <c r="CI18" s="5"/>
-      <c r="CJ18" s="5"/>
-      <c r="CK18" s="5"/>
-      <c r="CL18" s="5"/>
-      <c r="CM18" s="5"/>
-      <c r="CN18" s="5"/>
-      <c r="CO18" s="5"/>
-      <c r="CP18" s="5"/>
-      <c r="CQ18" s="5"/>
-      <c r="CR18" s="5"/>
-      <c r="CS18" s="5"/>
-      <c r="CT18" s="5"/>
-      <c r="CU18" s="5"/>
-      <c r="CV18" s="5"/>
-      <c r="CW18" s="5"/>
-      <c r="CX18" s="5"/>
-      <c r="CY18" s="5"/>
-      <c r="CZ18" s="5"/>
-      <c r="DA18" s="5"/>
-      <c r="DB18" s="5"/>
-      <c r="DC18" s="5"/>
-      <c r="DD18" s="5"/>
-      <c r="DE18" s="5"/>
-      <c r="DF18" s="5"/>
-      <c r="DG18" s="5"/>
-      <c r="DH18" s="5"/>
-      <c r="DI18" s="5"/>
-      <c r="DJ18" s="5"/>
-      <c r="DK18" s="5"/>
-      <c r="DL18" s="5"/>
-      <c r="DM18" s="5"/>
-      <c r="DN18" s="5"/>
-      <c r="DO18" s="5"/>
-      <c r="DP18" s="5"/>
-      <c r="DQ18" s="5"/>
-      <c r="DR18" s="5"/>
-      <c r="DS18" s="5"/>
-      <c r="DT18" s="5"/>
+      <c r="AV18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW18" s="3"/>
+      <c r="AX18" s="3"/>
+      <c r="AY18" s="3"/>
+      <c r="BA18" s="3"/>
+      <c r="BB18" s="3"/>
+      <c r="BC18" s="3"/>
+      <c r="BD18" s="3"/>
+      <c r="BE18" s="3"/>
+      <c r="BF18" s="3"/>
+      <c r="BG18" s="3"/>
+      <c r="BH18" s="3"/>
+      <c r="BI18" s="3"/>
+      <c r="BJ18" s="3"/>
+      <c r="BK18" s="3"/>
+      <c r="BL18" s="3"/>
+      <c r="BM18" s="3"/>
+      <c r="BN18" s="3"/>
+      <c r="BO18" s="3"/>
+      <c r="BP18" s="3"/>
+      <c r="BQ18" s="3"/>
+      <c r="BR18" s="3"/>
+      <c r="BS18" s="3"/>
+      <c r="BT18" s="3"/>
+      <c r="BU18" s="3"/>
+      <c r="BV18" s="3"/>
+      <c r="BW18" s="3"/>
+      <c r="BX18" s="3"/>
+      <c r="BY18" s="3"/>
+      <c r="BZ18" s="3"/>
+      <c r="CA18" s="3"/>
+      <c r="CB18" s="3"/>
+      <c r="CC18" s="3"/>
+      <c r="CD18" s="3"/>
+      <c r="CE18" s="3"/>
+      <c r="CF18" s="3"/>
+      <c r="CG18" s="3"/>
+      <c r="CH18" s="3"/>
+      <c r="CI18" s="3"/>
+      <c r="CJ18" s="3"/>
+      <c r="CK18" s="3"/>
+      <c r="CL18" s="3"/>
+      <c r="CM18" s="3"/>
+      <c r="CN18" s="3"/>
+      <c r="CO18" s="3"/>
+      <c r="CP18" s="3"/>
+      <c r="CQ18" s="3"/>
+      <c r="CR18" s="3"/>
+      <c r="CS18" s="3"/>
+      <c r="CT18" s="3"/>
+      <c r="CU18" s="3"/>
+      <c r="CV18" s="3"/>
+      <c r="CW18" s="3"/>
+      <c r="CX18" s="3"/>
+      <c r="CY18" s="3"/>
+      <c r="CZ18" s="3"/>
+      <c r="DA18" s="3"/>
+      <c r="DB18" s="3"/>
+      <c r="DC18" s="3"/>
+      <c r="DD18" s="3"/>
+      <c r="DE18" s="3"/>
+      <c r="DF18" s="3"/>
+      <c r="DG18" s="3"/>
+      <c r="DH18" s="3"/>
+      <c r="DI18" s="3"/>
+      <c r="DJ18" s="3"/>
+      <c r="DK18" s="3"/>
+      <c r="DL18" s="3"/>
+      <c r="DM18" s="3"/>
+      <c r="DN18" s="3"/>
+      <c r="DO18" s="3"/>
+      <c r="DP18" s="3"/>
+      <c r="DQ18" s="3"/>
+      <c r="DR18" s="3"/>
+      <c r="DS18" s="3"/>
+      <c r="DT18" s="3"/>
     </row>
     <row r="19" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A19">
@@ -4465,7 +4512,7 @@
       <c r="I19" t="s">
         <v>31</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K19" t="s">
@@ -4579,81 +4626,84 @@
       <c r="AU19" t="s">
         <v>31</v>
       </c>
-      <c r="AV19" s="2"/>
-      <c r="AW19" s="2"/>
-      <c r="AX19" s="2"/>
-      <c r="BA19" s="5"/>
-      <c r="BB19" s="5"/>
-      <c r="BC19" s="5"/>
-      <c r="BD19" s="5"/>
-      <c r="BE19" s="5"/>
-      <c r="BF19" s="5"/>
-      <c r="BG19" s="5"/>
-      <c r="BH19" s="5"/>
-      <c r="BI19" s="5"/>
-      <c r="BJ19" s="5"/>
-      <c r="BK19" s="5"/>
-      <c r="BL19" s="5"/>
-      <c r="BM19" s="5"/>
-      <c r="BN19" s="5"/>
-      <c r="BO19" s="5"/>
-      <c r="BP19" s="5"/>
-      <c r="BQ19" s="5"/>
-      <c r="BR19" s="5"/>
-      <c r="BS19" s="5"/>
-      <c r="BT19" s="5"/>
-      <c r="BU19" s="5"/>
-      <c r="BV19" s="5"/>
-      <c r="BW19" s="5"/>
-      <c r="BX19" s="5"/>
-      <c r="BY19" s="5"/>
-      <c r="BZ19" s="5"/>
-      <c r="CA19" s="5"/>
-      <c r="CB19" s="5"/>
-      <c r="CC19" s="5"/>
-      <c r="CD19" s="5"/>
-      <c r="CE19" s="5"/>
-      <c r="CF19" s="5"/>
-      <c r="CG19" s="5"/>
-      <c r="CH19" s="5"/>
-      <c r="CI19" s="5"/>
-      <c r="CJ19" s="5"/>
-      <c r="CK19" s="5"/>
-      <c r="CL19" s="5"/>
-      <c r="CM19" s="5"/>
-      <c r="CN19" s="5"/>
-      <c r="CO19" s="5"/>
-      <c r="CP19" s="5"/>
-      <c r="CQ19" s="5"/>
-      <c r="CR19" s="5"/>
-      <c r="CS19" s="5"/>
-      <c r="CT19" s="5"/>
-      <c r="CU19" s="5"/>
-      <c r="CV19" s="5"/>
-      <c r="CW19" s="5"/>
-      <c r="CX19" s="5"/>
-      <c r="CY19" s="5"/>
-      <c r="CZ19" s="5"/>
-      <c r="DA19" s="5"/>
-      <c r="DB19" s="5"/>
-      <c r="DC19" s="5"/>
-      <c r="DD19" s="5"/>
-      <c r="DE19" s="5"/>
-      <c r="DF19" s="5"/>
-      <c r="DG19" s="5"/>
-      <c r="DH19" s="5"/>
-      <c r="DI19" s="5"/>
-      <c r="DJ19" s="5"/>
-      <c r="DK19" s="5"/>
-      <c r="DL19" s="5"/>
-      <c r="DM19" s="5"/>
-      <c r="DN19" s="5"/>
-      <c r="DO19" s="5"/>
-      <c r="DP19" s="5"/>
-      <c r="DQ19" s="5"/>
-      <c r="DR19" s="5"/>
-      <c r="DS19" s="5"/>
-      <c r="DT19" s="5"/>
+      <c r="AV19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW19" s="3"/>
+      <c r="AX19" s="3"/>
+      <c r="AY19" s="3"/>
+      <c r="BA19" s="3"/>
+      <c r="BB19" s="3"/>
+      <c r="BC19" s="3"/>
+      <c r="BD19" s="3"/>
+      <c r="BE19" s="3"/>
+      <c r="BF19" s="3"/>
+      <c r="BG19" s="3"/>
+      <c r="BH19" s="3"/>
+      <c r="BI19" s="3"/>
+      <c r="BJ19" s="3"/>
+      <c r="BK19" s="3"/>
+      <c r="BL19" s="3"/>
+      <c r="BM19" s="3"/>
+      <c r="BN19" s="3"/>
+      <c r="BO19" s="3"/>
+      <c r="BP19" s="3"/>
+      <c r="BQ19" s="3"/>
+      <c r="BR19" s="3"/>
+      <c r="BS19" s="3"/>
+      <c r="BT19" s="3"/>
+      <c r="BU19" s="3"/>
+      <c r="BV19" s="3"/>
+      <c r="BW19" s="3"/>
+      <c r="BX19" s="3"/>
+      <c r="BY19" s="3"/>
+      <c r="BZ19" s="3"/>
+      <c r="CA19" s="3"/>
+      <c r="CB19" s="3"/>
+      <c r="CC19" s="3"/>
+      <c r="CD19" s="3"/>
+      <c r="CE19" s="3"/>
+      <c r="CF19" s="3"/>
+      <c r="CG19" s="3"/>
+      <c r="CH19" s="3"/>
+      <c r="CI19" s="3"/>
+      <c r="CJ19" s="3"/>
+      <c r="CK19" s="3"/>
+      <c r="CL19" s="3"/>
+      <c r="CM19" s="3"/>
+      <c r="CN19" s="3"/>
+      <c r="CO19" s="3"/>
+      <c r="CP19" s="3"/>
+      <c r="CQ19" s="3"/>
+      <c r="CR19" s="3"/>
+      <c r="CS19" s="3"/>
+      <c r="CT19" s="3"/>
+      <c r="CU19" s="3"/>
+      <c r="CV19" s="3"/>
+      <c r="CW19" s="3"/>
+      <c r="CX19" s="3"/>
+      <c r="CY19" s="3"/>
+      <c r="CZ19" s="3"/>
+      <c r="DA19" s="3"/>
+      <c r="DB19" s="3"/>
+      <c r="DC19" s="3"/>
+      <c r="DD19" s="3"/>
+      <c r="DE19" s="3"/>
+      <c r="DF19" s="3"/>
+      <c r="DG19" s="3"/>
+      <c r="DH19" s="3"/>
+      <c r="DI19" s="3"/>
+      <c r="DJ19" s="3"/>
+      <c r="DK19" s="3"/>
+      <c r="DL19" s="3"/>
+      <c r="DM19" s="3"/>
+      <c r="DN19" s="3"/>
+      <c r="DO19" s="3"/>
+      <c r="DP19" s="3"/>
+      <c r="DQ19" s="3"/>
+      <c r="DR19" s="3"/>
+      <c r="DS19" s="3"/>
+      <c r="DT19" s="3"/>
     </row>
     <row r="20" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A20">
@@ -4666,7 +4716,7 @@
       <c r="C20">
         <v>18</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J20" s="6" t="s">
         <v>40</v>
       </c>
       <c r="L20" t="s">
@@ -4777,81 +4827,84 @@
       <c r="AU20" t="s">
         <v>32</v>
       </c>
-      <c r="AV20" s="2"/>
-      <c r="AW20" s="2"/>
-      <c r="AX20" s="2"/>
-      <c r="BA20" s="5"/>
-      <c r="BB20" s="5"/>
-      <c r="BC20" s="5"/>
-      <c r="BD20" s="5"/>
-      <c r="BE20" s="5"/>
-      <c r="BF20" s="5"/>
-      <c r="BG20" s="5"/>
-      <c r="BH20" s="5"/>
-      <c r="BI20" s="5"/>
-      <c r="BJ20" s="5"/>
-      <c r="BK20" s="5"/>
-      <c r="BL20" s="5"/>
-      <c r="BM20" s="5"/>
-      <c r="BN20" s="5"/>
-      <c r="BO20" s="5"/>
-      <c r="BP20" s="5"/>
-      <c r="BQ20" s="5"/>
-      <c r="BR20" s="5"/>
-      <c r="BS20" s="5"/>
-      <c r="BT20" s="5"/>
-      <c r="BU20" s="5"/>
-      <c r="BV20" s="5"/>
-      <c r="BW20" s="5"/>
-      <c r="BX20" s="5"/>
-      <c r="BY20" s="5"/>
-      <c r="BZ20" s="5"/>
-      <c r="CA20" s="5"/>
-      <c r="CB20" s="5"/>
-      <c r="CC20" s="5"/>
-      <c r="CD20" s="5"/>
-      <c r="CE20" s="5"/>
-      <c r="CF20" s="5"/>
-      <c r="CG20" s="5"/>
-      <c r="CH20" s="5"/>
-      <c r="CI20" s="5"/>
-      <c r="CJ20" s="5"/>
-      <c r="CK20" s="5"/>
-      <c r="CL20" s="5"/>
-      <c r="CM20" s="5"/>
-      <c r="CN20" s="5"/>
-      <c r="CO20" s="5"/>
-      <c r="CP20" s="5"/>
-      <c r="CQ20" s="5"/>
-      <c r="CR20" s="5"/>
-      <c r="CS20" s="5"/>
-      <c r="CT20" s="5"/>
-      <c r="CU20" s="5"/>
-      <c r="CV20" s="5"/>
-      <c r="CW20" s="5"/>
-      <c r="CX20" s="5"/>
-      <c r="CY20" s="5"/>
-      <c r="CZ20" s="5"/>
-      <c r="DA20" s="5"/>
-      <c r="DB20" s="5"/>
-      <c r="DC20" s="5"/>
-      <c r="DD20" s="5"/>
-      <c r="DE20" s="5"/>
-      <c r="DF20" s="5"/>
-      <c r="DG20" s="5"/>
-      <c r="DH20" s="5"/>
-      <c r="DI20" s="5"/>
-      <c r="DJ20" s="5"/>
-      <c r="DK20" s="5"/>
-      <c r="DL20" s="5"/>
-      <c r="DM20" s="5"/>
-      <c r="DN20" s="5"/>
-      <c r="DO20" s="5"/>
-      <c r="DP20" s="5"/>
-      <c r="DQ20" s="5"/>
-      <c r="DR20" s="5"/>
-      <c r="DS20" s="5"/>
-      <c r="DT20" s="5"/>
+      <c r="AV20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW20" s="3"/>
+      <c r="AX20" s="3"/>
+      <c r="AY20" s="3"/>
+      <c r="BA20" s="3"/>
+      <c r="BB20" s="3"/>
+      <c r="BC20" s="3"/>
+      <c r="BD20" s="3"/>
+      <c r="BE20" s="3"/>
+      <c r="BF20" s="3"/>
+      <c r="BG20" s="3"/>
+      <c r="BH20" s="3"/>
+      <c r="BI20" s="3"/>
+      <c r="BJ20" s="3"/>
+      <c r="BK20" s="3"/>
+      <c r="BL20" s="3"/>
+      <c r="BM20" s="3"/>
+      <c r="BN20" s="3"/>
+      <c r="BO20" s="3"/>
+      <c r="BP20" s="3"/>
+      <c r="BQ20" s="3"/>
+      <c r="BR20" s="3"/>
+      <c r="BS20" s="3"/>
+      <c r="BT20" s="3"/>
+      <c r="BU20" s="3"/>
+      <c r="BV20" s="3"/>
+      <c r="BW20" s="3"/>
+      <c r="BX20" s="3"/>
+      <c r="BY20" s="3"/>
+      <c r="BZ20" s="3"/>
+      <c r="CA20" s="3"/>
+      <c r="CB20" s="3"/>
+      <c r="CC20" s="3"/>
+      <c r="CD20" s="3"/>
+      <c r="CE20" s="3"/>
+      <c r="CF20" s="3"/>
+      <c r="CG20" s="3"/>
+      <c r="CH20" s="3"/>
+      <c r="CI20" s="3"/>
+      <c r="CJ20" s="3"/>
+      <c r="CK20" s="3"/>
+      <c r="CL20" s="3"/>
+      <c r="CM20" s="3"/>
+      <c r="CN20" s="3"/>
+      <c r="CO20" s="3"/>
+      <c r="CP20" s="3"/>
+      <c r="CQ20" s="3"/>
+      <c r="CR20" s="3"/>
+      <c r="CS20" s="3"/>
+      <c r="CT20" s="3"/>
+      <c r="CU20" s="3"/>
+      <c r="CV20" s="3"/>
+      <c r="CW20" s="3"/>
+      <c r="CX20" s="3"/>
+      <c r="CY20" s="3"/>
+      <c r="CZ20" s="3"/>
+      <c r="DA20" s="3"/>
+      <c r="DB20" s="3"/>
+      <c r="DC20" s="3"/>
+      <c r="DD20" s="3"/>
+      <c r="DE20" s="3"/>
+      <c r="DF20" s="3"/>
+      <c r="DG20" s="3"/>
+      <c r="DH20" s="3"/>
+      <c r="DI20" s="3"/>
+      <c r="DJ20" s="3"/>
+      <c r="DK20" s="3"/>
+      <c r="DL20" s="3"/>
+      <c r="DM20" s="3"/>
+      <c r="DN20" s="3"/>
+      <c r="DO20" s="3"/>
+      <c r="DP20" s="3"/>
+      <c r="DQ20" s="3"/>
+      <c r="DR20" s="3"/>
+      <c r="DS20" s="3"/>
+      <c r="DT20" s="3"/>
     </row>
     <row r="21" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A21">
@@ -4882,7 +4935,7 @@
       <c r="I21" t="s">
         <v>31</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K21" t="s">
@@ -4996,81 +5049,84 @@
       <c r="AU21" t="s">
         <v>31</v>
       </c>
-      <c r="AV21" s="2"/>
-      <c r="AW21" s="2"/>
-      <c r="AX21" s="2"/>
-      <c r="BA21" s="5"/>
-      <c r="BB21" s="5"/>
-      <c r="BC21" s="5"/>
-      <c r="BD21" s="5"/>
-      <c r="BE21" s="5"/>
-      <c r="BF21" s="5"/>
-      <c r="BG21" s="5"/>
-      <c r="BH21" s="5"/>
-      <c r="BI21" s="5"/>
-      <c r="BJ21" s="5"/>
-      <c r="BK21" s="5"/>
-      <c r="BL21" s="5"/>
-      <c r="BM21" s="5"/>
-      <c r="BN21" s="5"/>
-      <c r="BO21" s="5"/>
-      <c r="BP21" s="5"/>
-      <c r="BQ21" s="5"/>
-      <c r="BR21" s="5"/>
-      <c r="BS21" s="5"/>
-      <c r="BT21" s="5"/>
-      <c r="BU21" s="5"/>
-      <c r="BV21" s="5"/>
-      <c r="BW21" s="5"/>
-      <c r="BX21" s="5"/>
-      <c r="BY21" s="5"/>
-      <c r="BZ21" s="5"/>
-      <c r="CA21" s="5"/>
-      <c r="CB21" s="5"/>
-      <c r="CC21" s="5"/>
-      <c r="CD21" s="5"/>
-      <c r="CE21" s="5"/>
-      <c r="CF21" s="5"/>
-      <c r="CG21" s="5"/>
-      <c r="CH21" s="5"/>
-      <c r="CI21" s="5"/>
-      <c r="CJ21" s="5"/>
-      <c r="CK21" s="5"/>
-      <c r="CL21" s="5"/>
-      <c r="CM21" s="5"/>
-      <c r="CN21" s="5"/>
-      <c r="CO21" s="5"/>
-      <c r="CP21" s="5"/>
-      <c r="CQ21" s="5"/>
-      <c r="CR21" s="5"/>
-      <c r="CS21" s="5"/>
-      <c r="CT21" s="5"/>
-      <c r="CU21" s="5"/>
-      <c r="CV21" s="5"/>
-      <c r="CW21" s="5"/>
-      <c r="CX21" s="5"/>
-      <c r="CY21" s="5"/>
-      <c r="CZ21" s="5"/>
-      <c r="DA21" s="5"/>
-      <c r="DB21" s="5"/>
-      <c r="DC21" s="5"/>
-      <c r="DD21" s="5"/>
-      <c r="DE21" s="5"/>
-      <c r="DF21" s="5"/>
-      <c r="DG21" s="5"/>
-      <c r="DH21" s="5"/>
-      <c r="DI21" s="5"/>
-      <c r="DJ21" s="5"/>
-      <c r="DK21" s="5"/>
-      <c r="DL21" s="5"/>
-      <c r="DM21" s="5"/>
-      <c r="DN21" s="5"/>
-      <c r="DO21" s="5"/>
-      <c r="DP21" s="5"/>
-      <c r="DQ21" s="5"/>
-      <c r="DR21" s="5"/>
-      <c r="DS21" s="5"/>
-      <c r="DT21" s="5"/>
+      <c r="AV21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW21" s="3"/>
+      <c r="AX21" s="3"/>
+      <c r="AY21" s="3"/>
+      <c r="BA21" s="3"/>
+      <c r="BB21" s="3"/>
+      <c r="BC21" s="3"/>
+      <c r="BD21" s="3"/>
+      <c r="BE21" s="3"/>
+      <c r="BF21" s="3"/>
+      <c r="BG21" s="3"/>
+      <c r="BH21" s="3"/>
+      <c r="BI21" s="3"/>
+      <c r="BJ21" s="3"/>
+      <c r="BK21" s="3"/>
+      <c r="BL21" s="3"/>
+      <c r="BM21" s="3"/>
+      <c r="BN21" s="3"/>
+      <c r="BO21" s="3"/>
+      <c r="BP21" s="3"/>
+      <c r="BQ21" s="3"/>
+      <c r="BR21" s="3"/>
+      <c r="BS21" s="3"/>
+      <c r="BT21" s="3"/>
+      <c r="BU21" s="3"/>
+      <c r="BV21" s="3"/>
+      <c r="BW21" s="3"/>
+      <c r="BX21" s="3"/>
+      <c r="BY21" s="3"/>
+      <c r="BZ21" s="3"/>
+      <c r="CA21" s="3"/>
+      <c r="CB21" s="3"/>
+      <c r="CC21" s="3"/>
+      <c r="CD21" s="3"/>
+      <c r="CE21" s="3"/>
+      <c r="CF21" s="3"/>
+      <c r="CG21" s="3"/>
+      <c r="CH21" s="3"/>
+      <c r="CI21" s="3"/>
+      <c r="CJ21" s="3"/>
+      <c r="CK21" s="3"/>
+      <c r="CL21" s="3"/>
+      <c r="CM21" s="3"/>
+      <c r="CN21" s="3"/>
+      <c r="CO21" s="3"/>
+      <c r="CP21" s="3"/>
+      <c r="CQ21" s="3"/>
+      <c r="CR21" s="3"/>
+      <c r="CS21" s="3"/>
+      <c r="CT21" s="3"/>
+      <c r="CU21" s="3"/>
+      <c r="CV21" s="3"/>
+      <c r="CW21" s="3"/>
+      <c r="CX21" s="3"/>
+      <c r="CY21" s="3"/>
+      <c r="CZ21" s="3"/>
+      <c r="DA21" s="3"/>
+      <c r="DB21" s="3"/>
+      <c r="DC21" s="3"/>
+      <c r="DD21" s="3"/>
+      <c r="DE21" s="3"/>
+      <c r="DF21" s="3"/>
+      <c r="DG21" s="3"/>
+      <c r="DH21" s="3"/>
+      <c r="DI21" s="3"/>
+      <c r="DJ21" s="3"/>
+      <c r="DK21" s="3"/>
+      <c r="DL21" s="3"/>
+      <c r="DM21" s="3"/>
+      <c r="DN21" s="3"/>
+      <c r="DO21" s="3"/>
+      <c r="DP21" s="3"/>
+      <c r="DQ21" s="3"/>
+      <c r="DR21" s="3"/>
+      <c r="DS21" s="3"/>
+      <c r="DT21" s="3"/>
     </row>
     <row r="22" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A22">
@@ -5101,7 +5157,7 @@
       <c r="I22" t="s">
         <v>31</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J22" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K22" t="s">
@@ -5215,81 +5271,84 @@
       <c r="AU22" t="s">
         <v>31</v>
       </c>
-      <c r="AV22" s="2"/>
-      <c r="AW22" s="2"/>
-      <c r="AX22" s="2"/>
-      <c r="BA22" s="5"/>
-      <c r="BB22" s="5"/>
-      <c r="BC22" s="5"/>
-      <c r="BD22" s="5"/>
-      <c r="BE22" s="5"/>
-      <c r="BF22" s="5"/>
-      <c r="BG22" s="5"/>
-      <c r="BH22" s="5"/>
-      <c r="BI22" s="5"/>
-      <c r="BJ22" s="5"/>
-      <c r="BK22" s="5"/>
-      <c r="BL22" s="5"/>
-      <c r="BM22" s="5"/>
-      <c r="BN22" s="5"/>
-      <c r="BO22" s="5"/>
-      <c r="BP22" s="5"/>
-      <c r="BQ22" s="5"/>
-      <c r="BR22" s="5"/>
-      <c r="BS22" s="5"/>
-      <c r="BT22" s="5"/>
-      <c r="BU22" s="5"/>
-      <c r="BV22" s="5"/>
-      <c r="BW22" s="5"/>
-      <c r="BX22" s="5"/>
-      <c r="BY22" s="5"/>
-      <c r="BZ22" s="5"/>
-      <c r="CA22" s="5"/>
-      <c r="CB22" s="5"/>
-      <c r="CC22" s="5"/>
-      <c r="CD22" s="5"/>
-      <c r="CE22" s="5"/>
-      <c r="CF22" s="5"/>
-      <c r="CG22" s="5"/>
-      <c r="CH22" s="5"/>
-      <c r="CI22" s="5"/>
-      <c r="CJ22" s="5"/>
-      <c r="CK22" s="5"/>
-      <c r="CL22" s="5"/>
-      <c r="CM22" s="5"/>
-      <c r="CN22" s="5"/>
-      <c r="CO22" s="5"/>
-      <c r="CP22" s="5"/>
-      <c r="CQ22" s="5"/>
-      <c r="CR22" s="5"/>
-      <c r="CS22" s="5"/>
-      <c r="CT22" s="5"/>
-      <c r="CU22" s="5"/>
-      <c r="CV22" s="5"/>
-      <c r="CW22" s="5"/>
-      <c r="CX22" s="5"/>
-      <c r="CY22" s="5"/>
-      <c r="CZ22" s="5"/>
-      <c r="DA22" s="5"/>
-      <c r="DB22" s="5"/>
-      <c r="DC22" s="5"/>
-      <c r="DD22" s="5"/>
-      <c r="DE22" s="5"/>
-      <c r="DF22" s="5"/>
-      <c r="DG22" s="5"/>
-      <c r="DH22" s="5"/>
-      <c r="DI22" s="5"/>
-      <c r="DJ22" s="5"/>
-      <c r="DK22" s="5"/>
-      <c r="DL22" s="5"/>
-      <c r="DM22" s="5"/>
-      <c r="DN22" s="5"/>
-      <c r="DO22" s="5"/>
-      <c r="DP22" s="5"/>
-      <c r="DQ22" s="5"/>
-      <c r="DR22" s="5"/>
-      <c r="DS22" s="5"/>
-      <c r="DT22" s="5"/>
+      <c r="AV22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW22" s="3"/>
+      <c r="AX22" s="3"/>
+      <c r="AY22" s="3"/>
+      <c r="BA22" s="3"/>
+      <c r="BB22" s="3"/>
+      <c r="BC22" s="3"/>
+      <c r="BD22" s="3"/>
+      <c r="BE22" s="3"/>
+      <c r="BF22" s="3"/>
+      <c r="BG22" s="3"/>
+      <c r="BH22" s="3"/>
+      <c r="BI22" s="3"/>
+      <c r="BJ22" s="3"/>
+      <c r="BK22" s="3"/>
+      <c r="BL22" s="3"/>
+      <c r="BM22" s="3"/>
+      <c r="BN22" s="3"/>
+      <c r="BO22" s="3"/>
+      <c r="BP22" s="3"/>
+      <c r="BQ22" s="3"/>
+      <c r="BR22" s="3"/>
+      <c r="BS22" s="3"/>
+      <c r="BT22" s="3"/>
+      <c r="BU22" s="3"/>
+      <c r="BV22" s="3"/>
+      <c r="BW22" s="3"/>
+      <c r="BX22" s="3"/>
+      <c r="BY22" s="3"/>
+      <c r="BZ22" s="3"/>
+      <c r="CA22" s="3"/>
+      <c r="CB22" s="3"/>
+      <c r="CC22" s="3"/>
+      <c r="CD22" s="3"/>
+      <c r="CE22" s="3"/>
+      <c r="CF22" s="3"/>
+      <c r="CG22" s="3"/>
+      <c r="CH22" s="3"/>
+      <c r="CI22" s="3"/>
+      <c r="CJ22" s="3"/>
+      <c r="CK22" s="3"/>
+      <c r="CL22" s="3"/>
+      <c r="CM22" s="3"/>
+      <c r="CN22" s="3"/>
+      <c r="CO22" s="3"/>
+      <c r="CP22" s="3"/>
+      <c r="CQ22" s="3"/>
+      <c r="CR22" s="3"/>
+      <c r="CS22" s="3"/>
+      <c r="CT22" s="3"/>
+      <c r="CU22" s="3"/>
+      <c r="CV22" s="3"/>
+      <c r="CW22" s="3"/>
+      <c r="CX22" s="3"/>
+      <c r="CY22" s="3"/>
+      <c r="CZ22" s="3"/>
+      <c r="DA22" s="3"/>
+      <c r="DB22" s="3"/>
+      <c r="DC22" s="3"/>
+      <c r="DD22" s="3"/>
+      <c r="DE22" s="3"/>
+      <c r="DF22" s="3"/>
+      <c r="DG22" s="3"/>
+      <c r="DH22" s="3"/>
+      <c r="DI22" s="3"/>
+      <c r="DJ22" s="3"/>
+      <c r="DK22" s="3"/>
+      <c r="DL22" s="3"/>
+      <c r="DM22" s="3"/>
+      <c r="DN22" s="3"/>
+      <c r="DO22" s="3"/>
+      <c r="DP22" s="3"/>
+      <c r="DQ22" s="3"/>
+      <c r="DR22" s="3"/>
+      <c r="DS22" s="3"/>
+      <c r="DT22" s="3"/>
     </row>
     <row r="23" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A23">
@@ -5320,7 +5379,7 @@
       <c r="I23" t="s">
         <v>31</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="J23" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K23" t="s">
@@ -5434,81 +5493,84 @@
       <c r="AU23" t="s">
         <v>31</v>
       </c>
-      <c r="AV23" s="2"/>
-      <c r="AW23" s="2"/>
-      <c r="AX23" s="2"/>
-      <c r="BA23" s="5"/>
-      <c r="BB23" s="5"/>
-      <c r="BC23" s="5"/>
-      <c r="BD23" s="5"/>
-      <c r="BE23" s="5"/>
-      <c r="BF23" s="5"/>
-      <c r="BG23" s="5"/>
-      <c r="BH23" s="5"/>
-      <c r="BI23" s="5"/>
-      <c r="BJ23" s="5"/>
-      <c r="BK23" s="5"/>
-      <c r="BL23" s="5"/>
-      <c r="BM23" s="5"/>
-      <c r="BN23" s="5"/>
-      <c r="BO23" s="5"/>
-      <c r="BP23" s="5"/>
-      <c r="BQ23" s="5"/>
-      <c r="BR23" s="5"/>
-      <c r="BS23" s="5"/>
-      <c r="BT23" s="5"/>
-      <c r="BU23" s="5"/>
-      <c r="BV23" s="5"/>
-      <c r="BW23" s="5"/>
-      <c r="BX23" s="5"/>
-      <c r="BY23" s="5"/>
-      <c r="BZ23" s="5"/>
-      <c r="CA23" s="5"/>
-      <c r="CB23" s="5"/>
-      <c r="CC23" s="5"/>
-      <c r="CD23" s="5"/>
-      <c r="CE23" s="5"/>
-      <c r="CF23" s="5"/>
-      <c r="CG23" s="5"/>
-      <c r="CH23" s="5"/>
-      <c r="CI23" s="5"/>
-      <c r="CJ23" s="5"/>
-      <c r="CK23" s="5"/>
-      <c r="CL23" s="5"/>
-      <c r="CM23" s="5"/>
-      <c r="CN23" s="5"/>
-      <c r="CO23" s="5"/>
-      <c r="CP23" s="5"/>
-      <c r="CQ23" s="5"/>
-      <c r="CR23" s="5"/>
-      <c r="CS23" s="5"/>
-      <c r="CT23" s="5"/>
-      <c r="CU23" s="5"/>
-      <c r="CV23" s="5"/>
-      <c r="CW23" s="5"/>
-      <c r="CX23" s="5"/>
-      <c r="CY23" s="5"/>
-      <c r="CZ23" s="5"/>
-      <c r="DA23" s="5"/>
-      <c r="DB23" s="5"/>
-      <c r="DC23" s="5"/>
-      <c r="DD23" s="5"/>
-      <c r="DE23" s="5"/>
-      <c r="DF23" s="5"/>
-      <c r="DG23" s="5"/>
-      <c r="DH23" s="5"/>
-      <c r="DI23" s="5"/>
-      <c r="DJ23" s="5"/>
-      <c r="DK23" s="5"/>
-      <c r="DL23" s="5"/>
-      <c r="DM23" s="5"/>
-      <c r="DN23" s="5"/>
-      <c r="DO23" s="5"/>
-      <c r="DP23" s="5"/>
-      <c r="DQ23" s="5"/>
-      <c r="DR23" s="5"/>
-      <c r="DS23" s="5"/>
-      <c r="DT23" s="5"/>
+      <c r="AV23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW23" s="3"/>
+      <c r="AX23" s="3"/>
+      <c r="AY23" s="3"/>
+      <c r="BA23" s="3"/>
+      <c r="BB23" s="3"/>
+      <c r="BC23" s="3"/>
+      <c r="BD23" s="3"/>
+      <c r="BE23" s="3"/>
+      <c r="BF23" s="3"/>
+      <c r="BG23" s="3"/>
+      <c r="BH23" s="3"/>
+      <c r="BI23" s="3"/>
+      <c r="BJ23" s="3"/>
+      <c r="BK23" s="3"/>
+      <c r="BL23" s="3"/>
+      <c r="BM23" s="3"/>
+      <c r="BN23" s="3"/>
+      <c r="BO23" s="3"/>
+      <c r="BP23" s="3"/>
+      <c r="BQ23" s="3"/>
+      <c r="BR23" s="3"/>
+      <c r="BS23" s="3"/>
+      <c r="BT23" s="3"/>
+      <c r="BU23" s="3"/>
+      <c r="BV23" s="3"/>
+      <c r="BW23" s="3"/>
+      <c r="BX23" s="3"/>
+      <c r="BY23" s="3"/>
+      <c r="BZ23" s="3"/>
+      <c r="CA23" s="3"/>
+      <c r="CB23" s="3"/>
+      <c r="CC23" s="3"/>
+      <c r="CD23" s="3"/>
+      <c r="CE23" s="3"/>
+      <c r="CF23" s="3"/>
+      <c r="CG23" s="3"/>
+      <c r="CH23" s="3"/>
+      <c r="CI23" s="3"/>
+      <c r="CJ23" s="3"/>
+      <c r="CK23" s="3"/>
+      <c r="CL23" s="3"/>
+      <c r="CM23" s="3"/>
+      <c r="CN23" s="3"/>
+      <c r="CO23" s="3"/>
+      <c r="CP23" s="3"/>
+      <c r="CQ23" s="3"/>
+      <c r="CR23" s="3"/>
+      <c r="CS23" s="3"/>
+      <c r="CT23" s="3"/>
+      <c r="CU23" s="3"/>
+      <c r="CV23" s="3"/>
+      <c r="CW23" s="3"/>
+      <c r="CX23" s="3"/>
+      <c r="CY23" s="3"/>
+      <c r="CZ23" s="3"/>
+      <c r="DA23" s="3"/>
+      <c r="DB23" s="3"/>
+      <c r="DC23" s="3"/>
+      <c r="DD23" s="3"/>
+      <c r="DE23" s="3"/>
+      <c r="DF23" s="3"/>
+      <c r="DG23" s="3"/>
+      <c r="DH23" s="3"/>
+      <c r="DI23" s="3"/>
+      <c r="DJ23" s="3"/>
+      <c r="DK23" s="3"/>
+      <c r="DL23" s="3"/>
+      <c r="DM23" s="3"/>
+      <c r="DN23" s="3"/>
+      <c r="DO23" s="3"/>
+      <c r="DP23" s="3"/>
+      <c r="DQ23" s="3"/>
+      <c r="DR23" s="3"/>
+      <c r="DS23" s="3"/>
+      <c r="DT23" s="3"/>
     </row>
     <row r="24" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A24">
@@ -5539,7 +5601,7 @@
       <c r="I24" t="s">
         <v>31</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K24" t="s">
@@ -5653,81 +5715,84 @@
       <c r="AU24" t="s">
         <v>31</v>
       </c>
-      <c r="AV24" s="2"/>
-      <c r="AW24" s="2"/>
-      <c r="AX24" s="2"/>
-      <c r="BA24" s="5"/>
-      <c r="BB24" s="5"/>
-      <c r="BC24" s="5"/>
-      <c r="BD24" s="5"/>
-      <c r="BE24" s="5"/>
-      <c r="BF24" s="5"/>
-      <c r="BG24" s="5"/>
-      <c r="BH24" s="5"/>
-      <c r="BI24" s="5"/>
-      <c r="BJ24" s="5"/>
-      <c r="BK24" s="5"/>
-      <c r="BL24" s="5"/>
-      <c r="BM24" s="5"/>
-      <c r="BN24" s="5"/>
-      <c r="BO24" s="5"/>
-      <c r="BP24" s="5"/>
-      <c r="BQ24" s="5"/>
-      <c r="BR24" s="5"/>
-      <c r="BS24" s="5"/>
-      <c r="BT24" s="5"/>
-      <c r="BU24" s="5"/>
-      <c r="BV24" s="5"/>
-      <c r="BW24" s="5"/>
-      <c r="BX24" s="5"/>
-      <c r="BY24" s="5"/>
-      <c r="BZ24" s="5"/>
-      <c r="CA24" s="5"/>
-      <c r="CB24" s="5"/>
-      <c r="CC24" s="5"/>
-      <c r="CD24" s="5"/>
-      <c r="CE24" s="5"/>
-      <c r="CF24" s="5"/>
-      <c r="CG24" s="5"/>
-      <c r="CH24" s="5"/>
-      <c r="CI24" s="5"/>
-      <c r="CJ24" s="5"/>
-      <c r="CK24" s="5"/>
-      <c r="CL24" s="5"/>
-      <c r="CM24" s="5"/>
-      <c r="CN24" s="5"/>
-      <c r="CO24" s="5"/>
-      <c r="CP24" s="5"/>
-      <c r="CQ24" s="5"/>
-      <c r="CR24" s="5"/>
-      <c r="CS24" s="5"/>
-      <c r="CT24" s="5"/>
-      <c r="CU24" s="5"/>
-      <c r="CV24" s="5"/>
-      <c r="CW24" s="5"/>
-      <c r="CX24" s="5"/>
-      <c r="CY24" s="5"/>
-      <c r="CZ24" s="5"/>
-      <c r="DA24" s="5"/>
-      <c r="DB24" s="5"/>
-      <c r="DC24" s="5"/>
-      <c r="DD24" s="5"/>
-      <c r="DE24" s="5"/>
-      <c r="DF24" s="5"/>
-      <c r="DG24" s="5"/>
-      <c r="DH24" s="5"/>
-      <c r="DI24" s="5"/>
-      <c r="DJ24" s="5"/>
-      <c r="DK24" s="5"/>
-      <c r="DL24" s="5"/>
-      <c r="DM24" s="5"/>
-      <c r="DN24" s="5"/>
-      <c r="DO24" s="5"/>
-      <c r="DP24" s="5"/>
-      <c r="DQ24" s="5"/>
-      <c r="DR24" s="5"/>
-      <c r="DS24" s="5"/>
-      <c r="DT24" s="5"/>
+      <c r="AV24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW24" s="3"/>
+      <c r="AX24" s="3"/>
+      <c r="AY24" s="3"/>
+      <c r="BA24" s="3"/>
+      <c r="BB24" s="3"/>
+      <c r="BC24" s="3"/>
+      <c r="BD24" s="3"/>
+      <c r="BE24" s="3"/>
+      <c r="BF24" s="3"/>
+      <c r="BG24" s="3"/>
+      <c r="BH24" s="3"/>
+      <c r="BI24" s="3"/>
+      <c r="BJ24" s="3"/>
+      <c r="BK24" s="3"/>
+      <c r="BL24" s="3"/>
+      <c r="BM24" s="3"/>
+      <c r="BN24" s="3"/>
+      <c r="BO24" s="3"/>
+      <c r="BP24" s="3"/>
+      <c r="BQ24" s="3"/>
+      <c r="BR24" s="3"/>
+      <c r="BS24" s="3"/>
+      <c r="BT24" s="3"/>
+      <c r="BU24" s="3"/>
+      <c r="BV24" s="3"/>
+      <c r="BW24" s="3"/>
+      <c r="BX24" s="3"/>
+      <c r="BY24" s="3"/>
+      <c r="BZ24" s="3"/>
+      <c r="CA24" s="3"/>
+      <c r="CB24" s="3"/>
+      <c r="CC24" s="3"/>
+      <c r="CD24" s="3"/>
+      <c r="CE24" s="3"/>
+      <c r="CF24" s="3"/>
+      <c r="CG24" s="3"/>
+      <c r="CH24" s="3"/>
+      <c r="CI24" s="3"/>
+      <c r="CJ24" s="3"/>
+      <c r="CK24" s="3"/>
+      <c r="CL24" s="3"/>
+      <c r="CM24" s="3"/>
+      <c r="CN24" s="3"/>
+      <c r="CO24" s="3"/>
+      <c r="CP24" s="3"/>
+      <c r="CQ24" s="3"/>
+      <c r="CR24" s="3"/>
+      <c r="CS24" s="3"/>
+      <c r="CT24" s="3"/>
+      <c r="CU24" s="3"/>
+      <c r="CV24" s="3"/>
+      <c r="CW24" s="3"/>
+      <c r="CX24" s="3"/>
+      <c r="CY24" s="3"/>
+      <c r="CZ24" s="3"/>
+      <c r="DA24" s="3"/>
+      <c r="DB24" s="3"/>
+      <c r="DC24" s="3"/>
+      <c r="DD24" s="3"/>
+      <c r="DE24" s="3"/>
+      <c r="DF24" s="3"/>
+      <c r="DG24" s="3"/>
+      <c r="DH24" s="3"/>
+      <c r="DI24" s="3"/>
+      <c r="DJ24" s="3"/>
+      <c r="DK24" s="3"/>
+      <c r="DL24" s="3"/>
+      <c r="DM24" s="3"/>
+      <c r="DN24" s="3"/>
+      <c r="DO24" s="3"/>
+      <c r="DP24" s="3"/>
+      <c r="DQ24" s="3"/>
+      <c r="DR24" s="3"/>
+      <c r="DS24" s="3"/>
+      <c r="DT24" s="3"/>
     </row>
     <row r="25" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A25">
@@ -5758,7 +5823,7 @@
       <c r="I25" t="s">
         <v>31</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="J25" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K25" t="s">
@@ -5872,81 +5937,84 @@
       <c r="AU25" t="s">
         <v>31</v>
       </c>
-      <c r="AV25" s="2"/>
-      <c r="AW25" s="2"/>
-      <c r="AX25" s="2"/>
-      <c r="BA25" s="5"/>
-      <c r="BB25" s="5"/>
-      <c r="BC25" s="5"/>
-      <c r="BD25" s="5"/>
-      <c r="BE25" s="5"/>
-      <c r="BF25" s="5"/>
-      <c r="BG25" s="5"/>
-      <c r="BH25" s="5"/>
-      <c r="BI25" s="5"/>
-      <c r="BJ25" s="5"/>
-      <c r="BK25" s="5"/>
-      <c r="BL25" s="5"/>
-      <c r="BM25" s="5"/>
-      <c r="BN25" s="5"/>
-      <c r="BO25" s="5"/>
-      <c r="BP25" s="5"/>
-      <c r="BQ25" s="5"/>
-      <c r="BR25" s="5"/>
-      <c r="BS25" s="5"/>
-      <c r="BT25" s="5"/>
-      <c r="BU25" s="5"/>
-      <c r="BV25" s="5"/>
-      <c r="BW25" s="5"/>
-      <c r="BX25" s="5"/>
-      <c r="BY25" s="5"/>
-      <c r="BZ25" s="5"/>
-      <c r="CA25" s="5"/>
-      <c r="CB25" s="5"/>
-      <c r="CC25" s="5"/>
-      <c r="CD25" s="5"/>
-      <c r="CE25" s="5"/>
-      <c r="CF25" s="5"/>
-      <c r="CG25" s="5"/>
-      <c r="CH25" s="5"/>
-      <c r="CI25" s="5"/>
-      <c r="CJ25" s="5"/>
-      <c r="CK25" s="5"/>
-      <c r="CL25" s="5"/>
-      <c r="CM25" s="5"/>
-      <c r="CN25" s="5"/>
-      <c r="CO25" s="5"/>
-      <c r="CP25" s="5"/>
-      <c r="CQ25" s="5"/>
-      <c r="CR25" s="5"/>
-      <c r="CS25" s="5"/>
-      <c r="CT25" s="5"/>
-      <c r="CU25" s="5"/>
-      <c r="CV25" s="5"/>
-      <c r="CW25" s="5"/>
-      <c r="CX25" s="5"/>
-      <c r="CY25" s="5"/>
-      <c r="CZ25" s="5"/>
-      <c r="DA25" s="5"/>
-      <c r="DB25" s="5"/>
-      <c r="DC25" s="5"/>
-      <c r="DD25" s="5"/>
-      <c r="DE25" s="5"/>
-      <c r="DF25" s="5"/>
-      <c r="DG25" s="5"/>
-      <c r="DH25" s="5"/>
-      <c r="DI25" s="5"/>
-      <c r="DJ25" s="5"/>
-      <c r="DK25" s="5"/>
-      <c r="DL25" s="5"/>
-      <c r="DM25" s="5"/>
-      <c r="DN25" s="5"/>
-      <c r="DO25" s="5"/>
-      <c r="DP25" s="5"/>
-      <c r="DQ25" s="5"/>
-      <c r="DR25" s="5"/>
-      <c r="DS25" s="5"/>
-      <c r="DT25" s="5"/>
+      <c r="AV25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW25" s="3"/>
+      <c r="AX25" s="3"/>
+      <c r="AY25" s="3"/>
+      <c r="BA25" s="3"/>
+      <c r="BB25" s="3"/>
+      <c r="BC25" s="3"/>
+      <c r="BD25" s="3"/>
+      <c r="BE25" s="3"/>
+      <c r="BF25" s="3"/>
+      <c r="BG25" s="3"/>
+      <c r="BH25" s="3"/>
+      <c r="BI25" s="3"/>
+      <c r="BJ25" s="3"/>
+      <c r="BK25" s="3"/>
+      <c r="BL25" s="3"/>
+      <c r="BM25" s="3"/>
+      <c r="BN25" s="3"/>
+      <c r="BO25" s="3"/>
+      <c r="BP25" s="3"/>
+      <c r="BQ25" s="3"/>
+      <c r="BR25" s="3"/>
+      <c r="BS25" s="3"/>
+      <c r="BT25" s="3"/>
+      <c r="BU25" s="3"/>
+      <c r="BV25" s="3"/>
+      <c r="BW25" s="3"/>
+      <c r="BX25" s="3"/>
+      <c r="BY25" s="3"/>
+      <c r="BZ25" s="3"/>
+      <c r="CA25" s="3"/>
+      <c r="CB25" s="3"/>
+      <c r="CC25" s="3"/>
+      <c r="CD25" s="3"/>
+      <c r="CE25" s="3"/>
+      <c r="CF25" s="3"/>
+      <c r="CG25" s="3"/>
+      <c r="CH25" s="3"/>
+      <c r="CI25" s="3"/>
+      <c r="CJ25" s="3"/>
+      <c r="CK25" s="3"/>
+      <c r="CL25" s="3"/>
+      <c r="CM25" s="3"/>
+      <c r="CN25" s="3"/>
+      <c r="CO25" s="3"/>
+      <c r="CP25" s="3"/>
+      <c r="CQ25" s="3"/>
+      <c r="CR25" s="3"/>
+      <c r="CS25" s="3"/>
+      <c r="CT25" s="3"/>
+      <c r="CU25" s="3"/>
+      <c r="CV25" s="3"/>
+      <c r="CW25" s="3"/>
+      <c r="CX25" s="3"/>
+      <c r="CY25" s="3"/>
+      <c r="CZ25" s="3"/>
+      <c r="DA25" s="3"/>
+      <c r="DB25" s="3"/>
+      <c r="DC25" s="3"/>
+      <c r="DD25" s="3"/>
+      <c r="DE25" s="3"/>
+      <c r="DF25" s="3"/>
+      <c r="DG25" s="3"/>
+      <c r="DH25" s="3"/>
+      <c r="DI25" s="3"/>
+      <c r="DJ25" s="3"/>
+      <c r="DK25" s="3"/>
+      <c r="DL25" s="3"/>
+      <c r="DM25" s="3"/>
+      <c r="DN25" s="3"/>
+      <c r="DO25" s="3"/>
+      <c r="DP25" s="3"/>
+      <c r="DQ25" s="3"/>
+      <c r="DR25" s="3"/>
+      <c r="DS25" s="3"/>
+      <c r="DT25" s="3"/>
     </row>
     <row r="26" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A26">
@@ -5977,7 +6045,7 @@
       <c r="I26" t="s">
         <v>31</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="J26" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K26" t="s">
@@ -6091,81 +6159,84 @@
       <c r="AU26" t="s">
         <v>31</v>
       </c>
-      <c r="AV26" s="2"/>
-      <c r="AW26" s="2"/>
-      <c r="AX26" s="2"/>
-      <c r="BA26" s="5"/>
-      <c r="BB26" s="5"/>
-      <c r="BC26" s="5"/>
-      <c r="BD26" s="5"/>
-      <c r="BE26" s="5"/>
-      <c r="BF26" s="5"/>
-      <c r="BG26" s="5"/>
-      <c r="BH26" s="5"/>
-      <c r="BI26" s="5"/>
-      <c r="BJ26" s="5"/>
-      <c r="BK26" s="5"/>
-      <c r="BL26" s="5"/>
-      <c r="BM26" s="5"/>
-      <c r="BN26" s="5"/>
-      <c r="BO26" s="5"/>
-      <c r="BP26" s="5"/>
-      <c r="BQ26" s="5"/>
-      <c r="BR26" s="5"/>
-      <c r="BS26" s="5"/>
-      <c r="BT26" s="5"/>
-      <c r="BU26" s="5"/>
-      <c r="BV26" s="5"/>
-      <c r="BW26" s="5"/>
-      <c r="BX26" s="5"/>
-      <c r="BY26" s="5"/>
-      <c r="BZ26" s="5"/>
-      <c r="CA26" s="5"/>
-      <c r="CB26" s="5"/>
-      <c r="CC26" s="5"/>
-      <c r="CD26" s="5"/>
-      <c r="CE26" s="5"/>
-      <c r="CF26" s="5"/>
-      <c r="CG26" s="5"/>
-      <c r="CH26" s="5"/>
-      <c r="CI26" s="5"/>
-      <c r="CJ26" s="5"/>
-      <c r="CK26" s="5"/>
-      <c r="CL26" s="5"/>
-      <c r="CM26" s="5"/>
-      <c r="CN26" s="5"/>
-      <c r="CO26" s="5"/>
-      <c r="CP26" s="5"/>
-      <c r="CQ26" s="5"/>
-      <c r="CR26" s="5"/>
-      <c r="CS26" s="5"/>
-      <c r="CT26" s="5"/>
-      <c r="CU26" s="5"/>
-      <c r="CV26" s="5"/>
-      <c r="CW26" s="5"/>
-      <c r="CX26" s="5"/>
-      <c r="CY26" s="5"/>
-      <c r="CZ26" s="5"/>
-      <c r="DA26" s="5"/>
-      <c r="DB26" s="5"/>
-      <c r="DC26" s="5"/>
-      <c r="DD26" s="5"/>
-      <c r="DE26" s="5"/>
-      <c r="DF26" s="5"/>
-      <c r="DG26" s="5"/>
-      <c r="DH26" s="5"/>
-      <c r="DI26" s="5"/>
-      <c r="DJ26" s="5"/>
-      <c r="DK26" s="5"/>
-      <c r="DL26" s="5"/>
-      <c r="DM26" s="5"/>
-      <c r="DN26" s="5"/>
-      <c r="DO26" s="5"/>
-      <c r="DP26" s="5"/>
-      <c r="DQ26" s="5"/>
-      <c r="DR26" s="5"/>
-      <c r="DS26" s="5"/>
-      <c r="DT26" s="5"/>
+      <c r="AV26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW26" s="3"/>
+      <c r="AX26" s="3"/>
+      <c r="AY26" s="3"/>
+      <c r="BA26" s="3"/>
+      <c r="BB26" s="3"/>
+      <c r="BC26" s="3"/>
+      <c r="BD26" s="3"/>
+      <c r="BE26" s="3"/>
+      <c r="BF26" s="3"/>
+      <c r="BG26" s="3"/>
+      <c r="BH26" s="3"/>
+      <c r="BI26" s="3"/>
+      <c r="BJ26" s="3"/>
+      <c r="BK26" s="3"/>
+      <c r="BL26" s="3"/>
+      <c r="BM26" s="3"/>
+      <c r="BN26" s="3"/>
+      <c r="BO26" s="3"/>
+      <c r="BP26" s="3"/>
+      <c r="BQ26" s="3"/>
+      <c r="BR26" s="3"/>
+      <c r="BS26" s="3"/>
+      <c r="BT26" s="3"/>
+      <c r="BU26" s="3"/>
+      <c r="BV26" s="3"/>
+      <c r="BW26" s="3"/>
+      <c r="BX26" s="3"/>
+      <c r="BY26" s="3"/>
+      <c r="BZ26" s="3"/>
+      <c r="CA26" s="3"/>
+      <c r="CB26" s="3"/>
+      <c r="CC26" s="3"/>
+      <c r="CD26" s="3"/>
+      <c r="CE26" s="3"/>
+      <c r="CF26" s="3"/>
+      <c r="CG26" s="3"/>
+      <c r="CH26" s="3"/>
+      <c r="CI26" s="3"/>
+      <c r="CJ26" s="3"/>
+      <c r="CK26" s="3"/>
+      <c r="CL26" s="3"/>
+      <c r="CM26" s="3"/>
+      <c r="CN26" s="3"/>
+      <c r="CO26" s="3"/>
+      <c r="CP26" s="3"/>
+      <c r="CQ26" s="3"/>
+      <c r="CR26" s="3"/>
+      <c r="CS26" s="3"/>
+      <c r="CT26" s="3"/>
+      <c r="CU26" s="3"/>
+      <c r="CV26" s="3"/>
+      <c r="CW26" s="3"/>
+      <c r="CX26" s="3"/>
+      <c r="CY26" s="3"/>
+      <c r="CZ26" s="3"/>
+      <c r="DA26" s="3"/>
+      <c r="DB26" s="3"/>
+      <c r="DC26" s="3"/>
+      <c r="DD26" s="3"/>
+      <c r="DE26" s="3"/>
+      <c r="DF26" s="3"/>
+      <c r="DG26" s="3"/>
+      <c r="DH26" s="3"/>
+      <c r="DI26" s="3"/>
+      <c r="DJ26" s="3"/>
+      <c r="DK26" s="3"/>
+      <c r="DL26" s="3"/>
+      <c r="DM26" s="3"/>
+      <c r="DN26" s="3"/>
+      <c r="DO26" s="3"/>
+      <c r="DP26" s="3"/>
+      <c r="DQ26" s="3"/>
+      <c r="DR26" s="3"/>
+      <c r="DS26" s="3"/>
+      <c r="DT26" s="3"/>
     </row>
     <row r="27" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A27">
@@ -6196,7 +6267,7 @@
       <c r="I27" t="s">
         <v>31</v>
       </c>
-      <c r="J27" s="8" t="s">
+      <c r="J27" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K27" t="s">
@@ -6310,81 +6381,84 @@
       <c r="AU27" t="s">
         <v>32</v>
       </c>
-      <c r="AV27" s="2"/>
-      <c r="AW27" s="2"/>
-      <c r="AX27" s="2"/>
-      <c r="BA27" s="5"/>
-      <c r="BB27" s="5"/>
-      <c r="BC27" s="5"/>
-      <c r="BD27" s="5"/>
-      <c r="BE27" s="5"/>
-      <c r="BF27" s="5"/>
-      <c r="BG27" s="5"/>
-      <c r="BH27" s="5"/>
-      <c r="BI27" s="5"/>
-      <c r="BJ27" s="5"/>
-      <c r="BK27" s="5"/>
-      <c r="BL27" s="5"/>
-      <c r="BM27" s="5"/>
-      <c r="BN27" s="5"/>
-      <c r="BO27" s="5"/>
-      <c r="BP27" s="5"/>
-      <c r="BQ27" s="5"/>
-      <c r="BR27" s="5"/>
-      <c r="BS27" s="5"/>
-      <c r="BT27" s="5"/>
-      <c r="BU27" s="5"/>
-      <c r="BV27" s="5"/>
-      <c r="BW27" s="5"/>
-      <c r="BX27" s="5"/>
-      <c r="BY27" s="5"/>
-      <c r="BZ27" s="5"/>
-      <c r="CA27" s="5"/>
-      <c r="CB27" s="5"/>
-      <c r="CC27" s="5"/>
-      <c r="CD27" s="5"/>
-      <c r="CE27" s="5"/>
-      <c r="CF27" s="5"/>
-      <c r="CG27" s="5"/>
-      <c r="CH27" s="5"/>
-      <c r="CI27" s="5"/>
-      <c r="CJ27" s="5"/>
-      <c r="CK27" s="5"/>
-      <c r="CL27" s="5"/>
-      <c r="CM27" s="5"/>
-      <c r="CN27" s="5"/>
-      <c r="CO27" s="5"/>
-      <c r="CP27" s="5"/>
-      <c r="CQ27" s="5"/>
-      <c r="CR27" s="5"/>
-      <c r="CS27" s="5"/>
-      <c r="CT27" s="5"/>
-      <c r="CU27" s="5"/>
-      <c r="CV27" s="5"/>
-      <c r="CW27" s="5"/>
-      <c r="CX27" s="5"/>
-      <c r="CY27" s="5"/>
-      <c r="CZ27" s="5"/>
-      <c r="DA27" s="5"/>
-      <c r="DB27" s="5"/>
-      <c r="DC27" s="5"/>
-      <c r="DD27" s="5"/>
-      <c r="DE27" s="5"/>
-      <c r="DF27" s="5"/>
-      <c r="DG27" s="5"/>
-      <c r="DH27" s="5"/>
-      <c r="DI27" s="5"/>
-      <c r="DJ27" s="5"/>
-      <c r="DK27" s="5"/>
-      <c r="DL27" s="5"/>
-      <c r="DM27" s="5"/>
-      <c r="DN27" s="5"/>
-      <c r="DO27" s="5"/>
-      <c r="DP27" s="5"/>
-      <c r="DQ27" s="5"/>
-      <c r="DR27" s="5"/>
-      <c r="DS27" s="5"/>
-      <c r="DT27" s="5"/>
+      <c r="AV27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW27" s="3"/>
+      <c r="AX27" s="3"/>
+      <c r="AY27" s="3"/>
+      <c r="BA27" s="3"/>
+      <c r="BB27" s="3"/>
+      <c r="BC27" s="3"/>
+      <c r="BD27" s="3"/>
+      <c r="BE27" s="3"/>
+      <c r="BF27" s="3"/>
+      <c r="BG27" s="3"/>
+      <c r="BH27" s="3"/>
+      <c r="BI27" s="3"/>
+      <c r="BJ27" s="3"/>
+      <c r="BK27" s="3"/>
+      <c r="BL27" s="3"/>
+      <c r="BM27" s="3"/>
+      <c r="BN27" s="3"/>
+      <c r="BO27" s="3"/>
+      <c r="BP27" s="3"/>
+      <c r="BQ27" s="3"/>
+      <c r="BR27" s="3"/>
+      <c r="BS27" s="3"/>
+      <c r="BT27" s="3"/>
+      <c r="BU27" s="3"/>
+      <c r="BV27" s="3"/>
+      <c r="BW27" s="3"/>
+      <c r="BX27" s="3"/>
+      <c r="BY27" s="3"/>
+      <c r="BZ27" s="3"/>
+      <c r="CA27" s="3"/>
+      <c r="CB27" s="3"/>
+      <c r="CC27" s="3"/>
+      <c r="CD27" s="3"/>
+      <c r="CE27" s="3"/>
+      <c r="CF27" s="3"/>
+      <c r="CG27" s="3"/>
+      <c r="CH27" s="3"/>
+      <c r="CI27" s="3"/>
+      <c r="CJ27" s="3"/>
+      <c r="CK27" s="3"/>
+      <c r="CL27" s="3"/>
+      <c r="CM27" s="3"/>
+      <c r="CN27" s="3"/>
+      <c r="CO27" s="3"/>
+      <c r="CP27" s="3"/>
+      <c r="CQ27" s="3"/>
+      <c r="CR27" s="3"/>
+      <c r="CS27" s="3"/>
+      <c r="CT27" s="3"/>
+      <c r="CU27" s="3"/>
+      <c r="CV27" s="3"/>
+      <c r="CW27" s="3"/>
+      <c r="CX27" s="3"/>
+      <c r="CY27" s="3"/>
+      <c r="CZ27" s="3"/>
+      <c r="DA27" s="3"/>
+      <c r="DB27" s="3"/>
+      <c r="DC27" s="3"/>
+      <c r="DD27" s="3"/>
+      <c r="DE27" s="3"/>
+      <c r="DF27" s="3"/>
+      <c r="DG27" s="3"/>
+      <c r="DH27" s="3"/>
+      <c r="DI27" s="3"/>
+      <c r="DJ27" s="3"/>
+      <c r="DK27" s="3"/>
+      <c r="DL27" s="3"/>
+      <c r="DM27" s="3"/>
+      <c r="DN27" s="3"/>
+      <c r="DO27" s="3"/>
+      <c r="DP27" s="3"/>
+      <c r="DQ27" s="3"/>
+      <c r="DR27" s="3"/>
+      <c r="DS27" s="3"/>
+      <c r="DT27" s="3"/>
     </row>
     <row r="28" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A28">
@@ -6415,7 +6489,7 @@
       <c r="I28" t="s">
         <v>31</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="J28" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K28" t="s">
@@ -6529,81 +6603,84 @@
       <c r="AU28" t="s">
         <v>31</v>
       </c>
-      <c r="AV28" s="2"/>
-      <c r="AW28" s="2"/>
-      <c r="AX28" s="2"/>
-      <c r="BA28" s="5"/>
-      <c r="BB28" s="5"/>
-      <c r="BC28" s="5"/>
-      <c r="BD28" s="5"/>
-      <c r="BE28" s="5"/>
-      <c r="BF28" s="5"/>
-      <c r="BG28" s="5"/>
-      <c r="BH28" s="5"/>
-      <c r="BI28" s="5"/>
-      <c r="BJ28" s="5"/>
-      <c r="BK28" s="5"/>
-      <c r="BL28" s="5"/>
-      <c r="BM28" s="5"/>
-      <c r="BN28" s="5"/>
-      <c r="BO28" s="5"/>
-      <c r="BP28" s="5"/>
-      <c r="BQ28" s="5"/>
-      <c r="BR28" s="5"/>
-      <c r="BS28" s="5"/>
-      <c r="BT28" s="5"/>
-      <c r="BU28" s="5"/>
-      <c r="BV28" s="5"/>
-      <c r="BW28" s="5"/>
-      <c r="BX28" s="5"/>
-      <c r="BY28" s="5"/>
-      <c r="BZ28" s="5"/>
-      <c r="CA28" s="5"/>
-      <c r="CB28" s="5"/>
-      <c r="CC28" s="5"/>
-      <c r="CD28" s="5"/>
-      <c r="CE28" s="5"/>
-      <c r="CF28" s="5"/>
-      <c r="CG28" s="5"/>
-      <c r="CH28" s="5"/>
-      <c r="CI28" s="5"/>
-      <c r="CJ28" s="5"/>
-      <c r="CK28" s="5"/>
-      <c r="CL28" s="5"/>
-      <c r="CM28" s="5"/>
-      <c r="CN28" s="5"/>
-      <c r="CO28" s="5"/>
-      <c r="CP28" s="5"/>
-      <c r="CQ28" s="5"/>
-      <c r="CR28" s="5"/>
-      <c r="CS28" s="5"/>
-      <c r="CT28" s="5"/>
-      <c r="CU28" s="5"/>
-      <c r="CV28" s="5"/>
-      <c r="CW28" s="5"/>
-      <c r="CX28" s="5"/>
-      <c r="CY28" s="5"/>
-      <c r="CZ28" s="5"/>
-      <c r="DA28" s="5"/>
-      <c r="DB28" s="5"/>
-      <c r="DC28" s="5"/>
-      <c r="DD28" s="5"/>
-      <c r="DE28" s="5"/>
-      <c r="DF28" s="5"/>
-      <c r="DG28" s="5"/>
-      <c r="DH28" s="5"/>
-      <c r="DI28" s="5"/>
-      <c r="DJ28" s="5"/>
-      <c r="DK28" s="5"/>
-      <c r="DL28" s="5"/>
-      <c r="DM28" s="5"/>
-      <c r="DN28" s="5"/>
-      <c r="DO28" s="5"/>
-      <c r="DP28" s="5"/>
-      <c r="DQ28" s="5"/>
-      <c r="DR28" s="5"/>
-      <c r="DS28" s="5"/>
-      <c r="DT28" s="5"/>
+      <c r="AV28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW28" s="3"/>
+      <c r="AX28" s="3"/>
+      <c r="AY28" s="3"/>
+      <c r="BA28" s="3"/>
+      <c r="BB28" s="3"/>
+      <c r="BC28" s="3"/>
+      <c r="BD28" s="3"/>
+      <c r="BE28" s="3"/>
+      <c r="BF28" s="3"/>
+      <c r="BG28" s="3"/>
+      <c r="BH28" s="3"/>
+      <c r="BI28" s="3"/>
+      <c r="BJ28" s="3"/>
+      <c r="BK28" s="3"/>
+      <c r="BL28" s="3"/>
+      <c r="BM28" s="3"/>
+      <c r="BN28" s="3"/>
+      <c r="BO28" s="3"/>
+      <c r="BP28" s="3"/>
+      <c r="BQ28" s="3"/>
+      <c r="BR28" s="3"/>
+      <c r="BS28" s="3"/>
+      <c r="BT28" s="3"/>
+      <c r="BU28" s="3"/>
+      <c r="BV28" s="3"/>
+      <c r="BW28" s="3"/>
+      <c r="BX28" s="3"/>
+      <c r="BY28" s="3"/>
+      <c r="BZ28" s="3"/>
+      <c r="CA28" s="3"/>
+      <c r="CB28" s="3"/>
+      <c r="CC28" s="3"/>
+      <c r="CD28" s="3"/>
+      <c r="CE28" s="3"/>
+      <c r="CF28" s="3"/>
+      <c r="CG28" s="3"/>
+      <c r="CH28" s="3"/>
+      <c r="CI28" s="3"/>
+      <c r="CJ28" s="3"/>
+      <c r="CK28" s="3"/>
+      <c r="CL28" s="3"/>
+      <c r="CM28" s="3"/>
+      <c r="CN28" s="3"/>
+      <c r="CO28" s="3"/>
+      <c r="CP28" s="3"/>
+      <c r="CQ28" s="3"/>
+      <c r="CR28" s="3"/>
+      <c r="CS28" s="3"/>
+      <c r="CT28" s="3"/>
+      <c r="CU28" s="3"/>
+      <c r="CV28" s="3"/>
+      <c r="CW28" s="3"/>
+      <c r="CX28" s="3"/>
+      <c r="CY28" s="3"/>
+      <c r="CZ28" s="3"/>
+      <c r="DA28" s="3"/>
+      <c r="DB28" s="3"/>
+      <c r="DC28" s="3"/>
+      <c r="DD28" s="3"/>
+      <c r="DE28" s="3"/>
+      <c r="DF28" s="3"/>
+      <c r="DG28" s="3"/>
+      <c r="DH28" s="3"/>
+      <c r="DI28" s="3"/>
+      <c r="DJ28" s="3"/>
+      <c r="DK28" s="3"/>
+      <c r="DL28" s="3"/>
+      <c r="DM28" s="3"/>
+      <c r="DN28" s="3"/>
+      <c r="DO28" s="3"/>
+      <c r="DP28" s="3"/>
+      <c r="DQ28" s="3"/>
+      <c r="DR28" s="3"/>
+      <c r="DS28" s="3"/>
+      <c r="DT28" s="3"/>
     </row>
     <row r="29" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A29">
@@ -6625,7 +6702,7 @@
       <c r="I29" t="s">
         <v>31</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="J29" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K29" t="s">
@@ -6739,81 +6816,84 @@
       <c r="AU29" t="s">
         <v>31</v>
       </c>
-      <c r="AV29" s="2"/>
-      <c r="AW29" s="2"/>
-      <c r="AX29" s="2"/>
-      <c r="BA29" s="5"/>
-      <c r="BB29" s="5"/>
-      <c r="BC29" s="5"/>
-      <c r="BD29" s="5"/>
-      <c r="BE29" s="5"/>
-      <c r="BF29" s="5"/>
-      <c r="BG29" s="5"/>
-      <c r="BH29" s="5"/>
-      <c r="BI29" s="5"/>
-      <c r="BJ29" s="5"/>
-      <c r="BK29" s="5"/>
-      <c r="BL29" s="5"/>
-      <c r="BM29" s="5"/>
-      <c r="BN29" s="5"/>
-      <c r="BO29" s="5"/>
-      <c r="BP29" s="5"/>
-      <c r="BQ29" s="5"/>
-      <c r="BR29" s="5"/>
-      <c r="BS29" s="5"/>
-      <c r="BT29" s="5"/>
-      <c r="BU29" s="5"/>
-      <c r="BV29" s="5"/>
-      <c r="BW29" s="5"/>
-      <c r="BX29" s="5"/>
-      <c r="BY29" s="5"/>
-      <c r="BZ29" s="5"/>
-      <c r="CA29" s="5"/>
-      <c r="CB29" s="5"/>
-      <c r="CC29" s="5"/>
-      <c r="CD29" s="5"/>
-      <c r="CE29" s="5"/>
-      <c r="CF29" s="5"/>
-      <c r="CG29" s="5"/>
-      <c r="CH29" s="5"/>
-      <c r="CI29" s="5"/>
-      <c r="CJ29" s="5"/>
-      <c r="CK29" s="5"/>
-      <c r="CL29" s="5"/>
-      <c r="CM29" s="5"/>
-      <c r="CN29" s="5"/>
-      <c r="CO29" s="5"/>
-      <c r="CP29" s="5"/>
-      <c r="CQ29" s="5"/>
-      <c r="CR29" s="5"/>
-      <c r="CS29" s="5"/>
-      <c r="CT29" s="5"/>
-      <c r="CU29" s="5"/>
-      <c r="CV29" s="5"/>
-      <c r="CW29" s="5"/>
-      <c r="CX29" s="5"/>
-      <c r="CY29" s="5"/>
-      <c r="CZ29" s="5"/>
-      <c r="DA29" s="5"/>
-      <c r="DB29" s="5"/>
-      <c r="DC29" s="5"/>
-      <c r="DD29" s="5"/>
-      <c r="DE29" s="5"/>
-      <c r="DF29" s="5"/>
-      <c r="DG29" s="5"/>
-      <c r="DH29" s="5"/>
-      <c r="DI29" s="5"/>
-      <c r="DJ29" s="5"/>
-      <c r="DK29" s="5"/>
-      <c r="DL29" s="5"/>
-      <c r="DM29" s="5"/>
-      <c r="DN29" s="5"/>
-      <c r="DO29" s="5"/>
-      <c r="DP29" s="5"/>
-      <c r="DQ29" s="5"/>
-      <c r="DR29" s="5"/>
-      <c r="DS29" s="5"/>
-      <c r="DT29" s="5"/>
+      <c r="AV29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW29" s="3"/>
+      <c r="AX29" s="3"/>
+      <c r="AY29" s="3"/>
+      <c r="BA29" s="3"/>
+      <c r="BB29" s="3"/>
+      <c r="BC29" s="3"/>
+      <c r="BD29" s="3"/>
+      <c r="BE29" s="3"/>
+      <c r="BF29" s="3"/>
+      <c r="BG29" s="3"/>
+      <c r="BH29" s="3"/>
+      <c r="BI29" s="3"/>
+      <c r="BJ29" s="3"/>
+      <c r="BK29" s="3"/>
+      <c r="BL29" s="3"/>
+      <c r="BM29" s="3"/>
+      <c r="BN29" s="3"/>
+      <c r="BO29" s="3"/>
+      <c r="BP29" s="3"/>
+      <c r="BQ29" s="3"/>
+      <c r="BR29" s="3"/>
+      <c r="BS29" s="3"/>
+      <c r="BT29" s="3"/>
+      <c r="BU29" s="3"/>
+      <c r="BV29" s="3"/>
+      <c r="BW29" s="3"/>
+      <c r="BX29" s="3"/>
+      <c r="BY29" s="3"/>
+      <c r="BZ29" s="3"/>
+      <c r="CA29" s="3"/>
+      <c r="CB29" s="3"/>
+      <c r="CC29" s="3"/>
+      <c r="CD29" s="3"/>
+      <c r="CE29" s="3"/>
+      <c r="CF29" s="3"/>
+      <c r="CG29" s="3"/>
+      <c r="CH29" s="3"/>
+      <c r="CI29" s="3"/>
+      <c r="CJ29" s="3"/>
+      <c r="CK29" s="3"/>
+      <c r="CL29" s="3"/>
+      <c r="CM29" s="3"/>
+      <c r="CN29" s="3"/>
+      <c r="CO29" s="3"/>
+      <c r="CP29" s="3"/>
+      <c r="CQ29" s="3"/>
+      <c r="CR29" s="3"/>
+      <c r="CS29" s="3"/>
+      <c r="CT29" s="3"/>
+      <c r="CU29" s="3"/>
+      <c r="CV29" s="3"/>
+      <c r="CW29" s="3"/>
+      <c r="CX29" s="3"/>
+      <c r="CY29" s="3"/>
+      <c r="CZ29" s="3"/>
+      <c r="DA29" s="3"/>
+      <c r="DB29" s="3"/>
+      <c r="DC29" s="3"/>
+      <c r="DD29" s="3"/>
+      <c r="DE29" s="3"/>
+      <c r="DF29" s="3"/>
+      <c r="DG29" s="3"/>
+      <c r="DH29" s="3"/>
+      <c r="DI29" s="3"/>
+      <c r="DJ29" s="3"/>
+      <c r="DK29" s="3"/>
+      <c r="DL29" s="3"/>
+      <c r="DM29" s="3"/>
+      <c r="DN29" s="3"/>
+      <c r="DO29" s="3"/>
+      <c r="DP29" s="3"/>
+      <c r="DQ29" s="3"/>
+      <c r="DR29" s="3"/>
+      <c r="DS29" s="3"/>
+      <c r="DT29" s="3"/>
     </row>
     <row r="30" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A30">
@@ -6844,7 +6924,7 @@
       <c r="I30" t="s">
         <v>31</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="J30" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K30" t="s">
@@ -6958,81 +7038,84 @@
       <c r="AU30" t="s">
         <v>31</v>
       </c>
-      <c r="AV30" s="2"/>
-      <c r="AW30" s="2"/>
-      <c r="AX30" s="2"/>
-      <c r="BA30" s="5"/>
-      <c r="BB30" s="5"/>
-      <c r="BC30" s="5"/>
-      <c r="BD30" s="5"/>
-      <c r="BE30" s="5"/>
-      <c r="BF30" s="5"/>
-      <c r="BG30" s="5"/>
-      <c r="BH30" s="5"/>
-      <c r="BI30" s="5"/>
-      <c r="BJ30" s="5"/>
-      <c r="BK30" s="5"/>
-      <c r="BL30" s="5"/>
-      <c r="BM30" s="5"/>
-      <c r="BN30" s="5"/>
-      <c r="BO30" s="5"/>
-      <c r="BP30" s="5"/>
-      <c r="BQ30" s="5"/>
-      <c r="BR30" s="5"/>
-      <c r="BS30" s="5"/>
-      <c r="BT30" s="5"/>
-      <c r="BU30" s="5"/>
-      <c r="BV30" s="5"/>
-      <c r="BW30" s="5"/>
-      <c r="BX30" s="5"/>
-      <c r="BY30" s="5"/>
-      <c r="BZ30" s="5"/>
-      <c r="CA30" s="5"/>
-      <c r="CB30" s="5"/>
-      <c r="CC30" s="5"/>
-      <c r="CD30" s="5"/>
-      <c r="CE30" s="5"/>
-      <c r="CF30" s="5"/>
-      <c r="CG30" s="5"/>
-      <c r="CH30" s="5"/>
-      <c r="CI30" s="5"/>
-      <c r="CJ30" s="5"/>
-      <c r="CK30" s="5"/>
-      <c r="CL30" s="5"/>
-      <c r="CM30" s="5"/>
-      <c r="CN30" s="5"/>
-      <c r="CO30" s="5"/>
-      <c r="CP30" s="5"/>
-      <c r="CQ30" s="5"/>
-      <c r="CR30" s="5"/>
-      <c r="CS30" s="5"/>
-      <c r="CT30" s="5"/>
-      <c r="CU30" s="5"/>
-      <c r="CV30" s="5"/>
-      <c r="CW30" s="5"/>
-      <c r="CX30" s="5"/>
-      <c r="CY30" s="5"/>
-      <c r="CZ30" s="5"/>
-      <c r="DA30" s="5"/>
-      <c r="DB30" s="5"/>
-      <c r="DC30" s="5"/>
-      <c r="DD30" s="5"/>
-      <c r="DE30" s="5"/>
-      <c r="DF30" s="5"/>
-      <c r="DG30" s="5"/>
-      <c r="DH30" s="5"/>
-      <c r="DI30" s="5"/>
-      <c r="DJ30" s="5"/>
-      <c r="DK30" s="5"/>
-      <c r="DL30" s="5"/>
-      <c r="DM30" s="5"/>
-      <c r="DN30" s="5"/>
-      <c r="DO30" s="5"/>
-      <c r="DP30" s="5"/>
-      <c r="DQ30" s="5"/>
-      <c r="DR30" s="5"/>
-      <c r="DS30" s="5"/>
-      <c r="DT30" s="5"/>
+      <c r="AV30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW30" s="3"/>
+      <c r="AX30" s="3"/>
+      <c r="AY30" s="3"/>
+      <c r="BA30" s="3"/>
+      <c r="BB30" s="3"/>
+      <c r="BC30" s="3"/>
+      <c r="BD30" s="3"/>
+      <c r="BE30" s="3"/>
+      <c r="BF30" s="3"/>
+      <c r="BG30" s="3"/>
+      <c r="BH30" s="3"/>
+      <c r="BI30" s="3"/>
+      <c r="BJ30" s="3"/>
+      <c r="BK30" s="3"/>
+      <c r="BL30" s="3"/>
+      <c r="BM30" s="3"/>
+      <c r="BN30" s="3"/>
+      <c r="BO30" s="3"/>
+      <c r="BP30" s="3"/>
+      <c r="BQ30" s="3"/>
+      <c r="BR30" s="3"/>
+      <c r="BS30" s="3"/>
+      <c r="BT30" s="3"/>
+      <c r="BU30" s="3"/>
+      <c r="BV30" s="3"/>
+      <c r="BW30" s="3"/>
+      <c r="BX30" s="3"/>
+      <c r="BY30" s="3"/>
+      <c r="BZ30" s="3"/>
+      <c r="CA30" s="3"/>
+      <c r="CB30" s="3"/>
+      <c r="CC30" s="3"/>
+      <c r="CD30" s="3"/>
+      <c r="CE30" s="3"/>
+      <c r="CF30" s="3"/>
+      <c r="CG30" s="3"/>
+      <c r="CH30" s="3"/>
+      <c r="CI30" s="3"/>
+      <c r="CJ30" s="3"/>
+      <c r="CK30" s="3"/>
+      <c r="CL30" s="3"/>
+      <c r="CM30" s="3"/>
+      <c r="CN30" s="3"/>
+      <c r="CO30" s="3"/>
+      <c r="CP30" s="3"/>
+      <c r="CQ30" s="3"/>
+      <c r="CR30" s="3"/>
+      <c r="CS30" s="3"/>
+      <c r="CT30" s="3"/>
+      <c r="CU30" s="3"/>
+      <c r="CV30" s="3"/>
+      <c r="CW30" s="3"/>
+      <c r="CX30" s="3"/>
+      <c r="CY30" s="3"/>
+      <c r="CZ30" s="3"/>
+      <c r="DA30" s="3"/>
+      <c r="DB30" s="3"/>
+      <c r="DC30" s="3"/>
+      <c r="DD30" s="3"/>
+      <c r="DE30" s="3"/>
+      <c r="DF30" s="3"/>
+      <c r="DG30" s="3"/>
+      <c r="DH30" s="3"/>
+      <c r="DI30" s="3"/>
+      <c r="DJ30" s="3"/>
+      <c r="DK30" s="3"/>
+      <c r="DL30" s="3"/>
+      <c r="DM30" s="3"/>
+      <c r="DN30" s="3"/>
+      <c r="DO30" s="3"/>
+      <c r="DP30" s="3"/>
+      <c r="DQ30" s="3"/>
+      <c r="DR30" s="3"/>
+      <c r="DS30" s="3"/>
+      <c r="DT30" s="3"/>
     </row>
     <row r="31" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A31">
@@ -7063,7 +7146,7 @@
       <c r="I31" t="s">
         <v>31</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="J31" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K31" t="s">
@@ -7177,6 +7260,22 @@
       <c r="AU31" t="s">
         <v>31</v>
       </c>
+      <c r="AV31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW31" s="3"/>
+      <c r="AX31" s="3"/>
+      <c r="AY31" s="3"/>
+      <c r="BA31" s="3"/>
+      <c r="BB31" s="3"/>
+      <c r="BC31" s="3"/>
+      <c r="BD31" s="3"/>
+      <c r="BE31" s="3"/>
+      <c r="BF31" s="3"/>
+      <c r="BG31" s="3"/>
+      <c r="BH31" s="3"/>
+      <c r="BI31" s="3"/>
+      <c r="BJ31" s="3"/>
     </row>
     <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
@@ -7207,7 +7306,7 @@
       <c r="I32" t="s">
         <v>31</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="J32" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K32" t="s">
@@ -7321,8 +7420,24 @@
       <c r="AU32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW32" s="3"/>
+      <c r="AX32" s="3"/>
+      <c r="AY32" s="3"/>
+      <c r="BA32" s="3"/>
+      <c r="BB32" s="3"/>
+      <c r="BC32" s="3"/>
+      <c r="BD32" s="3"/>
+      <c r="BE32" s="3"/>
+      <c r="BF32" s="3"/>
+      <c r="BG32" s="3"/>
+      <c r="BH32" s="3"/>
+      <c r="BI32" s="3"/>
+      <c r="BJ32" s="3"/>
+    </row>
+    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -7351,7 +7466,7 @@
       <c r="I33" t="s">
         <v>31</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="J33" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K33" t="s">
@@ -7465,8 +7580,24 @@
       <c r="AU33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW33" s="3"/>
+      <c r="AX33" s="3"/>
+      <c r="AY33" s="3"/>
+      <c r="BA33" s="3"/>
+      <c r="BB33" s="3"/>
+      <c r="BC33" s="3"/>
+      <c r="BD33" s="3"/>
+      <c r="BE33" s="3"/>
+      <c r="BF33" s="3"/>
+      <c r="BG33" s="3"/>
+      <c r="BH33" s="3"/>
+      <c r="BI33" s="3"/>
+      <c r="BJ33" s="3"/>
+    </row>
+    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -7495,7 +7626,7 @@
       <c r="I34" t="s">
         <v>31</v>
       </c>
-      <c r="J34" s="8" t="s">
+      <c r="J34" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K34" t="s">
@@ -7609,12 +7740,28 @@
       <c r="AU34" t="s">
         <v>31</v>
       </c>
+      <c r="AV34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW34" s="3"/>
+      <c r="AX34" s="3"/>
+      <c r="AY34" s="3"/>
+      <c r="BA34" s="3"/>
+      <c r="BB34" s="3"/>
+      <c r="BC34" s="3"/>
+      <c r="BD34" s="3"/>
+      <c r="BE34" s="3"/>
+      <c r="BF34" s="3"/>
+      <c r="BG34" s="3"/>
+      <c r="BH34" s="3"/>
+      <c r="BI34" s="3"/>
+      <c r="BJ34" s="3"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:N34">
     <sortCondition ref="B3:B34"/>
   </sortState>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"F"</formula>
@@ -7625,7 +7772,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF3:DH3 AU3:BA9 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 AU10:BB21 BD10:BK21 AU22:BK30 K31:K33 L31:T34 AU31:AU34 H33:I33">
+  <conditionalFormatting sqref="BF3:DH3 AU3:BA9 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 AU10:BB21 BD10:BK21 AU22:BK30 K31:K33 L31:T34 H33:I33 AU31:AV34">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C61BFD9-A35A-49DE-B499-4E9AECC02078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF834CF-2331-4F1F-B17A-1999CE061185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="47">
   <si>
     <t>Aluno</t>
   </si>
@@ -726,7 +726,9 @@
       <c r="AV1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AW1" s="1"/>
+      <c r="AW1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="AX1" s="1"/>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
@@ -916,7 +918,9 @@
       <c r="AV2" s="1">
         <v>46233</v>
       </c>
-      <c r="AW2" s="1"/>
+      <c r="AW2" s="1">
+        <v>46238</v>
+      </c>
       <c r="AX2" s="1"/>
       <c r="AY2" s="1"/>
       <c r="AZ2" s="1"/>
@@ -1107,7 +1111,9 @@
       <c r="AV3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW3" s="3"/>
+      <c r="AW3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX3" s="3"/>
       <c r="AY3" s="3"/>
       <c r="BA3" s="3"/>
@@ -1329,7 +1335,9 @@
       <c r="AV4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW4" s="3"/>
+      <c r="AW4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX4" s="3"/>
       <c r="AY4" s="3"/>
       <c r="BA4" s="3"/>
@@ -1551,7 +1559,9 @@
       <c r="AV5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW5" s="3"/>
+      <c r="AW5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX5" s="3"/>
       <c r="AY5" s="3"/>
       <c r="BA5" s="3"/>
@@ -1773,7 +1783,9 @@
       <c r="AV6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW6" s="3"/>
+      <c r="AW6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX6" s="3"/>
       <c r="AY6" s="3"/>
       <c r="BA6" s="3"/>
@@ -1995,7 +2007,9 @@
       <c r="AV7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW7" s="3"/>
+      <c r="AW7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX7" s="3"/>
       <c r="AY7" s="3"/>
       <c r="BA7" s="3"/>
@@ -2217,7 +2231,9 @@
       <c r="AV8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW8" s="3"/>
+      <c r="AW8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX8" s="3"/>
       <c r="AY8" s="3"/>
       <c r="BA8" s="3"/>
@@ -2439,7 +2455,9 @@
       <c r="AV9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW9" s="3"/>
+      <c r="AW9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX9" s="3"/>
       <c r="AY9" s="3"/>
       <c r="BA9" s="3"/>
@@ -2661,7 +2679,9 @@
       <c r="AV10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW10" s="3"/>
+      <c r="AW10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX10" s="3"/>
       <c r="AY10" s="3"/>
       <c r="BA10" s="3"/>
@@ -2874,7 +2894,9 @@
       <c r="AV11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW11" s="3"/>
+      <c r="AW11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX11" s="3"/>
       <c r="AY11" s="3"/>
       <c r="BA11" s="3"/>
@@ -3096,7 +3118,9 @@
       <c r="AV12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW12" s="3"/>
+      <c r="AW12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX12" s="3"/>
       <c r="AY12" s="3"/>
       <c r="BA12" s="3"/>
@@ -3318,7 +3342,9 @@
       <c r="AV13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW13" s="3"/>
+      <c r="AW13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX13" s="3"/>
       <c r="AY13" s="3"/>
       <c r="BA13" s="3"/>
@@ -3540,7 +3566,9 @@
       <c r="AV14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW14" s="3"/>
+      <c r="AW14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX14" s="3"/>
       <c r="AY14" s="3"/>
       <c r="BA14" s="3"/>
@@ -3762,7 +3790,9 @@
       <c r="AV15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW15" s="3"/>
+      <c r="AW15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX15" s="3"/>
       <c r="AY15" s="3"/>
       <c r="BA15" s="3"/>
@@ -3984,7 +4014,9 @@
       <c r="AV16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW16" s="3"/>
+      <c r="AW16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX16" s="3"/>
       <c r="AY16" s="3"/>
       <c r="BA16" s="3"/>
@@ -4185,7 +4217,9 @@
       <c r="AV17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW17" s="3"/>
+      <c r="AW17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX17" s="3"/>
       <c r="AY17" s="3"/>
       <c r="BA17" s="3"/>
@@ -4407,7 +4441,9 @@
       <c r="AV18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW18" s="3"/>
+      <c r="AW18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX18" s="3"/>
       <c r="AY18" s="3"/>
       <c r="BA18" s="3"/>
@@ -4629,7 +4665,9 @@
       <c r="AV19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW19" s="3"/>
+      <c r="AW19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX19" s="3"/>
       <c r="AY19" s="3"/>
       <c r="BA19" s="3"/>
@@ -4830,7 +4868,9 @@
       <c r="AV20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW20" s="3"/>
+      <c r="AW20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX20" s="3"/>
       <c r="AY20" s="3"/>
       <c r="BA20" s="3"/>
@@ -5052,7 +5092,9 @@
       <c r="AV21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW21" s="3"/>
+      <c r="AW21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX21" s="3"/>
       <c r="AY21" s="3"/>
       <c r="BA21" s="3"/>
@@ -5274,7 +5316,9 @@
       <c r="AV22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW22" s="3"/>
+      <c r="AW22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX22" s="3"/>
       <c r="AY22" s="3"/>
       <c r="BA22" s="3"/>
@@ -5496,7 +5540,9 @@
       <c r="AV23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW23" s="3"/>
+      <c r="AW23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX23" s="3"/>
       <c r="AY23" s="3"/>
       <c r="BA23" s="3"/>
@@ -5718,7 +5764,9 @@
       <c r="AV24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW24" s="3"/>
+      <c r="AW24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX24" s="3"/>
       <c r="AY24" s="3"/>
       <c r="BA24" s="3"/>
@@ -5940,7 +5988,9 @@
       <c r="AV25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW25" s="3"/>
+      <c r="AW25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX25" s="3"/>
       <c r="AY25" s="3"/>
       <c r="BA25" s="3"/>
@@ -6162,7 +6212,9 @@
       <c r="AV26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW26" s="3"/>
+      <c r="AW26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX26" s="3"/>
       <c r="AY26" s="3"/>
       <c r="BA26" s="3"/>
@@ -6384,7 +6436,9 @@
       <c r="AV27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW27" s="3"/>
+      <c r="AW27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX27" s="3"/>
       <c r="AY27" s="3"/>
       <c r="BA27" s="3"/>
@@ -6606,7 +6660,9 @@
       <c r="AV28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW28" s="3"/>
+      <c r="AW28" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="AX28" s="3"/>
       <c r="AY28" s="3"/>
       <c r="BA28" s="3"/>
@@ -6819,7 +6875,9 @@
       <c r="AV29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW29" s="3"/>
+      <c r="AW29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX29" s="3"/>
       <c r="AY29" s="3"/>
       <c r="BA29" s="3"/>
@@ -7041,7 +7099,9 @@
       <c r="AV30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW30" s="3"/>
+      <c r="AW30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX30" s="3"/>
       <c r="AY30" s="3"/>
       <c r="BA30" s="3"/>
@@ -7263,7 +7323,9 @@
       <c r="AV31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW31" s="3"/>
+      <c r="AW31" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX31" s="3"/>
       <c r="AY31" s="3"/>
       <c r="BA31" s="3"/>
@@ -7423,7 +7485,9 @@
       <c r="AV32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW32" s="3"/>
+      <c r="AW32" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX32" s="3"/>
       <c r="AY32" s="3"/>
       <c r="BA32" s="3"/>
@@ -7583,7 +7647,9 @@
       <c r="AV33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW33" s="3"/>
+      <c r="AW33" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX33" s="3"/>
       <c r="AY33" s="3"/>
       <c r="BA33" s="3"/>
@@ -7743,7 +7809,9 @@
       <c r="AV34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW34" s="3"/>
+      <c r="AW34" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AX34" s="3"/>
       <c r="AY34" s="3"/>
       <c r="BA34" s="3"/>
@@ -7772,7 +7840,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF3:DH3 AU3:BA9 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 AU10:BB21 BD10:BK21 AU22:BK30 K31:K33 L31:T34 H33:I33 AU31:AV34">
+  <conditionalFormatting sqref="BF3:DH3 AU3:BA9 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 AU10:BB21 BD10:BK21 AU22:BK30 K31:K33 L31:T34 AU31:AV34 H33:I33">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF834CF-2331-4F1F-B17A-1999CE061185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AC02D6-CC52-472E-896F-E51B0E01D337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -180,12 +180,15 @@
   <si>
     <t>FÉRIAS</t>
   </si>
+  <si>
+    <t>p5</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +222,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -241,7 +251,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -251,6 +261,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6661,7 +6672,7 @@
         <v>31</v>
       </c>
       <c r="AW28" s="3" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="AX28" s="3"/>
       <c r="AY28" s="3"/>
@@ -6875,7 +6886,7 @@
       <c r="AV29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW29" s="3" t="s">
+      <c r="AW29" s="7" t="s">
         <v>31</v>
       </c>
       <c r="AX29" s="3"/>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AC02D6-CC52-472E-896F-E51B0E01D337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F90631-6F98-4A0E-9A2E-F9770B12C270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -188,7 +188,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -222,13 +222,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -251,7 +244,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -261,7 +254,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,33 +567,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="49" max="51" width="7.6640625" customWidth="1"/>
-    <col min="52" max="52" width="7.6640625" style="3" customWidth="1"/>
-    <col min="53" max="107" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="7" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="7.7109375" customWidth="1"/>
+    <col min="52" max="52" width="7.7109375" style="3" customWidth="1"/>
+    <col min="53" max="107" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -740,7 +732,9 @@
       <c r="AW1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AX1" s="1"/>
+      <c r="AX1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
       <c r="BA1" s="1"/>
@@ -784,7 +778,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -932,7 +926,9 @@
       <c r="AW2" s="1">
         <v>46238</v>
       </c>
-      <c r="AX2" s="1"/>
+      <c r="AX2" s="1">
+        <v>46240</v>
+      </c>
       <c r="AY2" s="1"/>
       <c r="AZ2" s="1"/>
       <c r="BA2" s="1"/>
@@ -976,7 +972,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1125,7 +1121,9 @@
       <c r="AW3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX3" s="3"/>
+      <c r="AX3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY3" s="3"/>
       <c r="BA3" s="3"/>
       <c r="BB3" s="3"/>
@@ -1200,7 +1198,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1349,7 +1347,9 @@
       <c r="AW4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX4" s="3"/>
+      <c r="AX4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY4" s="3"/>
       <c r="BA4" s="3"/>
       <c r="BB4" s="3"/>
@@ -1424,7 +1424,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1573,7 +1573,9 @@
       <c r="AW5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX5" s="3"/>
+      <c r="AX5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY5" s="3"/>
       <c r="BA5" s="3"/>
       <c r="BB5" s="3"/>
@@ -1648,7 +1650,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1797,7 +1799,9 @@
       <c r="AW6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX6" s="3"/>
+      <c r="AX6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY6" s="3"/>
       <c r="BA6" s="3"/>
       <c r="BB6" s="3"/>
@@ -1872,7 +1876,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2021,7 +2025,9 @@
       <c r="AW7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX7" s="3"/>
+      <c r="AX7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY7" s="3"/>
       <c r="BA7" s="3"/>
       <c r="BB7" s="3"/>
@@ -2096,7 +2102,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2245,7 +2251,9 @@
       <c r="AW8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX8" s="3"/>
+      <c r="AX8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY8" s="3"/>
       <c r="BA8" s="3"/>
       <c r="BB8" s="3"/>
@@ -2320,7 +2328,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2469,7 +2477,9 @@
       <c r="AW9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX9" s="3"/>
+      <c r="AX9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY9" s="3"/>
       <c r="BA9" s="3"/>
       <c r="BB9" s="3"/>
@@ -2544,7 +2554,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2693,7 +2703,9 @@
       <c r="AW10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX10" s="3"/>
+      <c r="AX10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY10" s="3"/>
       <c r="BA10" s="3"/>
       <c r="BB10" s="3"/>
@@ -2768,7 +2780,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2908,7 +2920,9 @@
       <c r="AW11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX11" s="3"/>
+      <c r="AX11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY11" s="3"/>
       <c r="BA11" s="3"/>
       <c r="BB11" s="3"/>
@@ -2983,7 +2997,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3132,7 +3146,9 @@
       <c r="AW12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX12" s="3"/>
+      <c r="AX12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY12" s="3"/>
       <c r="BA12" s="3"/>
       <c r="BB12" s="3"/>
@@ -3207,7 +3223,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3356,7 +3372,9 @@
       <c r="AW13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX13" s="3"/>
+      <c r="AX13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY13" s="3"/>
       <c r="BA13" s="3"/>
       <c r="BB13" s="3"/>
@@ -3431,7 +3449,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3580,7 +3598,9 @@
       <c r="AW14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX14" s="3"/>
+      <c r="AX14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY14" s="3"/>
       <c r="BA14" s="3"/>
       <c r="BB14" s="3"/>
@@ -3655,7 +3675,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -3804,7 +3824,9 @@
       <c r="AW15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX15" s="3"/>
+      <c r="AX15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY15" s="3"/>
       <c r="BA15" s="3"/>
       <c r="BB15" s="3"/>
@@ -3879,7 +3901,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4028,7 +4050,9 @@
       <c r="AW16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX16" s="3"/>
+      <c r="AX16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY16" s="3"/>
       <c r="BA16" s="3"/>
       <c r="BB16" s="3"/>
@@ -4103,7 +4127,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4231,7 +4255,9 @@
       <c r="AW17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX17" s="3"/>
+      <c r="AX17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY17" s="3"/>
       <c r="BA17" s="3"/>
       <c r="BB17" s="3"/>
@@ -4306,7 +4332,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -4455,7 +4481,9 @@
       <c r="AW18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX18" s="3"/>
+      <c r="AX18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY18" s="3"/>
       <c r="BA18" s="3"/>
       <c r="BB18" s="3"/>
@@ -4530,7 +4558,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -4679,7 +4707,9 @@
       <c r="AW19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX19" s="3"/>
+      <c r="AX19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY19" s="3"/>
       <c r="BA19" s="3"/>
       <c r="BB19" s="3"/>
@@ -4754,7 +4784,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -4882,7 +4912,9 @@
       <c r="AW20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX20" s="3"/>
+      <c r="AX20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY20" s="3"/>
       <c r="BA20" s="3"/>
       <c r="BB20" s="3"/>
@@ -4957,7 +4989,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5106,7 +5138,9 @@
       <c r="AW21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX21" s="3"/>
+      <c r="AX21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY21" s="3"/>
       <c r="BA21" s="3"/>
       <c r="BB21" s="3"/>
@@ -5181,7 +5215,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -5330,7 +5364,9 @@
       <c r="AW22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX22" s="3"/>
+      <c r="AX22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY22" s="3"/>
       <c r="BA22" s="3"/>
       <c r="BB22" s="3"/>
@@ -5405,7 +5441,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -5554,7 +5590,9 @@
       <c r="AW23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX23" s="3"/>
+      <c r="AX23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY23" s="3"/>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3"/>
@@ -5629,7 +5667,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -5778,7 +5816,9 @@
       <c r="AW24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX24" s="3"/>
+      <c r="AX24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY24" s="3"/>
       <c r="BA24" s="3"/>
       <c r="BB24" s="3"/>
@@ -5853,7 +5893,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6002,7 +6042,9 @@
       <c r="AW25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX25" s="3"/>
+      <c r="AX25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY25" s="3"/>
       <c r="BA25" s="3"/>
       <c r="BB25" s="3"/>
@@ -6077,7 +6119,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -6226,7 +6268,9 @@
       <c r="AW26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX26" s="3"/>
+      <c r="AX26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY26" s="3"/>
       <c r="BA26" s="3"/>
       <c r="BB26" s="3"/>
@@ -6301,7 +6345,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -6450,7 +6494,9 @@
       <c r="AW27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX27" s="3"/>
+      <c r="AX27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY27" s="3"/>
       <c r="BA27" s="3"/>
       <c r="BB27" s="3"/>
@@ -6525,7 +6571,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -6674,7 +6720,9 @@
       <c r="AW28" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AX28" s="3"/>
+      <c r="AX28" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="AY28" s="3"/>
       <c r="BA28" s="3"/>
       <c r="BB28" s="3"/>
@@ -6749,7 +6797,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -6886,10 +6934,12 @@
       <c r="AV29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AW29" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="AX29" s="3"/>
+      <c r="AW29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AX29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY29" s="3"/>
       <c r="BA29" s="3"/>
       <c r="BB29" s="3"/>
@@ -6964,7 +7014,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -7113,7 +7163,9 @@
       <c r="AW30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX30" s="3"/>
+      <c r="AX30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY30" s="3"/>
       <c r="BA30" s="3"/>
       <c r="BB30" s="3"/>
@@ -7188,7 +7240,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -7337,7 +7389,9 @@
       <c r="AW31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX31" s="3"/>
+      <c r="AX31" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY31" s="3"/>
       <c r="BA31" s="3"/>
       <c r="BB31" s="3"/>
@@ -7350,7 +7404,7 @@
       <c r="BI31" s="3"/>
       <c r="BJ31" s="3"/>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -7499,7 +7553,9 @@
       <c r="AW32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX32" s="3"/>
+      <c r="AX32" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY32" s="3"/>
       <c r="BA32" s="3"/>
       <c r="BB32" s="3"/>
@@ -7512,7 +7568,7 @@
       <c r="BI32" s="3"/>
       <c r="BJ32" s="3"/>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -7661,7 +7717,9 @@
       <c r="AW33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX33" s="3"/>
+      <c r="AX33" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY33" s="3"/>
       <c r="BA33" s="3"/>
       <c r="BB33" s="3"/>
@@ -7674,7 +7732,7 @@
       <c r="BI33" s="3"/>
       <c r="BJ33" s="3"/>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -7823,7 +7881,9 @@
       <c r="AW34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AX34" s="3"/>
+      <c r="AX34" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="AY34" s="3"/>
       <c r="BA34" s="3"/>
       <c r="BB34" s="3"/>
@@ -7864,12 +7924,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7877,7 +7937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -7885,7 +7945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -7893,7 +7953,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -7901,7 +7961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -7909,7 +7969,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -7917,7 +7977,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -7925,7 +7985,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -7933,7 +7993,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -7941,7 +8001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -7949,7 +8009,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -7957,7 +8017,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -7965,7 +8025,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -7973,7 +8033,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -7981,7 +8041,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -7989,7 +8049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -7997,7 +8057,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -8005,7 +8065,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -8013,7 +8073,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -8021,7 +8081,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -8029,7 +8089,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -8037,7 +8097,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -8045,7 +8105,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -8053,7 +8113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -8061,7 +8121,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -8069,7 +8129,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -8077,7 +8137,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -8085,7 +8145,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -8093,7 +8153,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -8101,7 +8161,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -8109,7 +8169,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -8117,7 +8177,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -8125,7 +8185,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -8145,203 +8205,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F90631-6F98-4A0E-9A2E-F9770B12C270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2890F2A9-9EE9-4980-ABF1-DAC994755512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="48">
   <si>
     <t>Aluno</t>
   </si>
@@ -735,7 +735,9 @@
       <c r="AX1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AY1" s="1"/>
+      <c r="AY1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="AZ1" s="1"/>
       <c r="BA1" s="1"/>
       <c r="BB1" s="1"/>
@@ -929,7 +931,9 @@
       <c r="AX2" s="1">
         <v>46240</v>
       </c>
-      <c r="AY2" s="1"/>
+      <c r="AY2" s="1">
+        <v>46245</v>
+      </c>
       <c r="AZ2" s="1"/>
       <c r="BA2" s="1"/>
       <c r="BB2" s="1"/>
@@ -1124,7 +1128,9 @@
       <c r="AX3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY3" s="3"/>
+      <c r="AY3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA3" s="3"/>
       <c r="BB3" s="3"/>
       <c r="BC3" s="3"/>
@@ -1350,7 +1356,9 @@
       <c r="AX4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY4" s="3"/>
+      <c r="AY4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA4" s="3"/>
       <c r="BB4" s="3"/>
       <c r="BC4" s="3"/>
@@ -1576,7 +1584,9 @@
       <c r="AX5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY5" s="3"/>
+      <c r="AY5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA5" s="3"/>
       <c r="BB5" s="3"/>
       <c r="BC5" s="3"/>
@@ -1802,7 +1812,9 @@
       <c r="AX6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY6" s="3"/>
+      <c r="AY6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA6" s="3"/>
       <c r="BB6" s="3"/>
       <c r="BC6" s="3"/>
@@ -2028,7 +2040,9 @@
       <c r="AX7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY7" s="3"/>
+      <c r="AY7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA7" s="3"/>
       <c r="BB7" s="3"/>
       <c r="BC7" s="3"/>
@@ -2254,7 +2268,9 @@
       <c r="AX8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY8" s="3"/>
+      <c r="AY8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA8" s="3"/>
       <c r="BB8" s="3"/>
       <c r="BC8" s="3"/>
@@ -2480,7 +2496,9 @@
       <c r="AX9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY9" s="3"/>
+      <c r="AY9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA9" s="3"/>
       <c r="BB9" s="3"/>
       <c r="BC9" s="3"/>
@@ -2706,7 +2724,9 @@
       <c r="AX10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY10" s="3"/>
+      <c r="AY10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA10" s="3"/>
       <c r="BB10" s="3"/>
       <c r="BC10" s="3"/>
@@ -2923,7 +2943,9 @@
       <c r="AX11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY11" s="3"/>
+      <c r="AY11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA11" s="3"/>
       <c r="BB11" s="3"/>
       <c r="BC11" s="3"/>
@@ -3149,7 +3171,9 @@
       <c r="AX12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY12" s="3"/>
+      <c r="AY12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA12" s="3"/>
       <c r="BB12" s="3"/>
       <c r="BC12" s="3"/>
@@ -3375,7 +3399,9 @@
       <c r="AX13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY13" s="3"/>
+      <c r="AY13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA13" s="3"/>
       <c r="BB13" s="3"/>
       <c r="BC13" s="3"/>
@@ -3601,7 +3627,9 @@
       <c r="AX14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY14" s="3"/>
+      <c r="AY14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA14" s="3"/>
       <c r="BB14" s="3"/>
       <c r="BC14" s="3"/>
@@ -3827,7 +3855,9 @@
       <c r="AX15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY15" s="3"/>
+      <c r="AY15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA15" s="3"/>
       <c r="BB15" s="3"/>
       <c r="BC15" s="3"/>
@@ -4053,7 +4083,9 @@
       <c r="AX16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY16" s="3"/>
+      <c r="AY16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA16" s="3"/>
       <c r="BB16" s="3"/>
       <c r="BC16" s="3"/>
@@ -4258,7 +4290,9 @@
       <c r="AX17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY17" s="3"/>
+      <c r="AY17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA17" s="3"/>
       <c r="BB17" s="3"/>
       <c r="BC17" s="3"/>
@@ -4484,7 +4518,9 @@
       <c r="AX18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY18" s="3"/>
+      <c r="AY18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA18" s="3"/>
       <c r="BB18" s="3"/>
       <c r="BC18" s="3"/>
@@ -4710,7 +4746,9 @@
       <c r="AX19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY19" s="3"/>
+      <c r="AY19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA19" s="3"/>
       <c r="BB19" s="3"/>
       <c r="BC19" s="3"/>
@@ -4915,7 +4953,9 @@
       <c r="AX20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY20" s="3"/>
+      <c r="AY20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA20" s="3"/>
       <c r="BB20" s="3"/>
       <c r="BC20" s="3"/>
@@ -5141,7 +5181,9 @@
       <c r="AX21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY21" s="3"/>
+      <c r="AY21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA21" s="3"/>
       <c r="BB21" s="3"/>
       <c r="BC21" s="3"/>
@@ -5367,7 +5409,9 @@
       <c r="AX22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY22" s="3"/>
+      <c r="AY22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA22" s="3"/>
       <c r="BB22" s="3"/>
       <c r="BC22" s="3"/>
@@ -5593,7 +5637,9 @@
       <c r="AX23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY23" s="3"/>
+      <c r="AY23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3"/>
       <c r="BC23" s="3"/>
@@ -5819,7 +5865,9 @@
       <c r="AX24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY24" s="3"/>
+      <c r="AY24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA24" s="3"/>
       <c r="BB24" s="3"/>
       <c r="BC24" s="3"/>
@@ -6045,7 +6093,9 @@
       <c r="AX25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY25" s="3"/>
+      <c r="AY25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA25" s="3"/>
       <c r="BB25" s="3"/>
       <c r="BC25" s="3"/>
@@ -6271,7 +6321,9 @@
       <c r="AX26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY26" s="3"/>
+      <c r="AY26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA26" s="3"/>
       <c r="BB26" s="3"/>
       <c r="BC26" s="3"/>
@@ -6497,7 +6549,9 @@
       <c r="AX27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY27" s="3"/>
+      <c r="AY27" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BA27" s="3"/>
       <c r="BB27" s="3"/>
       <c r="BC27" s="3"/>
@@ -6723,7 +6777,9 @@
       <c r="AX28" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AY28" s="3"/>
+      <c r="AY28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA28" s="3"/>
       <c r="BB28" s="3"/>
       <c r="BC28" s="3"/>
@@ -6940,7 +6996,9 @@
       <c r="AX29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY29" s="3"/>
+      <c r="AY29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA29" s="3"/>
       <c r="BB29" s="3"/>
       <c r="BC29" s="3"/>
@@ -7166,7 +7224,9 @@
       <c r="AX30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY30" s="3"/>
+      <c r="AY30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA30" s="3"/>
       <c r="BB30" s="3"/>
       <c r="BC30" s="3"/>
@@ -7392,7 +7452,9 @@
       <c r="AX31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY31" s="3"/>
+      <c r="AY31" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA31" s="3"/>
       <c r="BB31" s="3"/>
       <c r="BC31" s="3"/>
@@ -7556,7 +7618,9 @@
       <c r="AX32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY32" s="3"/>
+      <c r="AY32" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA32" s="3"/>
       <c r="BB32" s="3"/>
       <c r="BC32" s="3"/>
@@ -7720,7 +7784,9 @@
       <c r="AX33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY33" s="3"/>
+      <c r="AY33" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA33" s="3"/>
       <c r="BB33" s="3"/>
       <c r="BC33" s="3"/>
@@ -7884,7 +7950,9 @@
       <c r="AX34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AY34" s="3"/>
+      <c r="AY34" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BA34" s="3"/>
       <c r="BB34" s="3"/>
       <c r="BC34" s="3"/>
@@ -7911,7 +7979,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF3:DH3 AU3:BA9 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 AU10:BB21 BD10:BK21 AU22:BK30 K31:K33 L31:T34 AU31:AV34 H33:I33">
+  <conditionalFormatting sqref="BF3:DH3 AU3:BA3 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 BD10:BK21 K31:K33 L31:T34 AU31:AV34 H33:I33 AZ22:BK26 AZ10:BB21 AZ4:BA9 AU4:AY26 AU27:BK28 AU29:AX30 AZ29:BK30 AY29:AY34">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2890F2A9-9EE9-4980-ABF1-DAC994755512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4746B870-720D-42BA-80C0-537BB40949B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="49">
   <si>
     <t>Aluno</t>
   </si>
@@ -182,6 +182,9 @@
   </si>
   <si>
     <t>p5</t>
+  </si>
+  <si>
+    <t>3/P</t>
   </si>
 </sst>
 </file>
@@ -567,33 +570,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="7" bestFit="1" customWidth="1"/>
-    <col min="50" max="51" width="7.7109375" customWidth="1"/>
-    <col min="52" max="52" width="7.7109375" style="3" customWidth="1"/>
-    <col min="53" max="107" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="49" max="51" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="7.6640625" style="3" customWidth="1"/>
+    <col min="53" max="107" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -780,7 +783,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -976,7 +979,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1204,7 +1207,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1432,7 +1435,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1660,7 +1663,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1888,7 +1891,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2116,7 +2119,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2344,7 +2347,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2572,7 +2575,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2800,7 +2803,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -3019,7 +3022,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3247,7 +3250,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3475,7 +3478,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3703,7 +3706,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -3931,7 +3934,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4159,7 +4162,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4366,7 +4369,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -4594,7 +4597,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -4822,7 +4825,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -5029,7 +5032,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5257,7 +5260,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -5485,7 +5488,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -5713,7 +5716,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -5941,7 +5944,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6169,7 +6172,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -6397,7 +6400,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -6550,7 +6553,7 @@
         <v>31</v>
       </c>
       <c r="AY27" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BA27" s="3"/>
       <c r="BB27" s="3"/>
@@ -6625,7 +6628,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -6853,7 +6856,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -7072,7 +7075,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -7300,7 +7303,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -7466,7 +7469,7 @@
       <c r="BI31" s="3"/>
       <c r="BJ31" s="3"/>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -7632,7 +7635,7 @@
       <c r="BI32" s="3"/>
       <c r="BJ32" s="3"/>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -7798,7 +7801,7 @@
       <c r="BI33" s="3"/>
       <c r="BJ33" s="3"/>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -7979,7 +7982,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BF3:DH3 AU3:BA3 BC3:BC21 D3:I30 K3:T30 BF4:BK9 BL4:DH30 BD10:BK21 K31:K33 L31:T34 AU31:AV34 H33:I33 AZ22:BK26 AZ10:BB21 AZ4:BA9 AU4:AY26 AU27:BK28 AU29:AX30 AZ29:BK30 AY29:AY34">
+  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BK9 AU4:AY26 BL4:DH30 AZ10:BB21 BD10:BK21 AZ22:BK26 AU27:BK28 AU29:AX30 AZ29:BK30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -7992,12 +7995,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8005,7 +8008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -8013,7 +8016,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -8021,7 +8024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -8029,7 +8032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -8037,7 +8040,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -8045,7 +8048,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -8053,7 +8056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -8061,7 +8064,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -8069,7 +8072,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -8077,7 +8080,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -8085,7 +8088,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -8093,7 +8096,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -8101,7 +8104,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -8109,7 +8112,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -8117,7 +8120,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -8125,7 +8128,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -8133,7 +8136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -8141,7 +8144,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -8149,7 +8152,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -8157,7 +8160,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -8165,7 +8168,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -8173,7 +8176,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -8181,7 +8184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -8189,7 +8192,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -8197,7 +8200,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -8205,7 +8208,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -8213,7 +8216,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -8221,7 +8224,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -8229,7 +8232,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -8237,7 +8240,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -8245,7 +8248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -8253,7 +8256,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -8273,203 +8276,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4746B870-720D-42BA-80C0-537BB40949B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12603D90-5AE5-403C-AD54-61CEB98CDA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="49">
   <si>
     <t>Aluno</t>
   </si>
@@ -570,33 +570,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="49" max="51" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="7.6640625" style="3" customWidth="1"/>
-    <col min="53" max="107" width="7.6640625" customWidth="1"/>
+    <col min="22" max="26" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="51" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="7.7109375" style="3" customWidth="1"/>
+    <col min="53" max="107" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -741,7 +740,9 @@
       <c r="AY1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AZ1" s="1"/>
+      <c r="AZ1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="BA1" s="1"/>
       <c r="BB1" s="1"/>
       <c r="BC1" s="1"/>
@@ -783,7 +784,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -937,7 +938,9 @@
       <c r="AY2" s="1">
         <v>46245</v>
       </c>
-      <c r="AZ2" s="1"/>
+      <c r="AZ2" s="1">
+        <v>46247</v>
+      </c>
       <c r="BA2" s="1"/>
       <c r="BB2" s="1"/>
       <c r="BC2" s="1"/>
@@ -979,7 +982,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1132,6 +1135,9 @@
         <v>31</v>
       </c>
       <c r="AY3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA3" s="3"/>
@@ -1207,7 +1213,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1360,6 +1366,9 @@
         <v>31</v>
       </c>
       <c r="AY4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA4" s="3"/>
@@ -1435,7 +1444,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1588,6 +1597,9 @@
         <v>31</v>
       </c>
       <c r="AY5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA5" s="3"/>
@@ -1663,7 +1675,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1816,6 +1828,9 @@
         <v>31</v>
       </c>
       <c r="AY6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA6" s="3"/>
@@ -1891,7 +1906,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2044,6 +2059,9 @@
         <v>31</v>
       </c>
       <c r="AY7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA7" s="3"/>
@@ -2119,7 +2137,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2272,6 +2290,9 @@
         <v>31</v>
       </c>
       <c r="AY8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA8" s="3"/>
@@ -2347,7 +2368,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2500,6 +2521,9 @@
         <v>31</v>
       </c>
       <c r="AY9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA9" s="3"/>
@@ -2575,7 +2599,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2728,6 +2752,9 @@
         <v>31</v>
       </c>
       <c r="AY10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA10" s="3"/>
@@ -2803,7 +2830,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -2948,6 +2975,9 @@
       </c>
       <c r="AY11" s="3" t="s">
         <v>31</v>
+      </c>
+      <c r="AZ11" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="BA11" s="3"/>
       <c r="BB11" s="3"/>
@@ -3022,7 +3052,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3175,6 +3205,9 @@
         <v>31</v>
       </c>
       <c r="AY12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA12" s="3"/>
@@ -3250,7 +3283,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3403,6 +3436,9 @@
         <v>31</v>
       </c>
       <c r="AY13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA13" s="3"/>
@@ -3478,7 +3514,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3631,6 +3667,9 @@
         <v>31</v>
       </c>
       <c r="AY14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA14" s="3"/>
@@ -3706,7 +3745,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -3859,6 +3898,9 @@
         <v>31</v>
       </c>
       <c r="AY15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA15" s="3"/>
@@ -3934,7 +3976,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4088,6 +4130,9 @@
       </c>
       <c r="AY16" s="3" t="s">
         <v>31</v>
+      </c>
+      <c r="AZ16" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="BA16" s="3"/>
       <c r="BB16" s="3"/>
@@ -4162,7 +4207,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4294,6 +4339,9 @@
         <v>31</v>
       </c>
       <c r="AY17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA17" s="3"/>
@@ -4369,7 +4417,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -4522,6 +4570,9 @@
         <v>31</v>
       </c>
       <c r="AY18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA18" s="3"/>
@@ -4597,7 +4648,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -4750,6 +4801,9 @@
         <v>31</v>
       </c>
       <c r="AY19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA19" s="3"/>
@@ -4825,7 +4879,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -4957,6 +5011,9 @@
         <v>31</v>
       </c>
       <c r="AY20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA20" s="3"/>
@@ -5032,7 +5089,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5185,6 +5242,9 @@
         <v>31</v>
       </c>
       <c r="AY21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA21" s="3"/>
@@ -5260,7 +5320,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -5413,6 +5473,9 @@
         <v>31</v>
       </c>
       <c r="AY22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA22" s="3"/>
@@ -5488,7 +5551,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -5641,6 +5704,9 @@
         <v>31</v>
       </c>
       <c r="AY23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA23" s="3"/>
@@ -5716,7 +5782,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -5869,6 +5935,9 @@
         <v>31</v>
       </c>
       <c r="AY24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA24" s="3"/>
@@ -5944,7 +6013,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6097,6 +6166,9 @@
         <v>31</v>
       </c>
       <c r="AY25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA25" s="3"/>
@@ -6172,7 +6244,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -6325,6 +6397,9 @@
         <v>31</v>
       </c>
       <c r="AY26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA26" s="3"/>
@@ -6400,7 +6475,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -6554,6 +6629,9 @@
       </c>
       <c r="AY27" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="AZ27" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="BA27" s="3"/>
       <c r="BB27" s="3"/>
@@ -6628,7 +6706,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -6781,6 +6859,9 @@
         <v>32</v>
       </c>
       <c r="AY28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA28" s="3"/>
@@ -6856,7 +6937,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -7000,6 +7081,9 @@
         <v>31</v>
       </c>
       <c r="AY29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA29" s="3"/>
@@ -7075,7 +7159,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -7228,6 +7312,9 @@
         <v>31</v>
       </c>
       <c r="AY30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA30" s="3"/>
@@ -7303,7 +7390,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -7456,6 +7543,9 @@
         <v>31</v>
       </c>
       <c r="AY31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA31" s="3"/>
@@ -7469,7 +7559,7 @@
       <c r="BI31" s="3"/>
       <c r="BJ31" s="3"/>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -7622,6 +7712,9 @@
         <v>31</v>
       </c>
       <c r="AY32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA32" s="3"/>
@@ -7635,7 +7728,7 @@
       <c r="BI32" s="3"/>
       <c r="BJ32" s="3"/>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -7788,6 +7881,9 @@
         <v>31</v>
       </c>
       <c r="AY33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA33" s="3"/>
@@ -7801,7 +7897,7 @@
       <c r="BI33" s="3"/>
       <c r="BJ33" s="3"/>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -7954,6 +8050,9 @@
         <v>31</v>
       </c>
       <c r="AY34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="BA34" s="3"/>
@@ -7995,12 +8094,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8008,7 +8107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -8016,7 +8115,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -8024,7 +8123,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -8032,7 +8131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -8040,7 +8139,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -8048,7 +8147,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -8056,7 +8155,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -8064,7 +8163,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -8072,7 +8171,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -8080,7 +8179,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -8088,7 +8187,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -8096,7 +8195,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -8104,7 +8203,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -8112,7 +8211,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -8120,7 +8219,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -8128,7 +8227,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -8136,7 +8235,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -8144,7 +8243,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -8152,7 +8251,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -8160,7 +8259,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -8168,7 +8267,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -8176,7 +8275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -8184,7 +8283,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -8192,7 +8291,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -8200,7 +8299,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -8208,7 +8307,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -8216,7 +8315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -8224,7 +8323,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -8232,7 +8331,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -8240,7 +8339,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -8248,7 +8347,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -8256,7 +8355,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -8276,203 +8375,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12603D90-5AE5-403C-AD54-61CEB98CDA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E09BA27-9904-406E-A8E9-F05049BF84C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="49">
   <si>
     <t>Aluno</t>
   </si>
@@ -743,8 +743,12 @@
       <c r="AZ1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="BA1" s="1"/>
-      <c r="BB1" s="1"/>
+      <c r="BA1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="BC1" s="1"/>
       <c r="BD1" s="1"/>
       <c r="BE1" s="1"/>
@@ -941,8 +945,12 @@
       <c r="AZ2" s="1">
         <v>46247</v>
       </c>
-      <c r="BA2" s="1"/>
-      <c r="BB2" s="1"/>
+      <c r="BA2" s="1">
+        <v>46252</v>
+      </c>
+      <c r="BB2" s="1">
+        <v>46254</v>
+      </c>
       <c r="BC2" s="1"/>
       <c r="BD2" s="1"/>
       <c r="BE2" s="1"/>
@@ -1140,7 +1148,9 @@
       <c r="AZ3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA3" s="3"/>
+      <c r="BA3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB3" s="3"/>
       <c r="BC3" s="3"/>
       <c r="BD3" s="3"/>
@@ -1371,7 +1381,9 @@
       <c r="AZ4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA4" s="3"/>
+      <c r="BA4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB4" s="3"/>
       <c r="BC4" s="3"/>
       <c r="BD4" s="3"/>
@@ -1602,7 +1614,9 @@
       <c r="AZ5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA5" s="3"/>
+      <c r="BA5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB5" s="3"/>
       <c r="BC5" s="3"/>
       <c r="BD5" s="3"/>
@@ -1833,7 +1847,9 @@
       <c r="AZ6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA6" s="3"/>
+      <c r="BA6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB6" s="3"/>
       <c r="BC6" s="3"/>
       <c r="BD6" s="3"/>
@@ -2064,7 +2080,9 @@
       <c r="AZ7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA7" s="3"/>
+      <c r="BA7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB7" s="3"/>
       <c r="BC7" s="3"/>
       <c r="BD7" s="3"/>
@@ -2295,7 +2313,9 @@
       <c r="AZ8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA8" s="3"/>
+      <c r="BA8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB8" s="3"/>
       <c r="BC8" s="3"/>
       <c r="BD8" s="3"/>
@@ -2526,7 +2546,9 @@
       <c r="AZ9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA9" s="3"/>
+      <c r="BA9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB9" s="3"/>
       <c r="BC9" s="3"/>
       <c r="BD9" s="3"/>
@@ -2757,7 +2779,9 @@
       <c r="AZ10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA10" s="3"/>
+      <c r="BA10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB10" s="3"/>
       <c r="BC10" s="3"/>
       <c r="BD10" s="3"/>
@@ -2979,7 +3003,9 @@
       <c r="AZ11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BA11" s="3"/>
+      <c r="BA11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB11" s="3"/>
       <c r="BC11" s="3"/>
       <c r="BD11" s="3"/>
@@ -3210,7 +3236,9 @@
       <c r="AZ12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA12" s="3"/>
+      <c r="BA12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB12" s="3"/>
       <c r="BC12" s="3"/>
       <c r="BD12" s="3"/>
@@ -3441,7 +3469,9 @@
       <c r="AZ13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA13" s="3"/>
+      <c r="BA13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB13" s="3"/>
       <c r="BC13" s="3"/>
       <c r="BD13" s="3"/>
@@ -3672,7 +3702,9 @@
       <c r="AZ14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA14" s="3"/>
+      <c r="BA14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB14" s="3"/>
       <c r="BC14" s="3"/>
       <c r="BD14" s="3"/>
@@ -3903,7 +3935,9 @@
       <c r="AZ15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA15" s="3"/>
+      <c r="BA15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB15" s="3"/>
       <c r="BC15" s="3"/>
       <c r="BD15" s="3"/>
@@ -4134,7 +4168,9 @@
       <c r="AZ16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BA16" s="3"/>
+      <c r="BA16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB16" s="3"/>
       <c r="BC16" s="3"/>
       <c r="BD16" s="3"/>
@@ -4344,7 +4380,9 @@
       <c r="AZ17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA17" s="3"/>
+      <c r="BA17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB17" s="3"/>
       <c r="BC17" s="3"/>
       <c r="BD17" s="3"/>
@@ -4575,7 +4613,9 @@
       <c r="AZ18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA18" s="3"/>
+      <c r="BA18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB18" s="3"/>
       <c r="BC18" s="3"/>
       <c r="BD18" s="3"/>
@@ -4806,7 +4846,9 @@
       <c r="AZ19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA19" s="3"/>
+      <c r="BA19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB19" s="3"/>
       <c r="BC19" s="3"/>
       <c r="BD19" s="3"/>
@@ -5016,7 +5058,9 @@
       <c r="AZ20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA20" s="3"/>
+      <c r="BA20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB20" s="3"/>
       <c r="BC20" s="3"/>
       <c r="BD20" s="3"/>
@@ -5247,7 +5291,9 @@
       <c r="AZ21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA21" s="3"/>
+      <c r="BA21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB21" s="3"/>
       <c r="BC21" s="3"/>
       <c r="BD21" s="3"/>
@@ -5478,7 +5524,9 @@
       <c r="AZ22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA22" s="3"/>
+      <c r="BA22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB22" s="3"/>
       <c r="BC22" s="3"/>
       <c r="BD22" s="3"/>
@@ -5709,7 +5757,9 @@
       <c r="AZ23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA23" s="3"/>
+      <c r="BA23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB23" s="3"/>
       <c r="BC23" s="3"/>
       <c r="BD23" s="3"/>
@@ -5940,7 +5990,9 @@
       <c r="AZ24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA24" s="3"/>
+      <c r="BA24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB24" s="3"/>
       <c r="BC24" s="3"/>
       <c r="BD24" s="3"/>
@@ -6171,7 +6223,9 @@
       <c r="AZ25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA25" s="3"/>
+      <c r="BA25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB25" s="3"/>
       <c r="BC25" s="3"/>
       <c r="BD25" s="3"/>
@@ -6402,7 +6456,9 @@
       <c r="AZ26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA26" s="3"/>
+      <c r="BA26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB26" s="3"/>
       <c r="BC26" s="3"/>
       <c r="BD26" s="3"/>
@@ -6633,7 +6689,9 @@
       <c r="AZ27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA27" s="3"/>
+      <c r="BA27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB27" s="3"/>
       <c r="BC27" s="3"/>
       <c r="BD27" s="3"/>
@@ -6864,7 +6922,9 @@
       <c r="AZ28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA28" s="3"/>
+      <c r="BA28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB28" s="3"/>
       <c r="BC28" s="3"/>
       <c r="BD28" s="3"/>
@@ -7086,7 +7146,9 @@
       <c r="AZ29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA29" s="3"/>
+      <c r="BA29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB29" s="3"/>
       <c r="BC29" s="3"/>
       <c r="BD29" s="3"/>
@@ -7317,7 +7379,9 @@
       <c r="AZ30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA30" s="3"/>
+      <c r="BA30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB30" s="3"/>
       <c r="BC30" s="3"/>
       <c r="BD30" s="3"/>
@@ -7548,7 +7612,9 @@
       <c r="AZ31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA31" s="3"/>
+      <c r="BA31" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB31" s="3"/>
       <c r="BC31" s="3"/>
       <c r="BD31" s="3"/>
@@ -7717,7 +7783,9 @@
       <c r="AZ32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA32" s="3"/>
+      <c r="BA32" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB32" s="3"/>
       <c r="BC32" s="3"/>
       <c r="BD32" s="3"/>
@@ -7886,7 +7954,9 @@
       <c r="AZ33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA33" s="3"/>
+      <c r="BA33" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB33" s="3"/>
       <c r="BC33" s="3"/>
       <c r="BD33" s="3"/>
@@ -8055,7 +8125,9 @@
       <c r="AZ34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BA34" s="3"/>
+      <c r="BA34" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BB34" s="3"/>
       <c r="BC34" s="3"/>
       <c r="BD34" s="3"/>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12603D90-5AE5-403C-AD54-61CEB98CDA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42835031-C181-4DD2-BCEB-9C3E3F85B63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8374,205 +8374,205 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
-  <dimension ref="A2:A34"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
+      <c r="A2" t="str">
+        <f>alunos!B2</f>
+        <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
-        <f>alunos!B2</f>
-        <v>Ana Beatriz Alves de Lima</v>
+        <f>alunos!B3</f>
+        <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <f>alunos!B3</f>
-        <v>Bianca Giovedy Pagotto</v>
+        <f>alunos!B4</f>
+        <v>Breno Frazão Callegari</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
-        <f>alunos!B4</f>
-        <v>Breno Frazão Callegari</v>
+        <f>alunos!B5</f>
+        <v>Davi Cruz Oliveira</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
-        <f>alunos!B5</f>
-        <v>Davi Cruz Oliveira</v>
+        <f>alunos!B6</f>
+        <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
-        <f>alunos!B6</f>
-        <v>Eduardo Moretti Varotti</v>
+        <f>alunos!B7</f>
+        <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
-        <f>alunos!B7</f>
-        <v>Gabriela Leticia da Silva</v>
+        <f>alunos!B8</f>
+        <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
-        <f>alunos!B8</f>
-        <v>Geovanna Martins Bertuol</v>
+        <f>alunos!B9</f>
+        <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
-        <f>alunos!B9</f>
-        <v>Giulia de Godoi Silveira</v>
+        <f>alunos!B10</f>
+        <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
-        <f>alunos!B10</f>
-        <v>Giuseppe de Moraes Vieira</v>
+        <f>alunos!B11</f>
+        <v>Gustavo Ferelli</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
-        <f>alunos!B11</f>
-        <v>Gustavo Ferelli</v>
+        <f>alunos!B12</f>
+        <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
-        <f>alunos!B12</f>
-        <v>Heitor Dorigan de Angeli</v>
+        <f>alunos!B13</f>
+        <v>Helena Politti Rossi</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
-        <f>alunos!B13</f>
-        <v>Helena Politti Rossi</v>
+        <f>alunos!B14</f>
+        <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
-        <f>alunos!B14</f>
-        <v>Isabela Marchiori Ferreira</v>
+        <f>alunos!B15</f>
+        <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
-        <f>alunos!B15</f>
-        <v>Isabelle Caroline Vizeu de Salles</v>
+        <f>alunos!B16</f>
+        <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
-        <f>alunos!B16</f>
-        <v>Larissa Guarizo Tolloto</v>
+        <f>alunos!B17</f>
+        <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
-        <f>alunos!B17</f>
-        <v>Leandro Imenes de Oliveira</v>
+        <f>alunos!B18</f>
+        <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
-        <f>alunos!B18</f>
-        <v>Letícia Aparecida Pinto de Souza</v>
+        <f>alunos!B19</f>
+        <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
-        <f>alunos!B19</f>
-        <v>Liara Guarizo Tolloto</v>
+        <f>alunos!B20</f>
+        <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
-        <f>alunos!B20</f>
-        <v>Luana Gabrielle de Oliveira</v>
+        <f>alunos!B21</f>
+        <v>Marina Henrique Moretti</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
-        <f>alunos!B21</f>
-        <v>Marina Henrique Moretti</v>
+        <f>alunos!B22</f>
+        <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
-        <f>alunos!B22</f>
-        <v>Matheus Dorigan Paiato</v>
+        <f>alunos!B23</f>
+        <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
-        <f>alunos!B23</f>
-        <v>Maycon Silva Gonçalves de Lima</v>
+        <f>alunos!B24</f>
+        <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
-        <f>alunos!B24</f>
-        <v>Nicolas Augusto dos Reis Lira</v>
+        <f>alunos!B25</f>
+        <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
-        <f>alunos!B25</f>
-        <v>Otávio Augusto Barbosa</v>
+        <f>alunos!B26</f>
+        <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
-        <f>alunos!B26</f>
-        <v>Pedro Henrique Souza Guarizo</v>
+        <f>alunos!B27</f>
+        <v>Renan Pavan Fazullo</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <f>alunos!B27</f>
-        <v>Renan Pavan Fazullo</v>
+        <f>alunos!B28</f>
+        <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <f>alunos!B28</f>
-        <v>Samyra Leite da Silva Ferreira</v>
+        <f>alunos!B29</f>
+        <v>Sara de Paula Souza</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <f>alunos!B29</f>
-        <v>Sara de Paula Souza</v>
+        <f>alunos!B30</f>
+        <v>Sofia Ohashi Faria</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
-        <f>alunos!B30</f>
-        <v>Sofia Ohashi Faria</v>
+        <f>alunos!B31</f>
+        <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
-        <f>alunos!B31</f>
-        <v>Tobias Gabriel Bueno de Godoi</v>
+        <f>alunos!B32</f>
+        <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
-        <f>alunos!B32</f>
-        <v>Víctor Henrique Santana Alves</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>
       </c>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E09BA27-9904-406E-A8E9-F05049BF84C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D61DF7E-6F04-4203-8971-9CB691927DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -570,32 +570,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="49" max="51" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="7.7109375" style="3" customWidth="1"/>
-    <col min="53" max="107" width="7.7109375" customWidth="1"/>
+    <col min="22" max="26" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="49" max="51" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="7.6640625" style="3" customWidth="1"/>
+    <col min="53" max="107" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -788,7 +788,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -990,7 +990,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1223,7 +1223,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1456,7 +1456,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1689,7 +1689,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1922,7 +1922,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2155,7 +2155,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2388,7 +2388,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2621,7 +2621,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2780,7 +2780,7 @@
         <v>31</v>
       </c>
       <c r="BA10" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="BB10" s="3"/>
       <c r="BC10" s="3"/>
@@ -2854,7 +2854,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -3078,7 +3078,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3311,7 +3311,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3544,7 +3544,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3777,7 +3777,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -4010,7 +4010,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4243,7 +4243,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4455,7 +4455,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -4688,7 +4688,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -4921,7 +4921,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -5133,7 +5133,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5366,7 +5366,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -5599,7 +5599,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -5832,7 +5832,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -6065,7 +6065,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6298,7 +6298,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -6457,7 +6457,7 @@
         <v>31</v>
       </c>
       <c r="BA26" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="BB26" s="3"/>
       <c r="BC26" s="3"/>
@@ -6531,7 +6531,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -6764,7 +6764,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -6997,7 +6997,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -7147,7 +7147,7 @@
         <v>31</v>
       </c>
       <c r="BA29" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="BB29" s="3"/>
       <c r="BC29" s="3"/>
@@ -7221,7 +7221,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -7454,7 +7454,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -7625,7 +7625,7 @@
       <c r="BI31" s="3"/>
       <c r="BJ31" s="3"/>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -7796,7 +7796,7 @@
       <c r="BI32" s="3"/>
       <c r="BJ32" s="3"/>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -7967,7 +7967,7 @@
       <c r="BI33" s="3"/>
       <c r="BJ33" s="3"/>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -8166,12 +8166,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8179,7 +8179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -8195,7 +8195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -8203,7 +8203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -8219,7 +8219,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -8227,7 +8227,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -8251,7 +8251,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -8259,7 +8259,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -8267,7 +8267,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -8283,7 +8283,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -8291,7 +8291,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -8299,7 +8299,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -8315,7 +8315,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -8323,7 +8323,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -8331,7 +8331,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -8339,7 +8339,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -8347,7 +8347,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -8363,7 +8363,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -8387,7 +8387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -8395,7 +8395,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -8403,7 +8403,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -8411,7 +8411,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -8427,7 +8427,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -8447,203 +8447,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D61DF7E-6F04-4203-8971-9CB691927DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7E18F4-2E09-45EC-98DC-C86F496488F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="49">
   <si>
     <t>Aluno</t>
   </si>
@@ -262,7 +262,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -570,32 +590,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="49" max="51" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="7.6640625" style="3" customWidth="1"/>
-    <col min="53" max="107" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="49" max="51" width="7" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="7" style="3" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="7" bestFit="1" customWidth="1"/>
+    <col min="55" max="107" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -749,8 +770,12 @@
       <c r="BB1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="BC1" s="1"/>
-      <c r="BD1" s="1"/>
+      <c r="BC1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="BE1" s="1"/>
       <c r="BF1" s="1"/>
       <c r="BG1" s="1"/>
@@ -788,7 +813,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -990,7 +1015,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1151,7 +1176,9 @@
       <c r="BA3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB3" s="3"/>
+      <c r="BB3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC3" s="3"/>
       <c r="BD3" s="3"/>
       <c r="BE3" s="3"/>
@@ -1223,7 +1250,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1384,7 +1411,9 @@
       <c r="BA4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB4" s="3"/>
+      <c r="BB4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC4" s="3"/>
       <c r="BD4" s="3"/>
       <c r="BE4" s="3"/>
@@ -1456,7 +1485,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1617,7 +1646,9 @@
       <c r="BA5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB5" s="3"/>
+      <c r="BB5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC5" s="3"/>
       <c r="BD5" s="3"/>
       <c r="BE5" s="3"/>
@@ -1689,7 +1720,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1850,7 +1881,9 @@
       <c r="BA6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB6" s="3"/>
+      <c r="BB6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC6" s="3"/>
       <c r="BD6" s="3"/>
       <c r="BE6" s="3"/>
@@ -1922,7 +1955,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2083,7 +2116,9 @@
       <c r="BA7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB7" s="3"/>
+      <c r="BB7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC7" s="3"/>
       <c r="BD7" s="3"/>
       <c r="BE7" s="3"/>
@@ -2155,7 +2190,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2316,7 +2351,9 @@
       <c r="BA8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB8" s="3"/>
+      <c r="BB8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC8" s="3"/>
       <c r="BD8" s="3"/>
       <c r="BE8" s="3"/>
@@ -2388,7 +2425,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2549,7 +2586,9 @@
       <c r="BA9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB9" s="3"/>
+      <c r="BB9" t="s">
+        <v>32</v>
+      </c>
       <c r="BC9" s="3"/>
       <c r="BD9" s="3"/>
       <c r="BE9" s="3"/>
@@ -2621,7 +2660,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2782,7 +2821,9 @@
       <c r="BA10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="BB10" s="3"/>
+      <c r="BB10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC10" s="3"/>
       <c r="BD10" s="3"/>
       <c r="BE10" s="3"/>
@@ -2854,7 +2895,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -3006,7 +3047,9 @@
       <c r="BA11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB11" s="3"/>
+      <c r="BB11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC11" s="3"/>
       <c r="BD11" s="3"/>
       <c r="BE11" s="3"/>
@@ -3078,7 +3121,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3239,7 +3282,9 @@
       <c r="BA12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB12" s="3"/>
+      <c r="BB12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC12" s="3"/>
       <c r="BD12" s="3"/>
       <c r="BE12" s="3"/>
@@ -3311,7 +3356,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3472,7 +3517,9 @@
       <c r="BA13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB13" s="3"/>
+      <c r="BB13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC13" s="3"/>
       <c r="BD13" s="3"/>
       <c r="BE13" s="3"/>
@@ -3544,7 +3591,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3705,7 +3752,9 @@
       <c r="BA14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB14" s="3"/>
+      <c r="BB14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC14" s="3"/>
       <c r="BD14" s="3"/>
       <c r="BE14" s="3"/>
@@ -3777,7 +3826,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -3938,7 +3987,9 @@
       <c r="BA15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB15" s="3"/>
+      <c r="BB15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC15" s="3"/>
       <c r="BD15" s="3"/>
       <c r="BE15" s="3"/>
@@ -4010,7 +4061,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4171,7 +4222,9 @@
       <c r="BA16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB16" s="3"/>
+      <c r="BB16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC16" s="3"/>
       <c r="BD16" s="3"/>
       <c r="BE16" s="3"/>
@@ -4243,7 +4296,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4383,7 +4436,9 @@
       <c r="BA17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB17" s="3"/>
+      <c r="BB17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC17" s="3"/>
       <c r="BD17" s="3"/>
       <c r="BE17" s="3"/>
@@ -4455,7 +4510,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -4616,7 +4671,9 @@
       <c r="BA18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB18" s="3"/>
+      <c r="BB18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC18" s="3"/>
       <c r="BD18" s="3"/>
       <c r="BE18" s="3"/>
@@ -4688,7 +4745,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -4849,7 +4906,9 @@
       <c r="BA19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB19" s="3"/>
+      <c r="BB19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC19" s="3"/>
       <c r="BD19" s="3"/>
       <c r="BE19" s="3"/>
@@ -4921,7 +4980,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -5061,7 +5120,9 @@
       <c r="BA20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB20" s="3"/>
+      <c r="BB20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC20" s="3"/>
       <c r="BD20" s="3"/>
       <c r="BE20" s="3"/>
@@ -5133,7 +5194,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5294,7 +5355,9 @@
       <c r="BA21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB21" s="3"/>
+      <c r="BB21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC21" s="3"/>
       <c r="BD21" s="3"/>
       <c r="BE21" s="3"/>
@@ -5366,7 +5429,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -5527,7 +5590,9 @@
       <c r="BA22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB22" s="3"/>
+      <c r="BB22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC22" s="3"/>
       <c r="BD22" s="3"/>
       <c r="BE22" s="3"/>
@@ -5599,7 +5664,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -5760,7 +5825,9 @@
       <c r="BA23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB23" s="3"/>
+      <c r="BB23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC23" s="3"/>
       <c r="BD23" s="3"/>
       <c r="BE23" s="3"/>
@@ -5832,7 +5899,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -5993,7 +6060,9 @@
       <c r="BA24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB24" s="3"/>
+      <c r="BB24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC24" s="3"/>
       <c r="BD24" s="3"/>
       <c r="BE24" s="3"/>
@@ -6065,7 +6134,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6226,7 +6295,9 @@
       <c r="BA25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB25" s="3"/>
+      <c r="BB25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC25" s="3"/>
       <c r="BD25" s="3"/>
       <c r="BE25" s="3"/>
@@ -6298,7 +6369,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -6459,7 +6530,9 @@
       <c r="BA26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="BB26" s="3"/>
+      <c r="BB26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC26" s="3"/>
       <c r="BD26" s="3"/>
       <c r="BE26" s="3"/>
@@ -6531,7 +6604,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -6692,7 +6765,9 @@
       <c r="BA27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB27" s="3"/>
+      <c r="BB27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC27" s="3"/>
       <c r="BD27" s="3"/>
       <c r="BE27" s="3"/>
@@ -6764,7 +6839,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -6925,7 +7000,9 @@
       <c r="BA28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB28" s="3"/>
+      <c r="BB28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC28" s="3"/>
       <c r="BD28" s="3"/>
       <c r="BE28" s="3"/>
@@ -6997,7 +7074,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -7149,7 +7226,9 @@
       <c r="BA29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="BB29" s="3"/>
+      <c r="BB29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC29" s="3"/>
       <c r="BD29" s="3"/>
       <c r="BE29" s="3"/>
@@ -7221,7 +7300,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -7382,7 +7461,9 @@
       <c r="BA30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB30" s="3"/>
+      <c r="BB30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC30" s="3"/>
       <c r="BD30" s="3"/>
       <c r="BE30" s="3"/>
@@ -7454,7 +7535,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -7615,7 +7696,9 @@
       <c r="BA31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB31" s="3"/>
+      <c r="BB31" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC31" s="3"/>
       <c r="BD31" s="3"/>
       <c r="BE31" s="3"/>
@@ -7625,7 +7708,7 @@
       <c r="BI31" s="3"/>
       <c r="BJ31" s="3"/>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -7786,7 +7869,9 @@
       <c r="BA32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB32" s="3"/>
+      <c r="BB32" t="s">
+        <v>32</v>
+      </c>
       <c r="BC32" s="3"/>
       <c r="BD32" s="3"/>
       <c r="BE32" s="3"/>
@@ -7796,7 +7881,7 @@
       <c r="BI32" s="3"/>
       <c r="BJ32" s="3"/>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -7957,7 +8042,9 @@
       <c r="BA33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB33" s="3"/>
+      <c r="BB33" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC33" s="3"/>
       <c r="BD33" s="3"/>
       <c r="BE33" s="3"/>
@@ -7967,7 +8054,7 @@
       <c r="BI33" s="3"/>
       <c r="BJ33" s="3"/>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -8128,7 +8215,9 @@
       <c r="BA34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BB34" s="3"/>
+      <c r="BB34" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BC34" s="3"/>
       <c r="BD34" s="3"/>
       <c r="BE34" s="3"/>
@@ -8144,17 +8233,27 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:AS34">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BK9 AU4:AY26 BL4:DH30 AZ10:BB21 BD10:BK21 AZ22:BK26 AU27:BK28 AU29:AX30 AZ29:BK30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB9">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BB32">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8166,12 +8265,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8179,7 +8278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -8187,7 +8286,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -8195,7 +8294,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -8203,7 +8302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -8211,7 +8310,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -8219,7 +8318,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -8227,7 +8326,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -8235,7 +8334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -8243,7 +8342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -8251,7 +8350,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -8259,7 +8358,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -8267,7 +8366,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -8275,7 +8374,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -8283,7 +8382,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -8291,7 +8390,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -8299,7 +8398,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -8307,7 +8406,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -8315,7 +8414,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -8323,7 +8422,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -8331,7 +8430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -8339,7 +8438,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -8347,7 +8446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -8355,7 +8454,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -8363,7 +8462,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -8371,7 +8470,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -8379,7 +8478,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -8387,7 +8486,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -8395,7 +8494,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -8403,7 +8502,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -8411,7 +8510,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -8419,7 +8518,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -8427,7 +8526,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -8447,203 +8546,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7E18F4-2E09-45EC-98DC-C86F496488F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B97BBAD-B711-49A9-89B7-843DA888EF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -590,33 +590,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="49" max="51" width="7" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="7" style="3" bestFit="1" customWidth="1"/>
     <col min="53" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="107" width="7.7109375" customWidth="1"/>
+    <col min="55" max="107" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -813,7 +813,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1015,7 +1015,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1250,7 +1250,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1485,7 +1485,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1720,7 +1720,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1955,7 +1955,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2190,7 +2190,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2425,7 +2425,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2660,7 +2660,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2895,7 +2895,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -3121,7 +3121,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3356,7 +3356,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3591,7 +3591,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3826,7 +3826,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -4061,7 +4061,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4296,7 +4296,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4510,7 +4510,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -4745,7 +4745,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -4980,7 +4980,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -5194,7 +5194,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5429,7 +5429,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -5664,7 +5664,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -5899,7 +5899,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -6134,7 +6134,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6369,7 +6369,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -6604,7 +6604,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -6839,7 +6839,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -7074,7 +7074,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -7300,7 +7300,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -7535,7 +7535,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -7708,7 +7708,7 @@
       <c r="BI31" s="3"/>
       <c r="BJ31" s="3"/>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -7881,7 +7881,7 @@
       <c r="BI32" s="3"/>
       <c r="BJ32" s="3"/>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8054,7 +8054,7 @@
       <c r="BI33" s="3"/>
       <c r="BJ33" s="3"/>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -8265,12 +8265,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8278,7 +8278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -8286,7 +8286,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -8294,7 +8294,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -8302,7 +8302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -8310,7 +8310,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -8318,7 +8318,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -8334,7 +8334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -8342,7 +8342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -8350,7 +8350,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -8358,7 +8358,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -8366,7 +8366,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -8374,7 +8374,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -8390,7 +8390,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -8406,7 +8406,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -8414,7 +8414,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -8430,7 +8430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -8438,7 +8438,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -8446,7 +8446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -8462,7 +8462,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -8470,7 +8470,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -8494,7 +8494,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -8510,7 +8510,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -8518,7 +8518,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -8526,7 +8526,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -8546,203 +8546,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B97BBAD-B711-49A9-89B7-843DA888EF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0EA78C-BA29-42F3-817D-47A083C2AFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="49">
   <si>
     <t>Aluno</t>
   </si>
@@ -590,33 +590,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="49" max="51" width="7" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="7" style="3" bestFit="1" customWidth="1"/>
     <col min="53" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="107" width="7.6640625" customWidth="1"/>
+    <col min="55" max="107" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -813,7 +813,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -976,7 +976,9 @@
       <c r="BB2" s="1">
         <v>46254</v>
       </c>
-      <c r="BC2" s="1"/>
+      <c r="BC2" s="1">
+        <v>46259</v>
+      </c>
       <c r="BD2" s="1"/>
       <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
@@ -1015,7 +1017,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1179,7 +1181,9 @@
       <c r="BB3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC3" s="3"/>
+      <c r="BC3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD3" s="3"/>
       <c r="BE3" s="3"/>
       <c r="BF3" s="3"/>
@@ -1250,7 +1254,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1414,7 +1418,9 @@
       <c r="BB4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC4" s="3"/>
+      <c r="BC4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD4" s="3"/>
       <c r="BE4" s="3"/>
       <c r="BF4" s="3"/>
@@ -1485,7 +1491,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1649,7 +1655,9 @@
       <c r="BB5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC5" s="3"/>
+      <c r="BC5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD5" s="3"/>
       <c r="BE5" s="3"/>
       <c r="BF5" s="3"/>
@@ -1720,7 +1728,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1884,7 +1892,9 @@
       <c r="BB6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC6" s="3"/>
+      <c r="BC6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD6" s="3"/>
       <c r="BE6" s="3"/>
       <c r="BF6" s="3"/>
@@ -1955,7 +1965,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2119,7 +2129,9 @@
       <c r="BB7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC7" s="3"/>
+      <c r="BC7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD7" s="3"/>
       <c r="BE7" s="3"/>
       <c r="BF7" s="3"/>
@@ -2190,7 +2202,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2354,7 +2366,9 @@
       <c r="BB8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC8" s="3"/>
+      <c r="BC8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD8" s="3"/>
       <c r="BE8" s="3"/>
       <c r="BF8" s="3"/>
@@ -2425,7 +2439,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2589,7 +2603,9 @@
       <c r="BB9" t="s">
         <v>32</v>
       </c>
-      <c r="BC9" s="3"/>
+      <c r="BC9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD9" s="3"/>
       <c r="BE9" s="3"/>
       <c r="BF9" s="3"/>
@@ -2660,7 +2676,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2824,7 +2840,9 @@
       <c r="BB10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC10" s="3"/>
+      <c r="BC10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD10" s="3"/>
       <c r="BE10" s="3"/>
       <c r="BF10" s="3"/>
@@ -2895,7 +2913,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -3050,7 +3068,9 @@
       <c r="BB11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC11" s="3"/>
+      <c r="BC11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD11" s="3"/>
       <c r="BE11" s="3"/>
       <c r="BF11" s="3"/>
@@ -3121,7 +3141,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3285,7 +3305,9 @@
       <c r="BB12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC12" s="3"/>
+      <c r="BC12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD12" s="3"/>
       <c r="BE12" s="3"/>
       <c r="BF12" s="3"/>
@@ -3356,7 +3378,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3520,7 +3542,9 @@
       <c r="BB13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC13" s="3"/>
+      <c r="BC13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD13" s="3"/>
       <c r="BE13" s="3"/>
       <c r="BF13" s="3"/>
@@ -3591,7 +3615,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3755,7 +3779,9 @@
       <c r="BB14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC14" s="3"/>
+      <c r="BC14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD14" s="3"/>
       <c r="BE14" s="3"/>
       <c r="BF14" s="3"/>
@@ -3826,7 +3852,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -3990,7 +4016,9 @@
       <c r="BB15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC15" s="3"/>
+      <c r="BC15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD15" s="3"/>
       <c r="BE15" s="3"/>
       <c r="BF15" s="3"/>
@@ -4061,7 +4089,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4225,7 +4253,9 @@
       <c r="BB16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC16" s="3"/>
+      <c r="BC16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD16" s="3"/>
       <c r="BE16" s="3"/>
       <c r="BF16" s="3"/>
@@ -4296,7 +4326,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4439,7 +4469,9 @@
       <c r="BB17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC17" s="3"/>
+      <c r="BC17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD17" s="3"/>
       <c r="BE17" s="3"/>
       <c r="BF17" s="3"/>
@@ -4510,7 +4542,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -4674,7 +4706,9 @@
       <c r="BB18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC18" s="3"/>
+      <c r="BC18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD18" s="3"/>
       <c r="BE18" s="3"/>
       <c r="BF18" s="3"/>
@@ -4745,7 +4779,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -4909,7 +4943,9 @@
       <c r="BB19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC19" s="3"/>
+      <c r="BC19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD19" s="3"/>
       <c r="BE19" s="3"/>
       <c r="BF19" s="3"/>
@@ -4980,7 +5016,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -5123,7 +5159,9 @@
       <c r="BB20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC20" s="3"/>
+      <c r="BC20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD20" s="3"/>
       <c r="BE20" s="3"/>
       <c r="BF20" s="3"/>
@@ -5194,7 +5232,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5358,7 +5396,9 @@
       <c r="BB21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC21" s="3"/>
+      <c r="BC21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD21" s="3"/>
       <c r="BE21" s="3"/>
       <c r="BF21" s="3"/>
@@ -5429,7 +5469,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -5593,7 +5633,9 @@
       <c r="BB22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC22" s="3"/>
+      <c r="BC22" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BD22" s="3"/>
       <c r="BE22" s="3"/>
       <c r="BF22" s="3"/>
@@ -5664,7 +5706,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -5828,7 +5870,9 @@
       <c r="BB23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC23" s="3"/>
+      <c r="BC23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD23" s="3"/>
       <c r="BE23" s="3"/>
       <c r="BF23" s="3"/>
@@ -5899,7 +5943,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -6063,7 +6107,9 @@
       <c r="BB24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC24" s="3"/>
+      <c r="BC24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD24" s="3"/>
       <c r="BE24" s="3"/>
       <c r="BF24" s="3"/>
@@ -6134,7 +6180,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6298,7 +6344,9 @@
       <c r="BB25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC25" s="3"/>
+      <c r="BC25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD25" s="3"/>
       <c r="BE25" s="3"/>
       <c r="BF25" s="3"/>
@@ -6369,7 +6417,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -6533,7 +6581,9 @@
       <c r="BB26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC26" s="3"/>
+      <c r="BC26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD26" s="3"/>
       <c r="BE26" s="3"/>
       <c r="BF26" s="3"/>
@@ -6604,7 +6654,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -6768,7 +6818,9 @@
       <c r="BB27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC27" s="3"/>
+      <c r="BC27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD27" s="3"/>
       <c r="BE27" s="3"/>
       <c r="BF27" s="3"/>
@@ -6839,7 +6891,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -7003,7 +7055,9 @@
       <c r="BB28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC28" s="3"/>
+      <c r="BC28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD28" s="3"/>
       <c r="BE28" s="3"/>
       <c r="BF28" s="3"/>
@@ -7074,7 +7128,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -7229,7 +7283,9 @@
       <c r="BB29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC29" s="3"/>
+      <c r="BC29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD29" s="3"/>
       <c r="BE29" s="3"/>
       <c r="BF29" s="3"/>
@@ -7300,7 +7356,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -7464,7 +7520,9 @@
       <c r="BB30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC30" s="3"/>
+      <c r="BC30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD30" s="3"/>
       <c r="BE30" s="3"/>
       <c r="BF30" s="3"/>
@@ -7535,7 +7593,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -7699,7 +7757,9 @@
       <c r="BB31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC31" s="3"/>
+      <c r="BC31" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD31" s="3"/>
       <c r="BE31" s="3"/>
       <c r="BF31" s="3"/>
@@ -7708,7 +7768,7 @@
       <c r="BI31" s="3"/>
       <c r="BJ31" s="3"/>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -7872,7 +7932,9 @@
       <c r="BB32" t="s">
         <v>32</v>
       </c>
-      <c r="BC32" s="3"/>
+      <c r="BC32" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD32" s="3"/>
       <c r="BE32" s="3"/>
       <c r="BF32" s="3"/>
@@ -7881,7 +7943,7 @@
       <c r="BI32" s="3"/>
       <c r="BJ32" s="3"/>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8045,7 +8107,9 @@
       <c r="BB33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC33" s="3"/>
+      <c r="BC33" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD33" s="3"/>
       <c r="BE33" s="3"/>
       <c r="BF33" s="3"/>
@@ -8054,7 +8118,7 @@
       <c r="BI33" s="3"/>
       <c r="BJ33" s="3"/>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -8218,7 +8282,9 @@
       <c r="BB34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BC34" s="3"/>
+      <c r="BC34" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BD34" s="3"/>
       <c r="BE34" s="3"/>
       <c r="BF34" s="3"/>
@@ -8265,12 +8331,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8278,7 +8344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -8286,7 +8352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -8294,7 +8360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -8302,7 +8368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -8310,7 +8376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -8318,7 +8384,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -8326,7 +8392,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -8334,7 +8400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -8342,7 +8408,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -8350,7 +8416,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -8358,7 +8424,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -8366,7 +8432,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -8374,7 +8440,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -8382,7 +8448,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -8390,7 +8456,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -8398,7 +8464,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -8406,7 +8472,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -8414,7 +8480,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -8422,7 +8488,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -8430,7 +8496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -8438,7 +8504,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -8446,7 +8512,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -8454,7 +8520,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -8462,7 +8528,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -8470,7 +8536,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -8478,7 +8544,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -8486,7 +8552,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -8494,7 +8560,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -8502,7 +8568,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -8510,7 +8576,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -8518,7 +8584,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -8526,7 +8592,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -8546,203 +8612,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0EA78C-BA29-42F3-817D-47A083C2AFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43063C59-B14B-4187-AAA5-117CA5496436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="50">
   <si>
     <t>Aluno</t>
   </si>
@@ -185,6 +185,9 @@
   </si>
   <si>
     <t>3/P</t>
+  </si>
+  <si>
+    <t>P/8</t>
   </si>
 </sst>
 </file>
@@ -590,33 +593,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="49" max="51" width="7" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="7" style="3" bestFit="1" customWidth="1"/>
     <col min="53" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="107" width="7.7109375" customWidth="1"/>
+    <col min="55" max="107" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -813,7 +816,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1017,7 +1020,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1254,7 +1257,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1491,7 +1494,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1728,7 +1731,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1965,7 +1968,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2202,7 +2205,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2439,7 +2442,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2676,7 +2679,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2913,7 +2916,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -3141,7 +3144,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3378,7 +3381,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3543,7 +3546,7 @@
         <v>31</v>
       </c>
       <c r="BC13" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="BD13" s="3"/>
       <c r="BE13" s="3"/>
@@ -3615,7 +3618,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3852,7 +3855,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -4089,7 +4092,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4326,7 +4329,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4542,7 +4545,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -4779,7 +4782,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -5016,7 +5019,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -5160,7 +5163,7 @@
         <v>31</v>
       </c>
       <c r="BC20" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="BD20" s="3"/>
       <c r="BE20" s="3"/>
@@ -5232,7 +5235,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5469,7 +5472,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -5706,7 +5709,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -5943,7 +5946,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -6180,7 +6183,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6417,7 +6420,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -6582,7 +6585,7 @@
         <v>31</v>
       </c>
       <c r="BC26" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="BD26" s="3"/>
       <c r="BE26" s="3"/>
@@ -6654,7 +6657,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -6891,7 +6894,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -7128,7 +7131,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -7284,7 +7287,7 @@
         <v>31</v>
       </c>
       <c r="BC29" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="BD29" s="3"/>
       <c r="BE29" s="3"/>
@@ -7356,7 +7359,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -7593,7 +7596,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -7768,7 +7771,7 @@
       <c r="BI31" s="3"/>
       <c r="BJ31" s="3"/>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -7943,7 +7946,7 @@
       <c r="BI32" s="3"/>
       <c r="BJ32" s="3"/>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8118,7 +8121,7 @@
       <c r="BI33" s="3"/>
       <c r="BJ33" s="3"/>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -8331,12 +8334,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8344,7 +8347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -8352,7 +8355,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -8360,7 +8363,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -8368,7 +8371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -8376,7 +8379,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -8384,7 +8387,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -8392,7 +8395,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -8400,7 +8403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -8408,7 +8411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -8416,7 +8419,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -8424,7 +8427,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -8432,7 +8435,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -8440,7 +8443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -8448,7 +8451,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -8456,7 +8459,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -8464,7 +8467,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -8472,7 +8475,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -8480,7 +8483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -8488,7 +8491,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -8496,7 +8499,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -8504,7 +8507,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -8512,7 +8515,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -8520,7 +8523,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -8528,7 +8531,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -8536,7 +8539,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -8544,7 +8547,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -8552,7 +8555,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -8560,7 +8563,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -8568,7 +8571,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -8576,7 +8579,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -8584,7 +8587,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -8592,7 +8595,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -8612,203 +8615,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43063C59-B14B-4187-AAA5-117CA5496436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B08FEBA-A1AA-4406-8A3B-5F021DF32FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="50">
   <si>
     <t>Aluno</t>
   </si>
@@ -265,7 +265,67 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -593,33 +653,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="49" max="51" width="7" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="7" style="3" bestFit="1" customWidth="1"/>
     <col min="53" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="107" width="7.6640625" customWidth="1"/>
+    <col min="55" max="107" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -816,7 +876,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -982,7 +1042,9 @@
       <c r="BC2" s="1">
         <v>46259</v>
       </c>
-      <c r="BD2" s="1"/>
+      <c r="BD2" s="1">
+        <v>46261</v>
+      </c>
       <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
       <c r="BG2" s="1"/>
@@ -1020,7 +1082,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1187,7 +1249,9 @@
       <c r="BC3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD3" s="3"/>
+      <c r="BD3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE3" s="3"/>
       <c r="BF3" s="3"/>
       <c r="BG3" s="3"/>
@@ -1257,7 +1321,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1424,7 +1488,9 @@
       <c r="BC4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD4" s="3"/>
+      <c r="BD4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE4" s="3"/>
       <c r="BF4" s="3"/>
       <c r="BG4" s="3"/>
@@ -1494,7 +1560,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1661,7 +1727,9 @@
       <c r="BC5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD5" s="3"/>
+      <c r="BD5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE5" s="3"/>
       <c r="BF5" s="3"/>
       <c r="BG5" s="3"/>
@@ -1731,7 +1799,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1898,7 +1966,9 @@
       <c r="BC6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD6" s="3"/>
+      <c r="BD6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE6" s="3"/>
       <c r="BF6" s="3"/>
       <c r="BG6" s="3"/>
@@ -1968,7 +2038,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2135,7 +2205,9 @@
       <c r="BC7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD7" s="3"/>
+      <c r="BD7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE7" s="3"/>
       <c r="BF7" s="3"/>
       <c r="BG7" s="3"/>
@@ -2205,7 +2277,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2372,7 +2444,9 @@
       <c r="BC8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD8" s="3"/>
+      <c r="BD8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE8" s="3"/>
       <c r="BF8" s="3"/>
       <c r="BG8" s="3"/>
@@ -2442,7 +2516,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2609,7 +2683,9 @@
       <c r="BC9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD9" s="3"/>
+      <c r="BD9" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BE9" s="3"/>
       <c r="BF9" s="3"/>
       <c r="BG9" s="3"/>
@@ -2679,7 +2755,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2846,7 +2922,9 @@
       <c r="BC10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD10" s="3"/>
+      <c r="BD10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE10" s="3"/>
       <c r="BF10" s="3"/>
       <c r="BG10" s="3"/>
@@ -2916,7 +2994,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -3074,7 +3152,9 @@
       <c r="BC11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD11" s="3"/>
+      <c r="BD11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE11" s="3"/>
       <c r="BF11" s="3"/>
       <c r="BG11" s="3"/>
@@ -3144,7 +3224,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3311,7 +3391,9 @@
       <c r="BC12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD12" s="3"/>
+      <c r="BD12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE12" s="3"/>
       <c r="BF12" s="3"/>
       <c r="BG12" s="3"/>
@@ -3381,7 +3463,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3548,7 +3630,9 @@
       <c r="BC13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="BD13" s="3"/>
+      <c r="BD13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE13" s="3"/>
       <c r="BF13" s="3"/>
       <c r="BG13" s="3"/>
@@ -3618,7 +3702,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3785,7 +3869,9 @@
       <c r="BC14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD14" s="3"/>
+      <c r="BD14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE14" s="3"/>
       <c r="BF14" s="3"/>
       <c r="BG14" s="3"/>
@@ -3855,7 +3941,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -4022,7 +4108,9 @@
       <c r="BC15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD15" s="3"/>
+      <c r="BD15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE15" s="3"/>
       <c r="BF15" s="3"/>
       <c r="BG15" s="3"/>
@@ -4092,7 +4180,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4259,7 +4347,9 @@
       <c r="BC16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD16" s="3"/>
+      <c r="BD16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE16" s="3"/>
       <c r="BF16" s="3"/>
       <c r="BG16" s="3"/>
@@ -4329,7 +4419,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4475,7 +4565,9 @@
       <c r="BC17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD17" s="3"/>
+      <c r="BD17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE17" s="3"/>
       <c r="BF17" s="3"/>
       <c r="BG17" s="3"/>
@@ -4545,7 +4637,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -4712,7 +4804,9 @@
       <c r="BC18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD18" s="3"/>
+      <c r="BD18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE18" s="3"/>
       <c r="BF18" s="3"/>
       <c r="BG18" s="3"/>
@@ -4782,7 +4876,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -4949,7 +5043,9 @@
       <c r="BC19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD19" s="3"/>
+      <c r="BD19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE19" s="3"/>
       <c r="BF19" s="3"/>
       <c r="BG19" s="3"/>
@@ -5019,7 +5115,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -5165,7 +5261,9 @@
       <c r="BC20" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="BD20" s="3"/>
+      <c r="BD20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE20" s="3"/>
       <c r="BF20" s="3"/>
       <c r="BG20" s="3"/>
@@ -5235,7 +5333,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5402,7 +5500,9 @@
       <c r="BC21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD21" s="3"/>
+      <c r="BD21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE21" s="3"/>
       <c r="BF21" s="3"/>
       <c r="BG21" s="3"/>
@@ -5472,7 +5572,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -5639,7 +5739,9 @@
       <c r="BC22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BD22" s="3"/>
+      <c r="BD22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE22" s="3"/>
       <c r="BF22" s="3"/>
       <c r="BG22" s="3"/>
@@ -5709,7 +5811,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -5876,7 +5978,9 @@
       <c r="BC23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD23" s="3"/>
+      <c r="BD23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE23" s="3"/>
       <c r="BF23" s="3"/>
       <c r="BG23" s="3"/>
@@ -5946,7 +6050,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -6113,7 +6217,9 @@
       <c r="BC24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD24" s="3"/>
+      <c r="BD24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE24" s="3"/>
       <c r="BF24" s="3"/>
       <c r="BG24" s="3"/>
@@ -6183,7 +6289,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6350,7 +6456,9 @@
       <c r="BC25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD25" s="3"/>
+      <c r="BD25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE25" s="3"/>
       <c r="BF25" s="3"/>
       <c r="BG25" s="3"/>
@@ -6420,7 +6528,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -6587,7 +6695,9 @@
       <c r="BC26" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="BD26" s="3"/>
+      <c r="BD26" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BE26" s="3"/>
       <c r="BF26" s="3"/>
       <c r="BG26" s="3"/>
@@ -6657,7 +6767,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -6824,7 +6934,9 @@
       <c r="BC27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD27" s="3"/>
+      <c r="BD27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE27" s="3"/>
       <c r="BF27" s="3"/>
       <c r="BG27" s="3"/>
@@ -6894,7 +7006,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -7061,7 +7173,9 @@
       <c r="BC28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD28" s="3"/>
+      <c r="BD28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE28" s="3"/>
       <c r="BF28" s="3"/>
       <c r="BG28" s="3"/>
@@ -7131,7 +7245,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -7289,7 +7403,9 @@
       <c r="BC29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="BD29" s="3"/>
+      <c r="BD29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE29" s="3"/>
       <c r="BF29" s="3"/>
       <c r="BG29" s="3"/>
@@ -7359,7 +7475,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -7526,7 +7642,9 @@
       <c r="BC30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD30" s="3"/>
+      <c r="BD30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE30" s="3"/>
       <c r="BF30" s="3"/>
       <c r="BG30" s="3"/>
@@ -7596,7 +7714,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -7763,7 +7881,9 @@
       <c r="BC31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD31" s="3"/>
+      <c r="BD31" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE31" s="3"/>
       <c r="BF31" s="3"/>
       <c r="BG31" s="3"/>
@@ -7771,7 +7891,7 @@
       <c r="BI31" s="3"/>
       <c r="BJ31" s="3"/>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -7938,7 +8058,9 @@
       <c r="BC32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD32" s="3"/>
+      <c r="BD32" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE32" s="3"/>
       <c r="BF32" s="3"/>
       <c r="BG32" s="3"/>
@@ -7946,7 +8068,7 @@
       <c r="BI32" s="3"/>
       <c r="BJ32" s="3"/>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8113,7 +8235,9 @@
       <c r="BC33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD33" s="3"/>
+      <c r="BD33" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE33" s="3"/>
       <c r="BF33" s="3"/>
       <c r="BG33" s="3"/>
@@ -8121,7 +8245,7 @@
       <c r="BI33" s="3"/>
       <c r="BJ33" s="3"/>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -8288,7 +8412,9 @@
       <c r="BC34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BD34" s="3"/>
+      <c r="BD34" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BE34" s="3"/>
       <c r="BF34" s="3"/>
       <c r="BG34" s="3"/>
@@ -8302,28 +8428,33 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:AS34">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BK9 AU4:AY26 BL4:DH30 AZ10:BB21 BD10:BK21 AZ22:BK26 AU27:BK28 AU29:AX30 AZ29:BK30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33">
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB9">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB32">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BD3:BD34">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BD3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -8334,12 +8465,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8347,7 +8478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -8355,7 +8486,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -8363,7 +8494,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -8371,7 +8502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -8379,7 +8510,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -8387,7 +8518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -8395,7 +8526,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -8403,7 +8534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -8411,7 +8542,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -8419,7 +8550,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -8427,7 +8558,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -8435,7 +8566,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -8443,7 +8574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -8451,7 +8582,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -8459,7 +8590,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -8467,7 +8598,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -8475,7 +8606,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -8483,7 +8614,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -8491,7 +8622,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -8499,7 +8630,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -8507,7 +8638,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -8515,7 +8646,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -8523,7 +8654,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -8531,7 +8662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -8539,7 +8670,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -8547,7 +8678,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -8555,7 +8686,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -8563,7 +8694,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -8571,7 +8702,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -8579,7 +8710,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -8587,7 +8718,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -8595,7 +8726,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -8615,203 +8746,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B08FEBA-A1AA-4406-8A3B-5F021DF32FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D76F4B6-5B21-4B25-8D5A-F71FDC252F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="50">
   <si>
     <t>Aluno</t>
   </si>
@@ -265,57 +265,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -653,33 +603,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="49" max="51" width="7" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="7" style="3" bestFit="1" customWidth="1"/>
     <col min="53" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="107" width="7.7109375" customWidth="1"/>
+    <col min="55" max="107" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -839,8 +789,12 @@
       <c r="BD1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="BE1" s="1"/>
-      <c r="BF1" s="1"/>
+      <c r="BE1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="BG1" s="1"/>
       <c r="BH1" s="1"/>
       <c r="BI1" s="1"/>
@@ -876,7 +830,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1045,8 +999,12 @@
       <c r="BD2" s="1">
         <v>46261</v>
       </c>
-      <c r="BE2" s="1"/>
-      <c r="BF2" s="1"/>
+      <c r="BE2" s="1">
+        <v>46266</v>
+      </c>
+      <c r="BF2" s="1">
+        <v>46268</v>
+      </c>
       <c r="BG2" s="1"/>
       <c r="BH2" s="1"/>
       <c r="BI2" s="1"/>
@@ -1082,7 +1040,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1252,7 +1210,9 @@
       <c r="BD3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE3" s="3"/>
+      <c r="BE3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF3" s="3"/>
       <c r="BG3" s="3"/>
       <c r="BH3" s="3"/>
@@ -1321,7 +1281,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1491,7 +1451,9 @@
       <c r="BD4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE4" s="3"/>
+      <c r="BE4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF4" s="3"/>
       <c r="BG4" s="3"/>
       <c r="BH4" s="3"/>
@@ -1560,7 +1522,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1730,7 +1692,9 @@
       <c r="BD5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE5" s="3"/>
+      <c r="BE5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF5" s="3"/>
       <c r="BG5" s="3"/>
       <c r="BH5" s="3"/>
@@ -1799,7 +1763,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1969,7 +1933,9 @@
       <c r="BD6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE6" s="3"/>
+      <c r="BE6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF6" s="3"/>
       <c r="BG6" s="3"/>
       <c r="BH6" s="3"/>
@@ -2038,7 +2004,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2208,7 +2174,9 @@
       <c r="BD7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE7" s="3"/>
+      <c r="BE7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF7" s="3"/>
       <c r="BG7" s="3"/>
       <c r="BH7" s="3"/>
@@ -2277,7 +2245,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2447,7 +2415,9 @@
       <c r="BD8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE8" s="3"/>
+      <c r="BE8" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BF8" s="3"/>
       <c r="BG8" s="3"/>
       <c r="BH8" s="3"/>
@@ -2516,7 +2486,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2686,7 +2656,9 @@
       <c r="BD9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BE9" s="3"/>
+      <c r="BE9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF9" s="3"/>
       <c r="BG9" s="3"/>
       <c r="BH9" s="3"/>
@@ -2755,7 +2727,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2925,7 +2897,9 @@
       <c r="BD10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE10" s="3"/>
+      <c r="BE10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF10" s="3"/>
       <c r="BG10" s="3"/>
       <c r="BH10" s="3"/>
@@ -2994,7 +2968,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -3155,7 +3129,9 @@
       <c r="BD11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE11" s="3"/>
+      <c r="BE11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF11" s="3"/>
       <c r="BG11" s="3"/>
       <c r="BH11" s="3"/>
@@ -3224,7 +3200,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3394,7 +3370,9 @@
       <c r="BD12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE12" s="3"/>
+      <c r="BE12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF12" s="3"/>
       <c r="BG12" s="3"/>
       <c r="BH12" s="3"/>
@@ -3463,7 +3441,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3633,7 +3611,9 @@
       <c r="BD13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE13" s="3"/>
+      <c r="BE13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF13" s="3"/>
       <c r="BG13" s="3"/>
       <c r="BH13" s="3"/>
@@ -3702,7 +3682,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3872,7 +3852,9 @@
       <c r="BD14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE14" s="3"/>
+      <c r="BE14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF14" s="3"/>
       <c r="BG14" s="3"/>
       <c r="BH14" s="3"/>
@@ -3941,7 +3923,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -4111,7 +4093,9 @@
       <c r="BD15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE15" s="3"/>
+      <c r="BE15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF15" s="3"/>
       <c r="BG15" s="3"/>
       <c r="BH15" s="3"/>
@@ -4180,7 +4164,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4350,7 +4334,9 @@
       <c r="BD16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE16" s="3"/>
+      <c r="BE16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF16" s="3"/>
       <c r="BG16" s="3"/>
       <c r="BH16" s="3"/>
@@ -4419,7 +4405,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4568,7 +4554,9 @@
       <c r="BD17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE17" s="3"/>
+      <c r="BE17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF17" s="3"/>
       <c r="BG17" s="3"/>
       <c r="BH17" s="3"/>
@@ -4637,7 +4625,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -4807,7 +4795,9 @@
       <c r="BD18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE18" s="3"/>
+      <c r="BE18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF18" s="3"/>
       <c r="BG18" s="3"/>
       <c r="BH18" s="3"/>
@@ -4876,7 +4866,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -5046,7 +5036,9 @@
       <c r="BD19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE19" s="3"/>
+      <c r="BE19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF19" s="3"/>
       <c r="BG19" s="3"/>
       <c r="BH19" s="3"/>
@@ -5115,7 +5107,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -5264,7 +5256,9 @@
       <c r="BD20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE20" s="3"/>
+      <c r="BE20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF20" s="3"/>
       <c r="BG20" s="3"/>
       <c r="BH20" s="3"/>
@@ -5333,7 +5327,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5503,7 +5497,9 @@
       <c r="BD21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE21" s="3"/>
+      <c r="BE21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF21" s="3"/>
       <c r="BG21" s="3"/>
       <c r="BH21" s="3"/>
@@ -5572,7 +5568,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -5742,7 +5738,9 @@
       <c r="BD22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE22" s="3"/>
+      <c r="BE22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF22" s="3"/>
       <c r="BG22" s="3"/>
       <c r="BH22" s="3"/>
@@ -5811,7 +5809,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -5981,7 +5979,9 @@
       <c r="BD23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE23" s="3"/>
+      <c r="BE23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF23" s="3"/>
       <c r="BG23" s="3"/>
       <c r="BH23" s="3"/>
@@ -6050,7 +6050,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -6220,7 +6220,9 @@
       <c r="BD24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE24" s="3"/>
+      <c r="BE24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF24" s="3"/>
       <c r="BG24" s="3"/>
       <c r="BH24" s="3"/>
@@ -6289,7 +6291,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6459,7 +6461,9 @@
       <c r="BD25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE25" s="3"/>
+      <c r="BE25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF25" s="3"/>
       <c r="BG25" s="3"/>
       <c r="BH25" s="3"/>
@@ -6528,7 +6532,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -6698,7 +6702,9 @@
       <c r="BD26" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BE26" s="3"/>
+      <c r="BE26" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="BF26" s="3"/>
       <c r="BG26" s="3"/>
       <c r="BH26" s="3"/>
@@ -6767,7 +6773,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -6937,7 +6943,9 @@
       <c r="BD27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE27" s="3"/>
+      <c r="BE27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF27" s="3"/>
       <c r="BG27" s="3"/>
       <c r="BH27" s="3"/>
@@ -7006,7 +7014,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -7176,7 +7184,9 @@
       <c r="BD28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE28" s="3"/>
+      <c r="BE28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF28" s="3"/>
       <c r="BG28" s="3"/>
       <c r="BH28" s="3"/>
@@ -7245,7 +7255,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -7406,7 +7416,9 @@
       <c r="BD29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE29" s="3"/>
+      <c r="BE29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF29" s="3"/>
       <c r="BG29" s="3"/>
       <c r="BH29" s="3"/>
@@ -7475,7 +7487,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -7645,7 +7657,9 @@
       <c r="BD30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE30" s="3"/>
+      <c r="BE30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF30" s="3"/>
       <c r="BG30" s="3"/>
       <c r="BH30" s="3"/>
@@ -7714,7 +7728,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -7884,14 +7898,16 @@
       <c r="BD31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE31" s="3"/>
+      <c r="BE31" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF31" s="3"/>
       <c r="BG31" s="3"/>
       <c r="BH31" s="3"/>
       <c r="BI31" s="3"/>
       <c r="BJ31" s="3"/>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -8061,14 +8077,16 @@
       <c r="BD32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE32" s="3"/>
+      <c r="BE32" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF32" s="3"/>
       <c r="BG32" s="3"/>
       <c r="BH32" s="3"/>
       <c r="BI32" s="3"/>
       <c r="BJ32" s="3"/>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8238,14 +8256,16 @@
       <c r="BD33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE33" s="3"/>
+      <c r="BE33" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF33" s="3"/>
       <c r="BG33" s="3"/>
       <c r="BH33" s="3"/>
       <c r="BI33" s="3"/>
       <c r="BJ33" s="3"/>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -8415,7 +8435,9 @@
       <c r="BD34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BE34" s="3"/>
+      <c r="BE34" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BF34" s="3"/>
       <c r="BG34" s="3"/>
       <c r="BH34" s="3"/>
@@ -8428,27 +8450,27 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:AS34">
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BK9 AU4:AY26 BL4:DH30 AZ10:BB21 BD10:BK21 AZ22:BK26 AU27:BK28 AU29:AX30 AZ29:BK30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="8" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB9">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB32">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8465,12 +8487,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8478,7 +8500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -8486,7 +8508,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -8494,7 +8516,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -8502,7 +8524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -8510,7 +8532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -8518,7 +8540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -8526,7 +8548,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -8534,7 +8556,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -8542,7 +8564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -8550,7 +8572,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -8558,7 +8580,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -8566,7 +8588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -8574,7 +8596,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -8582,7 +8604,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -8590,7 +8612,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -8598,7 +8620,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -8606,7 +8628,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -8614,7 +8636,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -8622,7 +8644,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -8630,7 +8652,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -8638,7 +8660,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -8646,7 +8668,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -8654,7 +8676,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -8662,7 +8684,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -8670,7 +8692,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -8678,7 +8700,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -8686,7 +8708,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -8694,7 +8716,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -8702,7 +8724,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -8710,7 +8732,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -8718,7 +8740,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -8726,7 +8748,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -8746,203 +8768,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D76F4B6-5B21-4B25-8D5A-F71FDC252F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3970F6C7-7D17-4BF6-87B8-464DEFD48345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="50">
   <si>
     <t>Aluno</t>
   </si>
@@ -603,33 +603,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DT34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="38" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="45" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="38" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="45" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="49" max="51" width="7" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="7" style="3" bestFit="1" customWidth="1"/>
     <col min="53" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="107" width="7.6640625" customWidth="1"/>
+    <col min="55" max="107" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
@@ -795,8 +795,12 @@
       <c r="BF1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="BG1" s="1"/>
-      <c r="BH1" s="1"/>
+      <c r="BG1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="BI1" s="1"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
@@ -830,7 +834,7 @@
       <c r="CM1" s="2"/>
       <c r="CN1" s="2"/>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1040,7 +1044,7 @@
       <c r="CM2" s="3"/>
       <c r="CN2" s="3"/>
     </row>
-    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:124" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>26132246</v>
@@ -1213,7 +1217,9 @@
       <c r="BE3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF3" s="3"/>
+      <c r="BF3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG3" s="3"/>
       <c r="BH3" s="3"/>
       <c r="BI3" s="3"/>
@@ -1281,7 +1287,7 @@
       <c r="DS3" s="3"/>
       <c r="DT3" s="3"/>
     </row>
-    <row r="4" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>26132200</v>
@@ -1454,7 +1460,9 @@
       <c r="BE4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF4" s="3"/>
+      <c r="BF4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG4" s="3"/>
       <c r="BH4" s="3"/>
       <c r="BI4" s="3"/>
@@ -1522,7 +1530,7 @@
       <c r="DS4" s="3"/>
       <c r="DT4" s="3"/>
     </row>
-    <row r="5" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>26132302</v>
@@ -1695,7 +1703,9 @@
       <c r="BE5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF5" s="3"/>
+      <c r="BF5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG5" s="3"/>
       <c r="BH5" s="3"/>
       <c r="BI5" s="3"/>
@@ -1763,7 +1773,7 @@
       <c r="DS5" s="3"/>
       <c r="DT5" s="3"/>
     </row>
-    <row r="6" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>26132277</v>
@@ -1936,7 +1946,9 @@
       <c r="BE6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF6" s="3"/>
+      <c r="BF6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG6" s="3"/>
       <c r="BH6" s="3"/>
       <c r="BI6" s="3"/>
@@ -2004,7 +2016,7 @@
       <c r="DS6" s="3"/>
       <c r="DT6" s="3"/>
     </row>
-    <row r="7" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>26132197</v>
@@ -2177,7 +2189,9 @@
       <c r="BE7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF7" s="3"/>
+      <c r="BF7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG7" s="3"/>
       <c r="BH7" s="3"/>
       <c r="BI7" s="3"/>
@@ -2245,7 +2259,7 @@
       <c r="DS7" s="3"/>
       <c r="DT7" s="3"/>
     </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>26132286</v>
@@ -2418,7 +2432,9 @@
       <c r="BE8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="BF8" s="3"/>
+      <c r="BF8" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG8" s="3"/>
       <c r="BH8" s="3"/>
       <c r="BI8" s="3"/>
@@ -2486,7 +2502,7 @@
       <c r="DS8" s="3"/>
       <c r="DT8" s="3"/>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>26132281</v>
@@ -2659,7 +2675,9 @@
       <c r="BE9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF9" s="3"/>
+      <c r="BF9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG9" s="3"/>
       <c r="BH9" s="3"/>
       <c r="BI9" s="3"/>
@@ -2727,7 +2745,7 @@
       <c r="DS9" s="3"/>
       <c r="DT9" s="3"/>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>26132340</v>
@@ -2900,7 +2918,9 @@
       <c r="BE10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF10" s="3"/>
+      <c r="BF10" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG10" s="3"/>
       <c r="BH10" s="3"/>
       <c r="BI10" s="3"/>
@@ -2968,7 +2988,7 @@
       <c r="DS10" s="3"/>
       <c r="DT10" s="3"/>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>26133020</v>
@@ -3132,7 +3152,9 @@
       <c r="BE11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF11" s="3"/>
+      <c r="BF11" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG11" s="3"/>
       <c r="BH11" s="3"/>
       <c r="BI11" s="3"/>
@@ -3200,7 +3222,7 @@
       <c r="DS11" s="3"/>
       <c r="DT11" s="3"/>
     </row>
-    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>26132271</v>
@@ -3373,7 +3395,9 @@
       <c r="BE12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF12" s="3"/>
+      <c r="BF12" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG12" s="3"/>
       <c r="BH12" s="3"/>
       <c r="BI12" s="3"/>
@@ -3441,7 +3465,7 @@
       <c r="DS12" s="3"/>
       <c r="DT12" s="3"/>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>26132244</v>
@@ -3614,7 +3638,9 @@
       <c r="BE13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF13" s="3"/>
+      <c r="BF13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG13" s="3"/>
       <c r="BH13" s="3"/>
       <c r="BI13" s="3"/>
@@ -3682,7 +3708,7 @@
       <c r="DS13" s="3"/>
       <c r="DT13" s="3"/>
     </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>26132204</v>
@@ -3855,7 +3881,9 @@
       <c r="BE14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF14" s="3"/>
+      <c r="BF14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG14" s="3"/>
       <c r="BH14" s="3"/>
       <c r="BI14" s="3"/>
@@ -3923,7 +3951,7 @@
       <c r="DS14" s="3"/>
       <c r="DT14" s="3"/>
     </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>26132220</v>
@@ -4096,7 +4124,9 @@
       <c r="BE15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF15" s="3"/>
+      <c r="BF15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG15" s="3"/>
       <c r="BH15" s="3"/>
       <c r="BI15" s="3"/>
@@ -4164,7 +4194,7 @@
       <c r="DS15" s="3"/>
       <c r="DT15" s="3"/>
     </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>26132184</v>
@@ -4337,7 +4367,9 @@
       <c r="BE16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF16" s="3"/>
+      <c r="BF16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG16" s="3"/>
       <c r="BH16" s="3"/>
       <c r="BI16" s="3"/>
@@ -4405,7 +4437,7 @@
       <c r="DS16" s="3"/>
       <c r="DT16" s="3"/>
     </row>
-    <row r="17" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>26133029</v>
@@ -4557,7 +4589,9 @@
       <c r="BE17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF17" s="3"/>
+      <c r="BF17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG17" s="3"/>
       <c r="BH17" s="3"/>
       <c r="BI17" s="3"/>
@@ -4625,7 +4659,7 @@
       <c r="DS17" s="3"/>
       <c r="DT17" s="3"/>
     </row>
-    <row r="18" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>26132288</v>
@@ -4798,7 +4832,9 @@
       <c r="BE18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF18" s="3"/>
+      <c r="BF18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG18" s="3"/>
       <c r="BH18" s="3"/>
       <c r="BI18" s="3"/>
@@ -4866,7 +4902,7 @@
       <c r="DS18" s="3"/>
       <c r="DT18" s="3"/>
     </row>
-    <row r="19" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>26132330</v>
@@ -5039,7 +5075,9 @@
       <c r="BE19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF19" s="3"/>
+      <c r="BF19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG19" s="3"/>
       <c r="BH19" s="3"/>
       <c r="BI19" s="3"/>
@@ -5107,7 +5145,7 @@
       <c r="DS19" s="3"/>
       <c r="DT19" s="3"/>
     </row>
-    <row r="20" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>26133024</v>
@@ -5259,7 +5297,9 @@
       <c r="BE20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF20" s="3"/>
+      <c r="BF20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG20" s="3"/>
       <c r="BH20" s="3"/>
       <c r="BI20" s="3"/>
@@ -5327,7 +5367,7 @@
       <c r="DS20" s="3"/>
       <c r="DT20" s="3"/>
     </row>
-    <row r="21" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>26132248</v>
@@ -5500,7 +5540,9 @@
       <c r="BE21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF21" s="3"/>
+      <c r="BF21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG21" s="3"/>
       <c r="BH21" s="3"/>
       <c r="BI21" s="3"/>
@@ -5568,7 +5610,7 @@
       <c r="DS21" s="3"/>
       <c r="DT21" s="3"/>
     </row>
-    <row r="22" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>26132180</v>
@@ -5741,7 +5783,9 @@
       <c r="BE22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF22" s="3"/>
+      <c r="BF22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG22" s="3"/>
       <c r="BH22" s="3"/>
       <c r="BI22" s="3"/>
@@ -5809,7 +5853,7 @@
       <c r="DS22" s="3"/>
       <c r="DT22" s="3"/>
     </row>
-    <row r="23" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>26132269</v>
@@ -5982,7 +6026,9 @@
       <c r="BE23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF23" s="3"/>
+      <c r="BF23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG23" s="3"/>
       <c r="BH23" s="3"/>
       <c r="BI23" s="3"/>
@@ -6050,7 +6096,7 @@
       <c r="DS23" s="3"/>
       <c r="DT23" s="3"/>
     </row>
-    <row r="24" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>26132202</v>
@@ -6223,7 +6269,9 @@
       <c r="BE24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF24" s="3"/>
+      <c r="BF24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG24" s="3"/>
       <c r="BH24" s="3"/>
       <c r="BI24" s="3"/>
@@ -6291,7 +6339,7 @@
       <c r="DS24" s="3"/>
       <c r="DT24" s="3"/>
     </row>
-    <row r="25" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>26132265</v>
@@ -6464,7 +6512,9 @@
       <c r="BE25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF25" s="3"/>
+      <c r="BF25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG25" s="3"/>
       <c r="BH25" s="3"/>
       <c r="BI25" s="3"/>
@@ -6532,7 +6582,7 @@
       <c r="DS25" s="3"/>
       <c r="DT25" s="3"/>
     </row>
-    <row r="26" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>26132252</v>
@@ -6705,7 +6755,9 @@
       <c r="BE26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="BF26" s="3"/>
+      <c r="BF26" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG26" s="3"/>
       <c r="BH26" s="3"/>
       <c r="BI26" s="3"/>
@@ -6773,7 +6825,7 @@
       <c r="DS26" s="3"/>
       <c r="DT26" s="3"/>
     </row>
-    <row r="27" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>26132242</v>
@@ -6946,7 +6998,9 @@
       <c r="BE27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF27" s="3"/>
+      <c r="BF27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG27" s="3"/>
       <c r="BH27" s="3"/>
       <c r="BI27" s="3"/>
@@ -7014,7 +7068,7 @@
       <c r="DS27" s="3"/>
       <c r="DT27" s="3"/>
     </row>
-    <row r="28" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>26132240</v>
@@ -7187,7 +7241,9 @@
       <c r="BE28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF28" s="3"/>
+      <c r="BF28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG28" s="3"/>
       <c r="BH28" s="3"/>
       <c r="BI28" s="3"/>
@@ -7255,7 +7311,7 @@
       <c r="DS28" s="3"/>
       <c r="DT28" s="3"/>
     </row>
-    <row r="29" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>26133022</v>
@@ -7419,7 +7475,9 @@
       <c r="BE29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF29" s="3"/>
+      <c r="BF29" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG29" s="3"/>
       <c r="BH29" s="3"/>
       <c r="BI29" s="3"/>
@@ -7487,7 +7545,7 @@
       <c r="DS29" s="3"/>
       <c r="DT29" s="3"/>
     </row>
-    <row r="30" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>26132250</v>
@@ -7660,7 +7718,9 @@
       <c r="BE30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF30" s="3"/>
+      <c r="BF30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG30" s="3"/>
       <c r="BH30" s="3"/>
       <c r="BI30" s="3"/>
@@ -7728,7 +7788,7 @@
       <c r="DS30" s="3"/>
       <c r="DT30" s="3"/>
     </row>
-    <row r="31" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>26132238</v>
@@ -7901,13 +7961,15 @@
       <c r="BE31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF31" s="3"/>
+      <c r="BF31" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG31" s="3"/>
       <c r="BH31" s="3"/>
       <c r="BI31" s="3"/>
       <c r="BJ31" s="3"/>
     </row>
-    <row r="32" spans="1:124" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>26132275</v>
@@ -8080,13 +8142,15 @@
       <c r="BE32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF32" s="3"/>
+      <c r="BF32" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG32" s="3"/>
       <c r="BH32" s="3"/>
       <c r="BI32" s="3"/>
       <c r="BJ32" s="3"/>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>26132256</v>
@@ -8259,13 +8323,15 @@
       <c r="BE33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF33" s="3"/>
+      <c r="BF33" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG33" s="3"/>
       <c r="BH33" s="3"/>
       <c r="BI33" s="3"/>
       <c r="BJ33" s="3"/>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>alunos!A33</f>
         <v>26132304</v>
@@ -8438,7 +8504,9 @@
       <c r="BE34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BF34" s="3"/>
+      <c r="BF34" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BG34" s="3"/>
       <c r="BH34" s="3"/>
       <c r="BI34" s="3"/>
@@ -8487,12 +8555,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8500,7 +8568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132246</v>
       </c>
@@ -8508,7 +8576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132200</v>
       </c>
@@ -8516,7 +8584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132302</v>
       </c>
@@ -8524,7 +8592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132277</v>
       </c>
@@ -8532,7 +8600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132197</v>
       </c>
@@ -8540,7 +8608,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132286</v>
       </c>
@@ -8548,7 +8616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132281</v>
       </c>
@@ -8556,7 +8624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132340</v>
       </c>
@@ -8564,7 +8632,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26133020</v>
       </c>
@@ -8572,7 +8640,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132271</v>
       </c>
@@ -8580,7 +8648,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132244</v>
       </c>
@@ -8588,7 +8656,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132204</v>
       </c>
@@ -8596,7 +8664,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132220</v>
       </c>
@@ -8604,7 +8672,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132184</v>
       </c>
@@ -8612,7 +8680,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26133029</v>
       </c>
@@ -8620,7 +8688,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132288</v>
       </c>
@@ -8628,7 +8696,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132330</v>
       </c>
@@ -8636,7 +8704,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26133024</v>
       </c>
@@ -8644,7 +8712,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132248</v>
       </c>
@@ -8652,7 +8720,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132180</v>
       </c>
@@ -8660,7 +8728,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132269</v>
       </c>
@@ -8668,7 +8736,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132202</v>
       </c>
@@ -8676,7 +8744,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132265</v>
       </c>
@@ -8684,7 +8752,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132252</v>
       </c>
@@ -8692,7 +8760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132242</v>
       </c>
@@ -8700,7 +8768,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132240</v>
       </c>
@@ -8708,7 +8776,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26133022</v>
       </c>
@@ -8716,7 +8784,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132250</v>
       </c>
@@ -8724,7 +8792,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132238</v>
       </c>
@@ -8732,7 +8800,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132275</v>
       </c>
@@ -8740,7 +8808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132256</v>
       </c>
@@ -8748,7 +8816,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132304</v>
       </c>
@@ -8768,203 +8836,203 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4DDCA2-EB43-4FE7-A5F4-0E4DC176FDD0}">
   <dimension ref="A2:A34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>alunos!B2</f>
         <v>Ana Beatriz Alves de Lima</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>alunos!B3</f>
         <v>Bianca Giovedy Pagotto</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>alunos!B4</f>
         <v>Breno Frazão Callegari</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>alunos!B5</f>
         <v>Davi Cruz Oliveira</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>alunos!B6</f>
         <v>Eduardo Moretti Varotti</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>alunos!B7</f>
         <v>Gabriela Leticia da Silva</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>alunos!B8</f>
         <v>Geovanna Martins Bertuol</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>alunos!B9</f>
         <v>Giulia de Godoi Silveira</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>alunos!B10</f>
         <v>Giuseppe de Moraes Vieira</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>alunos!B11</f>
         <v>Gustavo Ferelli</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>alunos!B12</f>
         <v>Heitor Dorigan de Angeli</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>alunos!B13</f>
         <v>Helena Politti Rossi</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>alunos!B14</f>
         <v>Isabela Marchiori Ferreira</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>alunos!B15</f>
         <v>Isabelle Caroline Vizeu de Salles</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>alunos!B16</f>
         <v>Larissa Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>alunos!B17</f>
         <v>Leandro Imenes de Oliveira</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>alunos!B18</f>
         <v>Letícia Aparecida Pinto de Souza</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>alunos!B19</f>
         <v>Liara Guarizo Tolloto</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>alunos!B20</f>
         <v>Luana Gabrielle de Oliveira</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>alunos!B21</f>
         <v>Marina Henrique Moretti</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>alunos!B22</f>
         <v>Matheus Dorigan Paiato</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>alunos!B23</f>
         <v>Maycon Silva Gonçalves de Lima</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>alunos!B24</f>
         <v>Nicolas Augusto dos Reis Lira</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>alunos!B25</f>
         <v>Otávio Augusto Barbosa</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>alunos!B26</f>
         <v>Pedro Henrique Souza Guarizo</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>alunos!B27</f>
         <v>Renan Pavan Fazullo</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>alunos!B28</f>
         <v>Samyra Leite da Silva Ferreira</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>alunos!B29</f>
         <v>Sara de Paula Souza</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>alunos!B30</f>
         <v>Sofia Ohashi Faria</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>alunos!B31</f>
         <v>Tobias Gabriel Bueno de Godoi</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>alunos!B32</f>
         <v>Víctor Henrique Santana Alves</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>alunos!B33</f>
         <v>Vitória Bueno da Silva</v>

--- a/ds/turmas/1DES_A/frequencia-2-A.xlsx
+++ b/ds/turmas/1DES_A/frequencia-2-A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3970F6C7-7D17-4BF6-87B8-464DEFD48345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D160B71-A20C-48C5-98A1-233FB11BADA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="52">
   <si>
     <t>Aluno</t>
   </si>
@@ -189,12 +189,18 @@
   <si>
     <t>P/8</t>
   </si>
+  <si>
+    <t>FERIADO</t>
+  </si>
+  <si>
+    <t>5P|F</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,6 +234,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -250,7 +263,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -260,12 +273,163 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -626,7 +790,9 @@
     <col min="49" max="51" width="7" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="7" style="3" bestFit="1" customWidth="1"/>
     <col min="53" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="107" width="7.7109375" customWidth="1"/>
+    <col min="55" max="58" width="7.7109375" customWidth="1"/>
+    <col min="59" max="59" width="8.5703125" customWidth="1"/>
+    <col min="60" max="107" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:124" x14ac:dyDescent="0.25">
@@ -1009,8 +1175,12 @@
       <c r="BF2" s="1">
         <v>46268</v>
       </c>
-      <c r="BG2" s="1"/>
-      <c r="BH2" s="1"/>
+      <c r="BG2" s="1">
+        <v>46273</v>
+      </c>
+      <c r="BH2" s="1">
+        <v>46275</v>
+      </c>
       <c r="BI2" s="1"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
@@ -1220,8 +1390,12 @@
       <c r="BF3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG3" s="3"/>
-      <c r="BH3" s="3"/>
+      <c r="BG3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI3" s="3"/>
       <c r="BJ3" s="3"/>
       <c r="BK3" s="3"/>
@@ -1463,8 +1637,12 @@
       <c r="BF4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG4" s="3"/>
-      <c r="BH4" s="3"/>
+      <c r="BG4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH4" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI4" s="3"/>
       <c r="BJ4" s="3"/>
       <c r="BK4" s="3"/>
@@ -1706,8 +1884,12 @@
       <c r="BF5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG5" s="3"/>
-      <c r="BH5" s="3"/>
+      <c r="BG5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH5" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI5" s="3"/>
       <c r="BJ5" s="3"/>
       <c r="BK5" s="3"/>
@@ -1949,8 +2131,12 @@
       <c r="BF6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG6" s="3"/>
-      <c r="BH6" s="3"/>
+      <c r="BG6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH6" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI6" s="3"/>
       <c r="BJ6" s="3"/>
       <c r="BK6" s="3"/>
@@ -2192,8 +2378,12 @@
       <c r="BF7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG7" s="3"/>
-      <c r="BH7" s="3"/>
+      <c r="BG7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI7" s="3"/>
       <c r="BJ7" s="3"/>
       <c r="BK7" s="3"/>
@@ -2435,8 +2625,12 @@
       <c r="BF8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG8" s="3"/>
-      <c r="BH8" s="3"/>
+      <c r="BG8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH8" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="BI8" s="3"/>
       <c r="BJ8" s="3"/>
       <c r="BK8" s="3"/>
@@ -2678,8 +2872,12 @@
       <c r="BF9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG9" s="3"/>
-      <c r="BH9" s="3"/>
+      <c r="BG9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH9" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI9" s="3"/>
       <c r="BJ9" s="3"/>
       <c r="BK9" s="3"/>
@@ -2921,8 +3119,12 @@
       <c r="BF10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG10" s="3"/>
-      <c r="BH10" s="3"/>
+      <c r="BG10" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH10" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BI10" s="3"/>
       <c r="BJ10" s="3"/>
       <c r="BK10" s="3"/>
@@ -3155,8 +3357,12 @@
       <c r="BF11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG11" s="3"/>
-      <c r="BH11" s="3"/>
+      <c r="BG11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH11" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BI11" s="3"/>
       <c r="BJ11" s="3"/>
       <c r="BK11" s="3"/>
@@ -3398,8 +3604,12 @@
       <c r="BF12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG12" s="3"/>
-      <c r="BH12" s="3"/>
+      <c r="BG12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH12" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BI12" s="3"/>
       <c r="BJ12" s="3"/>
       <c r="BK12" s="3"/>
@@ -3641,8 +3851,12 @@
       <c r="BF13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG13" s="3"/>
-      <c r="BH13" s="3"/>
+      <c r="BG13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH13" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI13" s="3"/>
       <c r="BJ13" s="3"/>
       <c r="BK13" s="3"/>
@@ -3884,8 +4098,12 @@
       <c r="BF14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG14" s="3"/>
-      <c r="BH14" s="3"/>
+      <c r="BG14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH14" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI14" s="3"/>
       <c r="BJ14" s="3"/>
       <c r="BK14" s="3"/>
@@ -4127,8 +4345,12 @@
       <c r="BF15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG15" s="3"/>
-      <c r="BH15" s="3"/>
+      <c r="BG15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH15" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI15" s="3"/>
       <c r="BJ15" s="3"/>
       <c r="BK15" s="3"/>
@@ -4370,8 +4592,12 @@
       <c r="BF16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG16" s="3"/>
-      <c r="BH16" s="3"/>
+      <c r="BG16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH16" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI16" s="3"/>
       <c r="BJ16" s="3"/>
       <c r="BK16" s="3"/>
@@ -4592,8 +4818,12 @@
       <c r="BF17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG17" s="3"/>
-      <c r="BH17" s="3"/>
+      <c r="BG17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH17" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI17" s="3"/>
       <c r="BJ17" s="3"/>
       <c r="BK17" s="3"/>
@@ -4835,8 +5065,12 @@
       <c r="BF18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG18" s="3"/>
-      <c r="BH18" s="3"/>
+      <c r="BG18" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH18" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI18" s="3"/>
       <c r="BJ18" s="3"/>
       <c r="BK18" s="3"/>
@@ -5078,8 +5312,12 @@
       <c r="BF19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG19" s="3"/>
-      <c r="BH19" s="3"/>
+      <c r="BG19" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH19" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI19" s="3"/>
       <c r="BJ19" s="3"/>
       <c r="BK19" s="3"/>
@@ -5300,8 +5538,12 @@
       <c r="BF20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG20" s="3"/>
-      <c r="BH20" s="3"/>
+      <c r="BG20" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH20" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI20" s="3"/>
       <c r="BJ20" s="3"/>
       <c r="BK20" s="3"/>
@@ -5543,8 +5785,12 @@
       <c r="BF21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG21" s="3"/>
-      <c r="BH21" s="3"/>
+      <c r="BG21" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH21" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="BI21" s="3"/>
       <c r="BJ21" s="3"/>
       <c r="BK21" s="3"/>
@@ -5786,8 +6032,12 @@
       <c r="BF22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG22" s="3"/>
-      <c r="BH22" s="3"/>
+      <c r="BG22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH22" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI22" s="3"/>
       <c r="BJ22" s="3"/>
       <c r="BK22" s="3"/>
@@ -6029,8 +6279,12 @@
       <c r="BF23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG23" s="3"/>
-      <c r="BH23" s="3"/>
+      <c r="BG23" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH23" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI23" s="3"/>
       <c r="BJ23" s="3"/>
       <c r="BK23" s="3"/>
@@ -6272,8 +6526,12 @@
       <c r="BF24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG24" s="3"/>
-      <c r="BH24" s="3"/>
+      <c r="BG24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH24" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI24" s="3"/>
       <c r="BJ24" s="3"/>
       <c r="BK24" s="3"/>
@@ -6515,8 +6773,12 @@
       <c r="BF25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG25" s="3"/>
-      <c r="BH25" s="3"/>
+      <c r="BG25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI25" s="3"/>
       <c r="BJ25" s="3"/>
       <c r="BK25" s="3"/>
@@ -6758,8 +7020,12 @@
       <c r="BF26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG26" s="3"/>
-      <c r="BH26" s="3"/>
+      <c r="BG26" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH26" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BI26" s="3"/>
       <c r="BJ26" s="3"/>
       <c r="BK26" s="3"/>
@@ -7001,8 +7267,12 @@
       <c r="BF27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG27" s="3"/>
-      <c r="BH27" s="3"/>
+      <c r="BG27" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI27" s="3"/>
       <c r="BJ27" s="3"/>
       <c r="BK27" s="3"/>
@@ -7244,8 +7514,12 @@
       <c r="BF28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG28" s="3"/>
-      <c r="BH28" s="3"/>
+      <c r="BG28" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH28" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI28" s="3"/>
       <c r="BJ28" s="3"/>
       <c r="BK28" s="3"/>
@@ -7478,8 +7752,12 @@
       <c r="BF29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG29" s="3"/>
-      <c r="BH29" s="3"/>
+      <c r="BG29" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH29" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="BI29" s="3"/>
       <c r="BJ29" s="3"/>
       <c r="BK29" s="3"/>
@@ -7721,8 +7999,12 @@
       <c r="BF30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG30" s="3"/>
-      <c r="BH30" s="3"/>
+      <c r="BG30" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH30" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI30" s="3"/>
       <c r="BJ30" s="3"/>
       <c r="BK30" s="3"/>
@@ -7964,8 +8246,12 @@
       <c r="BF31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG31" s="3"/>
-      <c r="BH31" s="3"/>
+      <c r="BG31" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH31" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI31" s="3"/>
       <c r="BJ31" s="3"/>
     </row>
@@ -8145,8 +8431,12 @@
       <c r="BF32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG32" s="3"/>
-      <c r="BH32" s="3"/>
+      <c r="BG32" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH32" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI32" s="3"/>
       <c r="BJ32" s="3"/>
     </row>
@@ -8326,8 +8616,12 @@
       <c r="BF33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG33" s="3"/>
-      <c r="BH33" s="3"/>
+      <c r="BG33" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH33" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI33" s="3"/>
       <c r="BJ33" s="3"/>
     </row>
@@ -8507,8 +8801,12 @@
       <c r="BF34" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="BG34" s="3"/>
-      <c r="BH34" s="3"/>
+      <c r="BG34" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BH34" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="BI34" s="3"/>
       <c r="BJ34" s="3"/>
     </row>
@@ -8518,33 +8816,43 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G31:I32">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:AS34">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BK9 AU4:AY26 BL4:DH30 AZ10:BB21 BD10:BK21 AZ22:BK26 AU27:BK28 AU29:AX30 AZ29:BK30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33">
-    <cfRule type="cellIs" dxfId="3" priority="8" operator="equal">
+  <conditionalFormatting sqref="AU3:BA3 BF3:DH3 BC3:BC21 D3:I30 K3:T30 AZ4:BA9 BF4:BF9 AU4:AY26 AZ10:BB21 BD10:BF21 AZ22:BF26 AU27:BF28 AU29:AX30 AZ29:BF30 AY29:AY34 K31:K33 L31:T34 AU31:AV34 H33:I33 BH4:DH30 BG4:BG34">
+    <cfRule type="cellIs" dxfId="12" priority="10" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB9">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB32">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD3:BD34">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BD3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BH8">
+    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BH8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BH3:BH34">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BD3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("F",BH3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
